--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -8,7 +8,8 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mjunior\Documents\Backup One Drive 10.02\Pessoais\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B051CDD9-5956-4186-8F5F-160583BA0FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88C4BD9-A339-4F43-A901-86474B053D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="0EBXfi/vgOVeygGXaeHj2/oyKW1czsf9/u6CnEAjfykKbHQA3OUxIBOTQiRbvsMgNaWf2cCQz9SrZi8/1TbMhA==" workbookSaltValue="XUkspHv8EA4O4CpN5hryww==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
   </bookViews>
@@ -1779,6 +1780,7 @@
     <xf numFmtId="0" fontId="20" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1836,7 +1838,6 @@
     <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -4425,11 +4426,11 @@
       <c r="E2" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="157" t="s">
+      <c r="F2" s="158" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
       <c r="I2" s="95" t="s">
         <v>17</v>
       </c>
@@ -7669,7 +7670,7 @@
         <f>VLOOKUP($AE17,$O$17:$X$20,10,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BL17" s="176">
+      <c r="BL17" s="157">
         <f>SUM(BL5:BL16)</f>
         <v>0</v>
       </c>
@@ -15203,24 +15204,24 @@
   <sheetData>
     <row r="1" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="159" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="160" t="s">
+      <c r="C2" s="161" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="161"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161"/>
-      <c r="H2" s="161"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
-      <c r="L2" s="161"/>
-      <c r="M2" s="161"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="158"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="162"/>
+      <c r="K2" s="162"/>
+      <c r="L2" s="162"/>
+      <c r="M2" s="162"/>
+      <c r="N2" s="163"/>
+      <c r="O2" s="159"/>
       <c r="P2" s="5" t="s">
         <v>102</v>
       </c>
@@ -15247,22 +15248,22 @@
       </c>
     </row>
     <row r="3" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="159"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="160"/>
+      <c r="C3" s="164" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="164"/>
-      <c r="H3" s="164"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="164"/>
-      <c r="K3" s="164"/>
-      <c r="L3" s="164"/>
-      <c r="M3" s="164"/>
-      <c r="N3" s="165"/>
-      <c r="O3" s="159"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
+      <c r="L3" s="165"/>
+      <c r="M3" s="165"/>
+      <c r="N3" s="166"/>
+      <c r="O3" s="160"/>
       <c r="P3" s="1" t="s">
         <v>103</v>
       </c>
@@ -47555,18 +47556,18 @@
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="134"/>
-      <c r="B3" s="166" t="s">
+      <c r="B3" s="167" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="167"/>
-      <c r="D3" s="167"/>
-      <c r="E3" s="167"/>
-      <c r="F3" s="167"/>
-      <c r="G3" s="167"/>
-      <c r="H3" s="167"/>
-      <c r="I3" s="167"/>
-      <c r="J3" s="167"/>
-      <c r="K3" s="168"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="168"/>
+      <c r="F3" s="168"/>
+      <c r="G3" s="168"/>
+      <c r="H3" s="168"/>
+      <c r="I3" s="168"/>
+      <c r="J3" s="168"/>
+      <c r="K3" s="169"/>
       <c r="L3" s="135"/>
       <c r="M3" s="136"/>
       <c r="N3" s="136"/>
@@ -47574,18 +47575,18 @@
       <c r="P3" s="136"/>
       <c r="Q3" s="136"/>
       <c r="W3" s="134"/>
-      <c r="X3" s="166" t="s">
+      <c r="X3" s="167" t="s">
         <v>73</v>
       </c>
-      <c r="Y3" s="167"/>
-      <c r="Z3" s="167"/>
-      <c r="AA3" s="167"/>
-      <c r="AB3" s="167"/>
-      <c r="AC3" s="167"/>
-      <c r="AD3" s="167"/>
-      <c r="AE3" s="167"/>
-      <c r="AF3" s="167"/>
-      <c r="AG3" s="168"/>
+      <c r="Y3" s="168"/>
+      <c r="Z3" s="168"/>
+      <c r="AA3" s="168"/>
+      <c r="AB3" s="168"/>
+      <c r="AC3" s="168"/>
+      <c r="AD3" s="168"/>
+      <c r="AE3" s="168"/>
+      <c r="AF3" s="168"/>
+      <c r="AG3" s="169"/>
       <c r="AH3" s="135"/>
       <c r="AI3" s="136"/>
       <c r="AJ3" s="136"/>
@@ -47602,19 +47603,19 @@
       <c r="D4" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="169" t="s">
+      <c r="E4" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="169"/>
-      <c r="G4" s="169" t="s">
+      <c r="F4" s="170"/>
+      <c r="G4" s="170" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="169"/>
-      <c r="I4" s="169"/>
-      <c r="J4" s="169" t="s">
+      <c r="H4" s="170"/>
+      <c r="I4" s="170"/>
+      <c r="J4" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="169"/>
+      <c r="K4" s="170"/>
       <c r="L4" s="139"/>
       <c r="M4" s="139"/>
       <c r="N4" s="139"/>
@@ -47629,19 +47630,19 @@
       <c r="Z4" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="AA4" s="169" t="s">
+      <c r="AA4" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="AB4" s="169"/>
-      <c r="AC4" s="169" t="s">
+      <c r="AB4" s="170"/>
+      <c r="AC4" s="170" t="s">
         <v>18</v>
       </c>
-      <c r="AD4" s="169"/>
-      <c r="AE4" s="169"/>
-      <c r="AF4" s="169" t="s">
+      <c r="AD4" s="170"/>
+      <c r="AE4" s="170"/>
+      <c r="AF4" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="AG4" s="169"/>
+      <c r="AG4" s="170"/>
       <c r="AH4" s="140"/>
       <c r="AI4" s="137"/>
       <c r="AJ4" s="137"/>
@@ -48165,18 +48166,18 @@
         <v>12</v>
       </c>
       <c r="W11" s="134"/>
-      <c r="X11" s="166" t="s">
+      <c r="X11" s="167" t="s">
         <v>74</v>
       </c>
-      <c r="Y11" s="167"/>
-      <c r="Z11" s="167"/>
-      <c r="AA11" s="167"/>
-      <c r="AB11" s="167"/>
-      <c r="AC11" s="167"/>
-      <c r="AD11" s="167"/>
-      <c r="AE11" s="167"/>
-      <c r="AF11" s="167"/>
-      <c r="AG11" s="168"/>
+      <c r="Y11" s="168"/>
+      <c r="Z11" s="168"/>
+      <c r="AA11" s="168"/>
+      <c r="AB11" s="168"/>
+      <c r="AC11" s="168"/>
+      <c r="AD11" s="168"/>
+      <c r="AE11" s="168"/>
+      <c r="AF11" s="168"/>
+      <c r="AG11" s="169"/>
       <c r="AH11" s="135"/>
       <c r="AI11" s="136"/>
       <c r="AJ11" s="136"/>
@@ -48246,19 +48247,19 @@
       <c r="Z12" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="AA12" s="169" t="s">
+      <c r="AA12" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="AB12" s="169"/>
-      <c r="AC12" s="169" t="s">
+      <c r="AB12" s="170"/>
+      <c r="AC12" s="170" t="s">
         <v>18</v>
       </c>
-      <c r="AD12" s="169"/>
-      <c r="AE12" s="169"/>
-      <c r="AF12" s="169" t="s">
+      <c r="AD12" s="170"/>
+      <c r="AE12" s="170"/>
+      <c r="AF12" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="AG12" s="169"/>
+      <c r="AG12" s="170"/>
       <c r="AH12" s="140"/>
       <c r="AI12" s="137"/>
       <c r="AJ12" s="137"/>
@@ -48633,18 +48634,18 @@
         <v>30</v>
       </c>
       <c r="W17" s="134"/>
-      <c r="X17" s="166" t="s">
+      <c r="X17" s="167" t="s">
         <v>77</v>
       </c>
-      <c r="Y17" s="167"/>
-      <c r="Z17" s="167"/>
-      <c r="AA17" s="167"/>
-      <c r="AB17" s="167"/>
-      <c r="AC17" s="167"/>
-      <c r="AD17" s="167"/>
-      <c r="AE17" s="167"/>
-      <c r="AF17" s="167"/>
-      <c r="AG17" s="168"/>
+      <c r="Y17" s="168"/>
+      <c r="Z17" s="168"/>
+      <c r="AA17" s="168"/>
+      <c r="AB17" s="168"/>
+      <c r="AC17" s="168"/>
+      <c r="AD17" s="168"/>
+      <c r="AE17" s="168"/>
+      <c r="AF17" s="168"/>
+      <c r="AG17" s="169"/>
       <c r="AH17" s="135"/>
       <c r="AI17" s="136"/>
       <c r="AJ17" s="136"/>
@@ -48703,19 +48704,19 @@
       <c r="Z18" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="AA18" s="169" t="s">
+      <c r="AA18" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="AB18" s="169"/>
-      <c r="AC18" s="169" t="s">
+      <c r="AB18" s="170"/>
+      <c r="AC18" s="170" t="s">
         <v>18</v>
       </c>
-      <c r="AD18" s="169"/>
-      <c r="AE18" s="169"/>
-      <c r="AF18" s="169" t="s">
+      <c r="AD18" s="170"/>
+      <c r="AE18" s="170"/>
+      <c r="AF18" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="AG18" s="169"/>
+      <c r="AG18" s="170"/>
       <c r="AH18" s="140"/>
       <c r="AI18" s="137"/>
       <c r="AJ18" s="137"/>
@@ -48907,18 +48908,18 @@
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" s="134"/>
-      <c r="B23" s="166" t="s">
+      <c r="B23" s="167" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="167"/>
-      <c r="D23" s="167"/>
-      <c r="E23" s="167"/>
-      <c r="F23" s="167"/>
-      <c r="G23" s="167"/>
-      <c r="H23" s="167"/>
-      <c r="I23" s="167"/>
-      <c r="J23" s="167"/>
-      <c r="K23" s="168"/>
+      <c r="C23" s="168"/>
+      <c r="D23" s="168"/>
+      <c r="E23" s="168"/>
+      <c r="F23" s="168"/>
+      <c r="G23" s="168"/>
+      <c r="H23" s="168"/>
+      <c r="I23" s="168"/>
+      <c r="J23" s="168"/>
+      <c r="K23" s="169"/>
       <c r="L23" s="135"/>
       <c r="M23" s="136"/>
       <c r="N23" s="136"/>
@@ -48933,18 +48934,18 @@
         <v>48</v>
       </c>
       <c r="W23" s="49"/>
-      <c r="X23" s="166" t="s">
+      <c r="X23" s="167" t="s">
         <v>79</v>
       </c>
-      <c r="Y23" s="167"/>
-      <c r="Z23" s="167"/>
-      <c r="AA23" s="167"/>
-      <c r="AB23" s="167"/>
-      <c r="AC23" s="167"/>
-      <c r="AD23" s="167"/>
-      <c r="AE23" s="167"/>
-      <c r="AF23" s="167"/>
-      <c r="AG23" s="168"/>
+      <c r="Y23" s="168"/>
+      <c r="Z23" s="168"/>
+      <c r="AA23" s="168"/>
+      <c r="AB23" s="168"/>
+      <c r="AC23" s="168"/>
+      <c r="AD23" s="168"/>
+      <c r="AE23" s="168"/>
+      <c r="AF23" s="168"/>
+      <c r="AG23" s="169"/>
       <c r="AH23" s="135"/>
       <c r="AI23" s="136"/>
       <c r="AJ23" s="136"/>
@@ -48960,19 +48961,19 @@
       <c r="D24" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="169" t="s">
+      <c r="E24" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="F24" s="169"/>
-      <c r="G24" s="169" t="s">
+      <c r="F24" s="170"/>
+      <c r="G24" s="170" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="169"/>
-      <c r="I24" s="169"/>
-      <c r="J24" s="169" t="s">
+      <c r="H24" s="170"/>
+      <c r="I24" s="170"/>
+      <c r="J24" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="K24" s="169"/>
+      <c r="K24" s="170"/>
       <c r="L24" s="139"/>
       <c r="M24" s="139"/>
       <c r="N24" s="139"/>
@@ -48994,19 +48995,19 @@
       <c r="Z24" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="AA24" s="169" t="s">
+      <c r="AA24" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="AB24" s="169"/>
-      <c r="AC24" s="169" t="s">
+      <c r="AB24" s="170"/>
+      <c r="AC24" s="170" t="s">
         <v>18</v>
       </c>
-      <c r="AD24" s="169"/>
-      <c r="AE24" s="169"/>
-      <c r="AF24" s="169" t="s">
+      <c r="AD24" s="170"/>
+      <c r="AE24" s="170"/>
+      <c r="AF24" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="AG24" s="169"/>
+      <c r="AG24" s="170"/>
       <c r="AH24" s="140"/>
       <c r="AI24" s="137"/>
       <c r="AJ24" s="137"/>
@@ -49397,54 +49398,54 @@
     </row>
     <row r="34" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B34" s="144"/>
-      <c r="Y34" s="175" t="s">
+      <c r="Y34" s="176" t="s">
         <v>81</v>
       </c>
-      <c r="Z34" s="175"/>
-      <c r="AA34" s="175"/>
-      <c r="AB34" s="170" t="str">
+      <c r="Z34" s="176"/>
+      <c r="AA34" s="176"/>
+      <c r="AB34" s="171" t="str">
         <f>IF(AI25="1º Lugar","",AI25)</f>
         <v/>
       </c>
-      <c r="AC34" s="170"/>
-      <c r="AD34" s="170"/>
-      <c r="AE34" s="170"/>
-      <c r="AF34" s="170"/>
-      <c r="AG34" s="170"/>
+      <c r="AC34" s="171"/>
+      <c r="AD34" s="171"/>
+      <c r="AE34" s="171"/>
+      <c r="AF34" s="171"/>
+      <c r="AG34" s="171"/>
     </row>
     <row r="35" spans="2:33" ht="18" x14ac:dyDescent="0.25">
       <c r="B35" s="144"/>
-      <c r="Y35" s="173" t="s">
+      <c r="Y35" s="174" t="s">
         <v>82</v>
       </c>
-      <c r="Z35" s="173"/>
-      <c r="AA35" s="173"/>
-      <c r="AB35" s="171" t="str">
+      <c r="Z35" s="174"/>
+      <c r="AA35" s="174"/>
+      <c r="AB35" s="172" t="str">
         <f>IF(M57="2º Lugar","",M57)</f>
         <v/>
       </c>
-      <c r="AC35" s="171"/>
-      <c r="AD35" s="171"/>
-      <c r="AE35" s="171"/>
-      <c r="AF35" s="171"/>
-      <c r="AG35" s="171"/>
+      <c r="AC35" s="172"/>
+      <c r="AD35" s="172"/>
+      <c r="AE35" s="172"/>
+      <c r="AF35" s="172"/>
+      <c r="AG35" s="172"/>
     </row>
     <row r="36" spans="2:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="144"/>
-      <c r="Y36" s="174" t="s">
+      <c r="Y36" s="175" t="s">
         <v>83</v>
       </c>
-      <c r="Z36" s="174"/>
-      <c r="AA36" s="174"/>
-      <c r="AB36" s="172" t="str">
+      <c r="Z36" s="175"/>
+      <c r="AA36" s="175"/>
+      <c r="AB36" s="173" t="str">
         <f>IF(AI19="3º Lugar","",AI19)</f>
         <v/>
       </c>
-      <c r="AC36" s="172"/>
-      <c r="AD36" s="172"/>
-      <c r="AE36" s="172"/>
-      <c r="AF36" s="172"/>
-      <c r="AG36" s="172"/>
+      <c r="AC36" s="173"/>
+      <c r="AD36" s="173"/>
+      <c r="AE36" s="173"/>
+      <c r="AF36" s="173"/>
+      <c r="AG36" s="173"/>
     </row>
     <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="141"/>
@@ -49779,14 +49780,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DBF2846C41E31A469E3CED25F2422E48" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5fe40c83f7497f6a132ba44389c75f2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8c20e6-817c-474f-b9c2-eb2b1ac24837" xmlns:ns4="dc8c2798-6aba-4af7-93a4-b89253b03650" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7827a91f6681aa3909757bf20cf55ac7" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
@@ -50013,7 +50006,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -50022,24 +50015,15 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E4CC2DB-337D-464E-B291-77CE670D3A8E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50058,10 +50042,27 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5989A7F-F0C9-44D0-8E07-DC82ED943A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F760DBF-8896-4317-A20B-F1ABD0B008CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BcI4NY5Ohir363+nRCln2YCzlnOeJyINjZ1aV0hb2IpPHmsHZPUFroFzrod6xokqyCn7GUW2N1Z+U/w2mbyNbQ==" workbookSaltValue="VvXyFesAZC8L8IOzNm6PtA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
@@ -2138,6 +2138,15 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2148,15 +2157,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9654,7 +9654,7 @@
       <c r="L33" s="183"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dle47BlCi5tsiQ7XfD/bmh4R3lXfrZDO2pxxvBb12fIJrpAerNcJb4tExM3y1onUI4ywzBW2zZoPHa6O5bD0eA==" saltValue="OBU2m1ZQzf8E9jKXKznlVg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="R7MKfGIr3q3KasSJACKADhTt/LYOodNa9tmtKJjgNCMenwB8F4JksD1Wb6Inyd7c0WaCL2TG1h5loB5f76zIiQ==" saltValue="vzSxU7R4LDF7bDaBkhG3gA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="3">
     <mergeCell ref="J31:L31"/>
     <mergeCell ref="J32:L32"/>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="AP6" s="48">
         <f t="shared" ref="AP6:AP17" si="4">RANK(AR6,$AR$6:$AR$17)+SUM(BB6:BE6)</f>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AQ6" s="50" t="str">
         <f>AF8</f>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="BB6" s="38">
         <f t="shared" ref="BB6:BB17" si="10">SUMPRODUCT(($AR$6:$AR$17=AR6)*($AY$6:$AY$17&gt;AY6))</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BC6" s="38">
         <f t="shared" ref="BC6:BC17" si="11">SUMPRODUCT(($AR$6:$AR$17=AR6)*($AY$6:$AY$17=AY6)*($AW$6:$AW$17&gt;AW6))</f>
@@ -11694,15 +11694,15 @@
       </c>
       <c r="BJ6" s="83" t="str">
         <f t="shared" ref="BJ6:BJ17" si="14">VLOOKUP($BI6,$AP$6:$AY$17,2,FALSE)</f>
-        <v>Qatar</v>
+        <v>Japão</v>
       </c>
       <c r="BK6" s="84">
         <f t="shared" ref="BK6:BK17" si="15">VLOOKUP($BI6,$AP$6:$AY$17,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL6" s="84">
         <f t="shared" ref="BL6:BL17" si="16">VLOOKUP($BI6,$AP$6:$AY$17,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM6" s="84">
         <f t="shared" ref="BM6:BM17" si="17">VLOOKUP($BI6,$AP$6:$AY$17,5,FALSE)</f>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="BN6" s="84">
         <f t="shared" ref="BN6:BN17" si="18">VLOOKUP($BI6,$AP$6:$AY$17,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO6" s="84">
         <f t="shared" ref="BO6:BO17" si="19">VLOOKUP($BI6,$AP$6:$AY$17,7,FALSE)</f>
@@ -11718,11 +11718,11 @@
       </c>
       <c r="BP6" s="84">
         <f t="shared" ref="BP6:BP17" si="20">VLOOKUP($BI6,$AP$6:$AY$17,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ6" s="84">
         <f t="shared" ref="BQ6:BQ17" si="21">VLOOKUP($BI6,$AP$6:$AY$17,9,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR6" s="85">
         <f t="shared" ref="BR6:BR17" si="22">VLOOKUP($BI6,$AP$6:$AY$17,10,FALSE)</f>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="AP7" s="48">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ7" s="50" t="str">
         <f>AF14</f>
@@ -11879,11 +11879,11 @@
       </c>
       <c r="AR7" s="38">
         <f t="shared" ref="AR7:AR17" si="26">(AT7*3)+(AU7*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS7" s="38">
         <f t="shared" ref="AS7:AS17" si="27">SUM(AT7:AV7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT7" s="38">
         <f t="shared" si="5"/>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="AU7" s="38">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV7" s="38">
         <f t="shared" si="7"/>
@@ -11899,11 +11899,11 @@
       </c>
       <c r="AW7" s="38">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX7" s="38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY7" s="38">
         <f t="shared" ref="AY7:AY17" si="28">AW7-AX7</f>
@@ -11922,7 +11922,7 @@
       </c>
       <c r="BC7" s="38">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD7" s="38">
         <f t="shared" si="12"/>
@@ -11941,15 +11941,15 @@
       </c>
       <c r="BJ7" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Haiti</v>
+        <v>Qatar</v>
       </c>
       <c r="BK7" s="84">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL7" s="84">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM7" s="84">
         <f t="shared" si="17"/>
@@ -11957,7 +11957,7 @@
       </c>
       <c r="BN7" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO7" s="84">
         <f t="shared" si="19"/>
@@ -11965,11 +11965,11 @@
       </c>
       <c r="BP7" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ7" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR7" s="85">
         <f t="shared" si="22"/>
@@ -12118,19 +12118,19 @@
       </c>
       <c r="AP8" s="48">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ8" s="50" t="str">
         <f>AF20</f>
-        <v>Haiti</v>
+        <v>Marrocos</v>
       </c>
       <c r="AR8" s="38">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS8" s="38">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT8" s="38">
         <f t="shared" si="5"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="AU8" s="38">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV8" s="38">
         <f t="shared" si="7"/>
@@ -12146,11 +12146,11 @@
       </c>
       <c r="AW8" s="38">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX8" s="38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY8" s="38">
         <f t="shared" si="28"/>
@@ -12161,7 +12161,7 @@
       </c>
       <c r="BA8" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Haiti</v>
+        <v>Marrocos</v>
       </c>
       <c r="BB8" s="38">
         <f t="shared" si="10"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="BC8" s="38">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD8" s="38">
         <f t="shared" si="12"/>
@@ -12188,15 +12188,15 @@
       </c>
       <c r="BJ8" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Austrália</v>
+        <v>Marrocos</v>
       </c>
       <c r="BK8" s="84">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL8" s="84">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM8" s="84">
         <f t="shared" si="17"/>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="BN8" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO8" s="84">
         <f t="shared" si="19"/>
@@ -12212,11 +12212,11 @@
       </c>
       <c r="BP8" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ8" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR8" s="85">
         <f t="shared" si="22"/>
@@ -12365,11 +12365,11 @@
       </c>
       <c r="AP9" s="48">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AQ9" s="50" t="str">
         <f>AF26</f>
-        <v>Austrália</v>
+        <v>Turquia</v>
       </c>
       <c r="AR9" s="38">
         <f t="shared" si="26"/>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="AS9" s="38">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT9" s="38">
         <f t="shared" si="5"/>
@@ -12389,7 +12389,7 @@
       </c>
       <c r="AV9" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW9" s="38">
         <f t="shared" si="8"/>
@@ -12397,26 +12397,26 @@
       </c>
       <c r="AX9" s="38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY9" s="38">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AZ9" s="38" t="s">
         <v>45</v>
       </c>
       <c r="BA9" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Austrália</v>
+        <v>Turquia</v>
       </c>
       <c r="BB9" s="38">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC9" s="38">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD9" s="38">
         <f t="shared" si="12"/>
@@ -12424,7 +12424,7 @@
       </c>
       <c r="BE9" s="38">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF9" s="54">
         <v>4</v>
@@ -12435,15 +12435,15 @@
       </c>
       <c r="BJ9" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Costa do Marfim</v>
+        <v>Bélgica</v>
       </c>
       <c r="BK9" s="84">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL9" s="84">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM9" s="84">
         <f t="shared" si="17"/>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="BN9" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO9" s="84">
         <f t="shared" si="19"/>
@@ -12459,11 +12459,11 @@
       </c>
       <c r="BP9" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ9" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR9" s="85">
         <f t="shared" si="22"/>
@@ -12485,11 +12485,15 @@
         <f>P12</f>
         <v>Canadá</v>
       </c>
-      <c r="F10" s="125"/>
+      <c r="F10" s="125">
+        <v>1</v>
+      </c>
       <c r="G10" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="125"/>
+      <c r="H10" s="125">
+        <v>1</v>
+      </c>
       <c r="I10" s="112" t="str">
         <f>P13</f>
         <v>Bósnia</v>
@@ -12500,11 +12504,11 @@
       </c>
       <c r="K10" s="59" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Canadá</v>
       </c>
       <c r="L10" s="59" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Bósnia</v>
       </c>
       <c r="M10" s="60" t="str">
         <f t="shared" si="3"/>
@@ -12543,11 +12547,11 @@
       <c r="AN10" s="80"/>
       <c r="AP10" s="48">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AQ10" s="50" t="str">
         <f>AF32</f>
-        <v>Costa do Marfim</v>
+        <v>Equador</v>
       </c>
       <c r="AR10" s="38">
         <f t="shared" si="26"/>
@@ -12555,7 +12559,7 @@
       </c>
       <c r="AS10" s="38">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT10" s="38">
         <f t="shared" si="5"/>
@@ -12567,7 +12571,7 @@
       </c>
       <c r="AV10" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW10" s="38">
         <f t="shared" si="8"/>
@@ -12575,18 +12579,18 @@
       </c>
       <c r="AX10" s="38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY10" s="38">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AZ10" s="38" t="s">
         <v>44</v>
       </c>
       <c r="BA10" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Costa do Marfim</v>
+        <v>Equador</v>
       </c>
       <c r="BB10" s="38">
         <f t="shared" si="10"/>
@@ -12594,7 +12598,7 @@
       </c>
       <c r="BC10" s="38">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD10" s="38">
         <f t="shared" si="12"/>
@@ -12602,7 +12606,7 @@
       </c>
       <c r="BE10" s="38">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BF10" s="39">
         <v>5</v>
@@ -12613,15 +12617,15 @@
       </c>
       <c r="BJ10" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Suécia</v>
+        <v>RD Congo</v>
       </c>
       <c r="BK10" s="84">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL10" s="84">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM10" s="84">
         <f t="shared" si="17"/>
@@ -12629,7 +12633,7 @@
       </c>
       <c r="BN10" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO10" s="84">
         <f t="shared" si="19"/>
@@ -12637,11 +12641,11 @@
       </c>
       <c r="BP10" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ10" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR10" s="85">
         <f t="shared" si="22"/>
@@ -12663,11 +12667,15 @@
         <f>P14</f>
         <v>Qatar</v>
       </c>
-      <c r="F11" s="123"/>
+      <c r="F11" s="123">
+        <v>1</v>
+      </c>
       <c r="G11" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="123"/>
+      <c r="H11" s="123">
+        <v>1</v>
+      </c>
       <c r="I11" s="113" t="str">
         <f>P15</f>
         <v>Suiça</v>
@@ -12678,11 +12686,11 @@
       </c>
       <c r="K11" s="38" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Qatar</v>
       </c>
       <c r="L11" s="38" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Suiça</v>
       </c>
       <c r="M11" s="39" t="str">
         <f t="shared" si="3"/>
@@ -12767,19 +12775,19 @@
       </c>
       <c r="AP11" s="48">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AQ11" s="50" t="str">
         <f>AF38</f>
-        <v>Suécia</v>
+        <v>Japão</v>
       </c>
       <c r="AR11" s="38">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS11" s="38">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT11" s="38">
         <f t="shared" si="5"/>
@@ -12787,7 +12795,7 @@
       </c>
       <c r="AU11" s="38">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV11" s="38">
         <f t="shared" si="7"/>
@@ -12795,11 +12803,11 @@
       </c>
       <c r="AW11" s="38">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX11" s="38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY11" s="38">
         <f t="shared" si="28"/>
@@ -12810,7 +12818,7 @@
       </c>
       <c r="BA11" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Suécia</v>
+        <v>Japão</v>
       </c>
       <c r="BB11" s="38">
         <f t="shared" si="10"/>
@@ -12826,7 +12834,7 @@
       </c>
       <c r="BE11" s="38">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BF11" s="39">
         <v>6</v>
@@ -12837,15 +12845,15 @@
       </c>
       <c r="BJ11" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Irã</v>
+        <v>Espanha</v>
       </c>
       <c r="BK11" s="84">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL11" s="84">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM11" s="84">
         <f t="shared" si="17"/>
@@ -12853,7 +12861,7 @@
       </c>
       <c r="BN11" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO11" s="84">
         <f t="shared" si="19"/>
@@ -12923,11 +12931,11 @@
       </c>
       <c r="Q12" s="38">
         <f>(S12*3)+(T12*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="38">
         <f>SUM(S12:U12)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="38">
         <f>COUNTIF(J:J,P12)</f>
@@ -12935,7 +12943,7 @@
       </c>
       <c r="T12" s="38">
         <f>COUNTIF(K:K,P12)+COUNTIF(L:L,P12)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" s="38">
         <f>COUNTIF(M:M,P12)</f>
@@ -12943,11 +12951,11 @@
       </c>
       <c r="V12" s="38">
         <f>SUMIF(E:E,P12,F:F)+SUMIF(I:I,P12,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="38">
         <f>SUMIF(E:E,P12,H:H)+SUMIF(I:I,P12,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" s="38">
         <f>V12-W12</f>
@@ -12982,11 +12990,11 @@
       </c>
       <c r="AG12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,5,FALSE)</f>
@@ -12994,7 +13002,7 @@
       </c>
       <c r="AJ12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,7,FALSE)</f>
@@ -13002,11 +13010,11 @@
       </c>
       <c r="AL12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN12" s="85">
         <f>VLOOKUP($AE12,$O$12:$X$15,10,FALSE)</f>
@@ -13014,19 +13022,19 @@
       </c>
       <c r="AP12" s="48">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ12" s="50" t="str">
         <f>AF44</f>
-        <v>Irã</v>
+        <v>Bélgica</v>
       </c>
       <c r="AR12" s="38">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS12" s="38">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT12" s="38">
         <f t="shared" si="5"/>
@@ -13034,7 +13042,7 @@
       </c>
       <c r="AU12" s="38">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV12" s="38">
         <f t="shared" si="7"/>
@@ -13042,11 +13050,11 @@
       </c>
       <c r="AW12" s="38">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX12" s="38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY12" s="38">
         <f t="shared" si="28"/>
@@ -13057,7 +13065,7 @@
       </c>
       <c r="BA12" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Irã</v>
+        <v>Bélgica</v>
       </c>
       <c r="BB12" s="38">
         <f t="shared" si="10"/>
@@ -13065,7 +13073,7 @@
       </c>
       <c r="BC12" s="38">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD12" s="38">
         <f t="shared" si="12"/>
@@ -13073,7 +13081,7 @@
       </c>
       <c r="BE12" s="38">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BF12" s="39">
         <v>7</v>
@@ -13084,7 +13092,7 @@
       </c>
       <c r="BJ12" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Arábia Saudita</v>
+        <v>República Tcheca</v>
       </c>
       <c r="BK12" s="84">
         <f t="shared" si="15"/>
@@ -13092,7 +13100,7 @@
       </c>
       <c r="BL12" s="84">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM12" s="84">
         <f t="shared" si="17"/>
@@ -13104,19 +13112,19 @@
       </c>
       <c r="BO12" s="84">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP12" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ12" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR12" s="85">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13170,11 +13178,11 @@
       </c>
       <c r="Q13" s="38">
         <f t="shared" ref="Q13:Q15" si="30">(S13*3)+(T13*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="38">
         <f t="shared" ref="R13:R15" si="31">SUM(S13:U13)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="38">
         <f>COUNTIF(J:J,P13)</f>
@@ -13182,7 +13190,7 @@
       </c>
       <c r="T13" s="38">
         <f>COUNTIF(K:K,P13)+COUNTIF(L:L,P13)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" s="38">
         <f>COUNTIF(M:M,P13)</f>
@@ -13190,11 +13198,11 @@
       </c>
       <c r="V13" s="38">
         <f>SUMIF(E:E,P13,F:F)+SUMIF(I:I,P13,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="38">
         <f>SUMIF(E:E,P13,H:H)+SUMIF(I:I,P13,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="38">
         <f t="shared" ref="X13:X15" si="32">V13-W13</f>
@@ -13229,11 +13237,11 @@
       </c>
       <c r="AG13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,5,FALSE)</f>
@@ -13241,7 +13249,7 @@
       </c>
       <c r="AJ13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,7,FALSE)</f>
@@ -13249,11 +13257,11 @@
       </c>
       <c r="AL13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN13" s="85">
         <f>VLOOKUP($AE13,$O$12:$X$15,10,FALSE)</f>
@@ -13261,19 +13269,19 @@
       </c>
       <c r="AP13" s="48">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ13" s="50" t="str">
         <f>AF50</f>
-        <v>Arábia Saudita</v>
+        <v>Espanha</v>
       </c>
       <c r="AR13" s="38">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS13" s="38">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT13" s="38">
         <f t="shared" si="5"/>
@@ -13281,7 +13289,7 @@
       </c>
       <c r="AU13" s="38">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV13" s="38">
         <f t="shared" si="7"/>
@@ -13304,7 +13312,7 @@
       </c>
       <c r="BA13" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Arábia Saudita</v>
+        <v>Espanha</v>
       </c>
       <c r="BB13" s="38">
         <f t="shared" si="10"/>
@@ -13312,7 +13320,7 @@
       </c>
       <c r="BC13" s="38">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BD13" s="38">
         <f t="shared" si="12"/>
@@ -13320,7 +13328,7 @@
       </c>
       <c r="BE13" s="38">
         <f t="shared" si="13"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BF13" s="54">
         <v>8</v>
@@ -13331,7 +13339,7 @@
       </c>
       <c r="BJ13" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Iraque</v>
+        <v>Equador</v>
       </c>
       <c r="BK13" s="84">
         <f t="shared" si="15"/>
@@ -13339,7 +13347,7 @@
       </c>
       <c r="BL13" s="84">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM13" s="84">
         <f t="shared" si="17"/>
@@ -13351,7 +13359,7 @@
       </c>
       <c r="BO13" s="84">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP13" s="84">
         <f t="shared" si="20"/>
@@ -13359,11 +13367,11 @@
       </c>
       <c r="BQ13" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR13" s="85">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:70" x14ac:dyDescent="0.25">
@@ -13417,11 +13425,11 @@
       </c>
       <c r="Q14" s="38">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="38">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="38">
         <f>COUNTIF(J:J,P14)</f>
@@ -13429,7 +13437,7 @@
       </c>
       <c r="T14" s="38">
         <f>COUNTIF(K:K,P14)+COUNTIF(L:L,P14)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" s="38">
         <f>COUNTIF(M:M,P14)</f>
@@ -13437,11 +13445,11 @@
       </c>
       <c r="V14" s="38">
         <f>SUMIF(E:E,P14,F:F)+SUMIF(I:I,P14,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="38">
         <f>SUMIF(E:E,P14,H:H)+SUMIF(I:I,P14,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="38">
         <f t="shared" si="32"/>
@@ -13476,11 +13484,11 @@
       </c>
       <c r="AG14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,5,FALSE)</f>
@@ -13488,7 +13496,7 @@
       </c>
       <c r="AJ14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,7,FALSE)</f>
@@ -13496,11 +13504,11 @@
       </c>
       <c r="AL14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN14" s="85">
         <f>VLOOKUP($AE14,$O$12:$X$15,10,FALSE)</f>
@@ -13508,11 +13516,11 @@
       </c>
       <c r="AP14" s="48">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ14" s="50" t="str">
         <f>AF56</f>
-        <v>Iraque</v>
+        <v>Senegal</v>
       </c>
       <c r="AR14" s="38">
         <f t="shared" si="26"/>
@@ -13520,7 +13528,7 @@
       </c>
       <c r="AS14" s="38">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT14" s="38">
         <f t="shared" si="5"/>
@@ -13532,30 +13540,30 @@
       </c>
       <c r="AV14" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW14" s="38">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX14" s="38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY14" s="38">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AZ14" s="38" t="s">
         <v>69</v>
       </c>
       <c r="BA14" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Iraque</v>
+        <v>Senegal</v>
       </c>
       <c r="BB14" s="38">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC14" s="38">
         <f t="shared" si="11"/>
@@ -13567,7 +13575,7 @@
       </c>
       <c r="BE14" s="38">
         <f t="shared" si="13"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BF14" s="39">
         <v>9</v>
@@ -13578,7 +13586,7 @@
       </c>
       <c r="BJ14" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Áustria</v>
+        <v>Panamá</v>
       </c>
       <c r="BK14" s="84">
         <f t="shared" si="15"/>
@@ -13586,7 +13594,7 @@
       </c>
       <c r="BL14" s="84">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM14" s="84">
         <f t="shared" si="17"/>
@@ -13598,7 +13606,7 @@
       </c>
       <c r="BO14" s="84">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP14" s="84">
         <f t="shared" si="20"/>
@@ -13606,11 +13614,11 @@
       </c>
       <c r="BQ14" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR14" s="85">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13664,11 +13672,11 @@
       </c>
       <c r="Q15" s="53">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="53">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="38">
         <f>COUNTIF(J:J,P15)</f>
@@ -13676,7 +13684,7 @@
       </c>
       <c r="T15" s="38">
         <f>COUNTIF(K:K,P15)+COUNTIF(L:L,P15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" s="38">
         <f>COUNTIF(M:M,P15)</f>
@@ -13684,11 +13692,11 @@
       </c>
       <c r="V15" s="53">
         <f>SUMIF(E:E,P15,F:F)+SUMIF(I:I,P15,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="53">
         <f>SUMIF(E:E,P15,H:H)+SUMIF(I:I,P15,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="53">
         <f t="shared" si="32"/>
@@ -13723,11 +13731,11 @@
       </c>
       <c r="AG15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,5,FALSE)</f>
@@ -13735,7 +13743,7 @@
       </c>
       <c r="AJ15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,7,FALSE)</f>
@@ -13743,11 +13751,11 @@
       </c>
       <c r="AL15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN15" s="88">
         <f>VLOOKUP($AE15,$O$12:$X$15,10,FALSE)</f>
@@ -13755,11 +13763,11 @@
       </c>
       <c r="AP15" s="48">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ15" s="50" t="str">
         <f>AF62</f>
-        <v>Áustria</v>
+        <v>Jordânia</v>
       </c>
       <c r="AR15" s="38">
         <f t="shared" si="26"/>
@@ -13767,7 +13775,7 @@
       </c>
       <c r="AS15" s="38">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT15" s="38">
         <f t="shared" si="5"/>
@@ -13779,30 +13787,30 @@
       </c>
       <c r="AV15" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW15" s="38">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX15" s="38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY15" s="38">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AZ15" s="38" t="s">
         <v>42</v>
       </c>
       <c r="BA15" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Áustria</v>
+        <v>Jordânia</v>
       </c>
       <c r="BB15" s="38">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC15" s="38">
         <f t="shared" si="11"/>
@@ -13814,7 +13822,7 @@
       </c>
       <c r="BE15" s="38">
         <f t="shared" si="13"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BF15" s="39">
         <v>10</v>
@@ -13825,7 +13833,7 @@
       </c>
       <c r="BJ15" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Uzbequistão</v>
+        <v>Senegal</v>
       </c>
       <c r="BK15" s="84">
         <f t="shared" si="15"/>
@@ -13833,7 +13841,7 @@
       </c>
       <c r="BL15" s="84">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM15" s="84">
         <f t="shared" si="17"/>
@@ -13845,19 +13853,19 @@
       </c>
       <c r="BO15" s="84">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP15" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ15" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR15" s="85">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="16" spans="1:70" x14ac:dyDescent="0.25">
@@ -13875,11 +13883,15 @@
         <f>P18</f>
         <v>Brasil</v>
       </c>
-      <c r="F16" s="125"/>
+      <c r="F16" s="125">
+        <v>1</v>
+      </c>
       <c r="G16" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="H16" s="125"/>
+      <c r="H16" s="125">
+        <v>1</v>
+      </c>
       <c r="I16" s="116" t="str">
         <f>P19</f>
         <v>Marrocos</v>
@@ -13890,11 +13902,11 @@
       </c>
       <c r="K16" s="59" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Brasil</v>
       </c>
       <c r="L16" s="59" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Marrocos</v>
       </c>
       <c r="M16" s="60" t="str">
         <f t="shared" si="3"/>
@@ -13933,19 +13945,19 @@
       <c r="AN16" s="80"/>
       <c r="AP16" s="48">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AQ16" s="50" t="str">
         <f>AF68</f>
-        <v>Uzbequistão</v>
+        <v>RD Congo</v>
       </c>
       <c r="AR16" s="38">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS16" s="38">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT16" s="38">
         <f t="shared" si="5"/>
@@ -13953,7 +13965,7 @@
       </c>
       <c r="AU16" s="38">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV16" s="38">
         <f t="shared" si="7"/>
@@ -13961,11 +13973,11 @@
       </c>
       <c r="AW16" s="38">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX16" s="38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY16" s="38">
         <f t="shared" si="28"/>
@@ -13976,7 +13988,7 @@
       </c>
       <c r="BA16" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Uzbequistão</v>
+        <v>RD Congo</v>
       </c>
       <c r="BB16" s="38">
         <f t="shared" si="10"/>
@@ -13984,7 +13996,7 @@
       </c>
       <c r="BC16" s="38">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD16" s="38">
         <f t="shared" si="12"/>
@@ -13992,7 +14004,7 @@
       </c>
       <c r="BE16" s="38">
         <f t="shared" si="13"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BF16" s="39">
         <v>11</v>
@@ -14003,7 +14015,7 @@
       </c>
       <c r="BJ16" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Gana</v>
+        <v>Jordânia</v>
       </c>
       <c r="BK16" s="84">
         <f t="shared" si="15"/>
@@ -14011,7 +14023,7 @@
       </c>
       <c r="BL16" s="84">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM16" s="84">
         <f t="shared" si="17"/>
@@ -14023,19 +14035,19 @@
       </c>
       <c r="BO16" s="84">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP16" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ16" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR16" s="85">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="17" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14053,18 +14065,22 @@
         <f>P20</f>
         <v>Haiti</v>
       </c>
-      <c r="F17" s="123"/>
+      <c r="F17" s="123">
+        <v>0</v>
+      </c>
       <c r="G17" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H17" s="123"/>
+      <c r="H17" s="123">
+        <v>1</v>
+      </c>
       <c r="I17" s="107" t="str">
         <f>P21</f>
         <v>Escócia</v>
       </c>
       <c r="J17" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Escócia</v>
       </c>
       <c r="K17" s="38" t="str">
         <f t="shared" si="1"/>
@@ -14076,7 +14092,7 @@
       </c>
       <c r="M17" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Haiti</v>
       </c>
       <c r="N17" s="46"/>
       <c r="O17" s="47" t="s">
@@ -14157,11 +14173,11 @@
       </c>
       <c r="AP17" s="48">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ17" s="50" t="str">
         <f>AF74</f>
-        <v>Gana</v>
+        <v>Panamá</v>
       </c>
       <c r="AR17" s="38">
         <f t="shared" si="26"/>
@@ -14169,7 +14185,7 @@
       </c>
       <c r="AS17" s="38">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT17" s="38">
         <f t="shared" si="5"/>
@@ -14181,7 +14197,7 @@
       </c>
       <c r="AV17" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW17" s="38">
         <f t="shared" si="8"/>
@@ -14189,18 +14205,18 @@
       </c>
       <c r="AX17" s="38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY17" s="38">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AZ17" s="38" t="s">
         <v>71</v>
       </c>
       <c r="BA17" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Gana</v>
+        <v>Panamá</v>
       </c>
       <c r="BB17" s="38">
         <f t="shared" si="10"/>
@@ -14208,7 +14224,7 @@
       </c>
       <c r="BC17" s="38">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD17" s="38">
         <f t="shared" si="12"/>
@@ -14216,7 +14232,7 @@
       </c>
       <c r="BE17" s="38">
         <f t="shared" si="13"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BF17" s="54">
         <v>12</v>
@@ -14227,7 +14243,7 @@
       </c>
       <c r="BJ17" s="86" t="str">
         <f t="shared" si="14"/>
-        <v>República Tcheca</v>
+        <v>Turquia</v>
       </c>
       <c r="BK17" s="87">
         <f t="shared" si="15"/>
@@ -14251,7 +14267,7 @@
       </c>
       <c r="BP17" s="87">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ17" s="87">
         <f t="shared" si="21"/>
@@ -14259,7 +14275,7 @@
       </c>
       <c r="BR17" s="88">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="18" spans="1:70" x14ac:dyDescent="0.25">
@@ -14305,7 +14321,7 @@
       <c r="N18" s="46"/>
       <c r="O18" s="47">
         <f>RANK(Q18,$Q$18:$Q$21)+SUM(Y18:AB18)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P18" s="49" t="str">
         <f>Sorteios!I6</f>
@@ -14313,11 +14329,11 @@
       </c>
       <c r="Q18" s="38">
         <f>(S18*3)+(T18*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="38">
         <f>SUM(S18:U18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="38">
         <f>COUNTIF(J:J,P18)</f>
@@ -14325,7 +14341,7 @@
       </c>
       <c r="T18" s="38">
         <f>COUNTIF(K:K,P18)+COUNTIF(L:L,P18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" s="38">
         <f>COUNTIF(M:M,P18)</f>
@@ -14333,11 +14349,11 @@
       </c>
       <c r="V18" s="38">
         <f>SUMIF(E:E,P18,F:F)+SUMIF(I:I,P18,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="38">
         <f>SUMIF(E:E,P18,H:H)+SUMIF(I:I,P18,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" s="38">
         <f>V18-W18</f>
@@ -14368,19 +14384,19 @@
       </c>
       <c r="AF18" s="83" t="str">
         <f>VLOOKUP($AE18,$O$18:$X$21,2,FALSE)</f>
-        <v>Brasil</v>
+        <v>Escócia</v>
       </c>
       <c r="AG18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,6,FALSE)</f>
@@ -14392,7 +14408,7 @@
       </c>
       <c r="AL18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,9,FALSE)</f>
@@ -14400,11 +14416,11 @@
       </c>
       <c r="AN18" s="85">
         <f>VLOOKUP($AE18,$O$18:$X$21,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL18" s="153">
         <f>SUM(BL6:BL17)</f>
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:70" x14ac:dyDescent="0.25">
@@ -14450,7 +14466,7 @@
       <c r="N19" s="46"/>
       <c r="O19" s="47">
         <f>RANK(Q19,$Q$18:$Q$21)+SUM(Y19:AB19)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" s="49" t="str">
         <f>Sorteios!I7</f>
@@ -14458,11 +14474,11 @@
       </c>
       <c r="Q19" s="38">
         <f t="shared" ref="Q19:Q21" si="33">(S19*3)+(T19*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="38">
         <f t="shared" ref="R19:R21" si="34">SUM(S19:U19)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" s="38">
         <f>COUNTIF(J:J,P19)</f>
@@ -14470,7 +14486,7 @@
       </c>
       <c r="T19" s="38">
         <f>COUNTIF(K:K,P19)+COUNTIF(L:L,P19)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" s="38">
         <f>COUNTIF(M:M,P19)</f>
@@ -14478,11 +14494,11 @@
       </c>
       <c r="V19" s="38">
         <f>SUMIF(E:E,P19,F:F)+SUMIF(I:I,P19,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="38">
         <f>SUMIF(E:E,P19,H:H)+SUMIF(I:I,P19,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" s="38">
         <f t="shared" ref="X19:X21" si="35">V19-W19</f>
@@ -14513,15 +14529,15 @@
       </c>
       <c r="AF19" s="83" t="str">
         <f>VLOOKUP($AE19,$O$18:$X$21,2,FALSE)</f>
-        <v>Marrocos</v>
+        <v>Brasil</v>
       </c>
       <c r="AG19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,5,FALSE)</f>
@@ -14529,7 +14545,7 @@
       </c>
       <c r="AJ19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,7,FALSE)</f>
@@ -14537,11 +14553,11 @@
       </c>
       <c r="AL19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN19" s="85">
         <f>VLOOKUP($AE19,$O$18:$X$21,10,FALSE)</f>
@@ -14591,7 +14607,7 @@
       <c r="N20" s="46"/>
       <c r="O20" s="47">
         <f>RANK(Q20,$Q$18:$Q$21)+SUM(Y20:AB20)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P20" s="49" t="str">
         <f>Sorteios!I8</f>
@@ -14603,7 +14619,7 @@
       </c>
       <c r="R20" s="38">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="38">
         <f>COUNTIF(J:J,P20)</f>
@@ -14615,7 +14631,7 @@
       </c>
       <c r="U20" s="38">
         <f>COUNTIF(M:M,P20)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="38">
         <f>SUMIF(E:E,P20,F:F)+SUMIF(I:I,P20,H:H)</f>
@@ -14623,11 +14639,11 @@
       </c>
       <c r="W20" s="38">
         <f>SUMIF(E:E,P20,H:H)+SUMIF(I:I,P20,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" s="38">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y20" s="38">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q20)*($X$18:$X$21&gt;X20))</f>
@@ -14643,7 +14659,7 @@
       </c>
       <c r="AB20" s="38">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q20)*($X$18:$X$21=X20)*($V$18:$V$21=V20)*($W$18:$W$21=W20)*($AC$18:$AC$21&lt;AC20))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="39">
         <v>3</v>
@@ -14654,15 +14670,15 @@
       </c>
       <c r="AF20" s="83" t="str">
         <f>VLOOKUP($AE20,$O$18:$X$21,2,FALSE)</f>
-        <v>Haiti</v>
+        <v>Marrocos</v>
       </c>
       <c r="AG20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,5,FALSE)</f>
@@ -14670,7 +14686,7 @@
       </c>
       <c r="AJ20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,7,FALSE)</f>
@@ -14678,11 +14694,11 @@
       </c>
       <c r="AL20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN20" s="85">
         <f>VLOOKUP($AE20,$O$18:$X$21,10,FALSE)</f>
@@ -14732,7 +14748,7 @@
       <c r="N21" s="55"/>
       <c r="O21" s="56">
         <f>RANK(Q21,$Q$18:$Q$21)+SUM(Y21:AB21)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P21" s="49" t="str">
         <f>Sorteios!I9</f>
@@ -14740,15 +14756,15 @@
       </c>
       <c r="Q21" s="53">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" s="53">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="38">
         <f>COUNTIF(J:J,P21)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" s="38">
         <f>COUNTIF(K:K,P21)+COUNTIF(L:L,P21)</f>
@@ -14760,7 +14776,7 @@
       </c>
       <c r="V21" s="53">
         <f>SUMIF(E:E,P21,F:F)+SUMIF(I:I,P21,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="53">
         <f>SUMIF(E:E,P21,H:H)+SUMIF(I:I,P21,F:F)</f>
@@ -14768,7 +14784,7 @@
       </c>
       <c r="X21" s="53">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" s="53">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q21)*($X$18:$X$21&gt;X21))</f>
@@ -14784,7 +14800,7 @@
       </c>
       <c r="AB21" s="53">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q21)*($X$18:$X$21=X21)*($V$18:$V$21=V21)*($W$18:$W$21=W21)*($AC$18:$AC$21&lt;AC21))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC21" s="54">
         <v>4</v>
@@ -14795,7 +14811,7 @@
       </c>
       <c r="AF21" s="86" t="str">
         <f>VLOOKUP($AE21,$O$18:$X$21,2,FALSE)</f>
-        <v>Escócia</v>
+        <v>Haiti</v>
       </c>
       <c r="AG21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,3,FALSE)</f>
@@ -14803,7 +14819,7 @@
       </c>
       <c r="AH21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,5,FALSE)</f>
@@ -14815,7 +14831,7 @@
       </c>
       <c r="AK21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,8,FALSE)</f>
@@ -14823,22 +14839,22 @@
       </c>
       <c r="AM21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN21" s="88">
         <f>VLOOKUP($AE21,$O$18:$X$21,10,FALSE)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP21" s="15">
         <v>1</v>
       </c>
       <c r="AQ21" s="15" t="str">
         <f t="shared" ref="AQ21:AQ28" si="36">VLOOKUP($BI6,$AP$6:$AZ$17,11,FALSE)</f>
-        <v>B</v>
+        <v>F</v>
       </c>
       <c r="AR21" s="15">
         <f>CODE(AQ21)</f>
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:70" x14ac:dyDescent="0.25">
@@ -14856,18 +14872,22 @@
         <f>P24</f>
         <v>Estados Unidos</v>
       </c>
-      <c r="F22" s="125"/>
+      <c r="F22" s="125">
+        <v>4</v>
+      </c>
       <c r="G22" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="125"/>
+      <c r="H22" s="125">
+        <v>1</v>
+      </c>
       <c r="I22" s="112" t="str">
         <f>P25</f>
         <v>Paraguai</v>
       </c>
       <c r="J22" s="59" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Estados Unidos</v>
       </c>
       <c r="K22" s="59" t="str">
         <f t="shared" si="1"/>
@@ -14879,7 +14899,7 @@
       </c>
       <c r="M22" s="60" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Paraguai</v>
       </c>
       <c r="N22" s="64"/>
       <c r="O22" s="62"/>
@@ -14917,11 +14937,11 @@
       </c>
       <c r="AQ22" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="AR22" s="15">
         <f t="shared" ref="AR22:AR28" si="37">CODE(AQ22)</f>
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:70" x14ac:dyDescent="0.25">
@@ -14939,18 +14959,22 @@
         <f>P26</f>
         <v>Austrália</v>
       </c>
-      <c r="F23" s="123"/>
+      <c r="F23" s="123">
+        <v>2</v>
+      </c>
       <c r="G23" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H23" s="123"/>
+      <c r="H23" s="123">
+        <v>0</v>
+      </c>
       <c r="I23" s="113" t="str">
         <f>P27</f>
         <v>Turquia</v>
       </c>
       <c r="J23" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Austrália</v>
       </c>
       <c r="K23" s="38" t="str">
         <f t="shared" si="1"/>
@@ -14962,7 +14986,7 @@
       </c>
       <c r="M23" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Turquia</v>
       </c>
       <c r="N23" s="45"/>
       <c r="O23" s="47" t="s">
@@ -15046,11 +15070,11 @@
       </c>
       <c r="AQ23" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="AR23" s="15">
         <f t="shared" si="37"/>
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:70" x14ac:dyDescent="0.25">
@@ -15104,15 +15128,15 @@
       </c>
       <c r="Q24" s="38">
         <f>(S24*3)+(T24*1)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24" s="38">
         <f>SUM(S24:U24)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" s="38">
         <f>COUNTIF(J:J,P24)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" s="38">
         <f>COUNTIF(K:K,P24)+COUNTIF(L:L,P24)</f>
@@ -15124,15 +15148,15 @@
       </c>
       <c r="V24" s="38">
         <f>SUMIF(E:E,P24,F:F)+SUMIF(I:I,P24,H:H)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W24" s="38">
         <f>SUMIF(E:E,P24,H:H)+SUMIF(I:I,P24,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" s="38">
         <f>V24-W24</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y24" s="38">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q24)*($X$24:$X$27&gt;X24))</f>
@@ -15163,15 +15187,15 @@
       </c>
       <c r="AG24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,6,FALSE)</f>
@@ -15183,26 +15207,26 @@
       </c>
       <c r="AL24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN24" s="85">
         <f>VLOOKUP($AE24,$O$24:$X$27,10,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP24" s="15">
         <v>4</v>
       </c>
       <c r="AQ24" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>E</v>
+        <v>G</v>
       </c>
       <c r="AR24" s="15">
         <f t="shared" si="37"/>
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:70" x14ac:dyDescent="0.25">
@@ -15248,7 +15272,7 @@
       <c r="N25" s="45"/>
       <c r="O25" s="47">
         <f>RANK(Q25,$Q$24:$Q$27)+SUM(Y25:AB25)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P25" s="49" t="str">
         <f>Sorteios!C15</f>
@@ -15260,7 +15284,7 @@
       </c>
       <c r="R25" s="38">
         <f t="shared" ref="R25:R27" si="39">SUM(S25:U25)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="38">
         <f>COUNTIF(J:J,P25)</f>
@@ -15272,23 +15296,23 @@
       </c>
       <c r="U25" s="38">
         <f>COUNTIF(M:M,P25)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="38">
         <f>SUMIF(E:E,P25,F:F)+SUMIF(I:I,P25,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="38">
         <f>SUMIF(E:E,P25,H:H)+SUMIF(I:I,P25,F:F)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X25" s="38">
         <f t="shared" ref="X25:X27" si="40">V25-W25</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Y25" s="38">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q25)*($X$24:$X$27&gt;X25))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25" s="38">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q25)*($X$24:$X$27=X25)*($V$24:$V$27&gt;V25))</f>
@@ -15300,7 +15324,7 @@
       </c>
       <c r="AB25" s="38">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q25)*($X$24:$X$27=X25)*($V$24:$V$27=V25)*($W$24:$W$27=W25)*($AC$24:$AC$27&lt;AC25))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" s="39">
         <v>2</v>
@@ -15311,19 +15335,19 @@
       </c>
       <c r="AF25" s="83" t="str">
         <f>VLOOKUP($AE25,$O$24:$X$27,2,FALSE)</f>
-        <v>Paraguai</v>
+        <v>Austrália</v>
       </c>
       <c r="AG25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,6,FALSE)</f>
@@ -15335,7 +15359,7 @@
       </c>
       <c r="AL25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,9,FALSE)</f>
@@ -15343,18 +15367,18 @@
       </c>
       <c r="AN25" s="85">
         <f>VLOOKUP($AE25,$O$24:$X$27,10,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP25" s="15">
         <v>5</v>
       </c>
       <c r="AQ25" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>F</v>
+        <v>K</v>
       </c>
       <c r="AR25" s="15">
         <f t="shared" si="37"/>
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:70" x14ac:dyDescent="0.25">
@@ -15400,7 +15424,7 @@
       <c r="N26" s="45"/>
       <c r="O26" s="47">
         <f>RANK(Q26,$Q$24:$Q$27)+SUM(Y26:AB26)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P26" s="49" t="str">
         <f>Sorteios!C16</f>
@@ -15408,15 +15432,15 @@
       </c>
       <c r="Q26" s="38">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" s="38">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="38">
         <f>COUNTIF(J:J,P26)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="38">
         <f>COUNTIF(K:K,P26)+COUNTIF(L:L,P26)</f>
@@ -15428,7 +15452,7 @@
       </c>
       <c r="V26" s="38">
         <f>SUMIF(E:E,P26,F:F)+SUMIF(I:I,P26,H:H)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" s="38">
         <f>SUMIF(E:E,P26,H:H)+SUMIF(I:I,P26,F:F)</f>
@@ -15436,11 +15460,11 @@
       </c>
       <c r="X26" s="38">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y26" s="38">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q26)*($X$24:$X$27&gt;X26))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" s="38">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q26)*($X$24:$X$27=X26)*($V$24:$V$27&gt;V26))</f>
@@ -15452,7 +15476,7 @@
       </c>
       <c r="AB26" s="38">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q26)*($X$24:$X$27=X26)*($V$24:$V$27=V26)*($W$24:$W$27=W26)*($AC$24:$AC$27&lt;AC26))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC26" s="39">
         <v>3</v>
@@ -15463,7 +15487,7 @@
       </c>
       <c r="AF26" s="83" t="str">
         <f>VLOOKUP($AE26,$O$24:$X$27,2,FALSE)</f>
-        <v>Austrália</v>
+        <v>Turquia</v>
       </c>
       <c r="AG26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,3,FALSE)</f>
@@ -15471,7 +15495,7 @@
       </c>
       <c r="AH26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,5,FALSE)</f>
@@ -15483,7 +15507,7 @@
       </c>
       <c r="AK26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,8,FALSE)</f>
@@ -15491,22 +15515,22 @@
       </c>
       <c r="AM26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,9,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN26" s="85">
         <f>VLOOKUP($AE26,$O$24:$X$27,10,FALSE)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AP26" s="15">
         <v>6</v>
       </c>
       <c r="AQ26" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>G</v>
+        <v>H</v>
       </c>
       <c r="AR26" s="15">
         <f t="shared" si="37"/>
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -15552,7 +15576,7 @@
       <c r="N27" s="57"/>
       <c r="O27" s="56">
         <f>RANK(Q27,$Q$24:$Q$27)+SUM(Y27:AB27)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P27" s="49" t="str">
         <f>Sorteios!C17</f>
@@ -15564,7 +15588,7 @@
       </c>
       <c r="R27" s="53">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="38">
         <f>COUNTIF(J:J,P27)</f>
@@ -15576,7 +15600,7 @@
       </c>
       <c r="U27" s="38">
         <f>COUNTIF(M:M,P27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="53">
         <f>SUMIF(E:E,P27,F:F)+SUMIF(I:I,P27,H:H)</f>
@@ -15584,11 +15608,11 @@
       </c>
       <c r="W27" s="53">
         <f>SUMIF(E:E,P27,H:H)+SUMIF(I:I,P27,F:F)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X27" s="53">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Y27" s="53">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q27)*($X$24:$X$27&gt;X27))</f>
@@ -15604,7 +15628,7 @@
       </c>
       <c r="AB27" s="53">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q27)*($X$24:$X$27=X27)*($V$24:$V$27=V27)*($W$24:$W$27=W27)*($AC$24:$AC$27&lt;AC27))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC27" s="54">
         <v>4</v>
@@ -15615,7 +15639,7 @@
       </c>
       <c r="AF27" s="86" t="str">
         <f>VLOOKUP($AE27,$O$24:$X$27,2,FALSE)</f>
-        <v>Turquia</v>
+        <v>Paraguai</v>
       </c>
       <c r="AG27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,3,FALSE)</f>
@@ -15623,7 +15647,7 @@
       </c>
       <c r="AH27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,5,FALSE)</f>
@@ -15635,30 +15659,30 @@
       </c>
       <c r="AK27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,9,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN27" s="88">
         <f>VLOOKUP($AE27,$O$24:$X$27,10,FALSE)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AP27" s="15">
         <v>7</v>
       </c>
       <c r="AQ27" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>H</v>
+        <v>A</v>
       </c>
       <c r="AR27" s="15">
         <f t="shared" si="37"/>
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:70" x14ac:dyDescent="0.25">
@@ -15676,18 +15700,22 @@
         <f>P30</f>
         <v>Alemanha</v>
       </c>
-      <c r="F28" s="125"/>
+      <c r="F28" s="125">
+        <v>7</v>
+      </c>
       <c r="G28" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="H28" s="125"/>
+      <c r="H28" s="125">
+        <v>1</v>
+      </c>
       <c r="I28" s="116" t="str">
         <f>P31</f>
         <v>Curaçau</v>
       </c>
       <c r="J28" s="59" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Alemanha</v>
       </c>
       <c r="K28" s="59" t="str">
         <f t="shared" si="1"/>
@@ -15699,7 +15727,7 @@
       </c>
       <c r="M28" s="60" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Curaçau</v>
       </c>
       <c r="N28" s="61"/>
       <c r="O28" s="62"/>
@@ -15737,11 +15765,11 @@
       </c>
       <c r="AQ28" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="AR28" s="15">
         <f t="shared" si="37"/>
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:70" x14ac:dyDescent="0.25">
@@ -15759,18 +15787,22 @@
         <f>P32</f>
         <v>Costa do Marfim</v>
       </c>
-      <c r="F29" s="123"/>
+      <c r="F29" s="123">
+        <v>1</v>
+      </c>
       <c r="G29" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H29" s="123"/>
+      <c r="H29" s="123">
+        <v>0</v>
+      </c>
       <c r="I29" s="107" t="str">
         <f>P33</f>
         <v>Equador</v>
       </c>
       <c r="J29" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Costa do Marfim</v>
       </c>
       <c r="K29" s="38" t="str">
         <f t="shared" si="1"/>
@@ -15782,7 +15814,7 @@
       </c>
       <c r="M29" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Equador</v>
       </c>
       <c r="N29" s="46"/>
       <c r="O29" s="47" t="s">
@@ -15913,15 +15945,15 @@
       </c>
       <c r="Q30" s="38">
         <f>(S30*3)+(T30*1)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R30" s="38">
         <f>SUM(S30:U30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="38">
         <f>COUNTIF(J:J,P30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" s="38">
         <f>COUNTIF(K:K,P30)+COUNTIF(L:L,P30)</f>
@@ -15933,15 +15965,15 @@
       </c>
       <c r="V30" s="38">
         <f>SUMIF(E:E,P30,F:F)+SUMIF(I:I,P30,H:H)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W30" s="38">
         <f>SUMIF(E:E,P30,H:H)+SUMIF(I:I,P30,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" s="38">
         <f>V30-W30</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y30" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q30)*($X$30:$X$33&gt;X30))</f>
@@ -15972,15 +16004,15 @@
       </c>
       <c r="AG30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,6,FALSE)</f>
@@ -15992,27 +16024,27 @@
       </c>
       <c r="AL30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,8,FALSE)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AM30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN30" s="85">
         <f>VLOOKUP($AE30,$O$30:$X$33,10,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ30" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,1))</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AR30" s="15" t="str">
         <f>_xlfn.CONCAT(3,AQ30)</f>
-        <v>3B</v>
+        <v>3A</v>
       </c>
       <c r="AS30" s="15" t="str">
         <f t="shared" ref="AS30:AS37" si="41">VLOOKUP(AQ30,$AZ$6:$BA$17,2,FALSE)</f>
-        <v>Qatar</v>
+        <v>República Tcheca</v>
       </c>
     </row>
     <row r="31" spans="1:70" x14ac:dyDescent="0.25">
@@ -16058,7 +16090,7 @@
       <c r="N31" s="46"/>
       <c r="O31" s="47">
         <f>RANK(Q31,$Q$30:$Q$33)+SUM(Y31:AB31)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P31" s="49" t="str">
         <f>Sorteios!F15</f>
@@ -16070,7 +16102,7 @@
       </c>
       <c r="R31" s="38">
         <f t="shared" ref="R31:R33" si="43">SUM(S31:U31)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="38">
         <f>COUNTIF(J:J,P31)</f>
@@ -16082,23 +16114,23 @@
       </c>
       <c r="U31" s="38">
         <f>COUNTIF(M:M,P31)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="38">
         <f>SUMIF(E:E,P31,F:F)+SUMIF(I:I,P31,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="38">
         <f>SUMIF(E:E,P31,H:H)+SUMIF(I:I,P31,F:F)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X31" s="38">
         <f t="shared" ref="X31:X33" si="44">V31-W31</f>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="Y31" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q31)*($X$30:$X$33&gt;X31))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z31" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q31)*($X$30:$X$33=X31)*($V$30:$V$33&gt;V31))</f>
@@ -16110,7 +16142,7 @@
       </c>
       <c r="AB31" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q31)*($X$30:$X$33=X31)*($V$30:$V$33=V31)*($W$30:$W$33=W31)*($AC$30:$AC$33&lt;AC31))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" s="39">
         <v>2</v>
@@ -16121,19 +16153,19 @@
       </c>
       <c r="AF31" s="83" t="str">
         <f>VLOOKUP($AE31,$O$30:$X$33,2,FALSE)</f>
-        <v>Curaçau</v>
+        <v>Costa do Marfim</v>
       </c>
       <c r="AG31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,6,FALSE)</f>
@@ -16145,7 +16177,7 @@
       </c>
       <c r="AL31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,9,FALSE)</f>
@@ -16153,19 +16185,19 @@
       </c>
       <c r="AN31" s="85">
         <f>VLOOKUP($AE31,$O$30:$X$33,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ31" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,2))</f>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="AR31" s="15" t="str">
         <f t="shared" ref="AR31:AR37" si="45">_xlfn.CONCAT(3,AQ31)</f>
-        <v>3C</v>
+        <v>3B</v>
       </c>
       <c r="AS31" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Haiti</v>
+        <v>Qatar</v>
       </c>
     </row>
     <row r="32" spans="1:70" x14ac:dyDescent="0.25">
@@ -16211,7 +16243,7 @@
       <c r="N32" s="46"/>
       <c r="O32" s="47">
         <f>RANK(Q32,$Q$30:$Q$33)+SUM(Y32:AB32)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P32" s="49" t="str">
         <f>Sorteios!F16</f>
@@ -16219,15 +16251,15 @@
       </c>
       <c r="Q32" s="38">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R32" s="38">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="38">
         <f>COUNTIF(J:J,P32)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" s="38">
         <f>COUNTIF(K:K,P32)+COUNTIF(L:L,P32)</f>
@@ -16239,7 +16271,7 @@
       </c>
       <c r="V32" s="38">
         <f>SUMIF(E:E,P32,F:F)+SUMIF(I:I,P32,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="38">
         <f>SUMIF(E:E,P32,H:H)+SUMIF(I:I,P32,F:F)</f>
@@ -16247,11 +16279,11 @@
       </c>
       <c r="X32" s="38">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q32)*($X$30:$X$33&gt;X32))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q32)*($X$30:$X$33=X32)*($V$30:$V$33&gt;V32))</f>
@@ -16263,7 +16295,7 @@
       </c>
       <c r="AB32" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q32)*($X$30:$X$33=X32)*($V$30:$V$33=V32)*($W$30:$W$33=W32)*($AC$30:$AC$33&lt;AC32))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC32" s="39">
         <v>3</v>
@@ -16274,7 +16306,7 @@
       </c>
       <c r="AF32" s="83" t="str">
         <f>VLOOKUP($AE32,$O$30:$X$33,2,FALSE)</f>
-        <v>Costa do Marfim</v>
+        <v>Equador</v>
       </c>
       <c r="AG32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,3,FALSE)</f>
@@ -16282,7 +16314,7 @@
       </c>
       <c r="AH32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,5,FALSE)</f>
@@ -16294,7 +16326,7 @@
       </c>
       <c r="AK32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,8,FALSE)</f>
@@ -16302,23 +16334,23 @@
       </c>
       <c r="AM32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN32" s="85">
         <f>VLOOKUP($AE32,$O$30:$X$33,10,FALSE)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ32" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,3))</f>
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="AR32" s="15" t="str">
         <f t="shared" si="45"/>
-        <v>3D</v>
+        <v>3C</v>
       </c>
       <c r="AS32" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Austrália</v>
+        <v>Marrocos</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -16364,7 +16396,7 @@
       <c r="N33" s="55"/>
       <c r="O33" s="56">
         <f>RANK(Q33,$Q$30:$Q$33)+SUM(Y33:AB33)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P33" s="49" t="str">
         <f>Sorteios!F17</f>
@@ -16376,7 +16408,7 @@
       </c>
       <c r="R33" s="53">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" s="38">
         <f>COUNTIF(J:J,P33)</f>
@@ -16388,7 +16420,7 @@
       </c>
       <c r="U33" s="38">
         <f>COUNTIF(M:M,P33)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="53">
         <f>SUMIF(E:E,P33,F:F)+SUMIF(I:I,P33,H:H)</f>
@@ -16396,11 +16428,11 @@
       </c>
       <c r="W33" s="53">
         <f>SUMIF(E:E,P33,H:H)+SUMIF(I:I,P33,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" s="53">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y33" s="53">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q33)*($X$30:$X$33&gt;X33))</f>
@@ -16416,7 +16448,7 @@
       </c>
       <c r="AB33" s="53">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q33)*($X$30:$X$33=X33)*($V$30:$V$33=V33)*($W$30:$W$33=W33)*($AC$30:$AC$33&lt;AC33))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC33" s="54">
         <v>4</v>
@@ -16427,7 +16459,7 @@
       </c>
       <c r="AF33" s="86" t="str">
         <f>VLOOKUP($AE33,$O$30:$X$33,2,FALSE)</f>
-        <v>Equador</v>
+        <v>Curaçau</v>
       </c>
       <c r="AG33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,3,FALSE)</f>
@@ -16435,7 +16467,7 @@
       </c>
       <c r="AH33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,5,FALSE)</f>
@@ -16447,19 +16479,19 @@
       </c>
       <c r="AK33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,9,FALSE)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AN33" s="88">
         <f>VLOOKUP($AE33,$O$30:$X$33,10,FALSE)</f>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AQ33" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,4))</f>
@@ -16471,7 +16503,7 @@
       </c>
       <c r="AS33" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Costa do Marfim</v>
+        <v>Equador</v>
       </c>
     </row>
     <row r="34" spans="1:45" x14ac:dyDescent="0.25">
@@ -16489,11 +16521,15 @@
         <f>P36</f>
         <v>Países Baixos</v>
       </c>
-      <c r="F34" s="125"/>
+      <c r="F34" s="125">
+        <v>2</v>
+      </c>
       <c r="G34" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="H34" s="125"/>
+      <c r="H34" s="125">
+        <v>2</v>
+      </c>
       <c r="I34" s="112" t="str">
         <f>P37</f>
         <v>Japão</v>
@@ -16504,11 +16540,11 @@
       </c>
       <c r="K34" s="59" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Países Baixos</v>
       </c>
       <c r="L34" s="59" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Japão</v>
       </c>
       <c r="M34" s="60" t="str">
         <f t="shared" si="3"/>
@@ -16555,7 +16591,7 @@
       </c>
       <c r="AS34" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Suécia</v>
+        <v>Japão</v>
       </c>
     </row>
     <row r="35" spans="1:45" x14ac:dyDescent="0.25">
@@ -16573,18 +16609,22 @@
         <f>P38</f>
         <v>Suécia</v>
       </c>
-      <c r="F35" s="123"/>
+      <c r="F35" s="123">
+        <v>5</v>
+      </c>
       <c r="G35" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H35" s="123"/>
+      <c r="H35" s="123">
+        <v>1</v>
+      </c>
       <c r="I35" s="113" t="str">
         <f>P39</f>
         <v>Tunísia</v>
       </c>
       <c r="J35" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Suécia</v>
       </c>
       <c r="K35" s="38" t="str">
         <f t="shared" si="1"/>
@@ -16596,7 +16636,7 @@
       </c>
       <c r="M35" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Tunísia</v>
       </c>
       <c r="N35" s="45"/>
       <c r="O35" s="47" t="s">
@@ -16685,7 +16725,7 @@
       </c>
       <c r="AS35" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Irã</v>
+        <v>Bélgica</v>
       </c>
     </row>
     <row r="36" spans="1:45" x14ac:dyDescent="0.25">
@@ -16731,7 +16771,7 @@
       <c r="N36" s="45"/>
       <c r="O36" s="47">
         <f>RANK(Q36,$Q$36:$Q$39)+SUM(Y36:AB36)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P36" s="49" t="str">
         <f>Sorteios!I14</f>
@@ -16739,11 +16779,11 @@
       </c>
       <c r="Q36" s="38">
         <f>(S36*3)+(T36*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="38">
         <f>SUM(S36:U36)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" s="38">
         <f>COUNTIF(J:J,P36)</f>
@@ -16751,7 +16791,7 @@
       </c>
       <c r="T36" s="38">
         <f>COUNTIF(K:K,P36)+COUNTIF(L:L,P36)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" s="38">
         <f>COUNTIF(M:M,P36)</f>
@@ -16759,11 +16799,11 @@
       </c>
       <c r="V36" s="38">
         <f>SUMIF(E:E,P36,F:F)+SUMIF(I:I,P36,H:H)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" s="38">
         <f>SUMIF(E:E,P36,H:H)+SUMIF(I:I,P36,F:F)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X36" s="38">
         <f>V36-W36</f>
@@ -16794,19 +16834,19 @@
       </c>
       <c r="AF36" s="83" t="str">
         <f>VLOOKUP($AE36,$O$36:$X$39,2,FALSE)</f>
-        <v>Países Baixos</v>
+        <v>Suécia</v>
       </c>
       <c r="AG36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,6,FALSE)</f>
@@ -16818,15 +16858,15 @@
       </c>
       <c r="AL36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,8,FALSE)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN36" s="85">
         <f>VLOOKUP($AE36,$O$36:$X$39,10,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AQ36" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,7))</f>
@@ -16838,7 +16878,7 @@
       </c>
       <c r="AS36" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Arábia Saudita</v>
+        <v>Espanha</v>
       </c>
     </row>
     <row r="37" spans="1:45" x14ac:dyDescent="0.25">
@@ -16884,7 +16924,7 @@
       <c r="N37" s="45"/>
       <c r="O37" s="47">
         <f>RANK(Q37,$Q$36:$Q$39)+SUM(Y37:AB37)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P37" s="49" t="str">
         <f>Sorteios!I15</f>
@@ -16892,11 +16932,11 @@
       </c>
       <c r="Q37" s="38">
         <f t="shared" ref="Q37:Q39" si="50">(S37*3)+(T37*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" s="38">
         <f t="shared" ref="R37:R39" si="51">SUM(S37:U37)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" s="38">
         <f>COUNTIF(J:J,P37)</f>
@@ -16904,7 +16944,7 @@
       </c>
       <c r="T37" s="38">
         <f>COUNTIF(K:K,P37)+COUNTIF(L:L,P37)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" s="38">
         <f>COUNTIF(M:M,P37)</f>
@@ -16912,11 +16952,11 @@
       </c>
       <c r="V37" s="38">
         <f>SUMIF(E:E,P37,F:F)+SUMIF(I:I,P37,H:H)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" s="38">
         <f>SUMIF(E:E,P37,H:H)+SUMIF(I:I,P37,F:F)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X37" s="38">
         <f t="shared" ref="X37:X39" si="52">V37-W37</f>
@@ -16947,15 +16987,15 @@
       </c>
       <c r="AF37" s="83" t="str">
         <f>VLOOKUP($AE37,$O$36:$X$39,2,FALSE)</f>
-        <v>Japão</v>
+        <v>Países Baixos</v>
       </c>
       <c r="AG37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,5,FALSE)</f>
@@ -16963,7 +17003,7 @@
       </c>
       <c r="AJ37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,7,FALSE)</f>
@@ -16971,11 +17011,11 @@
       </c>
       <c r="AL37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,9,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN37" s="85">
         <f>VLOOKUP($AE37,$O$36:$X$39,10,FALSE)</f>
@@ -16983,15 +17023,15 @@
       </c>
       <c r="AQ37" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,8))</f>
-        <v>I</v>
+        <v>K</v>
       </c>
       <c r="AR37" s="15" t="str">
         <f t="shared" si="45"/>
-        <v>3I</v>
+        <v>3K</v>
       </c>
       <c r="AS37" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Iraque</v>
+        <v>RD Congo</v>
       </c>
     </row>
     <row r="38" spans="1:45" x14ac:dyDescent="0.25">
@@ -17037,7 +17077,7 @@
       <c r="N38" s="45"/>
       <c r="O38" s="47">
         <f>RANK(Q38,$Q$36:$Q$39)+SUM(Y38:AB38)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P38" s="49" t="str">
         <f>Sorteios!I16</f>
@@ -17045,15 +17085,15 @@
       </c>
       <c r="Q38" s="38">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R38" s="38">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" s="38">
         <f>COUNTIF(J:J,P38)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" s="38">
         <f>COUNTIF(K:K,P38)+COUNTIF(L:L,P38)</f>
@@ -17065,15 +17105,15 @@
       </c>
       <c r="V38" s="38">
         <f>SUMIF(E:E,P38,F:F)+SUMIF(I:I,P38,H:H)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W38" s="38">
         <f>SUMIF(E:E,P38,H:H)+SUMIF(I:I,P38,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" s="38">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y38" s="38">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q38)*($X$36:$X$39&gt;X38))</f>
@@ -17089,7 +17129,7 @@
       </c>
       <c r="AB38" s="38">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q38)*($X$36:$X$39=X38)*($V$36:$V$39=V38)*($W$36:$W$39=W38)*($AC$36:$AC$39&lt;AC38))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC38" s="39">
         <v>3</v>
@@ -17100,15 +17140,15 @@
       </c>
       <c r="AF38" s="83" t="str">
         <f>VLOOKUP($AE38,$O$36:$X$39,2,FALSE)</f>
-        <v>Suécia</v>
+        <v>Japão</v>
       </c>
       <c r="AG38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,5,FALSE)</f>
@@ -17116,7 +17156,7 @@
       </c>
       <c r="AJ38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,7,FALSE)</f>
@@ -17124,11 +17164,11 @@
       </c>
       <c r="AL38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,9,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN38" s="85">
         <f>VLOOKUP($AE38,$O$36:$X$39,10,FALSE)</f>
@@ -17190,7 +17230,7 @@
       </c>
       <c r="R39" s="53">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" s="38">
         <f>COUNTIF(J:J,P39)</f>
@@ -17202,19 +17242,19 @@
       </c>
       <c r="U39" s="38">
         <f>COUNTIF(M:M,P39)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="53">
         <f>SUMIF(E:E,P39,F:F)+SUMIF(I:I,P39,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="53">
         <f>SUMIF(E:E,P39,H:H)+SUMIF(I:I,P39,F:F)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X39" s="53">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="Y39" s="53">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q39)*($X$36:$X$39&gt;X39))</f>
@@ -17230,7 +17270,7 @@
       </c>
       <c r="AB39" s="53">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q39)*($X$36:$X$39=X39)*($V$36:$V$39=V39)*($W$36:$W$39=W39)*($AC$36:$AC$39&lt;AC39))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC39" s="54">
         <v>4</v>
@@ -17249,7 +17289,7 @@
       </c>
       <c r="AH39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,5,FALSE)</f>
@@ -17261,27 +17301,27 @@
       </c>
       <c r="AK39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,9,FALSE)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN39" s="88">
         <f>VLOOKUP($AE39,$O$36:$X$39,10,FALSE)</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AQ39" s="15" t="str">
         <f>_xlfn.CONCAT(AQ30:AQ37)</f>
-        <v>BCDEFGHI</v>
+        <v>ABCEFGHK</v>
       </c>
       <c r="AR39" s="15" t="str">
         <f>VLOOKUP(AQ39,Dummy!O:X,10,FALSE)</f>
-        <v>3C3G3B3D3H3F3E3I</v>
+        <v>3H3G3B3C3A3F3E3K</v>
       </c>
     </row>
     <row r="40" spans="1:45" x14ac:dyDescent="0.25">
@@ -17299,11 +17339,15 @@
         <f>P42</f>
         <v>Bélgica</v>
       </c>
-      <c r="F40" s="125"/>
+      <c r="F40" s="125">
+        <v>1</v>
+      </c>
       <c r="G40" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="H40" s="125"/>
+      <c r="H40" s="125">
+        <v>1</v>
+      </c>
       <c r="I40" s="116" t="str">
         <f>P43</f>
         <v>Egito</v>
@@ -17314,11 +17358,11 @@
       </c>
       <c r="K40" s="59" t="str">
         <f t="shared" si="47"/>
-        <v/>
+        <v>Bélgica</v>
       </c>
       <c r="L40" s="59" t="str">
         <f t="shared" si="48"/>
-        <v/>
+        <v>Egito</v>
       </c>
       <c r="M40" s="60" t="str">
         <f t="shared" si="49"/>
@@ -17371,11 +17415,15 @@
         <f>P44</f>
         <v>Irã</v>
       </c>
-      <c r="F41" s="123"/>
+      <c r="F41" s="123">
+        <v>2</v>
+      </c>
       <c r="G41" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H41" s="123"/>
+      <c r="H41" s="123">
+        <v>2</v>
+      </c>
       <c r="I41" s="107" t="str">
         <f>P45</f>
         <v>Nova Zelândia</v>
@@ -17386,11 +17434,11 @@
       </c>
       <c r="K41" s="38" t="str">
         <f t="shared" si="47"/>
-        <v/>
+        <v>Irã</v>
       </c>
       <c r="L41" s="38" t="str">
         <f t="shared" si="48"/>
-        <v/>
+        <v>Nova Zelândia</v>
       </c>
       <c r="M41" s="39" t="str">
         <f t="shared" si="49"/>
@@ -17517,7 +17565,7 @@
       <c r="N42" s="46"/>
       <c r="O42" s="47">
         <f>RANK(Q42,$Q$42:$Q$45)+SUM(Y42:AB42)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P42" s="49" t="str">
         <f>Sorteios!C22</f>
@@ -17525,11 +17573,11 @@
       </c>
       <c r="Q42" s="38">
         <f>(S42*3)+(T42*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="38">
         <f>SUM(S42:U42)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" s="38">
         <f>COUNTIF(J:J,P42)</f>
@@ -17537,7 +17585,7 @@
       </c>
       <c r="T42" s="38">
         <f>COUNTIF(K:K,P42)+COUNTIF(L:L,P42)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U42" s="38">
         <f>COUNTIF(M:M,P42)</f>
@@ -17545,11 +17593,11 @@
       </c>
       <c r="V42" s="38">
         <f>SUMIF(E:E,P42,F:F)+SUMIF(I:I,P42,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" s="38">
         <f>SUMIF(E:E,P42,H:H)+SUMIF(I:I,P42,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" s="38">
         <f>V42-W42</f>
@@ -17561,7 +17609,7 @@
       </c>
       <c r="Z42" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q42)*($X$42:$X$45=X42)*($V$42:$V$45&gt;V42))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA42" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q42)*($X$42:$X$45=X42)*($V$42:$V$45=V42)*($W$42:$W$45&gt;W42))</f>
@@ -17580,15 +17628,15 @@
       </c>
       <c r="AF42" s="83" t="str">
         <f>VLOOKUP($AE42,$O$42:$X$45,2,FALSE)</f>
-        <v>Bélgica</v>
+        <v>Irã</v>
       </c>
       <c r="AG42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,5,FALSE)</f>
@@ -17596,7 +17644,7 @@
       </c>
       <c r="AJ42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,7,FALSE)</f>
@@ -17604,11 +17652,11 @@
       </c>
       <c r="AL42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,9,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN42" s="85">
         <f>VLOOKUP($AE42,$O$42:$X$45,10,FALSE)</f>
@@ -17658,7 +17706,7 @@
       <c r="N43" s="46"/>
       <c r="O43" s="47">
         <f>RANK(Q43,$Q$42:$Q$45)+SUM(Y43:AB43)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P43" s="49" t="str">
         <f>Sorteios!C23</f>
@@ -17666,11 +17714,11 @@
       </c>
       <c r="Q43" s="38">
         <f t="shared" ref="Q43:Q45" si="53">(S43*3)+(T43*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" s="38">
         <f t="shared" ref="R43:R45" si="54">SUM(S43:U43)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" s="38">
         <f>COUNTIF(J:J,P43)</f>
@@ -17678,7 +17726,7 @@
       </c>
       <c r="T43" s="38">
         <f>COUNTIF(K:K,P43)+COUNTIF(L:L,P43)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" s="38">
         <f>COUNTIF(M:M,P43)</f>
@@ -17686,11 +17734,11 @@
       </c>
       <c r="V43" s="38">
         <f>SUMIF(E:E,P43,F:F)+SUMIF(I:I,P43,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="38">
         <f>SUMIF(E:E,P43,H:H)+SUMIF(I:I,P43,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X43" s="38">
         <f t="shared" ref="X43:X45" si="55">V43-W43</f>
@@ -17702,7 +17750,7 @@
       </c>
       <c r="Z43" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q43)*($X$42:$X$45=X43)*($V$42:$V$45&gt;V43))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA43" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q43)*($X$42:$X$45=X43)*($V$42:$V$45=V43)*($W$42:$W$45&gt;W43))</f>
@@ -17721,15 +17769,15 @@
       </c>
       <c r="AF43" s="83" t="str">
         <f>VLOOKUP($AE43,$O$42:$X$45,2,FALSE)</f>
-        <v>Egito</v>
+        <v>Nova Zelândia</v>
       </c>
       <c r="AG43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,5,FALSE)</f>
@@ -17737,7 +17785,7 @@
       </c>
       <c r="AJ43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,7,FALSE)</f>
@@ -17745,11 +17793,11 @@
       </c>
       <c r="AL43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,9,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN43" s="85">
         <f>VLOOKUP($AE43,$O$42:$X$45,10,FALSE)</f>
@@ -17799,7 +17847,7 @@
       <c r="N44" s="46"/>
       <c r="O44" s="47">
         <f>RANK(Q44,$Q$42:$Q$45)+SUM(Y44:AB44)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P44" s="49" t="str">
         <f>Sorteios!C24</f>
@@ -17807,11 +17855,11 @@
       </c>
       <c r="Q44" s="38">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" s="38">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" s="38">
         <f>COUNTIF(J:J,P44)</f>
@@ -17819,7 +17867,7 @@
       </c>
       <c r="T44" s="38">
         <f>COUNTIF(K:K,P44)+COUNTIF(L:L,P44)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U44" s="38">
         <f>COUNTIF(M:M,P44)</f>
@@ -17827,11 +17875,11 @@
       </c>
       <c r="V44" s="38">
         <f>SUMIF(E:E,P44,F:F)+SUMIF(I:I,P44,H:H)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" s="38">
         <f>SUMIF(E:E,P44,H:H)+SUMIF(I:I,P44,F:F)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X44" s="38">
         <f t="shared" si="55"/>
@@ -17851,7 +17899,7 @@
       </c>
       <c r="AB44" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q44)*($X$42:$X$45=X44)*($V$42:$V$45=V44)*($W$42:$W$45=W44)*($AC$42:$AC$45&lt;AC44))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC44" s="39">
         <v>3</v>
@@ -17862,15 +17910,15 @@
       </c>
       <c r="AF44" s="83" t="str">
         <f>VLOOKUP($AE44,$O$42:$X$45,2,FALSE)</f>
-        <v>Irã</v>
+        <v>Bélgica</v>
       </c>
       <c r="AG44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,5,FALSE)</f>
@@ -17878,7 +17926,7 @@
       </c>
       <c r="AJ44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,7,FALSE)</f>
@@ -17886,11 +17934,11 @@
       </c>
       <c r="AL44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN44" s="85">
         <f>VLOOKUP($AE44,$O$42:$X$45,10,FALSE)</f>
@@ -17940,7 +17988,7 @@
       <c r="N45" s="55"/>
       <c r="O45" s="56">
         <f>RANK(Q45,$Q$42:$Q$45)+SUM(Y45:AB45)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P45" s="49" t="str">
         <f>Sorteios!C25</f>
@@ -17948,11 +17996,11 @@
       </c>
       <c r="Q45" s="53">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" s="53">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" s="38">
         <f>COUNTIF(J:J,P45)</f>
@@ -17960,7 +18008,7 @@
       </c>
       <c r="T45" s="38">
         <f>COUNTIF(K:K,P45)+COUNTIF(L:L,P45)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" s="38">
         <f>COUNTIF(M:M,P45)</f>
@@ -17968,11 +18016,11 @@
       </c>
       <c r="V45" s="53">
         <f>SUMIF(E:E,P45,F:F)+SUMIF(I:I,P45,H:H)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" s="53">
         <f>SUMIF(E:E,P45,H:H)+SUMIF(I:I,P45,F:F)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" s="53">
         <f t="shared" si="55"/>
@@ -17992,7 +18040,7 @@
       </c>
       <c r="AB45" s="53">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q45)*($X$42:$X$45=X45)*($V$42:$V$45=V45)*($W$42:$W$45=W45)*($AC$42:$AC$45&lt;AC45))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC45" s="54">
         <v>4</v>
@@ -18003,15 +18051,15 @@
       </c>
       <c r="AF45" s="86" t="str">
         <f>VLOOKUP($AE45,$O$42:$X$45,2,FALSE)</f>
-        <v>Nova Zelândia</v>
+        <v>Egito</v>
       </c>
       <c r="AG45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,5,FALSE)</f>
@@ -18019,7 +18067,7 @@
       </c>
       <c r="AJ45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,7,FALSE)</f>
@@ -18027,11 +18075,11 @@
       </c>
       <c r="AL45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN45" s="88">
         <f>VLOOKUP($AE45,$O$42:$X$45,10,FALSE)</f>
@@ -18053,29 +18101,33 @@
         <f>P48</f>
         <v>Espanha</v>
       </c>
-      <c r="F46" s="125"/>
+      <c r="F46" s="125">
+        <v>0</v>
+      </c>
       <c r="G46" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="H46" s="125"/>
+      <c r="H46" s="125">
+        <v>0</v>
+      </c>
       <c r="I46" s="112" t="str">
         <f>P49</f>
         <v>Cabo Verde</v>
       </c>
       <c r="J46" s="59" t="str">
-        <f t="shared" si="46"/>
+        <f>IF(F46=H46,"empate",IF(F46&gt;H46,E46,I46))</f>
         <v>empate</v>
       </c>
       <c r="K46" s="59" t="str">
-        <f t="shared" si="47"/>
-        <v/>
+        <f>IF(F46="","",IF(H46="","",IF(J46="empate",E46,"")))</f>
+        <v>Espanha</v>
       </c>
       <c r="L46" s="59" t="str">
-        <f t="shared" si="48"/>
-        <v/>
+        <f>IF(E46="","",IF(F46="","",IF(M46="empate",I46,"")))</f>
+        <v>Cabo Verde</v>
       </c>
       <c r="M46" s="60" t="str">
-        <f t="shared" si="49"/>
+        <f>IF(F46=H46,"empate",IF(F46&lt;H46,E46,I46))</f>
         <v>empate</v>
       </c>
       <c r="N46" s="64"/>
@@ -18125,29 +18177,33 @@
         <f>P50</f>
         <v>Arábia Saudita</v>
       </c>
-      <c r="F47" s="123"/>
+      <c r="F47" s="123">
+        <v>1</v>
+      </c>
       <c r="G47" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H47" s="123"/>
+      <c r="H47" s="123">
+        <v>1</v>
+      </c>
       <c r="I47" s="113" t="str">
         <f>P51</f>
         <v>Uruguai</v>
       </c>
       <c r="J47" s="38" t="str">
-        <f t="shared" si="46"/>
+        <f>IF(F47=H47,"empate",IF(F47&gt;H47,E47,I47))</f>
         <v>empate</v>
       </c>
       <c r="K47" s="38" t="str">
-        <f t="shared" si="47"/>
-        <v/>
+        <f>IF(F47="","",IF(H47="","",IF(J47="empate",E47,"")))</f>
+        <v>Arábia Saudita</v>
       </c>
       <c r="L47" s="38" t="str">
-        <f t="shared" si="48"/>
-        <v/>
+        <f>IF(E47="","",IF(F47="","",IF(M47="empate",I47,"")))</f>
+        <v>Uruguai</v>
       </c>
       <c r="M47" s="39" t="str">
-        <f t="shared" si="49"/>
+        <f>IF(F47=H47,"empate",IF(F47&lt;H47,E47,I47))</f>
         <v>empate</v>
       </c>
       <c r="N47" s="45"/>
@@ -18271,7 +18327,7 @@
       <c r="N48" s="45"/>
       <c r="O48" s="47">
         <f>RANK(Q48,$Q$48:$Q$51)+SUM(Y48:AB48)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P48" s="49" t="str">
         <f>Sorteios!F22</f>
@@ -18279,11 +18335,11 @@
       </c>
       <c r="Q48" s="38">
         <f>(S48*3)+(T48*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="38">
         <f>SUM(S48:U48)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" s="38">
         <f>COUNTIF(J:J,P48)</f>
@@ -18291,7 +18347,7 @@
       </c>
       <c r="T48" s="38">
         <f>COUNTIF(K:K,P48)+COUNTIF(L:L,P48)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" s="38">
         <f>COUNTIF(M:M,P48)</f>
@@ -18315,7 +18371,7 @@
       </c>
       <c r="Z48" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q48)*($X$48:$X$51=X48)*($V$48:$V$51&gt;V48))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA48" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q48)*($X$48:$X$51=X48)*($V$48:$V$51=V48)*($W$48:$W$51&gt;W48))</f>
@@ -18334,15 +18390,15 @@
       </c>
       <c r="AF48" s="83" t="str">
         <f>VLOOKUP($AE48,$O$48:$X$51,2,FALSE)</f>
-        <v>Espanha</v>
+        <v>Arábia Saudita</v>
       </c>
       <c r="AG48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,5,FALSE)</f>
@@ -18350,7 +18406,7 @@
       </c>
       <c r="AJ48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,7,FALSE)</f>
@@ -18358,11 +18414,11 @@
       </c>
       <c r="AL48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN48" s="85">
         <f>VLOOKUP($AE48,$O$48:$X$51,10,FALSE)</f>
@@ -18412,7 +18468,7 @@
       <c r="N49" s="45"/>
       <c r="O49" s="47">
         <f>RANK(Q49,$Q$48:$Q$51)+SUM(Y49:AB49)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P49" s="49" t="str">
         <f>Sorteios!F23</f>
@@ -18420,11 +18476,11 @@
       </c>
       <c r="Q49" s="38">
         <f t="shared" ref="Q49:Q51" si="56">(S49*3)+(T49*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" s="38">
         <f t="shared" ref="R49:R51" si="57">SUM(S49:U49)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" s="38">
         <f>COUNTIF(J:J,P49)</f>
@@ -18432,7 +18488,7 @@
       </c>
       <c r="T49" s="38">
         <f>COUNTIF(K:K,P49)+COUNTIF(L:L,P49)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" s="38">
         <f>COUNTIF(M:M,P49)</f>
@@ -18456,7 +18512,7 @@
       </c>
       <c r="Z49" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q49)*($X$48:$X$51=X49)*($V$48:$V$51&gt;V49))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA49" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q49)*($X$48:$X$51=X49)*($V$48:$V$51=V49)*($W$48:$W$51&gt;W49))</f>
@@ -18475,15 +18531,15 @@
       </c>
       <c r="AF49" s="83" t="str">
         <f>VLOOKUP($AE49,$O$48:$X$51,2,FALSE)</f>
-        <v>Cabo Verde</v>
+        <v>Uruguai</v>
       </c>
       <c r="AG49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,5,FALSE)</f>
@@ -18491,7 +18547,7 @@
       </c>
       <c r="AJ49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,7,FALSE)</f>
@@ -18499,11 +18555,11 @@
       </c>
       <c r="AL49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN49" s="85">
         <f>VLOOKUP($AE49,$O$48:$X$51,10,FALSE)</f>
@@ -18553,7 +18609,7 @@
       <c r="N50" s="45"/>
       <c r="O50" s="47">
         <f>RANK(Q50,$Q$48:$Q$51)+SUM(Y50:AB50)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P50" s="49" t="str">
         <f>Sorteios!F24</f>
@@ -18561,11 +18617,11 @@
       </c>
       <c r="Q50" s="38">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="38">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" s="38">
         <f>COUNTIF(J:J,P50)</f>
@@ -18573,7 +18629,7 @@
       </c>
       <c r="T50" s="38">
         <f>COUNTIF(K:K,P50)+COUNTIF(L:L,P50)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" s="38">
         <f>COUNTIF(M:M,P50)</f>
@@ -18581,11 +18637,11 @@
       </c>
       <c r="V50" s="38">
         <f>SUMIF(E:E,P50,F:F)+SUMIF(I:I,P50,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="38">
         <f>SUMIF(E:E,P50,H:H)+SUMIF(I:I,P50,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" s="38">
         <f t="shared" si="58"/>
@@ -18605,7 +18661,7 @@
       </c>
       <c r="AB50" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q50)*($X$48:$X$51=X50)*($V$48:$V$51=V50)*($W$48:$W$51=W50)*($AC$48:$AC$51&lt;AC50))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC50" s="39">
         <v>3</v>
@@ -18616,15 +18672,15 @@
       </c>
       <c r="AF50" s="83" t="str">
         <f>VLOOKUP($AE50,$O$48:$X$51,2,FALSE)</f>
-        <v>Arábia Saudita</v>
+        <v>Espanha</v>
       </c>
       <c r="AG50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,5,FALSE)</f>
@@ -18632,7 +18688,7 @@
       </c>
       <c r="AJ50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,7,FALSE)</f>
@@ -18694,7 +18750,7 @@
       <c r="N51" s="45"/>
       <c r="O51" s="68">
         <f>RANK(Q51,$Q$48:$Q$51)+SUM(Y51:AB51)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P51" s="49" t="str">
         <f>Sorteios!F25</f>
@@ -18702,11 +18758,11 @@
       </c>
       <c r="Q51" s="53">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" s="53">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" s="38">
         <f>COUNTIF(J:J,P51)</f>
@@ -18714,7 +18770,7 @@
       </c>
       <c r="T51" s="38">
         <f>COUNTIF(K:K,P51)+COUNTIF(L:L,P51)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U51" s="38">
         <f>COUNTIF(M:M,P51)</f>
@@ -18722,11 +18778,11 @@
       </c>
       <c r="V51" s="53">
         <f>SUMIF(E:E,P51,F:F)+SUMIF(I:I,P51,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="53">
         <f>SUMIF(E:E,P51,H:H)+SUMIF(I:I,P51,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X51" s="53">
         <f t="shared" si="58"/>
@@ -18746,7 +18802,7 @@
       </c>
       <c r="AB51" s="53">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q51)*($X$48:$X$51=X51)*($V$48:$V$51=V51)*($W$48:$W$51=W51)*($AC$48:$AC$51&lt;AC51))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC51" s="54">
         <v>4</v>
@@ -18757,15 +18813,15 @@
       </c>
       <c r="AF51" s="86" t="str">
         <f>VLOOKUP($AE51,$O$48:$X$51,2,FALSE)</f>
-        <v>Uruguai</v>
+        <v>Cabo Verde</v>
       </c>
       <c r="AG51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,5,FALSE)</f>
@@ -18773,7 +18829,7 @@
       </c>
       <c r="AJ51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,7,FALSE)</f>
@@ -18807,18 +18863,22 @@
         <f>P54</f>
         <v>França</v>
       </c>
-      <c r="F52" s="125"/>
+      <c r="F52" s="125">
+        <v>3</v>
+      </c>
       <c r="G52" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="H52" s="125"/>
+      <c r="H52" s="125">
+        <v>1</v>
+      </c>
       <c r="I52" s="116" t="str">
         <f>P55</f>
         <v>Senegal</v>
       </c>
       <c r="J52" s="59" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>França</v>
       </c>
       <c r="K52" s="59" t="str">
         <f t="shared" si="47"/>
@@ -18830,7 +18890,7 @@
       </c>
       <c r="M52" s="60" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Senegal</v>
       </c>
       <c r="N52" s="61"/>
       <c r="O52" s="62"/>
@@ -18879,18 +18939,22 @@
         <f>P56</f>
         <v>Iraque</v>
       </c>
-      <c r="F53" s="123"/>
+      <c r="F53" s="123">
+        <v>1</v>
+      </c>
       <c r="G53" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H53" s="123"/>
+      <c r="H53" s="123">
+        <v>4</v>
+      </c>
       <c r="I53" s="107" t="str">
         <f>P57</f>
         <v>Noruega</v>
       </c>
       <c r="J53" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Noruega</v>
       </c>
       <c r="K53" s="38" t="str">
         <f t="shared" si="47"/>
@@ -18902,7 +18966,7 @@
       </c>
       <c r="M53" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Iraque</v>
       </c>
       <c r="N53" s="46"/>
       <c r="O53" s="47" t="s">
@@ -19025,7 +19089,7 @@
       <c r="N54" s="46"/>
       <c r="O54" s="47">
         <f>RANK(Q54,$Q$54:$Q$57)+SUM(Y54:AB54)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P54" s="49" t="str">
         <f>Sorteios!I22</f>
@@ -19033,15 +19097,15 @@
       </c>
       <c r="Q54" s="38">
         <f>(S54*3)+(T54*1)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R54" s="38">
         <f>SUM(S54:U54)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" s="38">
         <f>COUNTIF(J:J,P54)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" s="38">
         <f>COUNTIF(K:K,P54)+COUNTIF(L:L,P54)</f>
@@ -19053,19 +19117,19 @@
       </c>
       <c r="V54" s="38">
         <f>SUMIF(E:E,P54,F:F)+SUMIF(I:I,P54,H:H)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W54" s="38">
         <f>SUMIF(E:E,P54,H:H)+SUMIF(I:I,P54,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X54" s="38">
         <f>V54-W54</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y54" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q54)*($X$54:$X$57&gt;X54))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z54" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q54)*($X$54:$X$57=X54)*($V$54:$V$57&gt;V54))</f>
@@ -19088,19 +19152,19 @@
       </c>
       <c r="AF54" s="83" t="str">
         <f>VLOOKUP($AE54,$O$54:$X$57,2,FALSE)</f>
-        <v>França</v>
+        <v>Noruega</v>
       </c>
       <c r="AG54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,6,FALSE)</f>
@@ -19112,15 +19176,15 @@
       </c>
       <c r="AL54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN54" s="85">
         <f>VLOOKUP($AE54,$O$54:$X$57,10,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:40" x14ac:dyDescent="0.25">
@@ -19166,7 +19230,7 @@
       <c r="N55" s="46"/>
       <c r="O55" s="47">
         <f>RANK(Q55,$Q$54:$Q$57)+SUM(Y55:AB55)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P55" s="49" t="str">
         <f>Sorteios!I23</f>
@@ -19178,7 +19242,7 @@
       </c>
       <c r="R55" s="38">
         <f t="shared" ref="R55:R57" si="60">SUM(S55:U55)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" s="38">
         <f>COUNTIF(J:J,P55)</f>
@@ -19190,19 +19254,19 @@
       </c>
       <c r="U55" s="38">
         <f>COUNTIF(M:M,P55)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" s="38">
         <f>SUMIF(E:E,P55,F:F)+SUMIF(I:I,P55,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="38">
         <f>SUMIF(E:E,P55,H:H)+SUMIF(I:I,P55,F:F)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X55" s="38">
         <f t="shared" ref="X55:X57" si="61">V55-W55</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Y55" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q55)*($X$54:$X$57&gt;X55))</f>
@@ -19218,7 +19282,7 @@
       </c>
       <c r="AB55" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q55)*($X$54:$X$57=X55)*($V$54:$V$57=V55)*($W$54:$W$57=W55)*($AC$54:$AC$57&lt;AC55))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC55" s="39">
         <v>2</v>
@@ -19229,19 +19293,19 @@
       </c>
       <c r="AF55" s="83" t="str">
         <f>VLOOKUP($AE55,$O$54:$X$57,2,FALSE)</f>
-        <v>Senegal</v>
+        <v>França</v>
       </c>
       <c r="AG55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,6,FALSE)</f>
@@ -19253,15 +19317,15 @@
       </c>
       <c r="AL55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN55" s="85">
         <f>VLOOKUP($AE55,$O$54:$X$57,10,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:40" x14ac:dyDescent="0.25">
@@ -19307,7 +19371,7 @@
       <c r="N56" s="46"/>
       <c r="O56" s="47">
         <f>RANK(Q56,$Q$54:$Q$57)+SUM(Y56:AB56)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P56" s="49" t="str">
         <f>Sorteios!I24</f>
@@ -19319,7 +19383,7 @@
       </c>
       <c r="R56" s="38">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" s="38">
         <f>COUNTIF(J:J,P56)</f>
@@ -19331,23 +19395,23 @@
       </c>
       <c r="U56" s="38">
         <f>COUNTIF(M:M,P56)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="38">
         <f>SUMIF(E:E,P56,F:F)+SUMIF(I:I,P56,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="38">
         <f>SUMIF(E:E,P56,H:H)+SUMIF(I:I,P56,F:F)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X56" s="38">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Y56" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q56)*($X$54:$X$57&gt;X56))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z56" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q56)*($X$54:$X$57=X56)*($V$54:$V$57&gt;V56))</f>
@@ -19359,7 +19423,7 @@
       </c>
       <c r="AB56" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q56)*($X$54:$X$57=X56)*($V$54:$V$57=V56)*($W$54:$W$57=W56)*($AC$54:$AC$57&lt;AC56))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC56" s="39">
         <v>3</v>
@@ -19370,7 +19434,7 @@
       </c>
       <c r="AF56" s="83" t="str">
         <f>VLOOKUP($AE56,$O$54:$X$57,2,FALSE)</f>
-        <v>Iraque</v>
+        <v>Senegal</v>
       </c>
       <c r="AG56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,3,FALSE)</f>
@@ -19378,7 +19442,7 @@
       </c>
       <c r="AH56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,5,FALSE)</f>
@@ -19390,19 +19454,19 @@
       </c>
       <c r="AK56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,9,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN56" s="85">
         <f>VLOOKUP($AE56,$O$54:$X$57,10,FALSE)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="57" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19448,7 +19512,7 @@
       <c r="N57" s="55"/>
       <c r="O57" s="47">
         <f>RANK(Q57,$Q$54:$Q$57)+SUM(Y57:AB57)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P57" s="69" t="str">
         <f>Sorteios!I25</f>
@@ -19456,15 +19520,15 @@
       </c>
       <c r="Q57" s="66">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R57" s="66">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" s="66">
         <f>COUNTIF(J:J,P57)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" s="66">
         <f>COUNTIF(K:K,P57)+COUNTIF(L:L,P57)</f>
@@ -19476,15 +19540,15 @@
       </c>
       <c r="V57" s="66">
         <f>SUMIF(E:E,P57,F:F)+SUMIF(I:I,P57,H:H)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W57" s="66">
         <f>SUMIF(E:E,P57,H:H)+SUMIF(I:I,P57,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X57" s="66">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y57" s="66">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q57)*($X$54:$X$57&gt;X57))</f>
@@ -19500,7 +19564,7 @@
       </c>
       <c r="AB57" s="66">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q57)*($X$54:$X$57=X57)*($V$54:$V$57=V57)*($W$54:$W$57=W57)*($AC$54:$AC$57&lt;AC57))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC57" s="67">
         <v>4</v>
@@ -19511,7 +19575,7 @@
       </c>
       <c r="AF57" s="86" t="str">
         <f>VLOOKUP($AE57,$O$54:$X$57,2,FALSE)</f>
-        <v>Noruega</v>
+        <v>Iraque</v>
       </c>
       <c r="AG57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,3,FALSE)</f>
@@ -19519,7 +19583,7 @@
       </c>
       <c r="AH57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,5,FALSE)</f>
@@ -19531,19 +19595,19 @@
       </c>
       <c r="AK57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,9,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN57" s="88">
         <f>VLOOKUP($AE57,$O$54:$X$57,10,FALSE)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="58" spans="1:40" x14ac:dyDescent="0.25">
@@ -19561,18 +19625,22 @@
         <f>P60</f>
         <v>Argentina</v>
       </c>
-      <c r="F58" s="127"/>
+      <c r="F58" s="127">
+        <v>3</v>
+      </c>
       <c r="G58" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="H58" s="127"/>
+      <c r="H58" s="127">
+        <v>0</v>
+      </c>
       <c r="I58" s="122" t="str">
         <f>P61</f>
         <v>Argélia</v>
       </c>
       <c r="J58" s="71" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Argentina</v>
       </c>
       <c r="K58" s="71" t="str">
         <f t="shared" si="47"/>
@@ -19584,7 +19652,7 @@
       </c>
       <c r="M58" s="72" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Argélia</v>
       </c>
       <c r="N58" s="45"/>
       <c r="O58" s="73"/>
@@ -19633,18 +19701,22 @@
         <f>P62</f>
         <v>Áustria</v>
       </c>
-      <c r="F59" s="123"/>
+      <c r="F59" s="123">
+        <v>3</v>
+      </c>
       <c r="G59" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H59" s="123"/>
+      <c r="H59" s="123">
+        <v>1</v>
+      </c>
       <c r="I59" s="113" t="str">
         <f>P63</f>
         <v>Jordânia</v>
       </c>
       <c r="J59" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Áustria</v>
       </c>
       <c r="K59" s="38" t="str">
         <f t="shared" si="47"/>
@@ -19656,7 +19728,7 @@
       </c>
       <c r="M59" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Jordânia</v>
       </c>
       <c r="N59" s="45"/>
       <c r="O59" s="47" t="s">
@@ -19787,15 +19859,15 @@
       </c>
       <c r="Q60" s="38">
         <f>(S60*3)+(T60*1)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R60" s="38">
         <f>SUM(S60:U60)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" s="38">
         <f>COUNTIF(J:J,P60)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" s="38">
         <f>COUNTIF(K:K,P60)+COUNTIF(L:L,P60)</f>
@@ -19807,7 +19879,7 @@
       </c>
       <c r="V60" s="38">
         <f>SUMIF(E:E,P60,F:F)+SUMIF(I:I,P60,H:H)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W60" s="38">
         <f>SUMIF(E:E,P60,H:H)+SUMIF(I:I,P60,F:F)</f>
@@ -19815,7 +19887,7 @@
       </c>
       <c r="X60" s="38">
         <f>V60-W60</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y60" s="38">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q60)*($X$60:$X$63&gt;X60))</f>
@@ -19846,15 +19918,15 @@
       </c>
       <c r="AG60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,6,FALSE)</f>
@@ -19866,7 +19938,7 @@
       </c>
       <c r="AL60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,9,FALSE)</f>
@@ -19874,7 +19946,7 @@
       </c>
       <c r="AN60" s="85">
         <f>VLOOKUP($AE60,$O$60:$X$63,10,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:40" x14ac:dyDescent="0.25">
@@ -19920,7 +19992,7 @@
       <c r="N61" s="45"/>
       <c r="O61" s="47">
         <f>RANK(Q61,$Q$60:$Q$63)+SUM(Y61:AB61)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P61" s="49" t="str">
         <f>Sorteios!C31</f>
@@ -19932,7 +20004,7 @@
       </c>
       <c r="R61" s="38">
         <f t="shared" ref="R61:R63" si="63">SUM(S61:U61)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" s="38">
         <f>COUNTIF(J:J,P61)</f>
@@ -19944,7 +20016,7 @@
       </c>
       <c r="U61" s="38">
         <f>COUNTIF(M:M,P61)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V61" s="38">
         <f>SUMIF(E:E,P61,F:F)+SUMIF(I:I,P61,H:H)</f>
@@ -19952,15 +20024,15 @@
       </c>
       <c r="W61" s="38">
         <f>SUMIF(E:E,P61,H:H)+SUMIF(I:I,P61,F:F)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X61" s="38">
         <f t="shared" ref="X61:X63" si="64">V61-W61</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Y61" s="38">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q61)*($X$60:$X$63&gt;X61))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z61" s="38">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q61)*($X$60:$X$63=X61)*($V$60:$V$63&gt;V61))</f>
@@ -19972,7 +20044,7 @@
       </c>
       <c r="AB61" s="38">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q61)*($X$60:$X$63=X61)*($V$60:$V$63=V61)*($W$60:$W$63=W61)*($AC$60:$AC$63&lt;AC61))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC61" s="39">
         <v>2</v>
@@ -19983,19 +20055,19 @@
       </c>
       <c r="AF61" s="83" t="str">
         <f>VLOOKUP($AE61,$O$60:$X$63,2,FALSE)</f>
-        <v>Argélia</v>
+        <v>Áustria</v>
       </c>
       <c r="AG61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,6,FALSE)</f>
@@ -20007,15 +20079,15 @@
       </c>
       <c r="AL61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN61" s="85">
         <f>VLOOKUP($AE61,$O$60:$X$63,10,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:40" x14ac:dyDescent="0.25">
@@ -20061,7 +20133,7 @@
       <c r="N62" s="45"/>
       <c r="O62" s="47">
         <f>RANK(Q62,$Q$60:$Q$63)+SUM(Y62:AB62)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P62" s="49" t="str">
         <f>Sorteios!C32</f>
@@ -20069,15 +20141,15 @@
       </c>
       <c r="Q62" s="38">
         <f>(S62*3)+(T62*1)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R62" s="38">
         <f>SUM(S62:U62)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" s="38">
         <f>COUNTIF(J:J,P62)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="38">
         <f>COUNTIF(K:K,P62)+COUNTIF(L:L,P62)</f>
@@ -20089,19 +20161,19 @@
       </c>
       <c r="V62" s="38">
         <f>SUMIF(E:E,P62,F:F)+SUMIF(I:I,P62,H:H)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W62" s="38">
         <f>SUMIF(E:E,P62,H:H)+SUMIF(I:I,P62,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X62" s="38">
         <f>V62-W62</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y62" s="38">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q62)*($X$60:$X$63&gt;X62))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z62" s="38">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q62)*($X$60:$X$63=X62)*($V$60:$V$63&gt;V62))</f>
@@ -20113,7 +20185,7 @@
       </c>
       <c r="AB62" s="38">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q62)*($X$60:$X$63=X62)*($V$60:$V$63=V62)*($W$60:$W$63=W62)*($AC$60:$AC$63&lt;AC62))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC62" s="39">
         <v>3</v>
@@ -20124,7 +20196,7 @@
       </c>
       <c r="AF62" s="83" t="str">
         <f>VLOOKUP($AE62,$O$60:$X$63,2,FALSE)</f>
-        <v>Áustria</v>
+        <v>Jordânia</v>
       </c>
       <c r="AG62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,3,FALSE)</f>
@@ -20132,7 +20204,7 @@
       </c>
       <c r="AH62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,5,FALSE)</f>
@@ -20144,19 +20216,19 @@
       </c>
       <c r="AK62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,9,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN62" s="85">
         <f>VLOOKUP($AE62,$O$60:$X$63,10,FALSE)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="63" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20202,7 +20274,7 @@
       <c r="N63" s="45"/>
       <c r="O63" s="68">
         <f>RANK(Q63,$Q$60:$Q$63)+SUM(Y63:AB63)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P63" s="49" t="str">
         <f>Sorteios!C33</f>
@@ -20214,7 +20286,7 @@
       </c>
       <c r="R63" s="53">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" s="38">
         <f>COUNTIF(J:J,P63)</f>
@@ -20226,19 +20298,19 @@
       </c>
       <c r="U63" s="38">
         <f>COUNTIF(M:M,P63)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V63" s="53">
         <f>SUMIF(E:E,P63,F:F)+SUMIF(I:I,P63,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W63" s="53">
         <f>SUMIF(E:E,P63,H:H)+SUMIF(I:I,P63,F:F)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X63" s="53">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Y63" s="53">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q63)*($X$60:$X$63&gt;X63))</f>
@@ -20254,7 +20326,7 @@
       </c>
       <c r="AB63" s="53">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q63)*($X$60:$X$63=X63)*($V$60:$V$63=V63)*($W$60:$W$63=W63)*($AC$60:$AC$63&lt;AC63))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC63" s="54">
         <v>4</v>
@@ -20265,7 +20337,7 @@
       </c>
       <c r="AF63" s="86" t="str">
         <f>VLOOKUP($AE63,$O$60:$X$63,2,FALSE)</f>
-        <v>Jordânia</v>
+        <v>Argélia</v>
       </c>
       <c r="AG63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,3,FALSE)</f>
@@ -20273,7 +20345,7 @@
       </c>
       <c r="AH63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,5,FALSE)</f>
@@ -20285,7 +20357,7 @@
       </c>
       <c r="AK63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,8,FALSE)</f>
@@ -20293,11 +20365,11 @@
       </c>
       <c r="AM63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,9,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN63" s="88">
         <f>VLOOKUP($AE63,$O$60:$X$63,10,FALSE)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="64" spans="1:40" x14ac:dyDescent="0.25">
@@ -20315,11 +20387,15 @@
         <f>P66</f>
         <v>Portugal</v>
       </c>
-      <c r="F64" s="125"/>
+      <c r="F64" s="125">
+        <v>1</v>
+      </c>
       <c r="G64" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="H64" s="125"/>
+      <c r="H64" s="125">
+        <v>1</v>
+      </c>
       <c r="I64" s="116" t="str">
         <f>P67</f>
         <v>RD Congo</v>
@@ -20330,11 +20406,11 @@
       </c>
       <c r="K64" s="59" t="str">
         <f t="shared" si="47"/>
-        <v/>
+        <v>Portugal</v>
       </c>
       <c r="L64" s="59" t="str">
         <f t="shared" si="48"/>
-        <v/>
+        <v>RD Congo</v>
       </c>
       <c r="M64" s="60" t="str">
         <f t="shared" si="49"/>
@@ -20387,18 +20463,22 @@
         <f>P68</f>
         <v>Uzbequistão</v>
       </c>
-      <c r="F65" s="123"/>
+      <c r="F65" s="123">
+        <v>1</v>
+      </c>
       <c r="G65" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H65" s="123"/>
+      <c r="H65" s="123">
+        <v>3</v>
+      </c>
       <c r="I65" s="107" t="str">
         <f>P69</f>
         <v>Colômbia</v>
       </c>
       <c r="J65" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Colômbia</v>
       </c>
       <c r="K65" s="38" t="str">
         <f t="shared" si="47"/>
@@ -20410,7 +20490,7 @@
       </c>
       <c r="M65" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Uzbequistão</v>
       </c>
       <c r="N65" s="46"/>
       <c r="O65" s="47" t="s">
@@ -20533,7 +20613,7 @@
       <c r="N66" s="46"/>
       <c r="O66" s="47">
         <f>RANK(Q66,$Q$66:$Q$69)+SUM(Y66:AB66)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P66" s="49" t="str">
         <f>Sorteios!F30</f>
@@ -20541,11 +20621,11 @@
       </c>
       <c r="Q66" s="38">
         <f>(S66*3)+(T66*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="38">
         <f>SUM(S66:U66)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" s="38">
         <f>COUNTIF(J:J,P66)</f>
@@ -20553,7 +20633,7 @@
       </c>
       <c r="T66" s="38">
         <f>COUNTIF(K:K,P66)+COUNTIF(L:L,P66)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U66" s="38">
         <f>COUNTIF(M:M,P66)</f>
@@ -20561,11 +20641,11 @@
       </c>
       <c r="V66" s="38">
         <f>SUMIF(E:E,P66,F:F)+SUMIF(I:I,P66,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="38">
         <f>SUMIF(E:E,P66,H:H)+SUMIF(I:I,P66,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X66" s="38">
         <f>V66-W66</f>
@@ -20596,19 +20676,19 @@
       </c>
       <c r="AF66" s="83" t="str">
         <f>VLOOKUP($AE66,$O$66:$X$69,2,FALSE)</f>
-        <v>Portugal</v>
+        <v>Colômbia</v>
       </c>
       <c r="AG66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,6,FALSE)</f>
@@ -20620,15 +20700,15 @@
       </c>
       <c r="AL66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN66" s="85">
         <f>VLOOKUP($AE66,$O$66:$X$69,10,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:40" x14ac:dyDescent="0.25">
@@ -20674,7 +20754,7 @@
       <c r="N67" s="46"/>
       <c r="O67" s="47">
         <f>RANK(Q67,$Q$66:$Q$69)+SUM(Y67:AB67)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P67" s="49" t="str">
         <f>Sorteios!F31</f>
@@ -20682,11 +20762,11 @@
       </c>
       <c r="Q67" s="38">
         <f t="shared" ref="Q67:Q69" si="65">(S67*3)+(T67*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" s="38">
         <f t="shared" ref="R67:R69" si="66">SUM(S67:U67)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S67" s="38">
         <f>COUNTIF(J:J,P67)</f>
@@ -20694,7 +20774,7 @@
       </c>
       <c r="T67" s="38">
         <f>COUNTIF(K:K,P67)+COUNTIF(L:L,P67)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U67" s="38">
         <f>COUNTIF(M:M,P67)</f>
@@ -20702,11 +20782,11 @@
       </c>
       <c r="V67" s="38">
         <f>SUMIF(E:E,P67,F:F)+SUMIF(I:I,P67,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" s="38">
         <f>SUMIF(E:E,P67,H:H)+SUMIF(I:I,P67,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X67" s="38">
         <f t="shared" ref="X67:X69" si="67">V67-W67</f>
@@ -20737,15 +20817,15 @@
       </c>
       <c r="AF67" s="83" t="str">
         <f>VLOOKUP($AE67,$O$66:$X$69,2,FALSE)</f>
-        <v>RD Congo</v>
+        <v>Portugal</v>
       </c>
       <c r="AG67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,5,FALSE)</f>
@@ -20753,7 +20833,7 @@
       </c>
       <c r="AJ67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,7,FALSE)</f>
@@ -20761,11 +20841,11 @@
       </c>
       <c r="AL67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN67" s="85">
         <f>VLOOKUP($AE67,$O$66:$X$69,10,FALSE)</f>
@@ -20815,7 +20895,7 @@
       <c r="N68" s="46"/>
       <c r="O68" s="47">
         <f>RANK(Q68,$Q$66:$Q$69)+SUM(Y68:AB68)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P68" s="49" t="str">
         <f>Sorteios!F32</f>
@@ -20827,7 +20907,7 @@
       </c>
       <c r="R68" s="38">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S68" s="38">
         <f>COUNTIF(J:J,P68)</f>
@@ -20839,19 +20919,19 @@
       </c>
       <c r="U68" s="38">
         <f>COUNTIF(M:M,P68)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V68" s="38">
         <f>SUMIF(E:E,P68,F:F)+SUMIF(I:I,P68,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="38">
         <f>SUMIF(E:E,P68,H:H)+SUMIF(I:I,P68,F:F)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X68" s="38">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Y68" s="38">
         <f>SUMPRODUCT(($Q$66:$Q$69=Q68)*($X$66:$X$69&gt;X68))</f>
@@ -20867,7 +20947,7 @@
       </c>
       <c r="AB68" s="38">
         <f>SUMPRODUCT(($Q$66:$Q$69=Q68)*($X$66:$X$69=X68)*($V$66:$V$69=V68)*($W$66:$W$69=W68)*($AC$66:$AC$69&lt;AC68))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC68" s="39">
         <v>3</v>
@@ -20878,15 +20958,15 @@
       </c>
       <c r="AF68" s="83" t="str">
         <f>VLOOKUP($AE68,$O$66:$X$69,2,FALSE)</f>
-        <v>Uzbequistão</v>
+        <v>RD Congo</v>
       </c>
       <c r="AG68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,5,FALSE)</f>
@@ -20894,7 +20974,7 @@
       </c>
       <c r="AJ68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,7,FALSE)</f>
@@ -20902,11 +20982,11 @@
       </c>
       <c r="AL68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN68" s="85">
         <f>VLOOKUP($AE68,$O$66:$X$69,10,FALSE)</f>
@@ -20956,7 +21036,7 @@
       <c r="N69" s="55"/>
       <c r="O69" s="56">
         <f>RANK(Q69,$Q$66:$Q$69)+SUM(Y69:AB69)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P69" s="74" t="str">
         <f>Sorteios!F33</f>
@@ -20964,15 +21044,15 @@
       </c>
       <c r="Q69" s="53">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R69" s="53">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S69" s="53">
         <f>COUNTIF(J:J,P69)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" s="53">
         <f>COUNTIF(K:K,P69)+COUNTIF(L:L,P69)</f>
@@ -20984,15 +21064,15 @@
       </c>
       <c r="V69" s="53">
         <f>SUMIF(E:E,P69,F:F)+SUMIF(I:I,P69,H:H)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W69" s="53">
         <f>SUMIF(E:E,P69,H:H)+SUMIF(I:I,P69,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X69" s="53">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y69" s="53">
         <f>SUMPRODUCT(($Q$66:$Q$69=Q69)*($X$66:$X$69&gt;X69))</f>
@@ -21008,7 +21088,7 @@
       </c>
       <c r="AB69" s="53">
         <f>SUMPRODUCT(($Q$66:$Q$69=Q69)*($X$66:$X$69=X69)*($V$66:$V$69=V69)*($W$66:$W$69=W69)*($AC$66:$AC$69&lt;AC69))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC69" s="54">
         <v>4</v>
@@ -21019,7 +21099,7 @@
       </c>
       <c r="AF69" s="86" t="str">
         <f>VLOOKUP($AE69,$O$66:$X$69,2,FALSE)</f>
-        <v>Colômbia</v>
+        <v>Uzbequistão</v>
       </c>
       <c r="AG69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,3,FALSE)</f>
@@ -21027,7 +21107,7 @@
       </c>
       <c r="AH69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,5,FALSE)</f>
@@ -21039,19 +21119,19 @@
       </c>
       <c r="AK69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,9,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN69" s="88">
         <f>VLOOKUP($AE69,$O$66:$X$69,10,FALSE)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="70" spans="1:40" x14ac:dyDescent="0.25">
@@ -21069,18 +21149,22 @@
         <f>P72</f>
         <v>Inglaterra</v>
       </c>
-      <c r="F70" s="125"/>
+      <c r="F70" s="125">
+        <v>4</v>
+      </c>
       <c r="G70" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="H70" s="125"/>
+      <c r="H70" s="125">
+        <v>2</v>
+      </c>
       <c r="I70" s="112" t="str">
         <f>P73</f>
         <v>Croácia</v>
       </c>
       <c r="J70" s="59" t="str">
         <f t="shared" si="68"/>
-        <v>empate</v>
+        <v>Inglaterra</v>
       </c>
       <c r="K70" s="59" t="str">
         <f t="shared" si="69"/>
@@ -21092,7 +21176,7 @@
       </c>
       <c r="M70" s="60" t="str">
         <f t="shared" si="71"/>
-        <v>empate</v>
+        <v>Croácia</v>
       </c>
       <c r="N70" s="64"/>
       <c r="O70" s="62"/>
@@ -21141,18 +21225,22 @@
         <f>P74</f>
         <v>Gana</v>
       </c>
-      <c r="F71" s="123"/>
+      <c r="F71" s="123">
+        <v>1</v>
+      </c>
       <c r="G71" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H71" s="123"/>
+      <c r="H71" s="123">
+        <v>0</v>
+      </c>
       <c r="I71" s="113" t="str">
         <f>P75</f>
         <v>Panamá</v>
       </c>
       <c r="J71" s="38" t="str">
         <f t="shared" si="68"/>
-        <v>empate</v>
+        <v>Gana</v>
       </c>
       <c r="K71" s="38" t="str">
         <f t="shared" si="69"/>
@@ -21164,7 +21252,7 @@
       </c>
       <c r="M71" s="39" t="str">
         <f t="shared" si="71"/>
-        <v>empate</v>
+        <v>Panamá</v>
       </c>
       <c r="N71" s="45"/>
       <c r="O71" s="47" t="s">
@@ -21295,15 +21383,15 @@
       </c>
       <c r="Q72" s="38">
         <f>(S72*3)+(T72*1)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R72" s="38">
         <f>SUM(S72:U72)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" s="38">
         <f>COUNTIF(J:J,P72)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" s="38">
         <f>COUNTIF(K:K,P72)+COUNTIF(L:L,P72)</f>
@@ -21315,15 +21403,15 @@
       </c>
       <c r="V72" s="38">
         <f>SUMIF(E:E,P72,F:F)+SUMIF(I:I,P72,H:H)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W72" s="38">
         <f>SUMIF(E:E,P72,H:H)+SUMIF(I:I,P72,F:F)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X72" s="38">
         <f>V72-W72</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y72" s="38">
         <f>SUMPRODUCT(($Q$72:$Q$75=Q72)*($X$72:$X$75&gt;X72))</f>
@@ -21354,15 +21442,15 @@
       </c>
       <c r="AG72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,6,FALSE)</f>
@@ -21374,15 +21462,15 @@
       </c>
       <c r="AL72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,9,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN72" s="85">
         <f>VLOOKUP($AE72,$O$72:$X$75,10,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:40" x14ac:dyDescent="0.25">
@@ -21428,7 +21516,7 @@
       <c r="N73" s="45"/>
       <c r="O73" s="47">
         <f>RANK(Q73,$Q$72:$Q$75)+SUM(Y73:AB73)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P73" s="49" t="str">
         <f>Sorteios!I31</f>
@@ -21440,7 +21528,7 @@
       </c>
       <c r="R73" s="38">
         <f t="shared" ref="R73:R75" si="73">SUM(S73:U73)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" s="38">
         <f>COUNTIF(J:J,P73)</f>
@@ -21452,23 +21540,23 @@
       </c>
       <c r="U73" s="38">
         <f>COUNTIF(M:M,P73)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V73" s="38">
         <f>SUMIF(E:E,P73,F:F)+SUMIF(I:I,P73,H:H)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W73" s="38">
         <f>SUMIF(E:E,P73,H:H)+SUMIF(I:I,P73,F:F)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X73" s="38">
         <f t="shared" ref="X73:X75" si="74">V73-W73</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Y73" s="38">
         <f t="shared" ref="Y73:Y75" si="75">SUMPRODUCT(($Q$72:$Q$75=Q73)*($X$72:$X$75&gt;X73))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z73" s="38">
         <f t="shared" ref="Z73:Z75" si="76">SUMPRODUCT(($Q$72:$Q$75=Q73)*($X$72:$X$75=X73)*($V$72:$V$75&gt;V73))</f>
@@ -21480,7 +21568,7 @@
       </c>
       <c r="AB73" s="38">
         <f t="shared" ref="AB73:AB75" si="78">SUMPRODUCT(($Q$72:$Q$75=Q73)*($X$72:$X$75=X73)*($V$72:$V$75=V73)*($W$72:$W$75=W73)*($AC$72:$AC$75&lt;AC73))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC73" s="39">
         <v>2</v>
@@ -21491,19 +21579,19 @@
       </c>
       <c r="AF73" s="83" t="str">
         <f t="shared" ref="AF73:AF75" si="79">VLOOKUP($AE73,$O$72:$X$75,2,FALSE)</f>
-        <v>Croácia</v>
+        <v>Gana</v>
       </c>
       <c r="AG73" s="84">
         <f t="shared" ref="AG73:AG75" si="80">VLOOKUP($AE73,$O$72:$X$75,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH73" s="84">
         <f t="shared" ref="AH73:AH75" si="81">VLOOKUP($AE73,$O$72:$X$75,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI73" s="84">
         <f t="shared" ref="AI73:AI75" si="82">VLOOKUP($AE73,$O$72:$X$75,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ73" s="84">
         <f t="shared" ref="AJ73:AJ75" si="83">VLOOKUP($AE73,$O$72:$X$75,6,FALSE)</f>
@@ -21515,7 +21603,7 @@
       </c>
       <c r="AL73" s="84">
         <f t="shared" ref="AL73:AL75" si="85">VLOOKUP($AE73,$O$72:$X$75,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM73" s="84">
         <f t="shared" ref="AM73:AM75" si="86">VLOOKUP($AE73,$O$72:$X$75,9,FALSE)</f>
@@ -21523,7 +21611,7 @@
       </c>
       <c r="AN73" s="85">
         <f t="shared" ref="AN73:AN75" si="87">VLOOKUP($AE73,$O$72:$X$75,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:40" x14ac:dyDescent="0.25">
@@ -21569,7 +21657,7 @@
       <c r="N74" s="45"/>
       <c r="O74" s="47">
         <f>RANK(Q74,$Q$72:$Q$75)+SUM(Y74:AB74)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P74" s="49" t="str">
         <f>Sorteios!I32</f>
@@ -21577,15 +21665,15 @@
       </c>
       <c r="Q74" s="38">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R74" s="38">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S74" s="38">
         <f>COUNTIF(J:J,P74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="38">
         <f>COUNTIF(K:K,P74)+COUNTIF(L:L,P74)</f>
@@ -21597,7 +21685,7 @@
       </c>
       <c r="V74" s="38">
         <f>SUMIF(E:E,P74,F:F)+SUMIF(I:I,P74,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" s="38">
         <f>SUMIF(E:E,P74,H:H)+SUMIF(I:I,P74,F:F)</f>
@@ -21605,11 +21693,11 @@
       </c>
       <c r="X74" s="38">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y74" s="38">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z74" s="38">
         <f t="shared" si="76"/>
@@ -21621,7 +21709,7 @@
       </c>
       <c r="AB74" s="38">
         <f t="shared" si="78"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC74" s="39">
         <v>3</v>
@@ -21632,7 +21720,7 @@
       </c>
       <c r="AF74" s="83" t="str">
         <f t="shared" si="79"/>
-        <v>Gana</v>
+        <v>Panamá</v>
       </c>
       <c r="AG74" s="84">
         <f t="shared" si="80"/>
@@ -21640,7 +21728,7 @@
       </c>
       <c r="AH74" s="84">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI74" s="84">
         <f t="shared" si="82"/>
@@ -21652,7 +21740,7 @@
       </c>
       <c r="AK74" s="84">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL74" s="84">
         <f t="shared" si="85"/>
@@ -21660,11 +21748,11 @@
       </c>
       <c r="AM74" s="84">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN74" s="85">
         <f t="shared" si="87"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="75" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -21710,7 +21798,7 @@
       <c r="N75" s="57"/>
       <c r="O75" s="56">
         <f>RANK(Q75,$Q$72:$Q$75)+SUM(Y75:AB75)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P75" s="49" t="str">
         <f>Sorteios!I33</f>
@@ -21722,7 +21810,7 @@
       </c>
       <c r="R75" s="53">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" s="38">
         <f>COUNTIF(J:J,P75)</f>
@@ -21734,7 +21822,7 @@
       </c>
       <c r="U75" s="38">
         <f>COUNTIF(M:M,P75)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V75" s="53">
         <f>SUMIF(E:E,P75,F:F)+SUMIF(I:I,P75,H:H)</f>
@@ -21742,11 +21830,11 @@
       </c>
       <c r="W75" s="53">
         <f>SUMIF(E:E,P75,H:H)+SUMIF(I:I,P75,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X75" s="53">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y75" s="53">
         <f t="shared" si="75"/>
@@ -21762,7 +21850,7 @@
       </c>
       <c r="AB75" s="53">
         <f t="shared" si="78"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC75" s="54">
         <v>4</v>
@@ -21773,7 +21861,7 @@
       </c>
       <c r="AF75" s="86" t="str">
         <f t="shared" si="79"/>
-        <v>Panamá</v>
+        <v>Croácia</v>
       </c>
       <c r="AG75" s="87">
         <f t="shared" si="80"/>
@@ -21781,7 +21869,7 @@
       </c>
       <c r="AH75" s="87">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI75" s="87">
         <f t="shared" si="82"/>
@@ -21793,19 +21881,19 @@
       </c>
       <c r="AK75" s="87">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL75" s="87">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM75" s="87">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN75" s="88">
         <f t="shared" si="87"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
   </sheetData>
@@ -54289,18 +54377,18 @@
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="130"/>
-      <c r="B3" s="197" t="s">
+      <c r="B3" s="193" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="199"/>
+      <c r="C3" s="194"/>
+      <c r="D3" s="194"/>
+      <c r="E3" s="194"/>
+      <c r="F3" s="194"/>
+      <c r="G3" s="194"/>
+      <c r="H3" s="194"/>
+      <c r="I3" s="194"/>
+      <c r="J3" s="194"/>
+      <c r="K3" s="195"/>
       <c r="L3" s="131"/>
       <c r="M3" s="132"/>
       <c r="N3" s="132"/>
@@ -54308,18 +54396,18 @@
       <c r="P3" s="132"/>
       <c r="Q3" s="132"/>
       <c r="W3" s="130"/>
-      <c r="X3" s="197" t="s">
+      <c r="X3" s="193" t="s">
         <v>73</v>
       </c>
-      <c r="Y3" s="198"/>
-      <c r="Z3" s="198"/>
-      <c r="AA3" s="198"/>
-      <c r="AB3" s="198"/>
-      <c r="AC3" s="198"/>
-      <c r="AD3" s="198"/>
-      <c r="AE3" s="198"/>
-      <c r="AF3" s="198"/>
-      <c r="AG3" s="199"/>
+      <c r="Y3" s="194"/>
+      <c r="Z3" s="194"/>
+      <c r="AA3" s="194"/>
+      <c r="AB3" s="194"/>
+      <c r="AC3" s="194"/>
+      <c r="AD3" s="194"/>
+      <c r="AE3" s="194"/>
+      <c r="AF3" s="194"/>
+      <c r="AG3" s="195"/>
       <c r="AH3" s="131"/>
       <c r="AI3" s="132"/>
       <c r="AJ3" s="132"/>
@@ -54336,19 +54424,19 @@
       <c r="D4" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="193" t="s">
+      <c r="E4" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="193"/>
-      <c r="G4" s="193" t="s">
+      <c r="F4" s="196"/>
+      <c r="G4" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="193"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193" t="s">
+      <c r="H4" s="196"/>
+      <c r="I4" s="196"/>
+      <c r="J4" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="193"/>
+      <c r="K4" s="196"/>
       <c r="L4" s="135"/>
       <c r="M4" s="135"/>
       <c r="N4" s="135"/>
@@ -54363,19 +54451,19 @@
       <c r="Z4" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA4" s="193" t="s">
+      <c r="AA4" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AB4" s="193"/>
-      <c r="AC4" s="193" t="s">
+      <c r="AB4" s="196"/>
+      <c r="AC4" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="AD4" s="193"/>
-      <c r="AE4" s="193"/>
-      <c r="AF4" s="193" t="s">
+      <c r="AD4" s="196"/>
+      <c r="AE4" s="196"/>
+      <c r="AF4" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AG4" s="193"/>
+      <c r="AG4" s="196"/>
       <c r="AH4" s="136"/>
       <c r="AI4" s="133"/>
       <c r="AJ4" s="133"/>
@@ -54459,7 +54547,7 @@
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B6" s="152">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C6" s="148">
         <v>46202</v>
@@ -54495,7 +54583,7 @@
       </c>
       <c r="P6" s="133" t="str">
         <f>'Fase de Grupos'!AR39</f>
-        <v>3C3G3B3D3H3F3E3I</v>
+        <v>3H3G3B3C3A3F3E3K</v>
       </c>
       <c r="W6" s="45"/>
       <c r="X6" s="152" t="s">
@@ -54650,11 +54738,11 @@
       </c>
       <c r="Q8" s="133" t="str">
         <f>MID($P$6,1,2)</f>
-        <v>3C</v>
+        <v>3H</v>
       </c>
       <c r="R8" s="15" t="str">
         <f>VLOOKUP(Q8,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Haiti</v>
+        <v>Espanha</v>
       </c>
       <c r="T8" s="15" t="s">
         <v>102</v>
@@ -54745,7 +54833,7 @@
       </c>
       <c r="R9" s="15" t="str">
         <f>VLOOKUP(Q9,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Irã</v>
+        <v>Bélgica</v>
       </c>
       <c r="T9" s="15" t="s">
         <v>137</v>
@@ -54885,11 +54973,11 @@
       </c>
       <c r="Q11" s="133" t="str">
         <f>MID($P$6,7,2)</f>
-        <v>3D</v>
+        <v>3C</v>
       </c>
       <c r="R11" s="15" t="str">
         <f>VLOOKUP(Q11,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Austrália</v>
+        <v>Marrocos</v>
       </c>
       <c r="T11" s="15" t="s">
         <v>138</v>
@@ -54899,18 +54987,18 @@
         <v>12</v>
       </c>
       <c r="W11" s="130"/>
-      <c r="X11" s="197" t="s">
+      <c r="X11" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="Y11" s="198"/>
-      <c r="Z11" s="198"/>
-      <c r="AA11" s="198"/>
-      <c r="AB11" s="198"/>
-      <c r="AC11" s="198"/>
-      <c r="AD11" s="198"/>
-      <c r="AE11" s="198"/>
-      <c r="AF11" s="198"/>
-      <c r="AG11" s="199"/>
+      <c r="Y11" s="194"/>
+      <c r="Z11" s="194"/>
+      <c r="AA11" s="194"/>
+      <c r="AB11" s="194"/>
+      <c r="AC11" s="194"/>
+      <c r="AD11" s="194"/>
+      <c r="AE11" s="194"/>
+      <c r="AF11" s="194"/>
+      <c r="AG11" s="195"/>
       <c r="AH11" s="131"/>
       <c r="AI11" s="132"/>
       <c r="AJ11" s="132"/>
@@ -54959,11 +55047,11 @@
       </c>
       <c r="Q12" s="133" t="str">
         <f>MID($P$6,9,2)</f>
-        <v>3H</v>
+        <v>3A</v>
       </c>
       <c r="R12" s="15" t="str">
         <f>VLOOKUP(Q12,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Arábia Saudita</v>
+        <v>República Tcheca</v>
       </c>
       <c r="T12" s="15" t="s">
         <v>139</v>
@@ -54980,19 +55068,19 @@
       <c r="Z12" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA12" s="193" t="s">
+      <c r="AA12" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AB12" s="193"/>
-      <c r="AC12" s="193" t="s">
+      <c r="AB12" s="196"/>
+      <c r="AC12" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="AD12" s="193"/>
-      <c r="AE12" s="193"/>
-      <c r="AF12" s="193" t="s">
+      <c r="AD12" s="196"/>
+      <c r="AE12" s="196"/>
+      <c r="AF12" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AG12" s="193"/>
+      <c r="AG12" s="196"/>
       <c r="AH12" s="136"/>
       <c r="AI12" s="133"/>
       <c r="AJ12" s="133"/>
@@ -55045,7 +55133,7 @@
       </c>
       <c r="R13" s="15" t="str">
         <f>VLOOKUP(Q13,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Suécia</v>
+        <v>Japão</v>
       </c>
       <c r="T13" s="15" t="s">
         <v>140</v>
@@ -55137,7 +55225,7 @@
       </c>
       <c r="R14" s="15" t="str">
         <f>VLOOKUP(Q14,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Costa do Marfim</v>
+        <v>Equador</v>
       </c>
       <c r="T14" s="15" t="s">
         <v>105</v>
@@ -55225,11 +55313,11 @@
       </c>
       <c r="Q15" s="133" t="str">
         <f>MID($P$6,15,2)</f>
-        <v>3I</v>
+        <v>3K</v>
       </c>
       <c r="R15" s="15" t="str">
         <f>VLOOKUP(Q15,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Iraque</v>
+        <v>RD Congo</v>
       </c>
       <c r="T15" s="15" t="s">
         <v>135</v>
@@ -55367,18 +55455,18 @@
         <v>30</v>
       </c>
       <c r="W17" s="130"/>
-      <c r="X17" s="197" t="s">
+      <c r="X17" s="193" t="s">
         <v>77</v>
       </c>
-      <c r="Y17" s="198"/>
-      <c r="Z17" s="198"/>
-      <c r="AA17" s="198"/>
-      <c r="AB17" s="198"/>
-      <c r="AC17" s="198"/>
-      <c r="AD17" s="198"/>
-      <c r="AE17" s="198"/>
-      <c r="AF17" s="198"/>
-      <c r="AG17" s="199"/>
+      <c r="Y17" s="194"/>
+      <c r="Z17" s="194"/>
+      <c r="AA17" s="194"/>
+      <c r="AB17" s="194"/>
+      <c r="AC17" s="194"/>
+      <c r="AD17" s="194"/>
+      <c r="AE17" s="194"/>
+      <c r="AF17" s="194"/>
+      <c r="AG17" s="195"/>
       <c r="AH17" s="131"/>
       <c r="AI17" s="132"/>
       <c r="AJ17" s="132"/>
@@ -55437,19 +55525,19 @@
       <c r="Z18" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA18" s="193" t="s">
+      <c r="AA18" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AB18" s="193"/>
-      <c r="AC18" s="193" t="s">
+      <c r="AB18" s="196"/>
+      <c r="AC18" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="AD18" s="193"/>
-      <c r="AE18" s="193"/>
-      <c r="AF18" s="193" t="s">
+      <c r="AD18" s="196"/>
+      <c r="AE18" s="196"/>
+      <c r="AF18" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AG18" s="193"/>
+      <c r="AG18" s="196"/>
       <c r="AH18" s="136"/>
       <c r="AI18" s="133"/>
       <c r="AJ18" s="133"/>
@@ -55641,18 +55729,18 @@
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" s="130"/>
-      <c r="B23" s="197" t="s">
+      <c r="B23" s="193" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="198"/>
-      <c r="D23" s="198"/>
-      <c r="E23" s="198"/>
-      <c r="F23" s="198"/>
-      <c r="G23" s="198"/>
-      <c r="H23" s="198"/>
-      <c r="I23" s="198"/>
-      <c r="J23" s="198"/>
-      <c r="K23" s="199"/>
+      <c r="C23" s="194"/>
+      <c r="D23" s="194"/>
+      <c r="E23" s="194"/>
+      <c r="F23" s="194"/>
+      <c r="G23" s="194"/>
+      <c r="H23" s="194"/>
+      <c r="I23" s="194"/>
+      <c r="J23" s="194"/>
+      <c r="K23" s="195"/>
       <c r="L23" s="131"/>
       <c r="M23" s="132"/>
       <c r="N23" s="132"/>
@@ -55667,18 +55755,18 @@
         <v>48</v>
       </c>
       <c r="W23" s="45"/>
-      <c r="X23" s="197" t="s">
+      <c r="X23" s="193" t="s">
         <v>79</v>
       </c>
-      <c r="Y23" s="198"/>
-      <c r="Z23" s="198"/>
-      <c r="AA23" s="198"/>
-      <c r="AB23" s="198"/>
-      <c r="AC23" s="198"/>
-      <c r="AD23" s="198"/>
-      <c r="AE23" s="198"/>
-      <c r="AF23" s="198"/>
-      <c r="AG23" s="199"/>
+      <c r="Y23" s="194"/>
+      <c r="Z23" s="194"/>
+      <c r="AA23" s="194"/>
+      <c r="AB23" s="194"/>
+      <c r="AC23" s="194"/>
+      <c r="AD23" s="194"/>
+      <c r="AE23" s="194"/>
+      <c r="AF23" s="194"/>
+      <c r="AG23" s="195"/>
       <c r="AH23" s="131"/>
       <c r="AI23" s="132"/>
       <c r="AJ23" s="132"/>
@@ -55694,19 +55782,19 @@
       <c r="D24" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="193" t="s">
+      <c r="E24" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="F24" s="193"/>
-      <c r="G24" s="193" t="s">
+      <c r="F24" s="196"/>
+      <c r="G24" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="193"/>
-      <c r="I24" s="193"/>
-      <c r="J24" s="193" t="s">
+      <c r="H24" s="196"/>
+      <c r="I24" s="196"/>
+      <c r="J24" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="K24" s="193"/>
+      <c r="K24" s="196"/>
       <c r="L24" s="135"/>
       <c r="M24" s="135"/>
       <c r="N24" s="135"/>
@@ -55728,19 +55816,19 @@
       <c r="Z24" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA24" s="193" t="s">
+      <c r="AA24" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AB24" s="193"/>
-      <c r="AC24" s="193" t="s">
+      <c r="AB24" s="196"/>
+      <c r="AC24" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="AD24" s="193"/>
-      <c r="AE24" s="193"/>
-      <c r="AF24" s="193" t="s">
+      <c r="AD24" s="196"/>
+      <c r="AE24" s="196"/>
+      <c r="AF24" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AG24" s="193"/>
+      <c r="AG24" s="196"/>
       <c r="AH24" s="136"/>
       <c r="AI24" s="133"/>
       <c r="AJ24" s="133"/>
@@ -56139,15 +56227,15 @@
       </c>
       <c r="Z34" s="202"/>
       <c r="AA34" s="202"/>
-      <c r="AB34" s="194" t="str">
+      <c r="AB34" s="197" t="str">
         <f>IF(AI25="1º Lugar","",AI25)</f>
         <v/>
       </c>
-      <c r="AC34" s="194"/>
-      <c r="AD34" s="194"/>
-      <c r="AE34" s="194"/>
-      <c r="AF34" s="194"/>
-      <c r="AG34" s="194"/>
+      <c r="AC34" s="197"/>
+      <c r="AD34" s="197"/>
+      <c r="AE34" s="197"/>
+      <c r="AF34" s="197"/>
+      <c r="AG34" s="197"/>
     </row>
     <row r="35" spans="2:33" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B35" s="140"/>
@@ -56159,15 +56247,15 @@
       </c>
       <c r="Z35" s="200"/>
       <c r="AA35" s="200"/>
-      <c r="AB35" s="195" t="str">
+      <c r="AB35" s="198" t="str">
         <f>IF(M57="2º Lugar","",M57)</f>
         <v/>
       </c>
-      <c r="AC35" s="195"/>
-      <c r="AD35" s="195"/>
-      <c r="AE35" s="195"/>
-      <c r="AF35" s="195"/>
-      <c r="AG35" s="195"/>
+      <c r="AC35" s="198"/>
+      <c r="AD35" s="198"/>
+      <c r="AE35" s="198"/>
+      <c r="AF35" s="198"/>
+      <c r="AG35" s="198"/>
     </row>
     <row r="36" spans="2:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="140"/>
@@ -56179,15 +56267,15 @@
       </c>
       <c r="Z36" s="201"/>
       <c r="AA36" s="201"/>
-      <c r="AB36" s="196" t="str">
+      <c r="AB36" s="199" t="str">
         <f>IF(AI19="3º Lugar","",AI19)</f>
         <v/>
       </c>
-      <c r="AC36" s="196"/>
-      <c r="AD36" s="196"/>
-      <c r="AE36" s="196"/>
-      <c r="AF36" s="196"/>
-      <c r="AG36" s="196"/>
+      <c r="AC36" s="199"/>
+      <c r="AD36" s="199"/>
+      <c r="AE36" s="199"/>
+      <c r="AF36" s="199"/>
+      <c r="AG36" s="199"/>
     </row>
     <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="137"/>
@@ -56343,8 +56431,22 @@
       <c r="K82" s="45"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NcafoOoEQ2MbNzyiK0DdoaXhnGtaouqyNETNtM1mFkFhB8eRUn0pz+sE7du8dGmgFWHYaZbDVZUwxcnGN1osbA==" saltValue="0X36Yq5ioWWlmaoOaDrxJQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="e9SwIN3P1gzBH+IVoOp3qqE533HDYkDzheVXRVNRaqt2vhimaHXLKZ+8sDUopKeiKAT5et9NZBvuLRUJOa6zQg==" saltValue="pxuBsAAmB/Bn8sNidXdYpQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AB34:AG34"/>
+    <mergeCell ref="AB35:AG35"/>
+    <mergeCell ref="AB36:AG36"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="Y35:AA35"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="AF24:AG24"/>
+    <mergeCell ref="Y34:AA34"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:I4"/>
@@ -56361,20 +56463,6 @@
     <mergeCell ref="AF18:AG18"/>
     <mergeCell ref="AA4:AB4"/>
     <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AB34:AG34"/>
-    <mergeCell ref="AB35:AG35"/>
-    <mergeCell ref="AB36:AG36"/>
-    <mergeCell ref="B23:K23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="Y35:AA35"/>
-    <mergeCell ref="Y36:AA36"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AC24:AE24"/>
-    <mergeCell ref="AF24:AG24"/>
-    <mergeCell ref="Y34:AA34"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A2 B2:K2 X9:AG10 X15:AG16 X20:AG21 B21:K22 AB34:AB36 A57:K58 H59:K61 B62:K71 B83:K1048576">
     <cfRule type="cellIs" dxfId="27" priority="76" operator="equal">
@@ -57137,6 +57225,12 @@
     <sortCondition ref="C59:C64"/>
   </sortState>
   <mergeCells count="16">
+    <mergeCell ref="N4:N6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="L4:L6"/>
     <mergeCell ref="AB4:AB6"/>
     <mergeCell ref="AD4:AD6"/>
     <mergeCell ref="AF4:AF6"/>
@@ -57147,12 +57241,6 @@
     <mergeCell ref="V4:V6"/>
     <mergeCell ref="X4:X6"/>
     <mergeCell ref="Z4:Z6"/>
-    <mergeCell ref="N4:N6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="J4:J6"/>
-    <mergeCell ref="L4:L6"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -57170,6 +57258,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DBF2846C41E31A469E3CED25F2422E48" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5fe40c83f7497f6a132ba44389c75f2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8c20e6-817c-474f-b9c2-eb2b1ac24837" xmlns:ns4="dc8c2798-6aba-4af7-93a4-b89253b03650" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7827a91f6681aa3909757bf20cf55ac7" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
@@ -57396,14 +57492,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
   <ds:schemaRefs>
@@ -57413,6 +57501,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E4CC2DB-337D-464E-B291-77CE670D3A8E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -57429,21 +57534,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F760DBF-8896-4317-A20B-F1ABD0B008CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97057822-33A9-45A9-BD20-F91D20B8EFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BcI4NY5Ohir363+nRCln2YCzlnOeJyINjZ1aV0hb2IpPHmsHZPUFroFzrod6xokqyCn7GUW2N1Z+U/w2mbyNbQ==" workbookSaltValue="VvXyFesAZC8L8IOzNm6PtA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
@@ -2138,15 +2138,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2157,6 +2148,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11497,18 +11497,22 @@
         <f>P6</f>
         <v>México</v>
       </c>
-      <c r="F6" s="123"/>
+      <c r="F6" s="123">
+        <v>1</v>
+      </c>
       <c r="G6" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="123"/>
+      <c r="H6" s="123">
+        <v>0</v>
+      </c>
       <c r="I6" s="107" t="str">
         <f>P8</f>
         <v>Coreia do Sul</v>
       </c>
       <c r="J6" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>México</v>
       </c>
       <c r="K6" s="38" t="str">
         <f t="shared" si="1"/>
@@ -11520,7 +11524,7 @@
       </c>
       <c r="M6" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="N6" s="46"/>
       <c r="O6" s="47">
@@ -11533,15 +11537,15 @@
       </c>
       <c r="Q6" s="38">
         <f>(S6*3)+(T6*1)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R6" s="38">
         <f>SUM(S6:U6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" s="38">
         <f>COUNTIF(J:J,P6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" s="38">
         <f>COUNTIF(K:K,P6)+COUNTIF(L:L,P6)</f>
@@ -11553,7 +11557,7 @@
       </c>
       <c r="V6" s="38">
         <f>SUMIF(E:E,P6,F:F)+SUMIF(I:I,P6,H:H)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W6" s="38">
         <f>SUMIF(E:E,P6,H:H)+SUMIF(I:I,P6,F:F)</f>
@@ -11561,7 +11565,7 @@
       </c>
       <c r="X6" s="38">
         <f>V6-W6</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" s="38">
         <f>SUMPRODUCT(($Q$6:$Q$9=Q6)*($X$6:$X$9&gt;X6))</f>
@@ -11592,15 +11596,15 @@
       </c>
       <c r="AG6" s="84">
         <f>VLOOKUP($AE6,$O$6:$X$9,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH6" s="84">
         <f>VLOOKUP($AE6,$O$6:$X$9,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI6" s="84">
         <f>VLOOKUP($AE6,$O$6:$X$9,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ6" s="84">
         <f>VLOOKUP($AE6,$O$6:$X$9,6,FALSE)</f>
@@ -11612,7 +11616,7 @@
       </c>
       <c r="AL6" s="84">
         <f>VLOOKUP($AE6,$O$6:$X$9,8,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM6" s="84">
         <f>VLOOKUP($AE6,$O$6:$X$9,9,FALSE)</f>
@@ -11620,11 +11624,11 @@
       </c>
       <c r="AN6" s="85">
         <f>VLOOKUP($AE6,$O$6:$X$9,10,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP6" s="48">
         <f t="shared" ref="AP6:AP17" si="4">RANK(AR6,$AR$6:$AR$17)+SUM(BB6:BE6)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ6" s="50" t="str">
         <f>AF8</f>
@@ -11632,11 +11636,11 @@
       </c>
       <c r="AR6" s="38">
         <f>(AT6*3)+(AU6*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS6" s="38">
         <f>SUM(AT6:AV6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT6" s="38">
         <f t="shared" ref="AT6:AT17" si="5">VLOOKUP(AQ6,$P$5:$X$75,4,FALSE)</f>
@@ -11644,7 +11648,7 @@
       </c>
       <c r="AU6" s="38">
         <f t="shared" ref="AU6:AU17" si="6">VLOOKUP(AQ6,$P$5:$X$75,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV6" s="38">
         <f t="shared" ref="AV6:AV17" si="7">VLOOKUP(AQ6,$P$5:$X$75,6,FALSE)</f>
@@ -11652,11 +11656,11 @@
       </c>
       <c r="AW6" s="38">
         <f t="shared" ref="AW6:AW17" si="8">VLOOKUP(AQ6,$P$5:$X$75,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX6" s="38">
         <f t="shared" ref="AX6:AX17" si="9">VLOOKUP(AQ6,$P$5:$X$75,8,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY6" s="38">
         <f>AW6-AX6</f>
@@ -11694,35 +11698,35 @@
       </c>
       <c r="BJ6" s="83" t="str">
         <f t="shared" ref="BJ6:BJ17" si="14">VLOOKUP($BI6,$AP$6:$AY$17,2,FALSE)</f>
-        <v>Japão</v>
+        <v>Suécia</v>
       </c>
       <c r="BK6" s="84">
         <f t="shared" ref="BK6:BK17" si="15">VLOOKUP($BI6,$AP$6:$AY$17,3,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL6" s="84">
         <f t="shared" ref="BL6:BL17" si="16">VLOOKUP($BI6,$AP$6:$AY$17,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM6" s="84">
         <f t="shared" ref="BM6:BM17" si="17">VLOOKUP($BI6,$AP$6:$AY$17,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN6" s="84">
         <f t="shared" ref="BN6:BN17" si="18">VLOOKUP($BI6,$AP$6:$AY$17,6,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO6" s="84">
         <f t="shared" ref="BO6:BO17" si="19">VLOOKUP($BI6,$AP$6:$AY$17,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP6" s="84">
         <f t="shared" ref="BP6:BP17" si="20">VLOOKUP($BI6,$AP$6:$AY$17,8,FALSE)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BQ6" s="84">
         <f t="shared" ref="BQ6:BQ17" si="21">VLOOKUP($BI6,$AP$6:$AY$17,9,FALSE)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BR6" s="85">
         <f t="shared" ref="BR6:BR17" si="22">VLOOKUP($BI6,$AP$6:$AY$17,10,FALSE)</f>
@@ -11744,11 +11748,15 @@
         <f>P9</f>
         <v>República Tcheca</v>
       </c>
-      <c r="F7" s="123"/>
+      <c r="F7" s="123">
+        <v>1</v>
+      </c>
       <c r="G7" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="123"/>
+      <c r="H7" s="123">
+        <v>1</v>
+      </c>
       <c r="I7" s="107" t="str">
         <f>P7</f>
         <v>África do Sul</v>
@@ -11759,11 +11767,11 @@
       </c>
       <c r="K7" s="38" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>República Tcheca</v>
       </c>
       <c r="L7" s="38" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>África do Sul</v>
       </c>
       <c r="M7" s="39" t="str">
         <f t="shared" si="3"/>
@@ -11780,11 +11788,11 @@
       </c>
       <c r="Q7" s="38">
         <f t="shared" ref="Q7:Q9" si="23">(S7*3)+(T7*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="38">
         <f t="shared" ref="R7:R9" si="24">SUM(S7:U7)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" s="38">
         <f>COUNTIF(J:J,P7)</f>
@@ -11792,7 +11800,7 @@
       </c>
       <c r="T7" s="38">
         <f>COUNTIF(K:K,P7)+COUNTIF(L:L,P7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" s="38">
         <f>COUNTIF(M:M,P7)</f>
@@ -11800,11 +11808,11 @@
       </c>
       <c r="V7" s="38">
         <f>SUMIF(E:E,P7,F:F)+SUMIF(I:I,P7,H:H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="38">
         <f>SUMIF(E:E,P7,H:H)+SUMIF(I:I,P7,F:F)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X7" s="38">
         <f t="shared" ref="X7:X9" si="25">V7-W7</f>
@@ -11843,7 +11851,7 @@
       </c>
       <c r="AH7" s="84">
         <f>VLOOKUP($AE7,$O$6:$X$9,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI7" s="84">
         <f>VLOOKUP($AE7,$O$6:$X$9,5,FALSE)</f>
@@ -11855,7 +11863,7 @@
       </c>
       <c r="AK7" s="84">
         <f>VLOOKUP($AE7,$O$6:$X$9,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL7" s="84">
         <f>VLOOKUP($AE7,$O$6:$X$9,8,FALSE)</f>
@@ -11863,19 +11871,19 @@
       </c>
       <c r="AM7" s="84">
         <f>VLOOKUP($AE7,$O$6:$X$9,9,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN7" s="85">
         <f>VLOOKUP($AE7,$O$6:$X$9,10,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP7" s="48">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AQ7" s="50" t="str">
         <f>AF14</f>
-        <v>Qatar</v>
+        <v>Bósnia</v>
       </c>
       <c r="AR7" s="38">
         <f t="shared" ref="AR7:AR17" si="26">(AT7*3)+(AU7*1)</f>
@@ -11883,7 +11891,7 @@
       </c>
       <c r="AS7" s="38">
         <f t="shared" ref="AS7:AS17" si="27">SUM(AT7:AV7)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT7" s="38">
         <f t="shared" si="5"/>
@@ -11895,34 +11903,34 @@
       </c>
       <c r="AV7" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW7" s="38">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX7" s="38">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AY7" s="38">
         <f t="shared" ref="AY7:AY17" si="28">AW7-AX7</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AZ7" s="38" t="s">
         <v>48</v>
       </c>
       <c r="BA7" s="38" t="str">
         <f t="shared" ref="BA7:BA17" si="29">AQ7</f>
-        <v>Qatar</v>
+        <v>Bósnia</v>
       </c>
       <c r="BB7" s="38">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC7" s="38">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD7" s="38">
         <f t="shared" si="12"/>
@@ -11941,27 +11949,27 @@
       </c>
       <c r="BJ7" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Qatar</v>
+        <v>Escócia</v>
       </c>
       <c r="BK7" s="84">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL7" s="84">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM7" s="84">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN7" s="84">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO7" s="84">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP7" s="84">
         <f t="shared" si="20"/>
@@ -12031,7 +12039,7 @@
       </c>
       <c r="R8" s="38">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" s="38">
         <f>COUNTIF(J:J,P8)</f>
@@ -12043,7 +12051,7 @@
       </c>
       <c r="U8" s="38">
         <f>COUNTIF(M:M,P8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="38">
         <f>SUMIF(E:E,P8,F:F)+SUMIF(I:I,P8,H:H)</f>
@@ -12051,15 +12059,15 @@
       </c>
       <c r="W8" s="38">
         <f>SUMIF(E:E,P8,H:H)+SUMIF(I:I,P8,F:F)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X8" s="38">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="38">
         <f>SUMPRODUCT(($Q$6:$Q$9=Q8)*($X$6:$X$9&gt;X8))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="38">
         <f>SUMPRODUCT(($Q$6:$Q$9=Q8)*($X$6:$X$9=X8)*($V$6:$V$9&gt;V8))</f>
@@ -12086,11 +12094,11 @@
       </c>
       <c r="AG8" s="84">
         <f>VLOOKUP($AE8,$O$6:$X$9,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" s="84">
         <f>VLOOKUP($AE8,$O$6:$X$9,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI8" s="84">
         <f>VLOOKUP($AE8,$O$6:$X$9,5,FALSE)</f>
@@ -12098,7 +12106,7 @@
       </c>
       <c r="AJ8" s="84">
         <f>VLOOKUP($AE8,$O$6:$X$9,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK8" s="84">
         <f>VLOOKUP($AE8,$O$6:$X$9,7,FALSE)</f>
@@ -12106,11 +12114,11 @@
       </c>
       <c r="AL8" s="84">
         <f>VLOOKUP($AE8,$O$6:$X$9,8,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM8" s="84">
         <f>VLOOKUP($AE8,$O$6:$X$9,9,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN8" s="85">
         <f>VLOOKUP($AE8,$O$6:$X$9,10,FALSE)</f>
@@ -12118,31 +12126,31 @@
       </c>
       <c r="AP8" s="48">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ8" s="50" t="str">
         <f>AF20</f>
-        <v>Marrocos</v>
+        <v>Escócia</v>
       </c>
       <c r="AR8" s="38">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS8" s="38">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT8" s="38">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU8" s="38">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV8" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW8" s="38">
         <f t="shared" si="8"/>
@@ -12161,7 +12169,7 @@
       </c>
       <c r="BA8" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Marrocos</v>
+        <v>Escócia</v>
       </c>
       <c r="BB8" s="38">
         <f t="shared" si="10"/>
@@ -12177,7 +12185,7 @@
       </c>
       <c r="BE8" s="38">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF8" s="39">
         <v>3</v>
@@ -12188,39 +12196,39 @@
       </c>
       <c r="BJ8" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Marrocos</v>
+        <v>Croácia</v>
       </c>
       <c r="BK8" s="84">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL8" s="84">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM8" s="84">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN8" s="84">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO8" s="84">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP8" s="84">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ8" s="84">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BR8" s="85">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12274,11 +12282,11 @@
       </c>
       <c r="Q9" s="38">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="38">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" s="38">
         <f>COUNTIF(J:J,P9)</f>
@@ -12286,7 +12294,7 @@
       </c>
       <c r="T9" s="38">
         <f>COUNTIF(K:K,P9)+COUNTIF(L:L,P9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" s="38">
         <f>COUNTIF(M:M,P9)</f>
@@ -12294,11 +12302,11 @@
       </c>
       <c r="V9" s="38">
         <f>SUMIF(E:E,P9,F:F)+SUMIF(I:I,P9,H:H)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W9" s="38">
         <f>SUMIF(E:E,P9,H:H)+SUMIF(I:I,P9,F:F)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X9" s="38">
         <f t="shared" si="25"/>
@@ -12333,11 +12341,11 @@
       </c>
       <c r="AG9" s="87">
         <f>VLOOKUP($AE9,$O$6:$X$9,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" s="87">
         <f>VLOOKUP($AE9,$O$6:$X$9,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI9" s="87">
         <f>VLOOKUP($AE9,$O$6:$X$9,5,FALSE)</f>
@@ -12345,7 +12353,7 @@
       </c>
       <c r="AJ9" s="87">
         <f>VLOOKUP($AE9,$O$6:$X$9,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" s="87">
         <f>VLOOKUP($AE9,$O$6:$X$9,7,FALSE)</f>
@@ -12353,11 +12361,11 @@
       </c>
       <c r="AL9" s="87">
         <f>VLOOKUP($AE9,$O$6:$X$9,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM9" s="87">
         <f>VLOOKUP($AE9,$O$6:$X$9,9,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN9" s="88">
         <f>VLOOKUP($AE9,$O$6:$X$9,10,FALSE)</f>
@@ -12365,23 +12373,23 @@
       </c>
       <c r="AP9" s="48">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AQ9" s="50" t="str">
         <f>AF26</f>
-        <v>Turquia</v>
+        <v>Paraguai</v>
       </c>
       <c r="AR9" s="38">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS9" s="38">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT9" s="38">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU9" s="38">
         <f t="shared" si="6"/>
@@ -12393,11 +12401,11 @@
       </c>
       <c r="AW9" s="38">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX9" s="38">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY9" s="38">
         <f t="shared" si="28"/>
@@ -12408,7 +12416,7 @@
       </c>
       <c r="BA9" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Turquia</v>
+        <v>Paraguai</v>
       </c>
       <c r="BB9" s="38">
         <f t="shared" si="10"/>
@@ -12416,7 +12424,7 @@
       </c>
       <c r="BC9" s="38">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD9" s="38">
         <f t="shared" si="12"/>
@@ -12435,39 +12443,39 @@
       </c>
       <c r="BJ9" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Bélgica</v>
+        <v>Paraguai</v>
       </c>
       <c r="BK9" s="84">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL9" s="84">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM9" s="84">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN9" s="84">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO9" s="84">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP9" s="84">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ9" s="84">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BR9" s="85">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="10" spans="1:70" x14ac:dyDescent="0.25">
@@ -12547,7 +12555,7 @@
       <c r="AN10" s="80"/>
       <c r="AP10" s="48">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ10" s="50" t="str">
         <f>AF32</f>
@@ -12555,11 +12563,11 @@
       </c>
       <c r="AR10" s="38">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS10" s="38">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT10" s="38">
         <f t="shared" si="5"/>
@@ -12567,7 +12575,7 @@
       </c>
       <c r="AU10" s="38">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV10" s="38">
         <f t="shared" si="7"/>
@@ -12598,7 +12606,7 @@
       </c>
       <c r="BC10" s="38">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD10" s="38">
         <f t="shared" si="12"/>
@@ -12617,39 +12625,39 @@
       </c>
       <c r="BJ10" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>RD Congo</v>
+        <v>Argélia</v>
       </c>
       <c r="BK10" s="84">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL10" s="84">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM10" s="84">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN10" s="84">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO10" s="84">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP10" s="84">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ10" s="84">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BR10" s="85">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="11" spans="1:70" x14ac:dyDescent="0.25">
@@ -12779,35 +12787,35 @@
       </c>
       <c r="AQ11" s="50" t="str">
         <f>AF38</f>
-        <v>Japão</v>
+        <v>Suécia</v>
       </c>
       <c r="AR11" s="38">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS11" s="38">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT11" s="38">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU11" s="38">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV11" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW11" s="38">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX11" s="38">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY11" s="38">
         <f t="shared" si="28"/>
@@ -12818,7 +12826,7 @@
       </c>
       <c r="BA11" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Japão</v>
+        <v>Suécia</v>
       </c>
       <c r="BB11" s="38">
         <f t="shared" si="10"/>
@@ -12845,15 +12853,15 @@
       </c>
       <c r="BJ11" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Espanha</v>
+        <v>Cabo Verde</v>
       </c>
       <c r="BK11" s="84">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL11" s="84">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM11" s="84">
         <f t="shared" si="17"/>
@@ -12861,7 +12869,7 @@
       </c>
       <c r="BN11" s="84">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO11" s="84">
         <f t="shared" si="19"/>
@@ -12869,11 +12877,11 @@
       </c>
       <c r="BP11" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ11" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR11" s="85">
         <f t="shared" si="22"/>
@@ -12895,18 +12903,22 @@
         <f>P12</f>
         <v>Canadá</v>
       </c>
-      <c r="F12" s="123"/>
+      <c r="F12" s="123">
+        <v>6</v>
+      </c>
       <c r="G12" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="123"/>
+      <c r="H12" s="123">
+        <v>0</v>
+      </c>
       <c r="I12" s="113" t="str">
         <f>P14</f>
         <v>Qatar</v>
       </c>
       <c r="J12" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Canadá</v>
       </c>
       <c r="K12" s="38" t="str">
         <f t="shared" si="1"/>
@@ -12918,7 +12930,7 @@
       </c>
       <c r="M12" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Qatar</v>
       </c>
       <c r="N12" s="46"/>
       <c r="O12" s="47">
@@ -12931,15 +12943,15 @@
       </c>
       <c r="Q12" s="38">
         <f>(S12*3)+(T12*1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R12" s="38">
         <f>SUM(S12:U12)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12" s="38">
         <f>COUNTIF(J:J,P12)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="38">
         <f>COUNTIF(K:K,P12)+COUNTIF(L:L,P12)</f>
@@ -12951,7 +12963,7 @@
       </c>
       <c r="V12" s="38">
         <f>SUMIF(E:E,P12,F:F)+SUMIF(I:I,P12,H:H)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W12" s="38">
         <f>SUMIF(E:E,P12,H:H)+SUMIF(I:I,P12,F:F)</f>
@@ -12959,7 +12971,7 @@
       </c>
       <c r="X12" s="38">
         <f>V12-W12</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y12" s="38">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q12)*($X$12:$X$15&gt;X12))</f>
@@ -12990,15 +13002,15 @@
       </c>
       <c r="AG12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,3,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,6,FALSE)</f>
@@ -13010,7 +13022,7 @@
       </c>
       <c r="AL12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,8,FALSE)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AM12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,9,FALSE)</f>
@@ -13018,11 +13030,11 @@
       </c>
       <c r="AN12" s="85">
         <f>VLOOKUP($AE12,$O$12:$X$15,10,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AP12" s="48">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AQ12" s="50" t="str">
         <f>AF44</f>
@@ -13030,11 +13042,11 @@
       </c>
       <c r="AR12" s="38">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS12" s="38">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT12" s="38">
         <f t="shared" si="5"/>
@@ -13042,7 +13054,7 @@
       </c>
       <c r="AU12" s="38">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV12" s="38">
         <f t="shared" si="7"/>
@@ -13081,7 +13093,7 @@
       </c>
       <c r="BE12" s="38">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF12" s="39">
         <v>7</v>
@@ -13092,15 +13104,15 @@
       </c>
       <c r="BJ12" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>República Tcheca</v>
+        <v>Bélgica</v>
       </c>
       <c r="BK12" s="84">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL12" s="84">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM12" s="84">
         <f t="shared" si="17"/>
@@ -13108,11 +13120,11 @@
       </c>
       <c r="BN12" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BO12" s="84">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP12" s="84">
         <f t="shared" si="20"/>
@@ -13120,11 +13132,11 @@
       </c>
       <c r="BQ12" s="84">
         <f t="shared" si="21"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR12" s="85">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13142,18 +13154,22 @@
         <f>P15</f>
         <v>Suiça</v>
       </c>
-      <c r="F13" s="123"/>
+      <c r="F13" s="123">
+        <v>4</v>
+      </c>
       <c r="G13" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H13" s="123"/>
+      <c r="H13" s="123">
+        <v>1</v>
+      </c>
       <c r="I13" s="113" t="str">
         <f>P13</f>
         <v>Bósnia</v>
       </c>
       <c r="J13" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Suiça</v>
       </c>
       <c r="K13" s="38" t="str">
         <f t="shared" si="1"/>
@@ -13165,12 +13181,12 @@
       </c>
       <c r="M13" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Bósnia</v>
       </c>
       <c r="N13" s="46"/>
       <c r="O13" s="47">
         <f>RANK(Q13,$Q$12:$Q$15)+SUM(Y13:AB13)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P13" s="49" t="str">
         <f>Sorteios!F7</f>
@@ -13182,7 +13198,7 @@
       </c>
       <c r="R13" s="38">
         <f t="shared" ref="R13:R15" si="31">SUM(S13:U13)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" s="38">
         <f>COUNTIF(J:J,P13)</f>
@@ -13194,19 +13210,19 @@
       </c>
       <c r="U13" s="38">
         <f>COUNTIF(M:M,P13)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="38">
         <f>SUMIF(E:E,P13,F:F)+SUMIF(I:I,P13,H:H)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W13" s="38">
         <f>SUMIF(E:E,P13,H:H)+SUMIF(I:I,P13,F:F)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X13" s="38">
         <f t="shared" ref="X13:X15" si="32">V13-W13</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Y13" s="38">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q13)*($X$12:$X$15&gt;X13))</f>
@@ -13222,7 +13238,7 @@
       </c>
       <c r="AB13" s="38">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q13)*($X$12:$X$15=X13)*($V$12:$V$15=V13)*($W$12:$W$15=W13)*($AC$12:$AC$15&lt;AC13))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" s="39">
         <v>2</v>
@@ -13233,19 +13249,19 @@
       </c>
       <c r="AF13" s="83" t="str">
         <f>VLOOKUP($AE13,$O$12:$X$15,2,FALSE)</f>
-        <v>Bósnia</v>
+        <v>Suiça</v>
       </c>
       <c r="AG13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,3,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,6,FALSE)</f>
@@ -13257,15 +13273,15 @@
       </c>
       <c r="AL13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,8,FALSE)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AM13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,9,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN13" s="85">
         <f>VLOOKUP($AE13,$O$12:$X$15,10,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP13" s="48">
         <f t="shared" si="4"/>
@@ -13273,15 +13289,15 @@
       </c>
       <c r="AQ13" s="50" t="str">
         <f>AF50</f>
-        <v>Espanha</v>
+        <v>Cabo Verde</v>
       </c>
       <c r="AR13" s="38">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS13" s="38">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT13" s="38">
         <f t="shared" si="5"/>
@@ -13289,7 +13305,7 @@
       </c>
       <c r="AU13" s="38">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV13" s="38">
         <f t="shared" si="7"/>
@@ -13297,11 +13313,11 @@
       </c>
       <c r="AW13" s="38">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX13" s="38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY13" s="38">
         <f t="shared" si="28"/>
@@ -13312,7 +13328,7 @@
       </c>
       <c r="BA13" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Espanha</v>
+        <v>Cabo Verde</v>
       </c>
       <c r="BB13" s="38">
         <f t="shared" si="10"/>
@@ -13320,7 +13336,7 @@
       </c>
       <c r="BC13" s="38">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BD13" s="38">
         <f t="shared" si="12"/>
@@ -13339,15 +13355,15 @@
       </c>
       <c r="BJ13" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Equador</v>
+        <v>República Tcheca</v>
       </c>
       <c r="BK13" s="84">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL13" s="84">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM13" s="84">
         <f t="shared" si="17"/>
@@ -13355,7 +13371,7 @@
       </c>
       <c r="BN13" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO13" s="84">
         <f t="shared" si="19"/>
@@ -13363,11 +13379,11 @@
       </c>
       <c r="BP13" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ13" s="84">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR13" s="85">
         <f t="shared" si="22"/>
@@ -13417,7 +13433,7 @@
       <c r="N14" s="46"/>
       <c r="O14" s="47">
         <f>RANK(Q14,$Q$12:$Q$15)+SUM(Y14:AB14)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P14" s="49" t="str">
         <f>Sorteios!F8</f>
@@ -13429,7 +13445,7 @@
       </c>
       <c r="R14" s="38">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" s="38">
         <f>COUNTIF(J:J,P14)</f>
@@ -13441,7 +13457,7 @@
       </c>
       <c r="U14" s="38">
         <f>COUNTIF(M:M,P14)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="38">
         <f>SUMIF(E:E,P14,F:F)+SUMIF(I:I,P14,H:H)</f>
@@ -13449,15 +13465,15 @@
       </c>
       <c r="W14" s="38">
         <f>SUMIF(E:E,P14,H:H)+SUMIF(I:I,P14,F:F)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X14" s="38">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="Y14" s="38">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q14)*($X$12:$X$15&gt;X14))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" s="38">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q14)*($X$12:$X$15=X14)*($V$12:$V$15&gt;V14))</f>
@@ -13469,7 +13485,7 @@
       </c>
       <c r="AB14" s="38">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q14)*($X$12:$X$15=X14)*($V$12:$V$15=V14)*($W$12:$W$15=W14)*($AC$12:$AC$15&lt;AC14))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="39">
         <v>3</v>
@@ -13480,7 +13496,7 @@
       </c>
       <c r="AF14" s="83" t="str">
         <f>VLOOKUP($AE14,$O$12:$X$15,2,FALSE)</f>
-        <v>Qatar</v>
+        <v>Bósnia</v>
       </c>
       <c r="AG14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,3,FALSE)</f>
@@ -13488,7 +13504,7 @@
       </c>
       <c r="AH14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,5,FALSE)</f>
@@ -13500,23 +13516,23 @@
       </c>
       <c r="AK14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,8,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,9,FALSE)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN14" s="85">
         <f>VLOOKUP($AE14,$O$12:$X$15,10,FALSE)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AP14" s="48">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ14" s="50" t="str">
         <f>AF56</f>
@@ -13528,7 +13544,7 @@
       </c>
       <c r="AS14" s="38">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT14" s="38">
         <f t="shared" si="5"/>
@@ -13540,19 +13556,19 @@
       </c>
       <c r="AV14" s="38">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW14" s="38">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX14" s="38">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY14" s="38">
         <f t="shared" si="28"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AZ14" s="38" t="s">
         <v>69</v>
@@ -13563,7 +13579,7 @@
       </c>
       <c r="BB14" s="38">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BC14" s="38">
         <f t="shared" si="11"/>
@@ -13586,15 +13602,15 @@
       </c>
       <c r="BJ14" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Panamá</v>
+        <v>RD Congo</v>
       </c>
       <c r="BK14" s="84">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL14" s="84">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM14" s="84">
         <f t="shared" si="17"/>
@@ -13602,7 +13618,7 @@
       </c>
       <c r="BN14" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO14" s="84">
         <f t="shared" si="19"/>
@@ -13610,11 +13626,11 @@
       </c>
       <c r="BP14" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ14" s="84">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR14" s="85">
         <f t="shared" si="22"/>
@@ -13664,7 +13680,7 @@
       <c r="N15" s="55"/>
       <c r="O15" s="56">
         <f>RANK(Q15,$Q$12:$Q$15)+SUM(Y15:AB15)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P15" s="49" t="str">
         <f>Sorteios!F9</f>
@@ -13672,15 +13688,15 @@
       </c>
       <c r="Q15" s="53">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R15" s="53">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" s="38">
         <f>COUNTIF(J:J,P15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" s="38">
         <f>COUNTIF(K:K,P15)+COUNTIF(L:L,P15)</f>
@@ -13692,19 +13708,19 @@
       </c>
       <c r="V15" s="53">
         <f>SUMIF(E:E,P15,F:F)+SUMIF(I:I,P15,H:H)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W15" s="53">
         <f>SUMIF(E:E,P15,H:H)+SUMIF(I:I,P15,F:F)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X15" s="53">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y15" s="53">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q15)*($X$12:$X$15&gt;X15))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" s="53">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q15)*($X$12:$X$15=X15)*($V$12:$V$15&gt;V15))</f>
@@ -13716,7 +13732,7 @@
       </c>
       <c r="AB15" s="53">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q15)*($X$12:$X$15=X15)*($V$12:$V$15=V15)*($W$12:$W$15=W15)*($AC$12:$AC$15&lt;AC15))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC15" s="54">
         <v>4</v>
@@ -13727,7 +13743,7 @@
       </c>
       <c r="AF15" s="86" t="str">
         <f>VLOOKUP($AE15,$O$12:$X$15,2,FALSE)</f>
-        <v>Suiça</v>
+        <v>Qatar</v>
       </c>
       <c r="AG15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,3,FALSE)</f>
@@ -13735,7 +13751,7 @@
       </c>
       <c r="AH15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,5,FALSE)</f>
@@ -13747,7 +13763,7 @@
       </c>
       <c r="AK15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,8,FALSE)</f>
@@ -13755,31 +13771,31 @@
       </c>
       <c r="AM15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,9,FALSE)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AN15" s="88">
         <f>VLOOKUP($AE15,$O$12:$X$15,10,FALSE)</f>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AP15" s="48">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AQ15" s="50" t="str">
         <f>AF62</f>
-        <v>Jordânia</v>
+        <v>Argélia</v>
       </c>
       <c r="AR15" s="38">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS15" s="38">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT15" s="38">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU15" s="38">
         <f t="shared" si="6"/>
@@ -13791,11 +13807,11 @@
       </c>
       <c r="AW15" s="38">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX15" s="38">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY15" s="38">
         <f t="shared" si="28"/>
@@ -13806,7 +13822,7 @@
       </c>
       <c r="BA15" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Jordânia</v>
+        <v>Argélia</v>
       </c>
       <c r="BB15" s="38">
         <f t="shared" si="10"/>
@@ -13833,15 +13849,15 @@
       </c>
       <c r="BJ15" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Senegal</v>
+        <v>Equador</v>
       </c>
       <c r="BK15" s="84">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL15" s="84">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM15" s="84">
         <f t="shared" si="17"/>
@@ -13849,7 +13865,7 @@
       </c>
       <c r="BN15" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO15" s="84">
         <f t="shared" si="19"/>
@@ -13857,15 +13873,15 @@
       </c>
       <c r="BP15" s="84">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ15" s="84">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR15" s="85">
         <f t="shared" si="22"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:70" x14ac:dyDescent="0.25">
@@ -13945,7 +13961,7 @@
       <c r="AN16" s="80"/>
       <c r="AP16" s="48">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AQ16" s="50" t="str">
         <f>AF68</f>
@@ -13957,7 +13973,7 @@
       </c>
       <c r="AS16" s="38">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT16" s="38">
         <f t="shared" si="5"/>
@@ -13969,7 +13985,7 @@
       </c>
       <c r="AV16" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW16" s="38">
         <f t="shared" si="8"/>
@@ -13977,11 +13993,11 @@
       </c>
       <c r="AX16" s="38">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY16" s="38">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AZ16" s="38" t="s">
         <v>70</v>
@@ -14004,7 +14020,7 @@
       </c>
       <c r="BE16" s="38">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BF16" s="39">
         <v>11</v>
@@ -14015,15 +14031,15 @@
       </c>
       <c r="BJ16" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Jordânia</v>
+        <v>Bósnia</v>
       </c>
       <c r="BK16" s="84">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL16" s="84">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM16" s="84">
         <f t="shared" si="17"/>
@@ -14031,7 +14047,7 @@
       </c>
       <c r="BN16" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO16" s="84">
         <f t="shared" si="19"/>
@@ -14039,15 +14055,15 @@
       </c>
       <c r="BP16" s="84">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ16" s="84">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BR16" s="85">
         <f t="shared" si="22"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="17" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14173,23 +14189,23 @@
       </c>
       <c r="AP17" s="48">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AQ17" s="50" t="str">
         <f>AF74</f>
-        <v>Panamá</v>
+        <v>Croácia</v>
       </c>
       <c r="AR17" s="38">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS17" s="38">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT17" s="38">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU17" s="38">
         <f t="shared" si="6"/>
@@ -14201,11 +14217,11 @@
       </c>
       <c r="AW17" s="38">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX17" s="38">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY17" s="38">
         <f t="shared" si="28"/>
@@ -14216,15 +14232,15 @@
       </c>
       <c r="BA17" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Panamá</v>
+        <v>Croácia</v>
       </c>
       <c r="BB17" s="38">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BC17" s="38">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD17" s="38">
         <f t="shared" si="12"/>
@@ -14232,7 +14248,7 @@
       </c>
       <c r="BE17" s="38">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF17" s="54">
         <v>12</v>
@@ -14243,7 +14259,7 @@
       </c>
       <c r="BJ17" s="86" t="str">
         <f t="shared" si="14"/>
-        <v>Turquia</v>
+        <v>Senegal</v>
       </c>
       <c r="BK17" s="87">
         <f t="shared" si="15"/>
@@ -14251,7 +14267,7 @@
       </c>
       <c r="BL17" s="87">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM17" s="87">
         <f t="shared" si="17"/>
@@ -14263,19 +14279,19 @@
       </c>
       <c r="BO17" s="87">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP17" s="87">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BQ17" s="87">
         <f t="shared" si="21"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BR17" s="88">
         <f t="shared" si="22"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="18" spans="1:70" x14ac:dyDescent="0.25">
@@ -14293,18 +14309,22 @@
         <f>P18</f>
         <v>Brasil</v>
       </c>
-      <c r="F18" s="123"/>
+      <c r="F18" s="123">
+        <v>3</v>
+      </c>
       <c r="G18" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="123"/>
+      <c r="H18" s="123">
+        <v>0</v>
+      </c>
       <c r="I18" s="107" t="str">
         <f>P20</f>
         <v>Haiti</v>
       </c>
       <c r="J18" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Brasil</v>
       </c>
       <c r="K18" s="38" t="str">
         <f t="shared" si="1"/>
@@ -14316,12 +14336,12 @@
       </c>
       <c r="M18" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Haiti</v>
       </c>
       <c r="N18" s="46"/>
       <c r="O18" s="47">
         <f>RANK(Q18,$Q$18:$Q$21)+SUM(Y18:AB18)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P18" s="49" t="str">
         <f>Sorteios!I6</f>
@@ -14329,15 +14349,15 @@
       </c>
       <c r="Q18" s="38">
         <f>(S18*3)+(T18*1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R18" s="38">
         <f>SUM(S18:U18)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S18" s="38">
         <f>COUNTIF(J:J,P18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" s="38">
         <f>COUNTIF(K:K,P18)+COUNTIF(L:L,P18)</f>
@@ -14349,7 +14369,7 @@
       </c>
       <c r="V18" s="38">
         <f>SUMIF(E:E,P18,F:F)+SUMIF(I:I,P18,H:H)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W18" s="38">
         <f>SUMIF(E:E,P18,H:H)+SUMIF(I:I,P18,F:F)</f>
@@ -14357,7 +14377,7 @@
       </c>
       <c r="X18" s="38">
         <f>V18-W18</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y18" s="38">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q18)*($X$18:$X$21&gt;X18))</f>
@@ -14384,15 +14404,15 @@
       </c>
       <c r="AF18" s="83" t="str">
         <f>VLOOKUP($AE18,$O$18:$X$21,2,FALSE)</f>
-        <v>Escócia</v>
+        <v>Brasil</v>
       </c>
       <c r="AG18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,5,FALSE)</f>
@@ -14400,7 +14420,7 @@
       </c>
       <c r="AJ18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,7,FALSE)</f>
@@ -14408,19 +14428,19 @@
       </c>
       <c r="AL18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,8,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AM18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN18" s="85">
         <f>VLOOKUP($AE18,$O$18:$X$21,10,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL18" s="153">
         <f>SUM(BL6:BL17)</f>
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:70" x14ac:dyDescent="0.25">
@@ -14438,18 +14458,22 @@
         <f>P21</f>
         <v>Escócia</v>
       </c>
-      <c r="F19" s="123"/>
+      <c r="F19" s="123">
+        <v>0</v>
+      </c>
       <c r="G19" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="123"/>
+      <c r="H19" s="123">
+        <v>1</v>
+      </c>
       <c r="I19" s="107" t="str">
         <f>P19</f>
         <v>Marrocos</v>
       </c>
       <c r="J19" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Marrocos</v>
       </c>
       <c r="K19" s="38" t="str">
         <f t="shared" si="1"/>
@@ -14461,12 +14485,12 @@
       </c>
       <c r="M19" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Escócia</v>
       </c>
       <c r="N19" s="46"/>
       <c r="O19" s="47">
         <f>RANK(Q19,$Q$18:$Q$21)+SUM(Y19:AB19)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P19" s="49" t="str">
         <f>Sorteios!I7</f>
@@ -14474,15 +14498,15 @@
       </c>
       <c r="Q19" s="38">
         <f t="shared" ref="Q19:Q21" si="33">(S19*3)+(T19*1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R19" s="38">
         <f t="shared" ref="R19:R21" si="34">SUM(S19:U19)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S19" s="38">
         <f>COUNTIF(J:J,P19)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" s="38">
         <f>COUNTIF(K:K,P19)+COUNTIF(L:L,P19)</f>
@@ -14494,7 +14518,7 @@
       </c>
       <c r="V19" s="38">
         <f>SUMIF(E:E,P19,F:F)+SUMIF(I:I,P19,H:H)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W19" s="38">
         <f>SUMIF(E:E,P19,H:H)+SUMIF(I:I,P19,F:F)</f>
@@ -14502,11 +14526,11 @@
       </c>
       <c r="X19" s="38">
         <f t="shared" ref="X19:X21" si="35">V19-W19</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" s="38">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q19)*($X$18:$X$21&gt;X19))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="38">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q19)*($X$18:$X$21=X19)*($V$18:$V$21&gt;V19))</f>
@@ -14518,7 +14542,7 @@
       </c>
       <c r="AB19" s="38">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q19)*($X$18:$X$21=X19)*($V$18:$V$21=V19)*($W$18:$W$21=W19)*($AC$18:$AC$21&lt;AC19))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" s="39">
         <v>2</v>
@@ -14529,19 +14553,19 @@
       </c>
       <c r="AF19" s="83" t="str">
         <f>VLOOKUP($AE19,$O$18:$X$21,2,FALSE)</f>
-        <v>Brasil</v>
+        <v>Marrocos</v>
       </c>
       <c r="AG19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,3,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,6,FALSE)</f>
@@ -14553,7 +14577,7 @@
       </c>
       <c r="AL19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,8,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,9,FALSE)</f>
@@ -14561,7 +14585,7 @@
       </c>
       <c r="AN19" s="85">
         <f>VLOOKUP($AE19,$O$18:$X$21,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:70" x14ac:dyDescent="0.25">
@@ -14619,7 +14643,7 @@
       </c>
       <c r="R20" s="38">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S20" s="38">
         <f>COUNTIF(J:J,P20)</f>
@@ -14631,7 +14655,7 @@
       </c>
       <c r="U20" s="38">
         <f>COUNTIF(M:M,P20)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20" s="38">
         <f>SUMIF(E:E,P20,F:F)+SUMIF(I:I,P20,H:H)</f>
@@ -14639,11 +14663,11 @@
       </c>
       <c r="W20" s="38">
         <f>SUMIF(E:E,P20,H:H)+SUMIF(I:I,P20,F:F)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X20" s="38">
         <f t="shared" si="35"/>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="Y20" s="38">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q20)*($X$18:$X$21&gt;X20))</f>
@@ -14670,27 +14694,27 @@
       </c>
       <c r="AF20" s="83" t="str">
         <f>VLOOKUP($AE20,$O$18:$X$21,2,FALSE)</f>
-        <v>Marrocos</v>
+        <v>Escócia</v>
       </c>
       <c r="AG20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,3,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,6,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,8,FALSE)</f>
@@ -14748,7 +14772,7 @@
       <c r="N21" s="55"/>
       <c r="O21" s="56">
         <f>RANK(Q21,$Q$18:$Q$21)+SUM(Y21:AB21)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P21" s="49" t="str">
         <f>Sorteios!I9</f>
@@ -14760,7 +14784,7 @@
       </c>
       <c r="R21" s="53">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S21" s="38">
         <f>COUNTIF(J:J,P21)</f>
@@ -14772,7 +14796,7 @@
       </c>
       <c r="U21" s="38">
         <f>COUNTIF(M:M,P21)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="53">
         <f>SUMIF(E:E,P21,F:F)+SUMIF(I:I,P21,H:H)</f>
@@ -14780,11 +14804,11 @@
       </c>
       <c r="W21" s="53">
         <f>SUMIF(E:E,P21,H:H)+SUMIF(I:I,P21,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" s="53">
         <f t="shared" si="35"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="53">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q21)*($X$18:$X$21&gt;X21))</f>
@@ -14819,7 +14843,7 @@
       </c>
       <c r="AH21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,5,FALSE)</f>
@@ -14831,7 +14855,7 @@
       </c>
       <c r="AK21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,8,FALSE)</f>
@@ -14839,11 +14863,11 @@
       </c>
       <c r="AM21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,9,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN21" s="88">
         <f>VLOOKUP($AE21,$O$18:$X$21,10,FALSE)</f>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="AP21" s="15">
         <v>1</v>
@@ -14937,11 +14961,11 @@
       </c>
       <c r="AQ22" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="AR22" s="15">
         <f t="shared" ref="AR22:AR28" si="37">CODE(AQ22)</f>
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:70" x14ac:dyDescent="0.25">
@@ -15070,11 +15094,11 @@
       </c>
       <c r="AQ23" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>C</v>
+        <v>L</v>
       </c>
       <c r="AR23" s="15">
         <f t="shared" si="37"/>
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:70" x14ac:dyDescent="0.25">
@@ -15092,18 +15116,22 @@
         <f>P24</f>
         <v>Estados Unidos</v>
       </c>
-      <c r="F24" s="123"/>
+      <c r="F24" s="123">
+        <v>2</v>
+      </c>
       <c r="G24" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H24" s="123"/>
+      <c r="H24" s="123">
+        <v>0</v>
+      </c>
       <c r="I24" s="113" t="str">
         <f>P26</f>
         <v>Austrália</v>
       </c>
       <c r="J24" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Estados Unidos</v>
       </c>
       <c r="K24" s="38" t="str">
         <f t="shared" si="1"/>
@@ -15115,7 +15143,7 @@
       </c>
       <c r="M24" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Austrália</v>
       </c>
       <c r="N24" s="45"/>
       <c r="O24" s="47">
@@ -15128,15 +15156,15 @@
       </c>
       <c r="Q24" s="38">
         <f>(S24*3)+(T24*1)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R24" s="38">
         <f>SUM(S24:U24)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S24" s="38">
         <f>COUNTIF(J:J,P24)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T24" s="38">
         <f>COUNTIF(K:K,P24)+COUNTIF(L:L,P24)</f>
@@ -15148,7 +15176,7 @@
       </c>
       <c r="V24" s="38">
         <f>SUMIF(E:E,P24,F:F)+SUMIF(I:I,P24,H:H)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W24" s="38">
         <f>SUMIF(E:E,P24,H:H)+SUMIF(I:I,P24,F:F)</f>
@@ -15156,7 +15184,7 @@
       </c>
       <c r="X24" s="38">
         <f>V24-W24</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y24" s="38">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q24)*($X$24:$X$27&gt;X24))</f>
@@ -15187,15 +15215,15 @@
       </c>
       <c r="AG24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,6,FALSE)</f>
@@ -15207,7 +15235,7 @@
       </c>
       <c r="AL24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,8,FALSE)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,9,FALSE)</f>
@@ -15215,18 +15243,18 @@
       </c>
       <c r="AN24" s="85">
         <f>VLOOKUP($AE24,$O$24:$X$27,10,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AP24" s="15">
         <v>4</v>
       </c>
       <c r="AQ24" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>G</v>
+        <v>D</v>
       </c>
       <c r="AR24" s="15">
         <f t="shared" si="37"/>
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:70" x14ac:dyDescent="0.25">
@@ -15244,18 +15272,22 @@
         <f>P27</f>
         <v>Turquia</v>
       </c>
-      <c r="F25" s="123"/>
+      <c r="F25" s="123">
+        <v>0</v>
+      </c>
       <c r="G25" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H25" s="123"/>
+      <c r="H25" s="123">
+        <v>1</v>
+      </c>
       <c r="I25" s="113" t="str">
         <f>P25</f>
         <v>Paraguai</v>
       </c>
       <c r="J25" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Paraguai</v>
       </c>
       <c r="K25" s="38" t="str">
         <f t="shared" si="1"/>
@@ -15267,12 +15299,12 @@
       </c>
       <c r="M25" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Turquia</v>
       </c>
       <c r="N25" s="45"/>
       <c r="O25" s="47">
         <f>RANK(Q25,$Q$24:$Q$27)+SUM(Y25:AB25)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P25" s="49" t="str">
         <f>Sorteios!C15</f>
@@ -15280,15 +15312,15 @@
       </c>
       <c r="Q25" s="38">
         <f t="shared" ref="Q25:Q27" si="38">(S25*3)+(T25*1)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R25" s="38">
         <f t="shared" ref="R25:R27" si="39">SUM(S25:U25)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S25" s="38">
         <f>COUNTIF(J:J,P25)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" s="38">
         <f>COUNTIF(K:K,P25)+COUNTIF(L:L,P25)</f>
@@ -15300,7 +15332,7 @@
       </c>
       <c r="V25" s="38">
         <f>SUMIF(E:E,P25,F:F)+SUMIF(I:I,P25,H:H)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W25" s="38">
         <f>SUMIF(E:E,P25,H:H)+SUMIF(I:I,P25,F:F)</f>
@@ -15308,7 +15340,7 @@
       </c>
       <c r="X25" s="38">
         <f t="shared" ref="X25:X27" si="40">V25-W25</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="Y25" s="38">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q25)*($X$24:$X$27&gt;X25))</f>
@@ -15343,7 +15375,7 @@
       </c>
       <c r="AH25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,5,FALSE)</f>
@@ -15355,7 +15387,7 @@
       </c>
       <c r="AK25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,8,FALSE)</f>
@@ -15363,22 +15395,22 @@
       </c>
       <c r="AM25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,9,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN25" s="85">
         <f>VLOOKUP($AE25,$O$24:$X$27,10,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP25" s="15">
         <v>5</v>
       </c>
       <c r="AQ25" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>K</v>
+        <v>J</v>
       </c>
       <c r="AR25" s="15">
         <f t="shared" si="37"/>
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:70" x14ac:dyDescent="0.25">
@@ -15436,7 +15468,7 @@
       </c>
       <c r="R26" s="38">
         <f t="shared" si="39"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S26" s="38">
         <f>COUNTIF(J:J,P26)</f>
@@ -15448,7 +15480,7 @@
       </c>
       <c r="U26" s="38">
         <f>COUNTIF(M:M,P26)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="38">
         <f>SUMIF(E:E,P26,F:F)+SUMIF(I:I,P26,H:H)</f>
@@ -15456,15 +15488,15 @@
       </c>
       <c r="W26" s="38">
         <f>SUMIF(E:E,P26,H:H)+SUMIF(I:I,P26,F:F)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X26" s="38">
         <f t="shared" si="40"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="38">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q26)*($X$24:$X$27&gt;X26))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="38">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q26)*($X$24:$X$27=X26)*($V$24:$V$27&gt;V26))</f>
@@ -15487,19 +15519,19 @@
       </c>
       <c r="AF26" s="83" t="str">
         <f>VLOOKUP($AE26,$O$24:$X$27,2,FALSE)</f>
-        <v>Turquia</v>
+        <v>Paraguai</v>
       </c>
       <c r="AG26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,6,FALSE)</f>
@@ -15511,11 +15543,11 @@
       </c>
       <c r="AL26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,9,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN26" s="85">
         <f>VLOOKUP($AE26,$O$24:$X$27,10,FALSE)</f>
@@ -15576,7 +15608,7 @@
       <c r="N27" s="57"/>
       <c r="O27" s="56">
         <f>RANK(Q27,$Q$24:$Q$27)+SUM(Y27:AB27)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P27" s="49" t="str">
         <f>Sorteios!C17</f>
@@ -15588,7 +15620,7 @@
       </c>
       <c r="R27" s="53">
         <f t="shared" si="39"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S27" s="38">
         <f>COUNTIF(J:J,P27)</f>
@@ -15600,7 +15632,7 @@
       </c>
       <c r="U27" s="38">
         <f>COUNTIF(M:M,P27)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" s="53">
         <f>SUMIF(E:E,P27,F:F)+SUMIF(I:I,P27,H:H)</f>
@@ -15608,11 +15640,11 @@
       </c>
       <c r="W27" s="53">
         <f>SUMIF(E:E,P27,H:H)+SUMIF(I:I,P27,F:F)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X27" s="53">
         <f t="shared" si="40"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="Y27" s="53">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q27)*($X$24:$X$27&gt;X27))</f>
@@ -15639,7 +15671,7 @@
       </c>
       <c r="AF27" s="86" t="str">
         <f>VLOOKUP($AE27,$O$24:$X$27,2,FALSE)</f>
-        <v>Paraguai</v>
+        <v>Turquia</v>
       </c>
       <c r="AG27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,3,FALSE)</f>
@@ -15647,7 +15679,7 @@
       </c>
       <c r="AH27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,5,FALSE)</f>
@@ -15659,15 +15691,15 @@
       </c>
       <c r="AK27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,8,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,9,FALSE)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN27" s="88">
         <f>VLOOKUP($AE27,$O$24:$X$27,10,FALSE)</f>
@@ -15678,11 +15710,11 @@
       </c>
       <c r="AQ27" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>A</v>
+        <v>G</v>
       </c>
       <c r="AR27" s="15">
         <f t="shared" si="37"/>
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:70" x14ac:dyDescent="0.25">
@@ -15765,11 +15797,11 @@
       </c>
       <c r="AQ28" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>E</v>
+        <v>A</v>
       </c>
       <c r="AR28" s="15">
         <f t="shared" si="37"/>
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:70" x14ac:dyDescent="0.25">
@@ -15909,18 +15941,22 @@
         <f>P30</f>
         <v>Alemanha</v>
       </c>
-      <c r="F30" s="123"/>
+      <c r="F30" s="123">
+        <v>2</v>
+      </c>
       <c r="G30" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H30" s="123"/>
+      <c r="H30" s="123">
+        <v>1</v>
+      </c>
       <c r="I30" s="107" t="str">
         <f>P32</f>
         <v>Costa do Marfim</v>
       </c>
       <c r="J30" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Alemanha</v>
       </c>
       <c r="K30" s="38" t="str">
         <f t="shared" si="1"/>
@@ -15932,7 +15968,7 @@
       </c>
       <c r="M30" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Costa do Marfim</v>
       </c>
       <c r="N30" s="46"/>
       <c r="O30" s="47">
@@ -15945,15 +15981,15 @@
       </c>
       <c r="Q30" s="38">
         <f>(S30*3)+(T30*1)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R30" s="38">
         <f>SUM(S30:U30)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S30" s="38">
         <f>COUNTIF(J:J,P30)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T30" s="38">
         <f>COUNTIF(K:K,P30)+COUNTIF(L:L,P30)</f>
@@ -15965,15 +16001,15 @@
       </c>
       <c r="V30" s="38">
         <f>SUMIF(E:E,P30,F:F)+SUMIF(I:I,P30,H:H)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W30" s="38">
         <f>SUMIF(E:E,P30,H:H)+SUMIF(I:I,P30,F:F)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X30" s="38">
         <f>V30-W30</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q30)*($X$30:$X$33&gt;X30))</f>
@@ -16004,15 +16040,15 @@
       </c>
       <c r="AG30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,6,FALSE)</f>
@@ -16024,15 +16060,15 @@
       </c>
       <c r="AL30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,8,FALSE)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AM30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,9,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN30" s="85">
         <f>VLOOKUP($AE30,$O$30:$X$33,10,FALSE)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ30" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,1))</f>
@@ -16062,11 +16098,15 @@
         <f>P33</f>
         <v>Equador</v>
       </c>
-      <c r="F31" s="123"/>
+      <c r="F31" s="123">
+        <v>0</v>
+      </c>
       <c r="G31" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H31" s="123"/>
+      <c r="H31" s="123">
+        <v>0</v>
+      </c>
       <c r="I31" s="107" t="str">
         <f>P31</f>
         <v>Curaçau</v>
@@ -16077,11 +16117,11 @@
       </c>
       <c r="K31" s="38" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Equador</v>
       </c>
       <c r="L31" s="38" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Curaçau</v>
       </c>
       <c r="M31" s="39" t="str">
         <f t="shared" si="3"/>
@@ -16098,11 +16138,11 @@
       </c>
       <c r="Q31" s="38">
         <f t="shared" ref="Q31:Q33" si="42">(S31*3)+(T31*1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="38">
         <f t="shared" ref="R31:R33" si="43">SUM(S31:U31)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S31" s="38">
         <f>COUNTIF(J:J,P31)</f>
@@ -16110,7 +16150,7 @@
       </c>
       <c r="T31" s="38">
         <f>COUNTIF(K:K,P31)+COUNTIF(L:L,P31)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" s="38">
         <f>COUNTIF(M:M,P31)</f>
@@ -16161,7 +16201,7 @@
       </c>
       <c r="AH31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,5,FALSE)</f>
@@ -16173,31 +16213,31 @@
       </c>
       <c r="AK31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,8,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,9,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN31" s="85">
         <f>VLOOKUP($AE31,$O$30:$X$33,10,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ31" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,2))</f>
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="AR31" s="15" t="str">
         <f t="shared" ref="AR31:AR37" si="45">_xlfn.CONCAT(3,AQ31)</f>
-        <v>3B</v>
+        <v>3C</v>
       </c>
       <c r="AS31" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Qatar</v>
+        <v>Escócia</v>
       </c>
     </row>
     <row r="32" spans="1:70" x14ac:dyDescent="0.25">
@@ -16255,7 +16295,7 @@
       </c>
       <c r="R32" s="38">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S32" s="38">
         <f>COUNTIF(J:J,P32)</f>
@@ -16267,23 +16307,23 @@
       </c>
       <c r="U32" s="38">
         <f>COUNTIF(M:M,P32)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="38">
         <f>SUMIF(E:E,P32,F:F)+SUMIF(I:I,P32,H:H)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W32" s="38">
         <f>SUMIF(E:E,P32,H:H)+SUMIF(I:I,P32,F:F)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X32" s="38">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q32)*($X$30:$X$33&gt;X32))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q32)*($X$30:$X$33=X32)*($V$30:$V$33&gt;V32))</f>
@@ -16310,11 +16350,11 @@
       </c>
       <c r="AG32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,5,FALSE)</f>
@@ -16322,7 +16362,7 @@
       </c>
       <c r="AJ32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,7,FALSE)</f>
@@ -16342,15 +16382,15 @@
       </c>
       <c r="AQ32" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,3))</f>
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="AR32" s="15" t="str">
         <f t="shared" si="45"/>
-        <v>3C</v>
+        <v>3D</v>
       </c>
       <c r="AS32" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Marrocos</v>
+        <v>Paraguai</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -16404,11 +16444,11 @@
       </c>
       <c r="Q33" s="53">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="53">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S33" s="38">
         <f>COUNTIF(J:J,P33)</f>
@@ -16416,7 +16456,7 @@
       </c>
       <c r="T33" s="38">
         <f>COUNTIF(K:K,P33)+COUNTIF(L:L,P33)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" s="38">
         <f>COUNTIF(M:M,P33)</f>
@@ -16463,11 +16503,11 @@
       </c>
       <c r="AG33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,5,FALSE)</f>
@@ -16475,7 +16515,7 @@
       </c>
       <c r="AJ33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,7,FALSE)</f>
@@ -16495,15 +16535,15 @@
       </c>
       <c r="AQ33" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,4))</f>
-        <v>E</v>
+        <v>F</v>
       </c>
       <c r="AR33" s="15" t="str">
         <f t="shared" si="45"/>
-        <v>3E</v>
+        <v>3F</v>
       </c>
       <c r="AS33" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Equador</v>
+        <v>Suécia</v>
       </c>
     </row>
     <row r="34" spans="1:45" x14ac:dyDescent="0.25">
@@ -16583,15 +16623,15 @@
       <c r="AN34" s="80"/>
       <c r="AQ34" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,5))</f>
-        <v>F</v>
+        <v>G</v>
       </c>
       <c r="AR34" s="15" t="str">
         <f t="shared" si="45"/>
-        <v>3F</v>
+        <v>3G</v>
       </c>
       <c r="AS34" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Japão</v>
+        <v>Bélgica</v>
       </c>
     </row>
     <row r="35" spans="1:45" x14ac:dyDescent="0.25">
@@ -16717,15 +16757,15 @@
       </c>
       <c r="AQ35" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,6))</f>
-        <v>G</v>
+        <v>H</v>
       </c>
       <c r="AR35" s="15" t="str">
         <f t="shared" si="45"/>
-        <v>3G</v>
+        <v>3H</v>
       </c>
       <c r="AS35" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Bélgica</v>
+        <v>Cabo Verde</v>
       </c>
     </row>
     <row r="36" spans="1:45" x14ac:dyDescent="0.25">
@@ -16743,18 +16783,22 @@
         <f>P36</f>
         <v>Países Baixos</v>
       </c>
-      <c r="F36" s="123"/>
+      <c r="F36" s="123">
+        <v>5</v>
+      </c>
       <c r="G36" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H36" s="123"/>
+      <c r="H36" s="123">
+        <v>1</v>
+      </c>
       <c r="I36" s="113" t="str">
         <f>P38</f>
         <v>Suécia</v>
       </c>
       <c r="J36" s="38" t="str">
         <f t="shared" ref="J36:J67" si="46">IF(F36=H36,"empate",IF(F36&gt;H36,E36,I36))</f>
-        <v>empate</v>
+        <v>Países Baixos</v>
       </c>
       <c r="K36" s="38" t="str">
         <f t="shared" ref="K36:K67" si="47">IF(F36="","",IF(H36="","",IF(J36="empate",E36,"")))</f>
@@ -16766,12 +16810,12 @@
       </c>
       <c r="M36" s="39" t="str">
         <f t="shared" ref="M36:M67" si="49">IF(F36=H36,"empate",IF(F36&lt;H36,E36,I36))</f>
-        <v>empate</v>
+        <v>Suécia</v>
       </c>
       <c r="N36" s="45"/>
       <c r="O36" s="47">
         <f>RANK(Q36,$Q$36:$Q$39)+SUM(Y36:AB36)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P36" s="49" t="str">
         <f>Sorteios!I14</f>
@@ -16779,15 +16823,15 @@
       </c>
       <c r="Q36" s="38">
         <f>(S36*3)+(T36*1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R36" s="38">
         <f>SUM(S36:U36)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S36" s="38">
         <f>COUNTIF(J:J,P36)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" s="38">
         <f>COUNTIF(K:K,P36)+COUNTIF(L:L,P36)</f>
@@ -16799,15 +16843,15 @@
       </c>
       <c r="V36" s="38">
         <f>SUMIF(E:E,P36,F:F)+SUMIF(I:I,P36,H:H)</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W36" s="38">
         <f>SUMIF(E:E,P36,H:H)+SUMIF(I:I,P36,F:F)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X36" s="38">
         <f>V36-W36</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y36" s="38">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q36)*($X$36:$X$39&gt;X36))</f>
@@ -16834,15 +16878,15 @@
       </c>
       <c r="AF36" s="83" t="str">
         <f>VLOOKUP($AE36,$O$36:$X$39,2,FALSE)</f>
-        <v>Suécia</v>
+        <v>Países Baixos</v>
       </c>
       <c r="AG36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,5,FALSE)</f>
@@ -16850,7 +16894,7 @@
       </c>
       <c r="AJ36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,7,FALSE)</f>
@@ -16858,11 +16902,11 @@
       </c>
       <c r="AL36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,8,FALSE)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,9,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN36" s="85">
         <f>VLOOKUP($AE36,$O$36:$X$39,10,FALSE)</f>
@@ -16870,15 +16914,15 @@
       </c>
       <c r="AQ36" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,7))</f>
-        <v>H</v>
+        <v>J</v>
       </c>
       <c r="AR36" s="15" t="str">
         <f t="shared" si="45"/>
-        <v>3H</v>
+        <v>3J</v>
       </c>
       <c r="AS36" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Espanha</v>
+        <v>Argélia</v>
       </c>
     </row>
     <row r="37" spans="1:45" x14ac:dyDescent="0.25">
@@ -16896,18 +16940,22 @@
         <f>P39</f>
         <v>Tunísia</v>
       </c>
-      <c r="F37" s="123"/>
+      <c r="F37" s="123">
+        <v>0</v>
+      </c>
       <c r="G37" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H37" s="123"/>
+      <c r="H37" s="123">
+        <v>4</v>
+      </c>
       <c r="I37" s="113" t="str">
         <f>P37</f>
         <v>Japão</v>
       </c>
       <c r="J37" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Japão</v>
       </c>
       <c r="K37" s="38" t="str">
         <f t="shared" si="47"/>
@@ -16919,12 +16967,12 @@
       </c>
       <c r="M37" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Tunísia</v>
       </c>
       <c r="N37" s="45"/>
       <c r="O37" s="47">
         <f>RANK(Q37,$Q$36:$Q$39)+SUM(Y37:AB37)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P37" s="49" t="str">
         <f>Sorteios!I15</f>
@@ -16932,15 +16980,15 @@
       </c>
       <c r="Q37" s="38">
         <f t="shared" ref="Q37:Q39" si="50">(S37*3)+(T37*1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R37" s="38">
         <f t="shared" ref="R37:R39" si="51">SUM(S37:U37)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S37" s="38">
         <f>COUNTIF(J:J,P37)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" s="38">
         <f>COUNTIF(K:K,P37)+COUNTIF(L:L,P37)</f>
@@ -16952,7 +17000,7 @@
       </c>
       <c r="V37" s="38">
         <f>SUMIF(E:E,P37,F:F)+SUMIF(I:I,P37,H:H)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W37" s="38">
         <f>SUMIF(E:E,P37,H:H)+SUMIF(I:I,P37,F:F)</f>
@@ -16960,7 +17008,7 @@
       </c>
       <c r="X37" s="38">
         <f t="shared" ref="X37:X39" si="52">V37-W37</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y37" s="38">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q37)*($X$36:$X$39&gt;X37))</f>
@@ -16968,7 +17016,7 @@
       </c>
       <c r="Z37" s="38">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q37)*($X$36:$X$39=X37)*($V$36:$V$39&gt;V37))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA37" s="38">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q37)*($X$36:$X$39=X37)*($V$36:$V$39=V37)*($W$36:$W$39&gt;W37))</f>
@@ -16976,7 +17024,7 @@
       </c>
       <c r="AB37" s="38">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q37)*($X$36:$X$39=X37)*($V$36:$V$39=V37)*($W$36:$W$39=W37)*($AC$36:$AC$39&lt;AC37))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC37" s="39">
         <v>2</v>
@@ -16987,19 +17035,19 @@
       </c>
       <c r="AF37" s="83" t="str">
         <f>VLOOKUP($AE37,$O$36:$X$39,2,FALSE)</f>
-        <v>Países Baixos</v>
+        <v>Japão</v>
       </c>
       <c r="AG37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,3,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,6,FALSE)</f>
@@ -17011,7 +17059,7 @@
       </c>
       <c r="AL37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,8,FALSE)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AM37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,9,FALSE)</f>
@@ -17019,19 +17067,19 @@
       </c>
       <c r="AN37" s="85">
         <f>VLOOKUP($AE37,$O$36:$X$39,10,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AQ37" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,8))</f>
-        <v>K</v>
+        <v>L</v>
       </c>
       <c r="AR37" s="15" t="str">
         <f t="shared" si="45"/>
-        <v>3K</v>
+        <v>3L</v>
       </c>
       <c r="AS37" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>RD Congo</v>
+        <v>Croácia</v>
       </c>
     </row>
     <row r="38" spans="1:45" x14ac:dyDescent="0.25">
@@ -17077,7 +17125,7 @@
       <c r="N38" s="45"/>
       <c r="O38" s="47">
         <f>RANK(Q38,$Q$36:$Q$39)+SUM(Y38:AB38)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P38" s="49" t="str">
         <f>Sorteios!I16</f>
@@ -17089,7 +17137,7 @@
       </c>
       <c r="R38" s="38">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S38" s="38">
         <f>COUNTIF(J:J,P38)</f>
@@ -17101,19 +17149,19 @@
       </c>
       <c r="U38" s="38">
         <f>COUNTIF(M:M,P38)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="38">
         <f>SUMIF(E:E,P38,F:F)+SUMIF(I:I,P38,H:H)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W38" s="38">
         <f>SUMIF(E:E,P38,H:H)+SUMIF(I:I,P38,F:F)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X38" s="38">
         <f t="shared" si="52"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y38" s="38">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q38)*($X$36:$X$39&gt;X38))</f>
@@ -17140,35 +17188,35 @@
       </c>
       <c r="AF38" s="83" t="str">
         <f>VLOOKUP($AE38,$O$36:$X$39,2,FALSE)</f>
-        <v>Japão</v>
+        <v>Suécia</v>
       </c>
       <c r="AG38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,3,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,6,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,8,FALSE)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AM38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,9,FALSE)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AN38" s="85">
         <f>VLOOKUP($AE38,$O$36:$X$39,10,FALSE)</f>
@@ -17230,7 +17278,7 @@
       </c>
       <c r="R39" s="53">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S39" s="38">
         <f>COUNTIF(J:J,P39)</f>
@@ -17242,7 +17290,7 @@
       </c>
       <c r="U39" s="38">
         <f>COUNTIF(M:M,P39)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V39" s="53">
         <f>SUMIF(E:E,P39,F:F)+SUMIF(I:I,P39,H:H)</f>
@@ -17250,11 +17298,11 @@
       </c>
       <c r="W39" s="53">
         <f>SUMIF(E:E,P39,H:H)+SUMIF(I:I,P39,F:F)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X39" s="53">
         <f t="shared" si="52"/>
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="Y39" s="53">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q39)*($X$36:$X$39&gt;X39))</f>
@@ -17289,7 +17337,7 @@
       </c>
       <c r="AH39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,5,FALSE)</f>
@@ -17301,7 +17349,7 @@
       </c>
       <c r="AK39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,8,FALSE)</f>
@@ -17309,19 +17357,19 @@
       </c>
       <c r="AM39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,9,FALSE)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AN39" s="88">
         <f>VLOOKUP($AE39,$O$36:$X$39,10,FALSE)</f>
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="AQ39" s="15" t="str">
         <f>_xlfn.CONCAT(AQ30:AQ37)</f>
-        <v>ABCEFGHK</v>
+        <v>ACDFGHJL</v>
       </c>
       <c r="AR39" s="15" t="str">
         <f>VLOOKUP(AQ39,Dummy!O:X,10,FALSE)</f>
-        <v>3H3G3B3C3A3F3E3K</v>
+        <v>3C3G3J3D3A3F3L3H</v>
       </c>
     </row>
     <row r="40" spans="1:45" x14ac:dyDescent="0.25">
@@ -17537,11 +17585,15 @@
         <f>P42</f>
         <v>Bélgica</v>
       </c>
-      <c r="F42" s="123"/>
+      <c r="F42" s="123">
+        <v>0</v>
+      </c>
       <c r="G42" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="123"/>
+      <c r="H42" s="123">
+        <v>0</v>
+      </c>
       <c r="I42" s="107" t="str">
         <f>P44</f>
         <v>Irã</v>
@@ -17552,11 +17604,11 @@
       </c>
       <c r="K42" s="38" t="str">
         <f t="shared" si="47"/>
-        <v/>
+        <v>Bélgica</v>
       </c>
       <c r="L42" s="38" t="str">
         <f t="shared" si="48"/>
-        <v/>
+        <v>Irã</v>
       </c>
       <c r="M42" s="39" t="str">
         <f t="shared" si="49"/>
@@ -17573,11 +17625,11 @@
       </c>
       <c r="Q42" s="38">
         <f>(S42*3)+(T42*1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42" s="38">
         <f>SUM(S42:U42)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S42" s="38">
         <f>COUNTIF(J:J,P42)</f>
@@ -17585,7 +17637,7 @@
       </c>
       <c r="T42" s="38">
         <f>COUNTIF(K:K,P42)+COUNTIF(L:L,P42)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U42" s="38">
         <f>COUNTIF(M:M,P42)</f>
@@ -17609,7 +17661,7 @@
       </c>
       <c r="Z42" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q42)*($X$42:$X$45=X42)*($V$42:$V$45&gt;V42))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA42" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q42)*($X$42:$X$45=X42)*($V$42:$V$45=V42)*($W$42:$W$45&gt;W42))</f>
@@ -17628,19 +17680,19 @@
       </c>
       <c r="AF42" s="83" t="str">
         <f>VLOOKUP($AE42,$O$42:$X$45,2,FALSE)</f>
-        <v>Irã</v>
+        <v>Egito</v>
       </c>
       <c r="AG42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,3,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,6,FALSE)</f>
@@ -17652,7 +17704,7 @@
       </c>
       <c r="AL42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,8,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,9,FALSE)</f>
@@ -17660,7 +17712,7 @@
       </c>
       <c r="AN42" s="85">
         <f>VLOOKUP($AE42,$O$42:$X$45,10,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:45" x14ac:dyDescent="0.25">
@@ -17678,18 +17730,22 @@
         <f>P45</f>
         <v>Nova Zelândia</v>
       </c>
-      <c r="F43" s="123"/>
+      <c r="F43" s="123">
+        <v>1</v>
+      </c>
       <c r="G43" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H43" s="123"/>
+      <c r="H43" s="123">
+        <v>3</v>
+      </c>
       <c r="I43" s="107" t="str">
         <f>P43</f>
         <v>Egito</v>
       </c>
       <c r="J43" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Egito</v>
       </c>
       <c r="K43" s="38" t="str">
         <f t="shared" si="47"/>
@@ -17701,12 +17757,12 @@
       </c>
       <c r="M43" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Nova Zelândia</v>
       </c>
       <c r="N43" s="46"/>
       <c r="O43" s="47">
         <f>RANK(Q43,$Q$42:$Q$45)+SUM(Y43:AB43)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P43" s="49" t="str">
         <f>Sorteios!C23</f>
@@ -17714,15 +17770,15 @@
       </c>
       <c r="Q43" s="38">
         <f t="shared" ref="Q43:Q45" si="53">(S43*3)+(T43*1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R43" s="38">
         <f t="shared" ref="R43:R45" si="54">SUM(S43:U43)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S43" s="38">
         <f>COUNTIF(J:J,P43)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" s="38">
         <f>COUNTIF(K:K,P43)+COUNTIF(L:L,P43)</f>
@@ -17734,15 +17790,15 @@
       </c>
       <c r="V43" s="38">
         <f>SUMIF(E:E,P43,F:F)+SUMIF(I:I,P43,H:H)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W43" s="38">
         <f>SUMIF(E:E,P43,H:H)+SUMIF(I:I,P43,F:F)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X43" s="38">
         <f t="shared" ref="X43:X45" si="55">V43-W43</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y43" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q43)*($X$42:$X$45&gt;X43))</f>
@@ -17750,7 +17806,7 @@
       </c>
       <c r="Z43" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q43)*($X$42:$X$45=X43)*($V$42:$V$45&gt;V43))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q43)*($X$42:$X$45=X43)*($V$42:$V$45=V43)*($W$42:$W$45&gt;W43))</f>
@@ -17758,7 +17814,7 @@
       </c>
       <c r="AB43" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q43)*($X$42:$X$45=X43)*($V$42:$V$45=V43)*($W$42:$W$45=W43)*($AC$42:$AC$45&lt;AC43))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC43" s="39">
         <v>2</v>
@@ -17769,15 +17825,15 @@
       </c>
       <c r="AF43" s="83" t="str">
         <f>VLOOKUP($AE43,$O$42:$X$45,2,FALSE)</f>
-        <v>Nova Zelândia</v>
+        <v>Irã</v>
       </c>
       <c r="AG43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,5,FALSE)</f>
@@ -17785,7 +17841,7 @@
       </c>
       <c r="AJ43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,7,FALSE)</f>
@@ -17847,7 +17903,7 @@
       <c r="N44" s="46"/>
       <c r="O44" s="47">
         <f>RANK(Q44,$Q$42:$Q$45)+SUM(Y44:AB44)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P44" s="49" t="str">
         <f>Sorteios!C24</f>
@@ -17855,11 +17911,11 @@
       </c>
       <c r="Q44" s="38">
         <f t="shared" si="53"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R44" s="38">
         <f t="shared" si="54"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S44" s="38">
         <f>COUNTIF(J:J,P44)</f>
@@ -17867,7 +17923,7 @@
       </c>
       <c r="T44" s="38">
         <f>COUNTIF(K:K,P44)+COUNTIF(L:L,P44)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U44" s="38">
         <f>COUNTIF(M:M,P44)</f>
@@ -17914,11 +17970,11 @@
       </c>
       <c r="AG44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,5,FALSE)</f>
@@ -17926,7 +17982,7 @@
       </c>
       <c r="AJ44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,7,FALSE)</f>
@@ -17988,7 +18044,7 @@
       <c r="N45" s="55"/>
       <c r="O45" s="56">
         <f>RANK(Q45,$Q$42:$Q$45)+SUM(Y45:AB45)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P45" s="49" t="str">
         <f>Sorteios!C25</f>
@@ -18000,7 +18056,7 @@
       </c>
       <c r="R45" s="53">
         <f t="shared" si="54"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S45" s="38">
         <f>COUNTIF(J:J,P45)</f>
@@ -18012,19 +18068,19 @@
       </c>
       <c r="U45" s="38">
         <f>COUNTIF(M:M,P45)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="53">
         <f>SUMIF(E:E,P45,F:F)+SUMIF(I:I,P45,H:H)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W45" s="53">
         <f>SUMIF(E:E,P45,H:H)+SUMIF(I:I,P45,F:F)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X45" s="53">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Y45" s="53">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q45)*($X$42:$X$45&gt;X45))</f>
@@ -18040,7 +18096,7 @@
       </c>
       <c r="AB45" s="53">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q45)*($X$42:$X$45=X45)*($V$42:$V$45=V45)*($W$42:$W$45=W45)*($AC$42:$AC$45&lt;AC45))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC45" s="54">
         <v>4</v>
@@ -18051,7 +18107,7 @@
       </c>
       <c r="AF45" s="86" t="str">
         <f>VLOOKUP($AE45,$O$42:$X$45,2,FALSE)</f>
-        <v>Egito</v>
+        <v>Nova Zelândia</v>
       </c>
       <c r="AG45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,3,FALSE)</f>
@@ -18059,7 +18115,7 @@
       </c>
       <c r="AH45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,5,FALSE)</f>
@@ -18071,19 +18127,19 @@
       </c>
       <c r="AK45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,8,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,9,FALSE)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN45" s="88">
         <f>VLOOKUP($AE45,$O$42:$X$45,10,FALSE)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="46" spans="1:45" x14ac:dyDescent="0.25">
@@ -18299,18 +18355,22 @@
         <f>P48</f>
         <v>Espanha</v>
       </c>
-      <c r="F48" s="123"/>
+      <c r="F48" s="123">
+        <v>4</v>
+      </c>
       <c r="G48" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H48" s="123"/>
+      <c r="H48" s="123">
+        <v>0</v>
+      </c>
       <c r="I48" s="113" t="str">
         <f>P50</f>
         <v>Arábia Saudita</v>
       </c>
       <c r="J48" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Espanha</v>
       </c>
       <c r="K48" s="38" t="str">
         <f t="shared" si="47"/>
@@ -18322,12 +18382,12 @@
       </c>
       <c r="M48" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Arábia Saudita</v>
       </c>
       <c r="N48" s="45"/>
       <c r="O48" s="47">
         <f>RANK(Q48,$Q$48:$Q$51)+SUM(Y48:AB48)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P48" s="49" t="str">
         <f>Sorteios!F22</f>
@@ -18335,15 +18395,15 @@
       </c>
       <c r="Q48" s="38">
         <f>(S48*3)+(T48*1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R48" s="38">
         <f>SUM(S48:U48)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S48" s="38">
         <f>COUNTIF(J:J,P48)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="38">
         <f>COUNTIF(K:K,P48)+COUNTIF(L:L,P48)</f>
@@ -18355,7 +18415,7 @@
       </c>
       <c r="V48" s="38">
         <f>SUMIF(E:E,P48,F:F)+SUMIF(I:I,P48,H:H)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W48" s="38">
         <f>SUMIF(E:E,P48,H:H)+SUMIF(I:I,P48,F:F)</f>
@@ -18363,7 +18423,7 @@
       </c>
       <c r="X48" s="38">
         <f>V48-W48</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y48" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q48)*($X$48:$X$51&gt;X48))</f>
@@ -18371,7 +18431,7 @@
       </c>
       <c r="Z48" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q48)*($X$48:$X$51=X48)*($V$48:$V$51&gt;V48))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA48" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q48)*($X$48:$X$51=X48)*($V$48:$V$51=V48)*($W$48:$W$51&gt;W48))</f>
@@ -18390,19 +18450,19 @@
       </c>
       <c r="AF48" s="83" t="str">
         <f>VLOOKUP($AE48,$O$48:$X$51,2,FALSE)</f>
-        <v>Arábia Saudita</v>
+        <v>Espanha</v>
       </c>
       <c r="AG48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,3,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,6,FALSE)</f>
@@ -18414,15 +18474,15 @@
       </c>
       <c r="AL48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,8,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AM48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,9,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN48" s="85">
         <f>VLOOKUP($AE48,$O$48:$X$51,10,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:40" x14ac:dyDescent="0.25">
@@ -18440,11 +18500,15 @@
         <f>P51</f>
         <v>Uruguai</v>
       </c>
-      <c r="F49" s="123"/>
+      <c r="F49" s="123">
+        <v>2</v>
+      </c>
       <c r="G49" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H49" s="123"/>
+      <c r="H49" s="123">
+        <v>2</v>
+      </c>
       <c r="I49" s="113" t="str">
         <f>P49</f>
         <v>Cabo Verde</v>
@@ -18455,11 +18519,11 @@
       </c>
       <c r="K49" s="38" t="str">
         <f t="shared" si="47"/>
-        <v/>
+        <v>Uruguai</v>
       </c>
       <c r="L49" s="38" t="str">
         <f t="shared" si="48"/>
-        <v/>
+        <v>Cabo Verde</v>
       </c>
       <c r="M49" s="39" t="str">
         <f t="shared" si="49"/>
@@ -18468,7 +18532,7 @@
       <c r="N49" s="45"/>
       <c r="O49" s="47">
         <f>RANK(Q49,$Q$48:$Q$51)+SUM(Y49:AB49)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P49" s="49" t="str">
         <f>Sorteios!F23</f>
@@ -18476,11 +18540,11 @@
       </c>
       <c r="Q49" s="38">
         <f t="shared" ref="Q49:Q51" si="56">(S49*3)+(T49*1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R49" s="38">
         <f t="shared" ref="R49:R51" si="57">SUM(S49:U49)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S49" s="38">
         <f>COUNTIF(J:J,P49)</f>
@@ -18488,7 +18552,7 @@
       </c>
       <c r="T49" s="38">
         <f>COUNTIF(K:K,P49)+COUNTIF(L:L,P49)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U49" s="38">
         <f>COUNTIF(M:M,P49)</f>
@@ -18496,11 +18560,11 @@
       </c>
       <c r="V49" s="38">
         <f>SUMIF(E:E,P49,F:F)+SUMIF(I:I,P49,H:H)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W49" s="38">
         <f>SUMIF(E:E,P49,H:H)+SUMIF(I:I,P49,F:F)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X49" s="38">
         <f t="shared" ref="X49:X51" si="58">V49-W49</f>
@@ -18512,7 +18576,7 @@
       </c>
       <c r="Z49" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q49)*($X$48:$X$51=X49)*($V$48:$V$51&gt;V49))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA49" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q49)*($X$48:$X$51=X49)*($V$48:$V$51=V49)*($W$48:$W$51&gt;W49))</f>
@@ -18520,7 +18584,7 @@
       </c>
       <c r="AB49" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q49)*($X$48:$X$51=X49)*($V$48:$V$51=V49)*($W$48:$W$51=W49)*($AC$48:$AC$51&lt;AC49))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC49" s="39">
         <v>2</v>
@@ -18535,11 +18599,11 @@
       </c>
       <c r="AG49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,5,FALSE)</f>
@@ -18547,7 +18611,7 @@
       </c>
       <c r="AJ49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,7,FALSE)</f>
@@ -18555,11 +18619,11 @@
       </c>
       <c r="AL49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,8,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,9,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN49" s="85">
         <f>VLOOKUP($AE49,$O$48:$X$51,10,FALSE)</f>
@@ -18609,7 +18673,7 @@
       <c r="N50" s="45"/>
       <c r="O50" s="47">
         <f>RANK(Q50,$Q$48:$Q$51)+SUM(Y50:AB50)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P50" s="49" t="str">
         <f>Sorteios!F24</f>
@@ -18621,7 +18685,7 @@
       </c>
       <c r="R50" s="38">
         <f t="shared" si="57"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S50" s="38">
         <f>COUNTIF(J:J,P50)</f>
@@ -18633,7 +18697,7 @@
       </c>
       <c r="U50" s="38">
         <f>COUNTIF(M:M,P50)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V50" s="38">
         <f>SUMIF(E:E,P50,F:F)+SUMIF(I:I,P50,H:H)</f>
@@ -18641,11 +18705,11 @@
       </c>
       <c r="W50" s="38">
         <f>SUMIF(E:E,P50,H:H)+SUMIF(I:I,P50,F:F)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X50" s="38">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="Y50" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q50)*($X$48:$X$51&gt;X50))</f>
@@ -18672,15 +18736,15 @@
       </c>
       <c r="AF50" s="83" t="str">
         <f>VLOOKUP($AE50,$O$48:$X$51,2,FALSE)</f>
-        <v>Espanha</v>
+        <v>Cabo Verde</v>
       </c>
       <c r="AG50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,5,FALSE)</f>
@@ -18688,7 +18752,7 @@
       </c>
       <c r="AJ50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,7,FALSE)</f>
@@ -18696,11 +18760,11 @@
       </c>
       <c r="AL50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,9,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN50" s="85">
         <f>VLOOKUP($AE50,$O$48:$X$51,10,FALSE)</f>
@@ -18758,11 +18822,11 @@
       </c>
       <c r="Q51" s="53">
         <f t="shared" si="56"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R51" s="53">
         <f t="shared" si="57"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S51" s="38">
         <f>COUNTIF(J:J,P51)</f>
@@ -18770,7 +18834,7 @@
       </c>
       <c r="T51" s="38">
         <f>COUNTIF(K:K,P51)+COUNTIF(L:L,P51)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U51" s="38">
         <f>COUNTIF(M:M,P51)</f>
@@ -18778,11 +18842,11 @@
       </c>
       <c r="V51" s="53">
         <f>SUMIF(E:E,P51,F:F)+SUMIF(I:I,P51,H:H)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W51" s="53">
         <f>SUMIF(E:E,P51,H:H)+SUMIF(I:I,P51,F:F)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X51" s="53">
         <f t="shared" si="58"/>
@@ -18802,7 +18866,7 @@
       </c>
       <c r="AB51" s="53">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q51)*($X$48:$X$51=X51)*($V$48:$V$51=V51)*($W$48:$W$51=W51)*($AC$48:$AC$51&lt;AC51))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC51" s="54">
         <v>4</v>
@@ -18813,7 +18877,7 @@
       </c>
       <c r="AF51" s="86" t="str">
         <f>VLOOKUP($AE51,$O$48:$X$51,2,FALSE)</f>
-        <v>Cabo Verde</v>
+        <v>Arábia Saudita</v>
       </c>
       <c r="AG51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,3,FALSE)</f>
@@ -18821,7 +18885,7 @@
       </c>
       <c r="AH51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,5,FALSE)</f>
@@ -18833,19 +18897,19 @@
       </c>
       <c r="AK51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,9,FALSE)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN51" s="88">
         <f>VLOOKUP($AE51,$O$48:$X$51,10,FALSE)</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="52" spans="1:40" x14ac:dyDescent="0.25">
@@ -19061,18 +19125,22 @@
         <f>P54</f>
         <v>França</v>
       </c>
-      <c r="F54" s="123"/>
+      <c r="F54" s="123">
+        <v>3</v>
+      </c>
       <c r="G54" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H54" s="123"/>
+      <c r="H54" s="123">
+        <v>0</v>
+      </c>
       <c r="I54" s="107" t="str">
         <f>P56</f>
         <v>Iraque</v>
       </c>
       <c r="J54" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>França</v>
       </c>
       <c r="K54" s="38" t="str">
         <f t="shared" si="47"/>
@@ -19084,12 +19152,12 @@
       </c>
       <c r="M54" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Iraque</v>
       </c>
       <c r="N54" s="46"/>
       <c r="O54" s="47">
         <f>RANK(Q54,$Q$54:$Q$57)+SUM(Y54:AB54)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P54" s="49" t="str">
         <f>Sorteios!I22</f>
@@ -19097,15 +19165,15 @@
       </c>
       <c r="Q54" s="38">
         <f>(S54*3)+(T54*1)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R54" s="38">
         <f>SUM(S54:U54)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S54" s="38">
         <f>COUNTIF(J:J,P54)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T54" s="38">
         <f>COUNTIF(K:K,P54)+COUNTIF(L:L,P54)</f>
@@ -19117,7 +19185,7 @@
       </c>
       <c r="V54" s="38">
         <f>SUMIF(E:E,P54,F:F)+SUMIF(I:I,P54,H:H)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W54" s="38">
         <f>SUMIF(E:E,P54,H:H)+SUMIF(I:I,P54,F:F)</f>
@@ -19125,11 +19193,11 @@
       </c>
       <c r="X54" s="38">
         <f>V54-W54</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y54" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q54)*($X$54:$X$57&gt;X54))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z54" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q54)*($X$54:$X$57=X54)*($V$54:$V$57&gt;V54))</f>
@@ -19152,19 +19220,19 @@
       </c>
       <c r="AF54" s="83" t="str">
         <f>VLOOKUP($AE54,$O$54:$X$57,2,FALSE)</f>
-        <v>Noruega</v>
+        <v>França</v>
       </c>
       <c r="AG54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,6,FALSE)</f>
@@ -19176,7 +19244,7 @@
       </c>
       <c r="AL54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,8,FALSE)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,9,FALSE)</f>
@@ -19184,7 +19252,7 @@
       </c>
       <c r="AN54" s="85">
         <f>VLOOKUP($AE54,$O$54:$X$57,10,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:40" x14ac:dyDescent="0.25">
@@ -19202,18 +19270,22 @@
         <f>P57</f>
         <v>Noruega</v>
       </c>
-      <c r="F55" s="123"/>
+      <c r="F55" s="123">
+        <v>3</v>
+      </c>
       <c r="G55" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H55" s="123"/>
+      <c r="H55" s="123">
+        <v>2</v>
+      </c>
       <c r="I55" s="107" t="str">
         <f>P55</f>
         <v>Senegal</v>
       </c>
       <c r="J55" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Noruega</v>
       </c>
       <c r="K55" s="38" t="str">
         <f t="shared" si="47"/>
@@ -19225,7 +19297,7 @@
       </c>
       <c r="M55" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Senegal</v>
       </c>
       <c r="N55" s="46"/>
       <c r="O55" s="47">
@@ -19242,7 +19314,7 @@
       </c>
       <c r="R55" s="38">
         <f t="shared" ref="R55:R57" si="60">SUM(S55:U55)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S55" s="38">
         <f>COUNTIF(J:J,P55)</f>
@@ -19254,19 +19326,19 @@
       </c>
       <c r="U55" s="38">
         <f>COUNTIF(M:M,P55)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V55" s="38">
         <f>SUMIF(E:E,P55,F:F)+SUMIF(I:I,P55,H:H)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W55" s="38">
         <f>SUMIF(E:E,P55,H:H)+SUMIF(I:I,P55,F:F)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X55" s="38">
         <f t="shared" ref="X55:X57" si="61">V55-W55</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="Y55" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q55)*($X$54:$X$57&gt;X55))</f>
@@ -19293,19 +19365,19 @@
       </c>
       <c r="AF55" s="83" t="str">
         <f>VLOOKUP($AE55,$O$54:$X$57,2,FALSE)</f>
-        <v>França</v>
+        <v>Noruega</v>
       </c>
       <c r="AG55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,6,FALSE)</f>
@@ -19317,15 +19389,15 @@
       </c>
       <c r="AL55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,8,FALSE)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AM55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,9,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN55" s="85">
         <f>VLOOKUP($AE55,$O$54:$X$57,10,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:40" x14ac:dyDescent="0.25">
@@ -19383,7 +19455,7 @@
       </c>
       <c r="R56" s="38">
         <f t="shared" si="60"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S56" s="38">
         <f>COUNTIF(J:J,P56)</f>
@@ -19395,7 +19467,7 @@
       </c>
       <c r="U56" s="38">
         <f>COUNTIF(M:M,P56)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V56" s="38">
         <f>SUMIF(E:E,P56,F:F)+SUMIF(I:I,P56,H:H)</f>
@@ -19403,11 +19475,11 @@
       </c>
       <c r="W56" s="38">
         <f>SUMIF(E:E,P56,H:H)+SUMIF(I:I,P56,F:F)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X56" s="38">
         <f t="shared" si="61"/>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="Y56" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q56)*($X$54:$X$57&gt;X56))</f>
@@ -19442,7 +19514,7 @@
       </c>
       <c r="AH56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,5,FALSE)</f>
@@ -19454,19 +19526,19 @@
       </c>
       <c r="AK56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,8,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,9,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN56" s="85">
         <f>VLOOKUP($AE56,$O$54:$X$57,10,FALSE)</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="57" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19512,7 +19584,7 @@
       <c r="N57" s="55"/>
       <c r="O57" s="47">
         <f>RANK(Q57,$Q$54:$Q$57)+SUM(Y57:AB57)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P57" s="69" t="str">
         <f>Sorteios!I25</f>
@@ -19520,15 +19592,15 @@
       </c>
       <c r="Q57" s="66">
         <f t="shared" si="59"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R57" s="66">
         <f t="shared" si="60"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S57" s="66">
         <f>COUNTIF(J:J,P57)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T57" s="66">
         <f>COUNTIF(K:K,P57)+COUNTIF(L:L,P57)</f>
@@ -19540,19 +19612,19 @@
       </c>
       <c r="V57" s="66">
         <f>SUMIF(E:E,P57,F:F)+SUMIF(I:I,P57,H:H)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W57" s="66">
         <f>SUMIF(E:E,P57,H:H)+SUMIF(I:I,P57,F:F)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X57" s="66">
         <f t="shared" si="61"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y57" s="66">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q57)*($X$54:$X$57&gt;X57))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z57" s="66">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q57)*($X$54:$X$57=X57)*($V$54:$V$57&gt;V57))</f>
@@ -19583,7 +19655,7 @@
       </c>
       <c r="AH57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,5,FALSE)</f>
@@ -19595,7 +19667,7 @@
       </c>
       <c r="AK57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,8,FALSE)</f>
@@ -19603,11 +19675,11 @@
       </c>
       <c r="AM57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,9,FALSE)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AN57" s="88">
         <f>VLOOKUP($AE57,$O$54:$X$57,10,FALSE)</f>
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="58" spans="1:40" x14ac:dyDescent="0.25">
@@ -19823,18 +19895,22 @@
         <f>P60</f>
         <v>Argentina</v>
       </c>
-      <c r="F60" s="123"/>
+      <c r="F60" s="123">
+        <v>2</v>
+      </c>
       <c r="G60" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H60" s="123"/>
+      <c r="H60" s="123">
+        <v>0</v>
+      </c>
       <c r="I60" s="113" t="str">
         <f>P62</f>
         <v>Áustria</v>
       </c>
       <c r="J60" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Argentina</v>
       </c>
       <c r="K60" s="38" t="str">
         <f t="shared" si="47"/>
@@ -19846,7 +19922,7 @@
       </c>
       <c r="M60" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Áustria</v>
       </c>
       <c r="N60" s="45"/>
       <c r="O60" s="47">
@@ -19859,15 +19935,15 @@
       </c>
       <c r="Q60" s="38">
         <f>(S60*3)+(T60*1)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R60" s="38">
         <f>SUM(S60:U60)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S60" s="38">
         <f>COUNTIF(J:J,P60)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T60" s="38">
         <f>COUNTIF(K:K,P60)+COUNTIF(L:L,P60)</f>
@@ -19879,7 +19955,7 @@
       </c>
       <c r="V60" s="38">
         <f>SUMIF(E:E,P60,F:F)+SUMIF(I:I,P60,H:H)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W60" s="38">
         <f>SUMIF(E:E,P60,H:H)+SUMIF(I:I,P60,F:F)</f>
@@ -19887,7 +19963,7 @@
       </c>
       <c r="X60" s="38">
         <f>V60-W60</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y60" s="38">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q60)*($X$60:$X$63&gt;X60))</f>
@@ -19918,15 +19994,15 @@
       </c>
       <c r="AG60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,6,FALSE)</f>
@@ -19938,7 +20014,7 @@
       </c>
       <c r="AL60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,8,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,9,FALSE)</f>
@@ -19946,7 +20022,7 @@
       </c>
       <c r="AN60" s="85">
         <f>VLOOKUP($AE60,$O$60:$X$63,10,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:40" x14ac:dyDescent="0.25">
@@ -19964,18 +20040,22 @@
         <f>P63</f>
         <v>Jordânia</v>
       </c>
-      <c r="F61" s="123"/>
+      <c r="F61" s="123">
+        <v>1</v>
+      </c>
       <c r="G61" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H61" s="123"/>
+      <c r="H61" s="123">
+        <v>2</v>
+      </c>
       <c r="I61" s="113" t="str">
         <f>P61</f>
         <v>Argélia</v>
       </c>
       <c r="J61" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Argélia</v>
       </c>
       <c r="K61" s="38" t="str">
         <f t="shared" si="47"/>
@@ -19987,12 +20067,12 @@
       </c>
       <c r="M61" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Jordânia</v>
       </c>
       <c r="N61" s="45"/>
       <c r="O61" s="47">
         <f>RANK(Q61,$Q$60:$Q$63)+SUM(Y61:AB61)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P61" s="49" t="str">
         <f>Sorteios!C31</f>
@@ -20000,15 +20080,15 @@
       </c>
       <c r="Q61" s="38">
         <f t="shared" ref="Q61:Q63" si="62">(S61*3)+(T61*1)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R61" s="38">
         <f t="shared" ref="R61:R63" si="63">SUM(S61:U61)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S61" s="38">
         <f>COUNTIF(J:J,P61)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="38">
         <f>COUNTIF(K:K,P61)+COUNTIF(L:L,P61)</f>
@@ -20020,15 +20100,15 @@
       </c>
       <c r="V61" s="38">
         <f>SUMIF(E:E,P61,F:F)+SUMIF(I:I,P61,H:H)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W61" s="38">
         <f>SUMIF(E:E,P61,H:H)+SUMIF(I:I,P61,F:F)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X61" s="38">
         <f t="shared" ref="X61:X63" si="64">V61-W61</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="Y61" s="38">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q61)*($X$60:$X$63&gt;X61))</f>
@@ -20063,7 +20143,7 @@
       </c>
       <c r="AH61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,5,FALSE)</f>
@@ -20075,7 +20155,7 @@
       </c>
       <c r="AK61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,8,FALSE)</f>
@@ -20083,11 +20163,11 @@
       </c>
       <c r="AM61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,9,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN61" s="85">
         <f>VLOOKUP($AE61,$O$60:$X$63,10,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:40" x14ac:dyDescent="0.25">
@@ -20145,7 +20225,7 @@
       </c>
       <c r="R62" s="38">
         <f>SUM(S62:U62)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S62" s="38">
         <f>COUNTIF(J:J,P62)</f>
@@ -20157,7 +20237,7 @@
       </c>
       <c r="U62" s="38">
         <f>COUNTIF(M:M,P62)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V62" s="38">
         <f>SUMIF(E:E,P62,F:F)+SUMIF(I:I,P62,H:H)</f>
@@ -20165,15 +20245,15 @@
       </c>
       <c r="W62" s="38">
         <f>SUMIF(E:E,P62,H:H)+SUMIF(I:I,P62,F:F)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X62" s="38">
         <f>V62-W62</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y62" s="38">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q62)*($X$60:$X$63&gt;X62))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="38">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q62)*($X$60:$X$63=X62)*($V$60:$V$63&gt;V62))</f>
@@ -20196,19 +20276,19 @@
       </c>
       <c r="AF62" s="83" t="str">
         <f>VLOOKUP($AE62,$O$60:$X$63,2,FALSE)</f>
-        <v>Jordânia</v>
+        <v>Argélia</v>
       </c>
       <c r="AG62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,6,FALSE)</f>
@@ -20220,11 +20300,11 @@
       </c>
       <c r="AL62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,8,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,9,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN62" s="85">
         <f>VLOOKUP($AE62,$O$60:$X$63,10,FALSE)</f>
@@ -20274,7 +20354,7 @@
       <c r="N63" s="45"/>
       <c r="O63" s="68">
         <f>RANK(Q63,$Q$60:$Q$63)+SUM(Y63:AB63)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P63" s="49" t="str">
         <f>Sorteios!C33</f>
@@ -20286,7 +20366,7 @@
       </c>
       <c r="R63" s="53">
         <f t="shared" si="63"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S63" s="38">
         <f>COUNTIF(J:J,P63)</f>
@@ -20298,19 +20378,19 @@
       </c>
       <c r="U63" s="38">
         <f>COUNTIF(M:M,P63)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V63" s="53">
         <f>SUMIF(E:E,P63,F:F)+SUMIF(I:I,P63,H:H)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W63" s="53">
         <f>SUMIF(E:E,P63,H:H)+SUMIF(I:I,P63,F:F)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X63" s="53">
         <f t="shared" si="64"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="Y63" s="53">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q63)*($X$60:$X$63&gt;X63))</f>
@@ -20337,7 +20417,7 @@
       </c>
       <c r="AF63" s="86" t="str">
         <f>VLOOKUP($AE63,$O$60:$X$63,2,FALSE)</f>
-        <v>Argélia</v>
+        <v>Jordânia</v>
       </c>
       <c r="AG63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,3,FALSE)</f>
@@ -20345,7 +20425,7 @@
       </c>
       <c r="AH63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,5,FALSE)</f>
@@ -20357,15 +20437,15 @@
       </c>
       <c r="AK63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,9,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN63" s="88">
         <f>VLOOKUP($AE63,$O$60:$X$63,10,FALSE)</f>
@@ -20585,18 +20665,22 @@
         <f>P66</f>
         <v>Portugal</v>
       </c>
-      <c r="F66" s="123"/>
+      <c r="F66" s="123">
+        <v>5</v>
+      </c>
       <c r="G66" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H66" s="123"/>
+      <c r="H66" s="123">
+        <v>0</v>
+      </c>
       <c r="I66" s="107" t="str">
         <f>P68</f>
         <v>Uzbequistão</v>
       </c>
       <c r="J66" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Portugal</v>
       </c>
       <c r="K66" s="38" t="str">
         <f t="shared" si="47"/>
@@ -20608,7 +20692,7 @@
       </c>
       <c r="M66" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Uzbequistão</v>
       </c>
       <c r="N66" s="46"/>
       <c r="O66" s="47">
@@ -20621,15 +20705,15 @@
       </c>
       <c r="Q66" s="38">
         <f>(S66*3)+(T66*1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R66" s="38">
         <f>SUM(S66:U66)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S66" s="38">
         <f>COUNTIF(J:J,P66)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="38">
         <f>COUNTIF(K:K,P66)+COUNTIF(L:L,P66)</f>
@@ -20641,7 +20725,7 @@
       </c>
       <c r="V66" s="38">
         <f>SUMIF(E:E,P66,F:F)+SUMIF(I:I,P66,H:H)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W66" s="38">
         <f>SUMIF(E:E,P66,H:H)+SUMIF(I:I,P66,F:F)</f>
@@ -20649,7 +20733,7 @@
       </c>
       <c r="X66" s="38">
         <f>V66-W66</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y66" s="38">
         <f>SUMPRODUCT(($Q$66:$Q$69=Q66)*($X$66:$X$69&gt;X66))</f>
@@ -20680,15 +20764,15 @@
       </c>
       <c r="AG66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,6,FALSE)</f>
@@ -20700,7 +20784,7 @@
       </c>
       <c r="AL66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,8,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,9,FALSE)</f>
@@ -20708,7 +20792,7 @@
       </c>
       <c r="AN66" s="85">
         <f>VLOOKUP($AE66,$O$66:$X$69,10,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:40" x14ac:dyDescent="0.25">
@@ -20726,18 +20810,22 @@
         <f>P69</f>
         <v>Colômbia</v>
       </c>
-      <c r="F67" s="123"/>
+      <c r="F67" s="123">
+        <v>1</v>
+      </c>
       <c r="G67" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H67" s="123"/>
+      <c r="H67" s="123">
+        <v>0</v>
+      </c>
       <c r="I67" s="107" t="str">
         <f>P67</f>
         <v>RD Congo</v>
       </c>
       <c r="J67" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Colômbia</v>
       </c>
       <c r="K67" s="38" t="str">
         <f t="shared" si="47"/>
@@ -20749,7 +20837,7 @@
       </c>
       <c r="M67" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>RD Congo</v>
       </c>
       <c r="N67" s="46"/>
       <c r="O67" s="47">
@@ -20766,7 +20854,7 @@
       </c>
       <c r="R67" s="38">
         <f t="shared" ref="R67:R69" si="66">SUM(S67:U67)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S67" s="38">
         <f>COUNTIF(J:J,P67)</f>
@@ -20778,7 +20866,7 @@
       </c>
       <c r="U67" s="38">
         <f>COUNTIF(M:M,P67)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V67" s="38">
         <f>SUMIF(E:E,P67,F:F)+SUMIF(I:I,P67,H:H)</f>
@@ -20786,11 +20874,11 @@
       </c>
       <c r="W67" s="38">
         <f>SUMIF(E:E,P67,H:H)+SUMIF(I:I,P67,F:F)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X67" s="38">
         <f t="shared" ref="X67:X69" si="67">V67-W67</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y67" s="38">
         <f>SUMPRODUCT(($Q$66:$Q$69=Q67)*($X$66:$X$69&gt;X67))</f>
@@ -20806,7 +20894,7 @@
       </c>
       <c r="AB67" s="38">
         <f>SUMPRODUCT(($Q$66:$Q$69=Q67)*($X$66:$X$69=X67)*($V$66:$V$69=V67)*($W$66:$W$69=W67)*($AC$66:$AC$69&lt;AC67))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC67" s="39">
         <v>2</v>
@@ -20821,15 +20909,15 @@
       </c>
       <c r="AG67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,3,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,6,FALSE)</f>
@@ -20841,7 +20929,7 @@
       </c>
       <c r="AL67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,8,FALSE)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AM67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,9,FALSE)</f>
@@ -20849,7 +20937,7 @@
       </c>
       <c r="AN67" s="85">
         <f>VLOOKUP($AE67,$O$66:$X$69,10,FALSE)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:40" x14ac:dyDescent="0.25">
@@ -20907,7 +20995,7 @@
       </c>
       <c r="R68" s="38">
         <f t="shared" si="66"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S68" s="38">
         <f>COUNTIF(J:J,P68)</f>
@@ -20919,7 +21007,7 @@
       </c>
       <c r="U68" s="38">
         <f>COUNTIF(M:M,P68)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V68" s="38">
         <f>SUMIF(E:E,P68,F:F)+SUMIF(I:I,P68,H:H)</f>
@@ -20927,11 +21015,11 @@
       </c>
       <c r="W68" s="38">
         <f>SUMIF(E:E,P68,H:H)+SUMIF(I:I,P68,F:F)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X68" s="38">
         <f t="shared" si="67"/>
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="Y68" s="38">
         <f>SUMPRODUCT(($Q$66:$Q$69=Q68)*($X$66:$X$69&gt;X68))</f>
@@ -20966,7 +21054,7 @@
       </c>
       <c r="AH68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,5,FALSE)</f>
@@ -20978,7 +21066,7 @@
       </c>
       <c r="AK68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,8,FALSE)</f>
@@ -20986,11 +21074,11 @@
       </c>
       <c r="AM68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,9,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN68" s="85">
         <f>VLOOKUP($AE68,$O$66:$X$69,10,FALSE)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -21044,15 +21132,15 @@
       </c>
       <c r="Q69" s="53">
         <f t="shared" si="65"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R69" s="53">
         <f t="shared" si="66"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S69" s="53">
         <f>COUNTIF(J:J,P69)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T69" s="53">
         <f>COUNTIF(K:K,P69)+COUNTIF(L:L,P69)</f>
@@ -21064,7 +21152,7 @@
       </c>
       <c r="V69" s="53">
         <f>SUMIF(E:E,P69,F:F)+SUMIF(I:I,P69,H:H)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W69" s="53">
         <f>SUMIF(E:E,P69,H:H)+SUMIF(I:I,P69,F:F)</f>
@@ -21072,7 +21160,7 @@
       </c>
       <c r="X69" s="53">
         <f t="shared" si="67"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y69" s="53">
         <f>SUMPRODUCT(($Q$66:$Q$69=Q69)*($X$66:$X$69&gt;X69))</f>
@@ -21107,7 +21195,7 @@
       </c>
       <c r="AH69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,5,FALSE)</f>
@@ -21119,7 +21207,7 @@
       </c>
       <c r="AK69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,8,FALSE)</f>
@@ -21127,11 +21215,11 @@
       </c>
       <c r="AM69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,9,FALSE)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AN69" s="88">
         <f>VLOOKUP($AE69,$O$66:$X$69,10,FALSE)</f>
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="70" spans="1:40" x14ac:dyDescent="0.25">
@@ -21347,11 +21435,15 @@
         <f>P72</f>
         <v>Inglaterra</v>
       </c>
-      <c r="F72" s="123"/>
+      <c r="F72" s="123">
+        <v>0</v>
+      </c>
       <c r="G72" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H72" s="123"/>
+      <c r="H72" s="123">
+        <v>0</v>
+      </c>
       <c r="I72" s="113" t="str">
         <f>P74</f>
         <v>Gana</v>
@@ -21362,11 +21454,11 @@
       </c>
       <c r="K72" s="38" t="str">
         <f t="shared" si="69"/>
-        <v/>
+        <v>Inglaterra</v>
       </c>
       <c r="L72" s="38" t="str">
         <f t="shared" si="70"/>
-        <v/>
+        <v>Gana</v>
       </c>
       <c r="M72" s="39" t="str">
         <f t="shared" si="71"/>
@@ -21383,11 +21475,11 @@
       </c>
       <c r="Q72" s="38">
         <f>(S72*3)+(T72*1)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R72" s="38">
         <f>SUM(S72:U72)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S72" s="38">
         <f>COUNTIF(J:J,P72)</f>
@@ -21395,7 +21487,7 @@
       </c>
       <c r="T72" s="38">
         <f>COUNTIF(K:K,P72)+COUNTIF(L:L,P72)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U72" s="38">
         <f>COUNTIF(M:M,P72)</f>
@@ -21442,11 +21534,11 @@
       </c>
       <c r="AG72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,5,FALSE)</f>
@@ -21454,7 +21546,7 @@
       </c>
       <c r="AJ72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,7,FALSE)</f>
@@ -21488,18 +21580,22 @@
         <f>P75</f>
         <v>Panamá</v>
       </c>
-      <c r="F73" s="123"/>
+      <c r="F73" s="123">
+        <v>0</v>
+      </c>
       <c r="G73" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H73" s="123"/>
+      <c r="H73" s="123">
+        <v>1</v>
+      </c>
       <c r="I73" s="113" t="str">
         <f>P73</f>
         <v>Croácia</v>
       </c>
       <c r="J73" s="38" t="str">
         <f t="shared" si="68"/>
-        <v>empate</v>
+        <v>Croácia</v>
       </c>
       <c r="K73" s="38" t="str">
         <f t="shared" si="69"/>
@@ -21511,12 +21607,12 @@
       </c>
       <c r="M73" s="39" t="str">
         <f t="shared" si="71"/>
-        <v>empate</v>
+        <v>Panamá</v>
       </c>
       <c r="N73" s="45"/>
       <c r="O73" s="47">
         <f>RANK(Q73,$Q$72:$Q$75)+SUM(Y73:AB73)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P73" s="49" t="str">
         <f>Sorteios!I31</f>
@@ -21524,15 +21620,15 @@
       </c>
       <c r="Q73" s="38">
         <f t="shared" ref="Q73:Q75" si="72">(S73*3)+(T73*1)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R73" s="38">
         <f t="shared" ref="R73:R75" si="73">SUM(S73:U73)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S73" s="38">
         <f>COUNTIF(J:J,P73)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" s="38">
         <f>COUNTIF(K:K,P73)+COUNTIF(L:L,P73)</f>
@@ -21544,7 +21640,7 @@
       </c>
       <c r="V73" s="38">
         <f>SUMIF(E:E,P73,F:F)+SUMIF(I:I,P73,H:H)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W73" s="38">
         <f>SUMIF(E:E,P73,H:H)+SUMIF(I:I,P73,F:F)</f>
@@ -21552,11 +21648,11 @@
       </c>
       <c r="X73" s="38">
         <f t="shared" ref="X73:X75" si="74">V73-W73</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Y73" s="38">
         <f t="shared" ref="Y73:Y75" si="75">SUMPRODUCT(($Q$72:$Q$75=Q73)*($X$72:$X$75&gt;X73))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z73" s="38">
         <f t="shared" ref="Z73:Z75" si="76">SUMPRODUCT(($Q$72:$Q$75=Q73)*($X$72:$X$75=X73)*($V$72:$V$75&gt;V73))</f>
@@ -21583,11 +21679,11 @@
       </c>
       <c r="AG73" s="84">
         <f t="shared" ref="AG73:AG75" si="80">VLOOKUP($AE73,$O$72:$X$75,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH73" s="84">
         <f t="shared" ref="AH73:AH75" si="81">VLOOKUP($AE73,$O$72:$X$75,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI73" s="84">
         <f t="shared" ref="AI73:AI75" si="82">VLOOKUP($AE73,$O$72:$X$75,5,FALSE)</f>
@@ -21595,7 +21691,7 @@
       </c>
       <c r="AJ73" s="84">
         <f t="shared" ref="AJ73:AJ75" si="83">VLOOKUP($AE73,$O$72:$X$75,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK73" s="84">
         <f t="shared" ref="AK73:AK75" si="84">VLOOKUP($AE73,$O$72:$X$75,7,FALSE)</f>
@@ -21665,11 +21761,11 @@
       </c>
       <c r="Q74" s="38">
         <f t="shared" si="72"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R74" s="38">
         <f t="shared" si="73"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S74" s="38">
         <f>COUNTIF(J:J,P74)</f>
@@ -21677,7 +21773,7 @@
       </c>
       <c r="T74" s="38">
         <f>COUNTIF(K:K,P74)+COUNTIF(L:L,P74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U74" s="38">
         <f>COUNTIF(M:M,P74)</f>
@@ -21720,19 +21816,19 @@
       </c>
       <c r="AF74" s="83" t="str">
         <f t="shared" si="79"/>
-        <v>Panamá</v>
+        <v>Croácia</v>
       </c>
       <c r="AG74" s="84">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH74" s="84">
         <f t="shared" si="81"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI74" s="84">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ74" s="84">
         <f t="shared" si="83"/>
@@ -21744,11 +21840,11 @@
       </c>
       <c r="AL74" s="84">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM74" s="84">
         <f t="shared" si="86"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN74" s="85">
         <f t="shared" si="87"/>
@@ -21798,7 +21894,7 @@
       <c r="N75" s="57"/>
       <c r="O75" s="56">
         <f>RANK(Q75,$Q$72:$Q$75)+SUM(Y75:AB75)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P75" s="49" t="str">
         <f>Sorteios!I33</f>
@@ -21810,7 +21906,7 @@
       </c>
       <c r="R75" s="53">
         <f t="shared" si="73"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S75" s="38">
         <f>COUNTIF(J:J,P75)</f>
@@ -21822,7 +21918,7 @@
       </c>
       <c r="U75" s="38">
         <f>COUNTIF(M:M,P75)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V75" s="53">
         <f>SUMIF(E:E,P75,F:F)+SUMIF(I:I,P75,H:H)</f>
@@ -21830,11 +21926,11 @@
       </c>
       <c r="W75" s="53">
         <f>SUMIF(E:E,P75,H:H)+SUMIF(I:I,P75,F:F)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X75" s="53">
         <f t="shared" si="74"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Y75" s="53">
         <f t="shared" si="75"/>
@@ -21861,7 +21957,7 @@
       </c>
       <c r="AF75" s="86" t="str">
         <f t="shared" si="79"/>
-        <v>Croácia</v>
+        <v>Panamá</v>
       </c>
       <c r="AG75" s="87">
         <f t="shared" si="80"/>
@@ -21869,7 +21965,7 @@
       </c>
       <c r="AH75" s="87">
         <f t="shared" si="81"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI75" s="87">
         <f t="shared" si="82"/>
@@ -21881,15 +21977,15 @@
       </c>
       <c r="AK75" s="87">
         <f t="shared" si="84"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL75" s="87">
         <f t="shared" si="85"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM75" s="87">
         <f t="shared" si="86"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN75" s="88">
         <f t="shared" si="87"/>
@@ -54377,18 +54473,18 @@
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="130"/>
-      <c r="B3" s="193" t="s">
+      <c r="B3" s="197" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="194"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="194"/>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="194"/>
-      <c r="K3" s="195"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="199"/>
       <c r="L3" s="131"/>
       <c r="M3" s="132"/>
       <c r="N3" s="132"/>
@@ -54396,18 +54492,18 @@
       <c r="P3" s="132"/>
       <c r="Q3" s="132"/>
       <c r="W3" s="130"/>
-      <c r="X3" s="193" t="s">
+      <c r="X3" s="197" t="s">
         <v>73</v>
       </c>
-      <c r="Y3" s="194"/>
-      <c r="Z3" s="194"/>
-      <c r="AA3" s="194"/>
-      <c r="AB3" s="194"/>
-      <c r="AC3" s="194"/>
-      <c r="AD3" s="194"/>
-      <c r="AE3" s="194"/>
-      <c r="AF3" s="194"/>
-      <c r="AG3" s="195"/>
+      <c r="Y3" s="198"/>
+      <c r="Z3" s="198"/>
+      <c r="AA3" s="198"/>
+      <c r="AB3" s="198"/>
+      <c r="AC3" s="198"/>
+      <c r="AD3" s="198"/>
+      <c r="AE3" s="198"/>
+      <c r="AF3" s="198"/>
+      <c r="AG3" s="199"/>
       <c r="AH3" s="131"/>
       <c r="AI3" s="132"/>
       <c r="AJ3" s="132"/>
@@ -54424,19 +54520,19 @@
       <c r="D4" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="196" t="s">
+      <c r="E4" s="193" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="196"/>
-      <c r="G4" s="196" t="s">
+      <c r="F4" s="193"/>
+      <c r="G4" s="193" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="196"/>
-      <c r="I4" s="196"/>
-      <c r="J4" s="196" t="s">
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="193" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="196"/>
+      <c r="K4" s="193"/>
       <c r="L4" s="135"/>
       <c r="M4" s="135"/>
       <c r="N4" s="135"/>
@@ -54451,19 +54547,19 @@
       <c r="Z4" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA4" s="196" t="s">
+      <c r="AA4" s="193" t="s">
         <v>17</v>
       </c>
-      <c r="AB4" s="196"/>
-      <c r="AC4" s="196" t="s">
+      <c r="AB4" s="193"/>
+      <c r="AC4" s="193" t="s">
         <v>18</v>
       </c>
-      <c r="AD4" s="196"/>
-      <c r="AE4" s="196"/>
-      <c r="AF4" s="196" t="s">
+      <c r="AD4" s="193"/>
+      <c r="AE4" s="193"/>
+      <c r="AF4" s="193" t="s">
         <v>17</v>
       </c>
-      <c r="AG4" s="196"/>
+      <c r="AG4" s="193"/>
       <c r="AH4" s="136"/>
       <c r="AI4" s="133"/>
       <c r="AJ4" s="133"/>
@@ -54583,7 +54679,7 @@
       </c>
       <c r="P6" s="133" t="str">
         <f>'Fase de Grupos'!AR39</f>
-        <v>3H3G3B3C3A3F3E3K</v>
+        <v>3C3G3J3D3A3F3L3H</v>
       </c>
       <c r="W6" s="45"/>
       <c r="X6" s="152" t="s">
@@ -54738,11 +54834,11 @@
       </c>
       <c r="Q8" s="133" t="str">
         <f>MID($P$6,1,2)</f>
-        <v>3H</v>
+        <v>3C</v>
       </c>
       <c r="R8" s="15" t="str">
         <f>VLOOKUP(Q8,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Espanha</v>
+        <v>Escócia</v>
       </c>
       <c r="T8" s="15" t="s">
         <v>102</v>
@@ -54901,11 +54997,11 @@
       </c>
       <c r="Q10" s="133" t="str">
         <f>MID($P$6,5,2)</f>
-        <v>3B</v>
+        <v>3J</v>
       </c>
       <c r="R10" s="15" t="str">
         <f>VLOOKUP(Q10,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Qatar</v>
+        <v>Argélia</v>
       </c>
       <c r="T10" s="15" t="s">
         <v>104</v>
@@ -54973,11 +55069,11 @@
       </c>
       <c r="Q11" s="133" t="str">
         <f>MID($P$6,7,2)</f>
-        <v>3C</v>
+        <v>3D</v>
       </c>
       <c r="R11" s="15" t="str">
         <f>VLOOKUP(Q11,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Marrocos</v>
+        <v>Paraguai</v>
       </c>
       <c r="T11" s="15" t="s">
         <v>138</v>
@@ -54987,18 +55083,18 @@
         <v>12</v>
       </c>
       <c r="W11" s="130"/>
-      <c r="X11" s="193" t="s">
+      <c r="X11" s="197" t="s">
         <v>74</v>
       </c>
-      <c r="Y11" s="194"/>
-      <c r="Z11" s="194"/>
-      <c r="AA11" s="194"/>
-      <c r="AB11" s="194"/>
-      <c r="AC11" s="194"/>
-      <c r="AD11" s="194"/>
-      <c r="AE11" s="194"/>
-      <c r="AF11" s="194"/>
-      <c r="AG11" s="195"/>
+      <c r="Y11" s="198"/>
+      <c r="Z11" s="198"/>
+      <c r="AA11" s="198"/>
+      <c r="AB11" s="198"/>
+      <c r="AC11" s="198"/>
+      <c r="AD11" s="198"/>
+      <c r="AE11" s="198"/>
+      <c r="AF11" s="198"/>
+      <c r="AG11" s="199"/>
       <c r="AH11" s="131"/>
       <c r="AI11" s="132"/>
       <c r="AJ11" s="132"/>
@@ -55068,19 +55164,19 @@
       <c r="Z12" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA12" s="196" t="s">
+      <c r="AA12" s="193" t="s">
         <v>17</v>
       </c>
-      <c r="AB12" s="196"/>
-      <c r="AC12" s="196" t="s">
+      <c r="AB12" s="193"/>
+      <c r="AC12" s="193" t="s">
         <v>18</v>
       </c>
-      <c r="AD12" s="196"/>
-      <c r="AE12" s="196"/>
-      <c r="AF12" s="196" t="s">
+      <c r="AD12" s="193"/>
+      <c r="AE12" s="193"/>
+      <c r="AF12" s="193" t="s">
         <v>17</v>
       </c>
-      <c r="AG12" s="196"/>
+      <c r="AG12" s="193"/>
       <c r="AH12" s="136"/>
       <c r="AI12" s="133"/>
       <c r="AJ12" s="133"/>
@@ -55133,7 +55229,7 @@
       </c>
       <c r="R13" s="15" t="str">
         <f>VLOOKUP(Q13,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Japão</v>
+        <v>Suécia</v>
       </c>
       <c r="T13" s="15" t="s">
         <v>140</v>
@@ -55221,11 +55317,11 @@
       </c>
       <c r="Q14" s="133" t="str">
         <f>MID($P$6,13,2)</f>
-        <v>3E</v>
+        <v>3L</v>
       </c>
       <c r="R14" s="15" t="str">
         <f>VLOOKUP(Q14,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Equador</v>
+        <v>Croácia</v>
       </c>
       <c r="T14" s="15" t="s">
         <v>105</v>
@@ -55313,11 +55409,11 @@
       </c>
       <c r="Q15" s="133" t="str">
         <f>MID($P$6,15,2)</f>
-        <v>3K</v>
+        <v>3H</v>
       </c>
       <c r="R15" s="15" t="str">
         <f>VLOOKUP(Q15,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>RD Congo</v>
+        <v>Cabo Verde</v>
       </c>
       <c r="T15" s="15" t="s">
         <v>135</v>
@@ -55455,18 +55551,18 @@
         <v>30</v>
       </c>
       <c r="W17" s="130"/>
-      <c r="X17" s="193" t="s">
+      <c r="X17" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="Y17" s="194"/>
-      <c r="Z17" s="194"/>
-      <c r="AA17" s="194"/>
-      <c r="AB17" s="194"/>
-      <c r="AC17" s="194"/>
-      <c r="AD17" s="194"/>
-      <c r="AE17" s="194"/>
-      <c r="AF17" s="194"/>
-      <c r="AG17" s="195"/>
+      <c r="Y17" s="198"/>
+      <c r="Z17" s="198"/>
+      <c r="AA17" s="198"/>
+      <c r="AB17" s="198"/>
+      <c r="AC17" s="198"/>
+      <c r="AD17" s="198"/>
+      <c r="AE17" s="198"/>
+      <c r="AF17" s="198"/>
+      <c r="AG17" s="199"/>
       <c r="AH17" s="131"/>
       <c r="AI17" s="132"/>
       <c r="AJ17" s="132"/>
@@ -55525,19 +55621,19 @@
       <c r="Z18" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA18" s="196" t="s">
+      <c r="AA18" s="193" t="s">
         <v>17</v>
       </c>
-      <c r="AB18" s="196"/>
-      <c r="AC18" s="196" t="s">
+      <c r="AB18" s="193"/>
+      <c r="AC18" s="193" t="s">
         <v>18</v>
       </c>
-      <c r="AD18" s="196"/>
-      <c r="AE18" s="196"/>
-      <c r="AF18" s="196" t="s">
+      <c r="AD18" s="193"/>
+      <c r="AE18" s="193"/>
+      <c r="AF18" s="193" t="s">
         <v>17</v>
       </c>
-      <c r="AG18" s="196"/>
+      <c r="AG18" s="193"/>
       <c r="AH18" s="136"/>
       <c r="AI18" s="133"/>
       <c r="AJ18" s="133"/>
@@ -55729,18 +55825,18 @@
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" s="130"/>
-      <c r="B23" s="193" t="s">
+      <c r="B23" s="197" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="194"/>
-      <c r="D23" s="194"/>
-      <c r="E23" s="194"/>
-      <c r="F23" s="194"/>
-      <c r="G23" s="194"/>
-      <c r="H23" s="194"/>
-      <c r="I23" s="194"/>
-      <c r="J23" s="194"/>
-      <c r="K23" s="195"/>
+      <c r="C23" s="198"/>
+      <c r="D23" s="198"/>
+      <c r="E23" s="198"/>
+      <c r="F23" s="198"/>
+      <c r="G23" s="198"/>
+      <c r="H23" s="198"/>
+      <c r="I23" s="198"/>
+      <c r="J23" s="198"/>
+      <c r="K23" s="199"/>
       <c r="L23" s="131"/>
       <c r="M23" s="132"/>
       <c r="N23" s="132"/>
@@ -55755,18 +55851,18 @@
         <v>48</v>
       </c>
       <c r="W23" s="45"/>
-      <c r="X23" s="193" t="s">
+      <c r="X23" s="197" t="s">
         <v>79</v>
       </c>
-      <c r="Y23" s="194"/>
-      <c r="Z23" s="194"/>
-      <c r="AA23" s="194"/>
-      <c r="AB23" s="194"/>
-      <c r="AC23" s="194"/>
-      <c r="AD23" s="194"/>
-      <c r="AE23" s="194"/>
-      <c r="AF23" s="194"/>
-      <c r="AG23" s="195"/>
+      <c r="Y23" s="198"/>
+      <c r="Z23" s="198"/>
+      <c r="AA23" s="198"/>
+      <c r="AB23" s="198"/>
+      <c r="AC23" s="198"/>
+      <c r="AD23" s="198"/>
+      <c r="AE23" s="198"/>
+      <c r="AF23" s="198"/>
+      <c r="AG23" s="199"/>
       <c r="AH23" s="131"/>
       <c r="AI23" s="132"/>
       <c r="AJ23" s="132"/>
@@ -55782,19 +55878,19 @@
       <c r="D24" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="196" t="s">
+      <c r="E24" s="193" t="s">
         <v>17</v>
       </c>
-      <c r="F24" s="196"/>
-      <c r="G24" s="196" t="s">
+      <c r="F24" s="193"/>
+      <c r="G24" s="193" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="196"/>
-      <c r="I24" s="196"/>
-      <c r="J24" s="196" t="s">
+      <c r="H24" s="193"/>
+      <c r="I24" s="193"/>
+      <c r="J24" s="193" t="s">
         <v>17</v>
       </c>
-      <c r="K24" s="196"/>
+      <c r="K24" s="193"/>
       <c r="L24" s="135"/>
       <c r="M24" s="135"/>
       <c r="N24" s="135"/>
@@ -55816,19 +55912,19 @@
       <c r="Z24" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA24" s="196" t="s">
+      <c r="AA24" s="193" t="s">
         <v>17</v>
       </c>
-      <c r="AB24" s="196"/>
-      <c r="AC24" s="196" t="s">
+      <c r="AB24" s="193"/>
+      <c r="AC24" s="193" t="s">
         <v>18</v>
       </c>
-      <c r="AD24" s="196"/>
-      <c r="AE24" s="196"/>
-      <c r="AF24" s="196" t="s">
+      <c r="AD24" s="193"/>
+      <c r="AE24" s="193"/>
+      <c r="AF24" s="193" t="s">
         <v>17</v>
       </c>
-      <c r="AG24" s="196"/>
+      <c r="AG24" s="193"/>
       <c r="AH24" s="136"/>
       <c r="AI24" s="133"/>
       <c r="AJ24" s="133"/>
@@ -56227,15 +56323,15 @@
       </c>
       <c r="Z34" s="202"/>
       <c r="AA34" s="202"/>
-      <c r="AB34" s="197" t="str">
+      <c r="AB34" s="194" t="str">
         <f>IF(AI25="1º Lugar","",AI25)</f>
         <v/>
       </c>
-      <c r="AC34" s="197"/>
-      <c r="AD34" s="197"/>
-      <c r="AE34" s="197"/>
-      <c r="AF34" s="197"/>
-      <c r="AG34" s="197"/>
+      <c r="AC34" s="194"/>
+      <c r="AD34" s="194"/>
+      <c r="AE34" s="194"/>
+      <c r="AF34" s="194"/>
+      <c r="AG34" s="194"/>
     </row>
     <row r="35" spans="2:33" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B35" s="140"/>
@@ -56247,15 +56343,15 @@
       </c>
       <c r="Z35" s="200"/>
       <c r="AA35" s="200"/>
-      <c r="AB35" s="198" t="str">
+      <c r="AB35" s="195" t="str">
         <f>IF(M57="2º Lugar","",M57)</f>
         <v/>
       </c>
-      <c r="AC35" s="198"/>
-      <c r="AD35" s="198"/>
-      <c r="AE35" s="198"/>
-      <c r="AF35" s="198"/>
-      <c r="AG35" s="198"/>
+      <c r="AC35" s="195"/>
+      <c r="AD35" s="195"/>
+      <c r="AE35" s="195"/>
+      <c r="AF35" s="195"/>
+      <c r="AG35" s="195"/>
     </row>
     <row r="36" spans="2:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="140"/>
@@ -56267,15 +56363,15 @@
       </c>
       <c r="Z36" s="201"/>
       <c r="AA36" s="201"/>
-      <c r="AB36" s="199" t="str">
+      <c r="AB36" s="196" t="str">
         <f>IF(AI19="3º Lugar","",AI19)</f>
         <v/>
       </c>
-      <c r="AC36" s="199"/>
-      <c r="AD36" s="199"/>
-      <c r="AE36" s="199"/>
-      <c r="AF36" s="199"/>
-      <c r="AG36" s="199"/>
+      <c r="AC36" s="196"/>
+      <c r="AD36" s="196"/>
+      <c r="AE36" s="196"/>
+      <c r="AF36" s="196"/>
+      <c r="AG36" s="196"/>
     </row>
     <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="137"/>
@@ -56433,20 +56529,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="e9SwIN3P1gzBH+IVoOp3qqE533HDYkDzheVXRVNRaqt2vhimaHXLKZ+8sDUopKeiKAT5et9NZBvuLRUJOa6zQg==" saltValue="pxuBsAAmB/Bn8sNidXdYpQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AB34:AG34"/>
-    <mergeCell ref="AB35:AG35"/>
-    <mergeCell ref="AB36:AG36"/>
-    <mergeCell ref="B23:K23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="Y35:AA35"/>
-    <mergeCell ref="Y36:AA36"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AC24:AE24"/>
-    <mergeCell ref="AF24:AG24"/>
-    <mergeCell ref="Y34:AA34"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:I4"/>
@@ -56463,6 +56545,20 @@
     <mergeCell ref="AF18:AG18"/>
     <mergeCell ref="AA4:AB4"/>
     <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AB34:AG34"/>
+    <mergeCell ref="AB35:AG35"/>
+    <mergeCell ref="AB36:AG36"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="Y35:AA35"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="AF24:AG24"/>
+    <mergeCell ref="Y34:AA34"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A2 B2:K2 X9:AG10 X15:AG16 X20:AG21 B21:K22 AB34:AB36 A57:K58 H59:K61 B62:K71 B83:K1048576">
     <cfRule type="cellIs" dxfId="27" priority="76" operator="equal">
@@ -57225,12 +57321,6 @@
     <sortCondition ref="C59:C64"/>
   </sortState>
   <mergeCells count="16">
-    <mergeCell ref="N4:N6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="J4:J6"/>
-    <mergeCell ref="L4:L6"/>
     <mergeCell ref="AB4:AB6"/>
     <mergeCell ref="AD4:AD6"/>
     <mergeCell ref="AF4:AF6"/>
@@ -57241,6 +57331,12 @@
     <mergeCell ref="V4:V6"/>
     <mergeCell ref="X4:X6"/>
     <mergeCell ref="Z4:Z6"/>
+    <mergeCell ref="N4:N6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="L4:L6"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -57249,20 +57345,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -57493,14 +57589,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
@@ -57513,6 +57601,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97057822-33A9-45A9-BD20-F91D20B8EFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE93637-9C6E-434F-8D2E-067AEB248404}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BcI4NY5Ohir363+nRCln2YCzlnOeJyINjZ1aV0hb2IpPHmsHZPUFroFzrod6xokqyCn7GUW2N1Z+U/w2mbyNbQ==" workbookSaltValue="VvXyFesAZC8L8IOzNm6PtA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9525" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="7" r:id="rId1"/>
@@ -26,17 +26,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -2178,6 +2167,123 @@
   </cellStyles>
   <dxfs count="91">
     <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
@@ -2657,123 +2763,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="4"/>
       </font>
     </dxf>
@@ -2973,17 +2962,6 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3088,6 +3066,17 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9048,25 +9037,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CB5EB0A-66D8-48B4-BC40-E2D214AFC03A}" name="Tabela1" displayName="Tabela1" ref="C3:E51" totalsRowShown="0" headerRowDxfId="90" dataDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CB5EB0A-66D8-48B4-BC40-E2D214AFC03A}" name="Tabela1" displayName="Tabela1" ref="C3:E51" totalsRowShown="0" headerRowDxfId="88" dataDxfId="87">
   <autoFilter ref="C3:E51" xr:uid="{9CB5EB0A-66D8-48B4-BC40-E2D214AFC03A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{BA403FB9-D643-4201-89E9-82280DBD496D}" name=" " dataDxfId="88"/>
-    <tableColumn id="2" xr3:uid="{8927B163-5C71-4390-8413-1CB7AFCDC479}" name="Times" dataDxfId="87"/>
-    <tableColumn id="3" xr3:uid="{95E8A229-CD3E-4FE0-BC0B-3E68BBDC2143}" name="  " dataDxfId="86"/>
+    <tableColumn id="1" xr3:uid="{BA403FB9-D643-4201-89E9-82280DBD496D}" name=" " dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{8927B163-5C71-4390-8413-1CB7AFCDC479}" name="Times" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{95E8A229-CD3E-4FE0-BC0B-3E68BBDC2143}" name="  " dataDxfId="84"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9104,7 +9093,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9210,7 +9199,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9352,7 +9341,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -9661,12 +9650,12 @@
     <mergeCell ref="J33:L33"/>
   </mergeCells>
   <conditionalFormatting sqref="J31:L31 J32:J33">
-    <cfRule type="cellIs" dxfId="85" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="2" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31:L33">
-    <cfRule type="expression" dxfId="84" priority="1">
+    <cfRule type="expression" dxfId="89" priority="1">
       <formula>M31&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10981,7 +10970,8 @@
     <col min="30" max="30" width="3" style="15" hidden="1" customWidth="1"/>
     <col min="31" max="31" width="2.7109375" style="15" customWidth="1"/>
     <col min="32" max="32" width="20.7109375" style="15" customWidth="1"/>
-    <col min="33" max="40" width="3.7109375" style="15" customWidth="1"/>
+    <col min="33" max="39" width="3.7109375" style="15" customWidth="1"/>
+    <col min="40" max="40" width="4" style="15" customWidth="1"/>
     <col min="41" max="41" width="9.140625" style="15"/>
     <col min="42" max="42" width="3.28515625" style="15" hidden="1" customWidth="1"/>
     <col min="43" max="43" width="10.42578125" style="15" hidden="1" customWidth="1"/>
@@ -11537,15 +11527,15 @@
       </c>
       <c r="Q6" s="38">
         <f>(S6*3)+(T6*1)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R6" s="38">
         <f>SUM(S6:U6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6" s="38">
         <f>COUNTIF(J:J,P6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T6" s="38">
         <f>COUNTIF(K:K,P6)+COUNTIF(L:L,P6)</f>
@@ -11557,7 +11547,7 @@
       </c>
       <c r="V6" s="38">
         <f>SUMIF(E:E,P6,F:F)+SUMIF(I:I,P6,H:H)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W6" s="38">
         <f>SUMIF(E:E,P6,H:H)+SUMIF(I:I,P6,F:F)</f>
@@ -11565,7 +11555,7 @@
       </c>
       <c r="X6" s="38">
         <f>V6-W6</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y6" s="38">
         <f>SUMPRODUCT(($Q$6:$Q$9=Q6)*($X$6:$X$9&gt;X6))</f>
@@ -11596,15 +11586,15 @@
       </c>
       <c r="AG6" s="84">
         <f>VLOOKUP($AE6,$O$6:$X$9,3,FALSE)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AH6" s="84">
         <f>VLOOKUP($AE6,$O$6:$X$9,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI6" s="84">
         <f>VLOOKUP($AE6,$O$6:$X$9,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ6" s="84">
         <f>VLOOKUP($AE6,$O$6:$X$9,6,FALSE)</f>
@@ -11616,7 +11606,7 @@
       </c>
       <c r="AL6" s="84">
         <f>VLOOKUP($AE6,$O$6:$X$9,8,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM6" s="84">
         <f>VLOOKUP($AE6,$O$6:$X$9,9,FALSE)</f>
@@ -11624,35 +11614,35 @@
       </c>
       <c r="AN6" s="85">
         <f>VLOOKUP($AE6,$O$6:$X$9,10,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AP6" s="48">
         <f t="shared" ref="AP6:AP17" si="4">RANK(AR6,$AR$6:$AR$17)+SUM(BB6:BE6)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ6" s="50" t="str">
         <f>AF8</f>
-        <v>República Tcheca</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="AR6" s="38">
         <f>(AT6*3)+(AU6*1)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS6" s="38">
         <f>SUM(AT6:AV6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT6" s="38">
         <f t="shared" ref="AT6:AT17" si="5">VLOOKUP(AQ6,$P$5:$X$75,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" s="38">
         <f t="shared" ref="AU6:AU17" si="6">VLOOKUP(AQ6,$P$5:$X$75,5,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV6" s="38">
         <f t="shared" ref="AV6:AV17" si="7">VLOOKUP(AQ6,$P$5:$X$75,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW6" s="38">
         <f t="shared" ref="AW6:AW17" si="8">VLOOKUP(AQ6,$P$5:$X$75,7,FALSE)</f>
@@ -11671,11 +11661,11 @@
       </c>
       <c r="BA6" s="38" t="str">
         <f>AQ6</f>
-        <v>República Tcheca</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="BB6" s="38">
         <f t="shared" ref="BB6:BB17" si="10">SUMPRODUCT(($AR$6:$AR$17=AR6)*($AY$6:$AY$17&gt;AY6))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BC6" s="38">
         <f t="shared" ref="BC6:BC17" si="11">SUMPRODUCT(($AR$6:$AR$17=AR6)*($AY$6:$AY$17=AY6)*($AW$6:$AW$17&gt;AW6))</f>
@@ -11698,15 +11688,15 @@
       </c>
       <c r="BJ6" s="83" t="str">
         <f t="shared" ref="BJ6:BJ17" si="14">VLOOKUP($BI6,$AP$6:$AY$17,2,FALSE)</f>
-        <v>Suécia</v>
+        <v>RD Congo</v>
       </c>
       <c r="BK6" s="84">
         <f t="shared" ref="BK6:BK17" si="15">VLOOKUP($BI6,$AP$6:$AY$17,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL6" s="84">
         <f t="shared" ref="BL6:BL17" si="16">VLOOKUP($BI6,$AP$6:$AY$17,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM6" s="84">
         <f t="shared" ref="BM6:BM17" si="17">VLOOKUP($BI6,$AP$6:$AY$17,5,FALSE)</f>
@@ -11714,7 +11704,7 @@
       </c>
       <c r="BN6" s="84">
         <f t="shared" ref="BN6:BN17" si="18">VLOOKUP($BI6,$AP$6:$AY$17,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO6" s="84">
         <f t="shared" ref="BO6:BO17" si="19">VLOOKUP($BI6,$AP$6:$AY$17,7,FALSE)</f>
@@ -11722,15 +11712,15 @@
       </c>
       <c r="BP6" s="84">
         <f t="shared" ref="BP6:BP17" si="20">VLOOKUP($BI6,$AP$6:$AY$17,8,FALSE)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BQ6" s="84">
         <f t="shared" ref="BQ6:BQ17" si="21">VLOOKUP($BI6,$AP$6:$AY$17,9,FALSE)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BR6" s="85">
         <f t="shared" ref="BR6:BR17" si="22">VLOOKUP($BI6,$AP$6:$AY$17,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:70" x14ac:dyDescent="0.25">
@@ -11780,7 +11770,7 @@
       <c r="N7" s="46"/>
       <c r="O7" s="47">
         <f>RANK(Q7,$Q$6:$Q$9)+SUM(Y7:AB7)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P7" s="49" t="str">
         <f>Sorteios!C7</f>
@@ -11788,15 +11778,15 @@
       </c>
       <c r="Q7" s="38">
         <f t="shared" ref="Q7:Q9" si="23">(S7*3)+(T7*1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R7" s="38">
         <f t="shared" ref="R7:R9" si="24">SUM(S7:U7)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7" s="38">
         <f>COUNTIF(J:J,P7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" s="38">
         <f>COUNTIF(K:K,P7)+COUNTIF(L:L,P7)</f>
@@ -11808,7 +11798,7 @@
       </c>
       <c r="V7" s="38">
         <f>SUMIF(E:E,P7,F:F)+SUMIF(I:I,P7,H:H)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W7" s="38">
         <f>SUMIF(E:E,P7,H:H)+SUMIF(I:I,P7,F:F)</f>
@@ -11816,11 +11806,11 @@
       </c>
       <c r="X7" s="38">
         <f t="shared" ref="X7:X9" si="25">V7-W7</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Y7" s="38">
         <f>SUMPRODUCT(($Q$6:$Q$9=Q7)*($X$6:$X$9&gt;X7))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="38">
         <f>SUMPRODUCT(($Q$6:$Q$9=Q7)*($X$6:$X$9=X7)*($V$6:$V$9&gt;V7))</f>
@@ -11843,15 +11833,15 @@
       </c>
       <c r="AF7" s="83" t="str">
         <f>VLOOKUP($AE7,$O$6:$X$9,2,FALSE)</f>
-        <v>Coreia do Sul</v>
+        <v>África do Sul</v>
       </c>
       <c r="AG7" s="84">
         <f>VLOOKUP($AE7,$O$6:$X$9,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH7" s="84">
         <f>VLOOKUP($AE7,$O$6:$X$9,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI7" s="84">
         <f>VLOOKUP($AE7,$O$6:$X$9,5,FALSE)</f>
@@ -11859,7 +11849,7 @@
       </c>
       <c r="AJ7" s="84">
         <f>VLOOKUP($AE7,$O$6:$X$9,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK7" s="84">
         <f>VLOOKUP($AE7,$O$6:$X$9,7,FALSE)</f>
@@ -11871,15 +11861,15 @@
       </c>
       <c r="AM7" s="84">
         <f>VLOOKUP($AE7,$O$6:$X$9,9,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN7" s="85">
         <f>VLOOKUP($AE7,$O$6:$X$9,10,FALSE)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP7" s="48">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AQ7" s="50" t="str">
         <f>AF14</f>
@@ -11887,15 +11877,15 @@
       </c>
       <c r="AR7" s="38">
         <f t="shared" ref="AR7:AR17" si="26">(AT7*3)+(AU7*1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS7" s="38">
         <f t="shared" ref="AS7:AS17" si="27">SUM(AT7:AV7)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT7" s="38">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" s="38">
         <f t="shared" si="6"/>
@@ -11907,15 +11897,15 @@
       </c>
       <c r="AW7" s="38">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX7" s="38">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY7" s="38">
         <f t="shared" ref="AY7:AY17" si="28">AW7-AX7</f>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="AZ7" s="38" t="s">
         <v>48</v>
@@ -11926,7 +11916,7 @@
       </c>
       <c r="BB7" s="38">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC7" s="38">
         <f t="shared" si="11"/>
@@ -11949,15 +11939,15 @@
       </c>
       <c r="BJ7" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Escócia</v>
+        <v>Suécia</v>
       </c>
       <c r="BK7" s="84">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL7" s="84">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM7" s="84">
         <f t="shared" si="17"/>
@@ -11965,7 +11955,7 @@
       </c>
       <c r="BN7" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO7" s="84">
         <f t="shared" si="19"/>
@@ -11973,11 +11963,11 @@
       </c>
       <c r="BP7" s="84">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BQ7" s="84">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BR7" s="85">
         <f t="shared" si="22"/>
@@ -11999,18 +11989,22 @@
         <f>P9</f>
         <v>República Tcheca</v>
       </c>
-      <c r="F8" s="123"/>
+      <c r="F8" s="123">
+        <v>0</v>
+      </c>
       <c r="G8" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="123"/>
+      <c r="H8" s="123">
+        <v>3</v>
+      </c>
       <c r="I8" s="107" t="str">
         <f>P6</f>
         <v>México</v>
       </c>
       <c r="J8" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>México</v>
       </c>
       <c r="K8" s="38" t="str">
         <f t="shared" si="1"/>
@@ -12022,12 +12016,12 @@
       </c>
       <c r="M8" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>República Tcheca</v>
       </c>
       <c r="N8" s="46"/>
       <c r="O8" s="47">
         <f>RANK(Q8,$Q$6:$Q$9)+SUM(Y8:AB8)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" s="49" t="str">
         <f>Sorteios!C8</f>
@@ -12039,7 +12033,7 @@
       </c>
       <c r="R8" s="38">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S8" s="38">
         <f>COUNTIF(J:J,P8)</f>
@@ -12051,7 +12045,7 @@
       </c>
       <c r="U8" s="38">
         <f>COUNTIF(M:M,P8)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V8" s="38">
         <f>SUMIF(E:E,P8,F:F)+SUMIF(I:I,P8,H:H)</f>
@@ -12059,11 +12053,11 @@
       </c>
       <c r="W8" s="38">
         <f>SUMIF(E:E,P8,H:H)+SUMIF(I:I,P8,F:F)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X8" s="38">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y8" s="38">
         <f>SUMPRODUCT(($Q$6:$Q$9=Q8)*($X$6:$X$9&gt;X8))</f>
@@ -12090,27 +12084,27 @@
       </c>
       <c r="AF8" s="83" t="str">
         <f>VLOOKUP($AE8,$O$6:$X$9,2,FALSE)</f>
-        <v>República Tcheca</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="AG8" s="84">
         <f>VLOOKUP($AE8,$O$6:$X$9,3,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH8" s="84">
         <f>VLOOKUP($AE8,$O$6:$X$9,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI8" s="84">
         <f>VLOOKUP($AE8,$O$6:$X$9,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="84">
         <f>VLOOKUP($AE8,$O$6:$X$9,6,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="84">
         <f>VLOOKUP($AE8,$O$6:$X$9,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL8" s="84">
         <f>VLOOKUP($AE8,$O$6:$X$9,8,FALSE)</f>
@@ -12126,7 +12120,7 @@
       </c>
       <c r="AP8" s="48">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AQ8" s="50" t="str">
         <f>AF20</f>
@@ -12138,7 +12132,7 @@
       </c>
       <c r="AS8" s="38">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT8" s="38">
         <f t="shared" si="5"/>
@@ -12150,7 +12144,7 @@
       </c>
       <c r="AV8" s="38">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW8" s="38">
         <f t="shared" si="8"/>
@@ -12158,11 +12152,11 @@
       </c>
       <c r="AX8" s="38">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY8" s="38">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AZ8" s="38" t="s">
         <v>50</v>
@@ -12173,11 +12167,11 @@
       </c>
       <c r="BB8" s="38">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC8" s="38">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD8" s="38">
         <f t="shared" si="12"/>
@@ -12196,15 +12190,15 @@
       </c>
       <c r="BJ8" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Croácia</v>
+        <v>Equador</v>
       </c>
       <c r="BK8" s="84">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL8" s="84">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM8" s="84">
         <f t="shared" si="17"/>
@@ -12212,7 +12206,7 @@
       </c>
       <c r="BN8" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO8" s="84">
         <f t="shared" si="19"/>
@@ -12220,15 +12214,15 @@
       </c>
       <c r="BP8" s="84">
         <f t="shared" si="20"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ8" s="84">
         <f t="shared" si="21"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BR8" s="85">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12246,18 +12240,22 @@
         <f>P7</f>
         <v>África do Sul</v>
       </c>
-      <c r="F9" s="124"/>
+      <c r="F9" s="124">
+        <v>1</v>
+      </c>
       <c r="G9" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="124"/>
+      <c r="H9" s="124">
+        <v>0</v>
+      </c>
       <c r="I9" s="109" t="str">
         <f>P8</f>
         <v>Coreia do Sul</v>
       </c>
       <c r="J9" s="53" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>África do Sul</v>
       </c>
       <c r="K9" s="53" t="str">
         <f t="shared" si="1"/>
@@ -12269,12 +12267,12 @@
       </c>
       <c r="M9" s="54" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="N9" s="55"/>
       <c r="O9" s="56">
         <f>RANK(Q9,$Q$6:$Q$9)+SUM(Y9:AB9)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P9" s="49" t="str">
         <f>Sorteios!C9</f>
@@ -12286,7 +12284,7 @@
       </c>
       <c r="R9" s="38">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S9" s="38">
         <f>COUNTIF(J:J,P9)</f>
@@ -12298,7 +12296,7 @@
       </c>
       <c r="U9" s="38">
         <f>COUNTIF(M:M,P9)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V9" s="38">
         <f>SUMIF(E:E,P9,F:F)+SUMIF(I:I,P9,H:H)</f>
@@ -12306,11 +12304,11 @@
       </c>
       <c r="W9" s="38">
         <f>SUMIF(E:E,P9,H:H)+SUMIF(I:I,P9,F:F)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X9" s="38">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="Y9" s="38">
         <f>SUMPRODUCT(($Q$6:$Q$9=Q9)*($X$6:$X$9&gt;X9))</f>
@@ -12337,7 +12335,7 @@
       </c>
       <c r="AF9" s="86" t="str">
         <f>VLOOKUP($AE9,$O$6:$X$9,2,FALSE)</f>
-        <v>África do Sul</v>
+        <v>República Tcheca</v>
       </c>
       <c r="AG9" s="87">
         <f>VLOOKUP($AE9,$O$6:$X$9,3,FALSE)</f>
@@ -12345,7 +12343,7 @@
       </c>
       <c r="AH9" s="87">
         <f>VLOOKUP($AE9,$O$6:$X$9,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI9" s="87">
         <f>VLOOKUP($AE9,$O$6:$X$9,5,FALSE)</f>
@@ -12357,23 +12355,23 @@
       </c>
       <c r="AK9" s="87">
         <f>VLOOKUP($AE9,$O$6:$X$9,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL9" s="87">
         <f>VLOOKUP($AE9,$O$6:$X$9,8,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM9" s="87">
         <f>VLOOKUP($AE9,$O$6:$X$9,9,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN9" s="88">
         <f>VLOOKUP($AE9,$O$6:$X$9,10,FALSE)</f>
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AP9" s="48">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AQ9" s="50" t="str">
         <f>AF26</f>
@@ -12381,11 +12379,11 @@
       </c>
       <c r="AR9" s="38">
         <f t="shared" si="26"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS9" s="38">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT9" s="38">
         <f t="shared" si="5"/>
@@ -12393,7 +12391,7 @@
       </c>
       <c r="AU9" s="38">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV9" s="38">
         <f t="shared" si="7"/>
@@ -12420,11 +12418,11 @@
       </c>
       <c r="BB9" s="38">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC9" s="38">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD9" s="38">
         <f t="shared" si="12"/>
@@ -12443,15 +12441,15 @@
       </c>
       <c r="BJ9" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Paraguai</v>
+        <v>Gana</v>
       </c>
       <c r="BK9" s="84">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL9" s="84">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM9" s="84">
         <f t="shared" si="17"/>
@@ -12459,7 +12457,7 @@
       </c>
       <c r="BN9" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO9" s="84">
         <f t="shared" si="19"/>
@@ -12471,11 +12469,11 @@
       </c>
       <c r="BQ9" s="84">
         <f t="shared" si="21"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BR9" s="85">
         <f t="shared" si="22"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:70" x14ac:dyDescent="0.25">
@@ -12555,7 +12553,7 @@
       <c r="AN10" s="80"/>
       <c r="AP10" s="48">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AQ10" s="50" t="str">
         <f>AF32</f>
@@ -12563,15 +12561,15 @@
       </c>
       <c r="AR10" s="38">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS10" s="38">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT10" s="38">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU10" s="38">
         <f t="shared" si="6"/>
@@ -12583,15 +12581,15 @@
       </c>
       <c r="AW10" s="38">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX10" s="38">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY10" s="38">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ10" s="38" t="s">
         <v>44</v>
@@ -12602,11 +12600,11 @@
       </c>
       <c r="BB10" s="38">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC10" s="38">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD10" s="38">
         <f t="shared" si="12"/>
@@ -12625,15 +12623,15 @@
       </c>
       <c r="BJ10" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Argélia</v>
+        <v>Bósnia</v>
       </c>
       <c r="BK10" s="84">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL10" s="84">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM10" s="84">
         <f t="shared" si="17"/>
@@ -12641,7 +12639,7 @@
       </c>
       <c r="BN10" s="84">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO10" s="84">
         <f t="shared" si="19"/>
@@ -12649,15 +12647,15 @@
       </c>
       <c r="BP10" s="84">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BQ10" s="84">
         <f t="shared" si="21"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BR10" s="85">
         <f t="shared" si="22"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:70" x14ac:dyDescent="0.25">
@@ -12783,7 +12781,7 @@
       </c>
       <c r="AP11" s="48">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ11" s="50" t="str">
         <f>AF38</f>
@@ -12791,11 +12789,11 @@
       </c>
       <c r="AR11" s="38">
         <f t="shared" si="26"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS11" s="38">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT11" s="38">
         <f t="shared" si="5"/>
@@ -12803,7 +12801,7 @@
       </c>
       <c r="AU11" s="38">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV11" s="38">
         <f t="shared" si="7"/>
@@ -12811,11 +12809,11 @@
       </c>
       <c r="AW11" s="38">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX11" s="38">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY11" s="38">
         <f t="shared" si="28"/>
@@ -12830,7 +12828,7 @@
       </c>
       <c r="BB11" s="38">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC11" s="38">
         <f t="shared" si="11"/>
@@ -12853,39 +12851,39 @@
       </c>
       <c r="BJ11" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Cabo Verde</v>
+        <v>Argélia</v>
       </c>
       <c r="BK11" s="84">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BL11" s="84">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM11" s="84">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN11" s="84">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO11" s="84">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP11" s="84">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BQ11" s="84">
         <f t="shared" si="21"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BR11" s="85">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="12" spans="1:70" x14ac:dyDescent="0.25">
@@ -12935,7 +12933,7 @@
       <c r="N12" s="46"/>
       <c r="O12" s="47">
         <f>RANK(Q12,$Q$12:$Q$15)+SUM(Y12:AB12)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P12" s="49" t="str">
         <f>Sorteios!F6</f>
@@ -12947,7 +12945,7 @@
       </c>
       <c r="R12" s="38">
         <f>SUM(S12:U12)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12" s="38">
         <f>COUNTIF(J:J,P12)</f>
@@ -12959,19 +12957,19 @@
       </c>
       <c r="U12" s="38">
         <f>COUNTIF(M:M,P12)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="38">
         <f>SUMIF(E:E,P12,F:F)+SUMIF(I:I,P12,H:H)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12" s="38">
         <f>SUMIF(E:E,P12,H:H)+SUMIF(I:I,P12,F:F)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X12" s="38">
         <f>V12-W12</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y12" s="38">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q12)*($X$12:$X$15&gt;X12))</f>
@@ -12998,19 +12996,19 @@
       </c>
       <c r="AF12" s="83" t="str">
         <f>VLOOKUP($AE12,$O$12:$X$15,2,FALSE)</f>
-        <v>Canadá</v>
+        <v>Suiça</v>
       </c>
       <c r="AG12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,3,FALSE)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AH12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,6,FALSE)</f>
@@ -13026,27 +13024,27 @@
       </c>
       <c r="AM12" s="84">
         <f>VLOOKUP($AE12,$O$12:$X$15,9,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN12" s="85">
         <f>VLOOKUP($AE12,$O$12:$X$15,10,FALSE)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AP12" s="48">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ12" s="50" t="str">
         <f>AF44</f>
-        <v>Bélgica</v>
+        <v>Irã</v>
       </c>
       <c r="AR12" s="38">
         <f t="shared" si="26"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS12" s="38">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT12" s="38">
         <f t="shared" si="5"/>
@@ -13054,7 +13052,7 @@
       </c>
       <c r="AU12" s="38">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV12" s="38">
         <f t="shared" si="7"/>
@@ -13062,11 +13060,11 @@
       </c>
       <c r="AW12" s="38">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX12" s="38">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY12" s="38">
         <f t="shared" si="28"/>
@@ -13077,15 +13075,15 @@
       </c>
       <c r="BA12" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Bélgica</v>
+        <v>Irã</v>
       </c>
       <c r="BB12" s="38">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC12" s="38">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD12" s="38">
         <f t="shared" si="12"/>
@@ -13104,39 +13102,39 @@
       </c>
       <c r="BJ12" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Bélgica</v>
+        <v>Paraguai</v>
       </c>
       <c r="BK12" s="84">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BL12" s="84">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM12" s="84">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN12" s="84">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO12" s="84">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP12" s="84">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ12" s="84">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BR12" s="85">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="13" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13194,15 +13192,15 @@
       </c>
       <c r="Q13" s="38">
         <f t="shared" ref="Q13:Q15" si="30">(S13*3)+(T13*1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R13" s="38">
         <f t="shared" ref="R13:R15" si="31">SUM(S13:U13)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13" s="38">
         <f>COUNTIF(J:J,P13)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="38">
         <f>COUNTIF(K:K,P13)+COUNTIF(L:L,P13)</f>
@@ -13214,19 +13212,19 @@
       </c>
       <c r="V13" s="38">
         <f>SUMIF(E:E,P13,F:F)+SUMIF(I:I,P13,H:H)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W13" s="38">
         <f>SUMIF(E:E,P13,H:H)+SUMIF(I:I,P13,F:F)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13" s="38">
         <f t="shared" ref="X13:X15" si="32">V13-W13</f>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="Y13" s="38">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q13)*($X$12:$X$15&gt;X13))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" s="38">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q13)*($X$12:$X$15=X13)*($V$12:$V$15&gt;V13))</f>
@@ -13249,7 +13247,7 @@
       </c>
       <c r="AF13" s="83" t="str">
         <f>VLOOKUP($AE13,$O$12:$X$15,2,FALSE)</f>
-        <v>Suiça</v>
+        <v>Canadá</v>
       </c>
       <c r="AG13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,3,FALSE)</f>
@@ -13257,7 +13255,7 @@
       </c>
       <c r="AH13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,5,FALSE)</f>
@@ -13269,27 +13267,27 @@
       </c>
       <c r="AK13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,8,FALSE)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AM13" s="84">
         <f>VLOOKUP($AE13,$O$12:$X$15,9,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN13" s="85">
         <f>VLOOKUP($AE13,$O$12:$X$15,10,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AP13" s="48">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AQ13" s="50" t="str">
         <f>AF50</f>
-        <v>Cabo Verde</v>
+        <v>Uruguai</v>
       </c>
       <c r="AR13" s="38">
         <f t="shared" si="26"/>
@@ -13297,7 +13295,7 @@
       </c>
       <c r="AS13" s="38">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT13" s="38">
         <f t="shared" si="5"/>
@@ -13309,26 +13307,26 @@
       </c>
       <c r="AV13" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW13" s="38">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX13" s="38">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY13" s="38">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AZ13" s="38" t="s">
         <v>62</v>
       </c>
       <c r="BA13" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Cabo Verde</v>
+        <v>Uruguai</v>
       </c>
       <c r="BB13" s="38">
         <f t="shared" si="10"/>
@@ -13355,39 +13353,39 @@
       </c>
       <c r="BJ13" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>República Tcheca</v>
+        <v>Senegal</v>
       </c>
       <c r="BK13" s="84">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL13" s="84">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM13" s="84">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN13" s="84">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO13" s="84">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP13" s="84">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BQ13" s="84">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BR13" s="85">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:70" x14ac:dyDescent="0.25">
@@ -13405,18 +13403,22 @@
         <f>P15</f>
         <v>Suiça</v>
       </c>
-      <c r="F14" s="123"/>
+      <c r="F14" s="123">
+        <v>2</v>
+      </c>
       <c r="G14" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="123"/>
+      <c r="H14" s="123">
+        <v>1</v>
+      </c>
       <c r="I14" s="113" t="str">
         <f>P12</f>
         <v>Canadá</v>
       </c>
       <c r="J14" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Suiça</v>
       </c>
       <c r="K14" s="38" t="str">
         <f t="shared" si="1"/>
@@ -13428,7 +13430,7 @@
       </c>
       <c r="M14" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Canadá</v>
       </c>
       <c r="N14" s="46"/>
       <c r="O14" s="47">
@@ -13445,7 +13447,7 @@
       </c>
       <c r="R14" s="38">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S14" s="38">
         <f>COUNTIF(J:J,P14)</f>
@@ -13457,23 +13459,23 @@
       </c>
       <c r="U14" s="38">
         <f>COUNTIF(M:M,P14)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V14" s="38">
         <f>SUMIF(E:E,P14,F:F)+SUMIF(I:I,P14,H:H)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W14" s="38">
         <f>SUMIF(E:E,P14,H:H)+SUMIF(I:I,P14,F:F)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X14" s="38">
         <f t="shared" si="32"/>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="Y14" s="38">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q14)*($X$12:$X$15&gt;X14))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="38">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q14)*($X$12:$X$15=X14)*($V$12:$V$15&gt;V14))</f>
@@ -13500,15 +13502,15 @@
       </c>
       <c r="AG14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,3,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,6,FALSE)</f>
@@ -13520,19 +13522,19 @@
       </c>
       <c r="AL14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,8,FALSE)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AM14" s="84">
         <f>VLOOKUP($AE14,$O$12:$X$15,9,FALSE)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN14" s="85">
         <f>VLOOKUP($AE14,$O$12:$X$15,10,FALSE)</f>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="AP14" s="48">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AQ14" s="50" t="str">
         <f>AF56</f>
@@ -13540,15 +13542,15 @@
       </c>
       <c r="AR14" s="38">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS14" s="38">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT14" s="38">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" s="38">
         <f t="shared" si="6"/>
@@ -13560,7 +13562,7 @@
       </c>
       <c r="AW14" s="38">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AX14" s="38">
         <f t="shared" si="9"/>
@@ -13568,7 +13570,7 @@
       </c>
       <c r="AY14" s="38">
         <f t="shared" si="28"/>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="AZ14" s="38" t="s">
         <v>69</v>
@@ -13602,15 +13604,15 @@
       </c>
       <c r="BJ14" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>RD Congo</v>
+        <v>Irã</v>
       </c>
       <c r="BK14" s="84">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL14" s="84">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM14" s="84">
         <f t="shared" si="17"/>
@@ -13618,23 +13620,23 @@
       </c>
       <c r="BN14" s="84">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BO14" s="84">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP14" s="84">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ14" s="84">
         <f t="shared" si="21"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR14" s="85">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13652,18 +13654,22 @@
         <f>P13</f>
         <v>Bósnia</v>
       </c>
-      <c r="F15" s="124"/>
+      <c r="F15" s="124">
+        <v>3</v>
+      </c>
       <c r="G15" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="124"/>
+      <c r="H15" s="124">
+        <v>1</v>
+      </c>
       <c r="I15" s="114" t="str">
         <f>P14</f>
         <v>Qatar</v>
       </c>
       <c r="J15" s="53" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Bósnia</v>
       </c>
       <c r="K15" s="53" t="str">
         <f t="shared" si="1"/>
@@ -13675,12 +13681,12 @@
       </c>
       <c r="M15" s="54" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Qatar</v>
       </c>
       <c r="N15" s="55"/>
       <c r="O15" s="56">
         <f>RANK(Q15,$Q$12:$Q$15)+SUM(Y15:AB15)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P15" s="49" t="str">
         <f>Sorteios!F9</f>
@@ -13688,15 +13694,15 @@
       </c>
       <c r="Q15" s="53">
         <f t="shared" si="30"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R15" s="53">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S15" s="38">
         <f>COUNTIF(J:J,P15)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" s="38">
         <f>COUNTIF(K:K,P15)+COUNTIF(L:L,P15)</f>
@@ -13708,19 +13714,19 @@
       </c>
       <c r="V15" s="53">
         <f>SUMIF(E:E,P15,F:F)+SUMIF(I:I,P15,H:H)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W15" s="53">
         <f>SUMIF(E:E,P15,H:H)+SUMIF(I:I,P15,F:F)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X15" s="53">
         <f t="shared" si="32"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y15" s="53">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q15)*($X$12:$X$15&gt;X15))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="53">
         <f>SUMPRODUCT(($Q$12:$Q$15=Q15)*($X$12:$X$15=X15)*($V$12:$V$15&gt;V15))</f>
@@ -13751,7 +13757,7 @@
       </c>
       <c r="AH15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,5,FALSE)</f>
@@ -13763,23 +13769,23 @@
       </c>
       <c r="AK15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,8,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM15" s="87">
         <f>VLOOKUP($AE15,$O$12:$X$15,9,FALSE)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AN15" s="88">
         <f>VLOOKUP($AE15,$O$12:$X$15,10,FALSE)</f>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AP15" s="48">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ15" s="50" t="str">
         <f>AF62</f>
@@ -13787,11 +13793,11 @@
       </c>
       <c r="AR15" s="38">
         <f t="shared" si="26"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS15" s="38">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT15" s="38">
         <f t="shared" si="5"/>
@@ -13799,7 +13805,7 @@
       </c>
       <c r="AU15" s="38">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV15" s="38">
         <f t="shared" si="7"/>
@@ -13807,11 +13813,11 @@
       </c>
       <c r="AW15" s="38">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX15" s="38">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY15" s="38">
         <f t="shared" si="28"/>
@@ -13826,7 +13832,7 @@
       </c>
       <c r="BB15" s="38">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC15" s="38">
         <f t="shared" si="11"/>
@@ -13838,7 +13844,7 @@
       </c>
       <c r="BE15" s="38">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF15" s="39">
         <v>10</v>
@@ -13849,35 +13855,35 @@
       </c>
       <c r="BJ15" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Equador</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="BK15" s="84">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL15" s="84">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM15" s="84">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN15" s="84">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO15" s="84">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP15" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ15" s="84">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR15" s="85">
         <f t="shared" si="22"/>
@@ -13961,7 +13967,7 @@
       <c r="AN16" s="80"/>
       <c r="AP16" s="48">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AQ16" s="50" t="str">
         <f>AF68</f>
@@ -13969,15 +13975,15 @@
       </c>
       <c r="AR16" s="38">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS16" s="38">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT16" s="38">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" s="38">
         <f t="shared" si="6"/>
@@ -13989,15 +13995,15 @@
       </c>
       <c r="AW16" s="38">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX16" s="38">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY16" s="38">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AZ16" s="38" t="s">
         <v>70</v>
@@ -14012,7 +14018,7 @@
       </c>
       <c r="BC16" s="38">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD16" s="38">
         <f t="shared" si="12"/>
@@ -14031,35 +14037,35 @@
       </c>
       <c r="BJ16" s="83" t="str">
         <f t="shared" si="14"/>
-        <v>Bósnia</v>
+        <v>Escócia</v>
       </c>
       <c r="BK16" s="84">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL16" s="84">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM16" s="84">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN16" s="84">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO16" s="84">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP16" s="84">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ16" s="84">
         <f t="shared" si="21"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BR16" s="85">
         <f t="shared" si="22"/>
@@ -14189,19 +14195,19 @@
       </c>
       <c r="AP17" s="48">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ17" s="50" t="str">
         <f>AF74</f>
-        <v>Croácia</v>
+        <v>Gana</v>
       </c>
       <c r="AR17" s="38">
         <f t="shared" si="26"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS17" s="38">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT17" s="38">
         <f t="shared" si="5"/>
@@ -14209,7 +14215,7 @@
       </c>
       <c r="AU17" s="38">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV17" s="38">
         <f t="shared" si="7"/>
@@ -14217,30 +14223,30 @@
       </c>
       <c r="AW17" s="38">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX17" s="38">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY17" s="38">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ17" s="38" t="s">
         <v>71</v>
       </c>
       <c r="BA17" s="38" t="str">
         <f t="shared" si="29"/>
-        <v>Croácia</v>
+        <v>Gana</v>
       </c>
       <c r="BB17" s="38">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC17" s="38">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD17" s="38">
         <f t="shared" si="12"/>
@@ -14248,7 +14254,7 @@
       </c>
       <c r="BE17" s="38">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF17" s="54">
         <v>12</v>
@@ -14259,15 +14265,15 @@
       </c>
       <c r="BJ17" s="86" t="str">
         <f t="shared" si="14"/>
-        <v>Senegal</v>
+        <v>Uruguai</v>
       </c>
       <c r="BK17" s="87">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL17" s="87">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM17" s="87">
         <f t="shared" si="17"/>
@@ -14275,11 +14281,11 @@
       </c>
       <c r="BN17" s="87">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BO17" s="87">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP17" s="87">
         <f t="shared" si="20"/>
@@ -14287,11 +14293,11 @@
       </c>
       <c r="BQ17" s="87">
         <f t="shared" si="21"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BR17" s="88">
         <f t="shared" si="22"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18" spans="1:70" x14ac:dyDescent="0.25">
@@ -14349,15 +14355,15 @@
       </c>
       <c r="Q18" s="38">
         <f>(S18*3)+(T18*1)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R18" s="38">
         <f>SUM(S18:U18)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S18" s="38">
         <f>COUNTIF(J:J,P18)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" s="38">
         <f>COUNTIF(K:K,P18)+COUNTIF(L:L,P18)</f>
@@ -14369,7 +14375,7 @@
       </c>
       <c r="V18" s="38">
         <f>SUMIF(E:E,P18,F:F)+SUMIF(I:I,P18,H:H)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W18" s="38">
         <f>SUMIF(E:E,P18,H:H)+SUMIF(I:I,P18,F:F)</f>
@@ -14377,7 +14383,7 @@
       </c>
       <c r="X18" s="38">
         <f>V18-W18</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y18" s="38">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q18)*($X$18:$X$21&gt;X18))</f>
@@ -14408,15 +14414,15 @@
       </c>
       <c r="AG18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,3,FALSE)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AH18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,6,FALSE)</f>
@@ -14428,7 +14434,7 @@
       </c>
       <c r="AL18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,8,FALSE)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AM18" s="84">
         <f>VLOOKUP($AE18,$O$18:$X$21,9,FALSE)</f>
@@ -14436,11 +14442,11 @@
       </c>
       <c r="AN18" s="85">
         <f>VLOOKUP($AE18,$O$18:$X$21,10,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BL18" s="153">
         <f>SUM(BL6:BL17)</f>
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:70" x14ac:dyDescent="0.25">
@@ -14498,15 +14504,15 @@
       </c>
       <c r="Q19" s="38">
         <f t="shared" ref="Q19:Q21" si="33">(S19*3)+(T19*1)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R19" s="38">
         <f t="shared" ref="R19:R21" si="34">SUM(S19:U19)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S19" s="38">
         <f>COUNTIF(J:J,P19)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T19" s="38">
         <f>COUNTIF(K:K,P19)+COUNTIF(L:L,P19)</f>
@@ -14518,15 +14524,15 @@
       </c>
       <c r="V19" s="38">
         <f>SUMIF(E:E,P19,F:F)+SUMIF(I:I,P19,H:H)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W19" s="38">
         <f>SUMIF(E:E,P19,H:H)+SUMIF(I:I,P19,F:F)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X19" s="38">
         <f t="shared" ref="X19:X21" si="35">V19-W19</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y19" s="38">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q19)*($X$18:$X$21&gt;X19))</f>
@@ -14557,15 +14563,15 @@
       </c>
       <c r="AG19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,3,FALSE)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AH19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,6,FALSE)</f>
@@ -14577,15 +14583,15 @@
       </c>
       <c r="AL19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,8,FALSE)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AM19" s="84">
         <f>VLOOKUP($AE19,$O$18:$X$21,9,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN19" s="85">
         <f>VLOOKUP($AE19,$O$18:$X$21,10,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:70" x14ac:dyDescent="0.25">
@@ -14603,18 +14609,22 @@
         <f>P21</f>
         <v>Escócia</v>
       </c>
-      <c r="F20" s="123"/>
+      <c r="F20" s="123">
+        <v>0</v>
+      </c>
       <c r="G20" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="123"/>
+      <c r="H20" s="123">
+        <v>3</v>
+      </c>
       <c r="I20" s="107" t="str">
         <f>P18</f>
         <v>Brasil</v>
       </c>
       <c r="J20" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Brasil</v>
       </c>
       <c r="K20" s="38" t="str">
         <f t="shared" si="1"/>
@@ -14626,7 +14636,7 @@
       </c>
       <c r="M20" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Escócia</v>
       </c>
       <c r="N20" s="46"/>
       <c r="O20" s="47">
@@ -14643,7 +14653,7 @@
       </c>
       <c r="R20" s="38">
         <f t="shared" si="34"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S20" s="38">
         <f>COUNTIF(J:J,P20)</f>
@@ -14655,19 +14665,19 @@
       </c>
       <c r="U20" s="38">
         <f>COUNTIF(M:M,P20)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V20" s="38">
         <f>SUMIF(E:E,P20,F:F)+SUMIF(I:I,P20,H:H)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" s="38">
         <f>SUMIF(E:E,P20,H:H)+SUMIF(I:I,P20,F:F)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X20" s="38">
         <f t="shared" si="35"/>
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="Y20" s="38">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q20)*($X$18:$X$21&gt;X20))</f>
@@ -14702,7 +14712,7 @@
       </c>
       <c r="AH20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,5,FALSE)</f>
@@ -14714,7 +14724,7 @@
       </c>
       <c r="AK20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,8,FALSE)</f>
@@ -14722,11 +14732,11 @@
       </c>
       <c r="AM20" s="84">
         <f>VLOOKUP($AE20,$O$18:$X$21,9,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN20" s="85">
         <f>VLOOKUP($AE20,$O$18:$X$21,10,FALSE)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14744,18 +14754,22 @@
         <f>P19</f>
         <v>Marrocos</v>
       </c>
-      <c r="F21" s="124"/>
+      <c r="F21" s="124">
+        <v>4</v>
+      </c>
       <c r="G21" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="124"/>
+      <c r="H21" s="124">
+        <v>2</v>
+      </c>
       <c r="I21" s="109" t="str">
         <f>P20</f>
         <v>Haiti</v>
       </c>
       <c r="J21" s="53" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Marrocos</v>
       </c>
       <c r="K21" s="53" t="str">
         <f t="shared" si="1"/>
@@ -14767,7 +14781,7 @@
       </c>
       <c r="M21" s="54" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Haiti</v>
       </c>
       <c r="N21" s="55"/>
       <c r="O21" s="56">
@@ -14784,7 +14798,7 @@
       </c>
       <c r="R21" s="53">
         <f t="shared" si="34"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S21" s="38">
         <f>COUNTIF(J:J,P21)</f>
@@ -14796,7 +14810,7 @@
       </c>
       <c r="U21" s="38">
         <f>COUNTIF(M:M,P21)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" s="53">
         <f>SUMIF(E:E,P21,F:F)+SUMIF(I:I,P21,H:H)</f>
@@ -14804,11 +14818,11 @@
       </c>
       <c r="W21" s="53">
         <f>SUMIF(E:E,P21,H:H)+SUMIF(I:I,P21,F:F)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X21" s="53">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Y21" s="53">
         <f>SUMPRODUCT(($Q$18:$Q$21=Q21)*($X$18:$X$21&gt;X21))</f>
@@ -14843,7 +14857,7 @@
       </c>
       <c r="AH21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,5,FALSE)</f>
@@ -14855,30 +14869,30 @@
       </c>
       <c r="AK21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,7,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM21" s="87">
         <f>VLOOKUP($AE21,$O$18:$X$21,9,FALSE)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AN21" s="88">
         <f>VLOOKUP($AE21,$O$18:$X$21,10,FALSE)</f>
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="AP21" s="15">
         <v>1</v>
       </c>
       <c r="AQ21" s="15" t="str">
         <f t="shared" ref="AQ21:AQ28" si="36">VLOOKUP($BI6,$AP$6:$AZ$17,11,FALSE)</f>
-        <v>F</v>
+        <v>K</v>
       </c>
       <c r="AR21" s="15">
         <f>CODE(AQ21)</f>
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:70" x14ac:dyDescent="0.25">
@@ -14961,11 +14975,11 @@
       </c>
       <c r="AQ22" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>C</v>
+        <v>F</v>
       </c>
       <c r="AR22" s="15">
         <f t="shared" ref="AR22:AR28" si="37">CODE(AQ22)</f>
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:70" x14ac:dyDescent="0.25">
@@ -15094,11 +15108,11 @@
       </c>
       <c r="AQ23" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>L</v>
+        <v>E</v>
       </c>
       <c r="AR23" s="15">
         <f t="shared" si="37"/>
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:70" x14ac:dyDescent="0.25">
@@ -15160,7 +15174,7 @@
       </c>
       <c r="R24" s="38">
         <f>SUM(S24:U24)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S24" s="38">
         <f>COUNTIF(J:J,P24)</f>
@@ -15172,19 +15186,19 @@
       </c>
       <c r="U24" s="38">
         <f>COUNTIF(M:M,P24)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="38">
         <f>SUMIF(E:E,P24,F:F)+SUMIF(I:I,P24,H:H)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W24" s="38">
         <f>SUMIF(E:E,P24,H:H)+SUMIF(I:I,P24,F:F)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X24" s="38">
         <f>V24-W24</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y24" s="38">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q24)*($X$24:$X$27&gt;X24))</f>
@@ -15219,7 +15233,7 @@
       </c>
       <c r="AH24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,5,FALSE)</f>
@@ -15231,30 +15245,30 @@
       </c>
       <c r="AK24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,8,FALSE)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM24" s="84">
         <f>VLOOKUP($AE24,$O$24:$X$27,9,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN24" s="85">
         <f>VLOOKUP($AE24,$O$24:$X$27,10,FALSE)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP24" s="15">
         <v>4</v>
       </c>
       <c r="AQ24" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>D</v>
+        <v>L</v>
       </c>
       <c r="AR24" s="15">
         <f t="shared" si="37"/>
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:70" x14ac:dyDescent="0.25">
@@ -15312,11 +15326,11 @@
       </c>
       <c r="Q25" s="38">
         <f t="shared" ref="Q25:Q27" si="38">(S25*3)+(T25*1)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R25" s="38">
         <f t="shared" ref="R25:R27" si="39">SUM(S25:U25)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S25" s="38">
         <f>COUNTIF(J:J,P25)</f>
@@ -15324,7 +15338,7 @@
       </c>
       <c r="T25" s="38">
         <f>COUNTIF(K:K,P25)+COUNTIF(L:L,P25)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="38">
         <f>COUNTIF(M:M,P25)</f>
@@ -15371,11 +15385,11 @@
       </c>
       <c r="AG25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,5,FALSE)</f>
@@ -15383,7 +15397,7 @@
       </c>
       <c r="AJ25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK25" s="84">
         <f>VLOOKUP($AE25,$O$24:$X$27,7,FALSE)</f>
@@ -15406,11 +15420,11 @@
       </c>
       <c r="AQ25" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>J</v>
+        <v>B</v>
       </c>
       <c r="AR25" s="15">
         <f t="shared" si="37"/>
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:70" x14ac:dyDescent="0.25">
@@ -15428,18 +15442,22 @@
         <f>P27</f>
         <v>Turquia</v>
       </c>
-      <c r="F26" s="123"/>
+      <c r="F26" s="123">
+        <v>3</v>
+      </c>
       <c r="G26" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H26" s="123"/>
+      <c r="H26" s="123">
+        <v>2</v>
+      </c>
       <c r="I26" s="113" t="str">
         <f>P24</f>
         <v>Estados Unidos</v>
       </c>
       <c r="J26" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Turquia</v>
       </c>
       <c r="K26" s="38" t="str">
         <f t="shared" si="1"/>
@@ -15451,7 +15469,7 @@
       </c>
       <c r="M26" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Estados Unidos</v>
       </c>
       <c r="N26" s="45"/>
       <c r="O26" s="47">
@@ -15464,11 +15482,11 @@
       </c>
       <c r="Q26" s="38">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R26" s="38">
         <f t="shared" si="39"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S26" s="38">
         <f>COUNTIF(J:J,P26)</f>
@@ -15476,7 +15494,7 @@
       </c>
       <c r="T26" s="38">
         <f>COUNTIF(K:K,P26)+COUNTIF(L:L,P26)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" s="38">
         <f>COUNTIF(M:M,P26)</f>
@@ -15523,11 +15541,11 @@
       </c>
       <c r="AG26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,5,FALSE)</f>
@@ -15535,7 +15553,7 @@
       </c>
       <c r="AJ26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK26" s="84">
         <f>VLOOKUP($AE26,$O$24:$X$27,7,FALSE)</f>
@@ -15558,11 +15576,11 @@
       </c>
       <c r="AQ26" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>H</v>
+        <v>J</v>
       </c>
       <c r="AR26" s="15">
         <f t="shared" si="37"/>
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -15580,11 +15598,15 @@
         <f>P25</f>
         <v>Paraguai</v>
       </c>
-      <c r="F27" s="124"/>
+      <c r="F27" s="124">
+        <v>0</v>
+      </c>
       <c r="G27" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="H27" s="124"/>
+      <c r="H27" s="124">
+        <v>0</v>
+      </c>
       <c r="I27" s="114" t="str">
         <f>P26</f>
         <v>Austrália</v>
@@ -15595,11 +15617,11 @@
       </c>
       <c r="K27" s="53" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Paraguai</v>
       </c>
       <c r="L27" s="53" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Austrália</v>
       </c>
       <c r="M27" s="54" t="str">
         <f t="shared" si="3"/>
@@ -15616,15 +15638,15 @@
       </c>
       <c r="Q27" s="53">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" s="53">
         <f t="shared" si="39"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S27" s="38">
         <f>COUNTIF(J:J,P27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" s="38">
         <f>COUNTIF(K:K,P27)+COUNTIF(L:L,P27)</f>
@@ -15636,15 +15658,15 @@
       </c>
       <c r="V27" s="53">
         <f>SUMIF(E:E,P27,F:F)+SUMIF(I:I,P27,H:H)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" s="53">
         <f>SUMIF(E:E,P27,H:H)+SUMIF(I:I,P27,F:F)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X27" s="53">
         <f t="shared" si="40"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="Y27" s="53">
         <f>SUMPRODUCT(($Q$24:$Q$27=Q27)*($X$24:$X$27&gt;X27))</f>
@@ -15675,15 +15697,15 @@
       </c>
       <c r="AG27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,6,FALSE)</f>
@@ -15695,26 +15717,26 @@
       </c>
       <c r="AL27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM27" s="87">
         <f>VLOOKUP($AE27,$O$24:$X$27,9,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN27" s="88">
         <f>VLOOKUP($AE27,$O$24:$X$27,10,FALSE)</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AP27" s="15">
         <v>7</v>
       </c>
       <c r="AQ27" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>G</v>
+        <v>D</v>
       </c>
       <c r="AR27" s="15">
         <f t="shared" si="37"/>
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:70" x14ac:dyDescent="0.25">
@@ -15797,11 +15819,11 @@
       </c>
       <c r="AQ28" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>A</v>
+        <v>I</v>
       </c>
       <c r="AR28" s="15">
         <f t="shared" si="37"/>
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:70" x14ac:dyDescent="0.25">
@@ -15985,7 +16007,7 @@
       </c>
       <c r="R30" s="38">
         <f>SUM(S30:U30)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S30" s="38">
         <f>COUNTIF(J:J,P30)</f>
@@ -15997,19 +16019,19 @@
       </c>
       <c r="U30" s="38">
         <f>COUNTIF(M:M,P30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="38">
         <f>SUMIF(E:E,P30,F:F)+SUMIF(I:I,P30,H:H)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W30" s="38">
         <f>SUMIF(E:E,P30,H:H)+SUMIF(I:I,P30,F:F)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X30" s="38">
         <f>V30-W30</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y30" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q30)*($X$30:$X$33&gt;X30))</f>
@@ -16044,7 +16066,7 @@
       </c>
       <c r="AH30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,5,FALSE)</f>
@@ -16056,31 +16078,31 @@
       </c>
       <c r="AK30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,8,FALSE)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM30" s="84">
         <f>VLOOKUP($AE30,$O$30:$X$33,9,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN30" s="85">
         <f>VLOOKUP($AE30,$O$30:$X$33,10,FALSE)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ30" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,1))</f>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AR30" s="15" t="str">
         <f>_xlfn.CONCAT(3,AQ30)</f>
-        <v>3A</v>
+        <v>3B</v>
       </c>
       <c r="AS30" s="15" t="str">
         <f t="shared" ref="AS30:AS37" si="41">VLOOKUP(AQ30,$AZ$6:$BA$17,2,FALSE)</f>
-        <v>República Tcheca</v>
+        <v>Bósnia</v>
       </c>
     </row>
     <row r="31" spans="1:70" x14ac:dyDescent="0.25">
@@ -16142,7 +16164,7 @@
       </c>
       <c r="R31" s="38">
         <f t="shared" ref="R31:R33" si="43">SUM(S31:U31)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S31" s="38">
         <f>COUNTIF(J:J,P31)</f>
@@ -16154,7 +16176,7 @@
       </c>
       <c r="U31" s="38">
         <f>COUNTIF(M:M,P31)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V31" s="38">
         <f>SUMIF(E:E,P31,F:F)+SUMIF(I:I,P31,H:H)</f>
@@ -16162,15 +16184,15 @@
       </c>
       <c r="W31" s="38">
         <f>SUMIF(E:E,P31,H:H)+SUMIF(I:I,P31,F:F)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X31" s="38">
         <f t="shared" ref="X31:X33" si="44">V31-W31</f>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="Y31" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q31)*($X$30:$X$33&gt;X31))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q31)*($X$30:$X$33=X31)*($V$30:$V$33&gt;V31))</f>
@@ -16197,15 +16219,15 @@
       </c>
       <c r="AG31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,6,FALSE)</f>
@@ -16217,7 +16239,7 @@
       </c>
       <c r="AL31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,8,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM31" s="84">
         <f>VLOOKUP($AE31,$O$30:$X$33,9,FALSE)</f>
@@ -16225,19 +16247,19 @@
       </c>
       <c r="AN31" s="85">
         <f>VLOOKUP($AE31,$O$30:$X$33,10,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ31" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,2))</f>
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="AR31" s="15" t="str">
         <f t="shared" ref="AR31:AR37" si="45">_xlfn.CONCAT(3,AQ31)</f>
-        <v>3C</v>
+        <v>3D</v>
       </c>
       <c r="AS31" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Escócia</v>
+        <v>Paraguai</v>
       </c>
     </row>
     <row r="32" spans="1:70" x14ac:dyDescent="0.25">
@@ -16255,18 +16277,22 @@
         <f>P33</f>
         <v>Equador</v>
       </c>
-      <c r="F32" s="123"/>
+      <c r="F32" s="123">
+        <v>2</v>
+      </c>
       <c r="G32" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="123"/>
+      <c r="H32" s="123">
+        <v>1</v>
+      </c>
       <c r="I32" s="107" t="str">
         <f>P30</f>
         <v>Alemanha</v>
       </c>
       <c r="J32" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Equador</v>
       </c>
       <c r="K32" s="38" t="str">
         <f t="shared" si="1"/>
@@ -16278,7 +16304,7 @@
       </c>
       <c r="M32" s="39" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Alemanha</v>
       </c>
       <c r="N32" s="46"/>
       <c r="O32" s="47">
@@ -16291,15 +16317,15 @@
       </c>
       <c r="Q32" s="38">
         <f t="shared" si="42"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R32" s="38">
         <f t="shared" si="43"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S32" s="38">
         <f>COUNTIF(J:J,P32)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T32" s="38">
         <f>COUNTIF(K:K,P32)+COUNTIF(L:L,P32)</f>
@@ -16311,7 +16337,7 @@
       </c>
       <c r="V32" s="38">
         <f>SUMIF(E:E,P32,F:F)+SUMIF(I:I,P32,H:H)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W32" s="38">
         <f>SUMIF(E:E,P32,H:H)+SUMIF(I:I,P32,F:F)</f>
@@ -16319,11 +16345,11 @@
       </c>
       <c r="X32" s="38">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y32" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q32)*($X$30:$X$33&gt;X32))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" s="38">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q32)*($X$30:$X$33=X32)*($V$30:$V$33&gt;V32))</f>
@@ -16350,15 +16376,15 @@
       </c>
       <c r="AG32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,3,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,6,FALSE)</f>
@@ -16370,27 +16396,27 @@
       </c>
       <c r="AL32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM32" s="84">
         <f>VLOOKUP($AE32,$O$30:$X$33,9,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN32" s="85">
         <f>VLOOKUP($AE32,$O$30:$X$33,10,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ32" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,3))</f>
-        <v>D</v>
+        <v>E</v>
       </c>
       <c r="AR32" s="15" t="str">
         <f t="shared" si="45"/>
-        <v>3D</v>
+        <v>3E</v>
       </c>
       <c r="AS32" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Paraguai</v>
+        <v>Equador</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -16408,18 +16434,22 @@
         <f>P31</f>
         <v>Curaçau</v>
       </c>
-      <c r="F33" s="124"/>
+      <c r="F33" s="124">
+        <v>0</v>
+      </c>
       <c r="G33" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="H33" s="124"/>
+      <c r="H33" s="124">
+        <v>2</v>
+      </c>
       <c r="I33" s="109" t="str">
         <f>P32</f>
         <v>Costa do Marfim</v>
       </c>
       <c r="J33" s="53" t="str">
         <f t="shared" si="0"/>
-        <v>empate</v>
+        <v>Costa do Marfim</v>
       </c>
       <c r="K33" s="53" t="str">
         <f t="shared" si="1"/>
@@ -16431,7 +16461,7 @@
       </c>
       <c r="M33" s="54" t="str">
         <f t="shared" si="3"/>
-        <v>empate</v>
+        <v>Curaçau</v>
       </c>
       <c r="N33" s="55"/>
       <c r="O33" s="56">
@@ -16444,15 +16474,15 @@
       </c>
       <c r="Q33" s="53">
         <f t="shared" si="42"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R33" s="53">
         <f t="shared" si="43"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S33" s="38">
         <f>COUNTIF(J:J,P33)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" s="38">
         <f>COUNTIF(K:K,P33)+COUNTIF(L:L,P33)</f>
@@ -16464,15 +16494,15 @@
       </c>
       <c r="V33" s="53">
         <f>SUMIF(E:E,P33,F:F)+SUMIF(I:I,P33,H:H)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W33" s="53">
         <f>SUMIF(E:E,P33,H:H)+SUMIF(I:I,P33,F:F)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X33" s="53">
         <f t="shared" si="44"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="53">
         <f>SUMPRODUCT(($Q$30:$Q$33=Q33)*($X$30:$X$33&gt;X33))</f>
@@ -16507,7 +16537,7 @@
       </c>
       <c r="AH33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,5,FALSE)</f>
@@ -16519,7 +16549,7 @@
       </c>
       <c r="AK33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,8,FALSE)</f>
@@ -16527,11 +16557,11 @@
       </c>
       <c r="AM33" s="87">
         <f>VLOOKUP($AE33,$O$30:$X$33,9,FALSE)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AN33" s="88">
         <f>VLOOKUP($AE33,$O$30:$X$33,10,FALSE)</f>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AQ33" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,4))</f>
@@ -16623,15 +16653,15 @@
       <c r="AN34" s="80"/>
       <c r="AQ34" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,5))</f>
-        <v>G</v>
+        <v>I</v>
       </c>
       <c r="AR34" s="15" t="str">
         <f t="shared" si="45"/>
-        <v>3G</v>
+        <v>3I</v>
       </c>
       <c r="AS34" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Bélgica</v>
+        <v>Senegal</v>
       </c>
     </row>
     <row r="35" spans="1:45" x14ac:dyDescent="0.25">
@@ -16757,15 +16787,15 @@
       </c>
       <c r="AQ35" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,6))</f>
-        <v>H</v>
+        <v>J</v>
       </c>
       <c r="AR35" s="15" t="str">
         <f t="shared" si="45"/>
-        <v>3H</v>
+        <v>3J</v>
       </c>
       <c r="AS35" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Cabo Verde</v>
+        <v>Argélia</v>
       </c>
     </row>
     <row r="36" spans="1:45" x14ac:dyDescent="0.25">
@@ -16823,15 +16853,15 @@
       </c>
       <c r="Q36" s="38">
         <f>(S36*3)+(T36*1)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R36" s="38">
         <f>SUM(S36:U36)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S36" s="38">
         <f>COUNTIF(J:J,P36)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T36" s="38">
         <f>COUNTIF(K:K,P36)+COUNTIF(L:L,P36)</f>
@@ -16843,15 +16873,15 @@
       </c>
       <c r="V36" s="38">
         <f>SUMIF(E:E,P36,F:F)+SUMIF(I:I,P36,H:H)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W36" s="38">
         <f>SUMIF(E:E,P36,H:H)+SUMIF(I:I,P36,F:F)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X36" s="38">
         <f>V36-W36</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y36" s="38">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q36)*($X$36:$X$39&gt;X36))</f>
@@ -16882,15 +16912,15 @@
       </c>
       <c r="AG36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,3,FALSE)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AH36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,6,FALSE)</f>
@@ -16902,27 +16932,27 @@
       </c>
       <c r="AL36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,8,FALSE)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AM36" s="84">
         <f>VLOOKUP($AE36,$O$36:$X$39,9,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN36" s="85">
         <f>VLOOKUP($AE36,$O$36:$X$39,10,FALSE)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ36" s="15" t="str">
         <f>CHAR(SMALL($AR$21:$AR$28,7))</f>
-        <v>J</v>
+        <v>K</v>
       </c>
       <c r="AR36" s="15" t="str">
         <f t="shared" si="45"/>
-        <v>3J</v>
+        <v>3K</v>
       </c>
       <c r="AS36" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Argélia</v>
+        <v>RD Congo</v>
       </c>
     </row>
     <row r="37" spans="1:45" x14ac:dyDescent="0.25">
@@ -16980,11 +17010,11 @@
       </c>
       <c r="Q37" s="38">
         <f t="shared" ref="Q37:Q39" si="50">(S37*3)+(T37*1)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R37" s="38">
         <f t="shared" ref="R37:R39" si="51">SUM(S37:U37)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S37" s="38">
         <f>COUNTIF(J:J,P37)</f>
@@ -16992,7 +17022,7 @@
       </c>
       <c r="T37" s="38">
         <f>COUNTIF(K:K,P37)+COUNTIF(L:L,P37)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U37" s="38">
         <f>COUNTIF(M:M,P37)</f>
@@ -17000,11 +17030,11 @@
       </c>
       <c r="V37" s="38">
         <f>SUMIF(E:E,P37,F:F)+SUMIF(I:I,P37,H:H)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W37" s="38">
         <f>SUMIF(E:E,P37,H:H)+SUMIF(I:I,P37,F:F)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X37" s="38">
         <f t="shared" ref="X37:X39" si="52">V37-W37</f>
@@ -17016,7 +17046,7 @@
       </c>
       <c r="Z37" s="38">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q37)*($X$36:$X$39=X37)*($V$36:$V$39&gt;V37))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="38">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q37)*($X$36:$X$39=X37)*($V$36:$V$39=V37)*($W$36:$W$39&gt;W37))</f>
@@ -17039,11 +17069,11 @@
       </c>
       <c r="AG37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,3,FALSE)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,5,FALSE)</f>
@@ -17051,7 +17081,7 @@
       </c>
       <c r="AJ37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,7,FALSE)</f>
@@ -17059,11 +17089,11 @@
       </c>
       <c r="AL37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,8,FALSE)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM37" s="84">
         <f>VLOOKUP($AE37,$O$36:$X$39,9,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN37" s="85">
         <f>VLOOKUP($AE37,$O$36:$X$39,10,FALSE)</f>
@@ -17079,7 +17109,7 @@
       </c>
       <c r="AS37" s="15" t="str">
         <f t="shared" si="41"/>
-        <v>Croácia</v>
+        <v>Gana</v>
       </c>
     </row>
     <row r="38" spans="1:45" x14ac:dyDescent="0.25">
@@ -17097,18 +17127,22 @@
         <f>P39</f>
         <v>Tunísia</v>
       </c>
-      <c r="F38" s="123"/>
+      <c r="F38" s="123">
+        <v>1</v>
+      </c>
       <c r="G38" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H38" s="123"/>
+      <c r="H38" s="123">
+        <v>3</v>
+      </c>
       <c r="I38" s="113" t="str">
         <f>P36</f>
         <v>Países Baixos</v>
       </c>
       <c r="J38" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Países Baixos</v>
       </c>
       <c r="K38" s="38" t="str">
         <f t="shared" si="47"/>
@@ -17120,7 +17154,7 @@
       </c>
       <c r="M38" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Tunísia</v>
       </c>
       <c r="N38" s="45"/>
       <c r="O38" s="47">
@@ -17133,11 +17167,11 @@
       </c>
       <c r="Q38" s="38">
         <f t="shared" si="50"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R38" s="38">
         <f t="shared" si="51"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S38" s="38">
         <f>COUNTIF(J:J,P38)</f>
@@ -17145,7 +17179,7 @@
       </c>
       <c r="T38" s="38">
         <f>COUNTIF(K:K,P38)+COUNTIF(L:L,P38)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" s="38">
         <f>COUNTIF(M:M,P38)</f>
@@ -17153,11 +17187,11 @@
       </c>
       <c r="V38" s="38">
         <f>SUMIF(E:E,P38,F:F)+SUMIF(I:I,P38,H:H)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W38" s="38">
         <f>SUMIF(E:E,P38,H:H)+SUMIF(I:I,P38,F:F)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X38" s="38">
         <f t="shared" si="52"/>
@@ -17192,11 +17226,11 @@
       </c>
       <c r="AG38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,5,FALSE)</f>
@@ -17204,7 +17238,7 @@
       </c>
       <c r="AJ38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,7,FALSE)</f>
@@ -17212,11 +17246,11 @@
       </c>
       <c r="AL38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,8,FALSE)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM38" s="84">
         <f>VLOOKUP($AE38,$O$36:$X$39,9,FALSE)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN38" s="85">
         <f>VLOOKUP($AE38,$O$36:$X$39,10,FALSE)</f>
@@ -17238,11 +17272,15 @@
         <f>P37</f>
         <v>Japão</v>
       </c>
-      <c r="F39" s="124"/>
+      <c r="F39" s="124">
+        <v>1</v>
+      </c>
       <c r="G39" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="H39" s="124"/>
+      <c r="H39" s="124">
+        <v>1</v>
+      </c>
       <c r="I39" s="114" t="str">
         <f>P38</f>
         <v>Suécia</v>
@@ -17253,11 +17291,11 @@
       </c>
       <c r="K39" s="53" t="str">
         <f t="shared" si="47"/>
-        <v/>
+        <v>Japão</v>
       </c>
       <c r="L39" s="53" t="str">
         <f t="shared" si="48"/>
-        <v/>
+        <v>Suécia</v>
       </c>
       <c r="M39" s="54" t="str">
         <f t="shared" si="49"/>
@@ -17278,7 +17316,7 @@
       </c>
       <c r="R39" s="53">
         <f t="shared" si="51"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S39" s="38">
         <f>COUNTIF(J:J,P39)</f>
@@ -17290,19 +17328,19 @@
       </c>
       <c r="U39" s="38">
         <f>COUNTIF(M:M,P39)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V39" s="53">
         <f>SUMIF(E:E,P39,F:F)+SUMIF(I:I,P39,H:H)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W39" s="53">
         <f>SUMIF(E:E,P39,H:H)+SUMIF(I:I,P39,F:F)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="X39" s="53">
         <f t="shared" si="52"/>
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="Y39" s="53">
         <f>SUMPRODUCT(($Q$36:$Q$39=Q39)*($X$36:$X$39&gt;X39))</f>
@@ -17337,7 +17375,7 @@
       </c>
       <c r="AH39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,5,FALSE)</f>
@@ -17349,27 +17387,27 @@
       </c>
       <c r="AK39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,7,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,8,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM39" s="87">
         <f>VLOOKUP($AE39,$O$36:$X$39,9,FALSE)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AN39" s="88">
         <f>VLOOKUP($AE39,$O$36:$X$39,10,FALSE)</f>
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="AQ39" s="15" t="str">
         <f>_xlfn.CONCAT(AQ30:AQ37)</f>
-        <v>ACDFGHJL</v>
+        <v>BDEFIJKL</v>
       </c>
       <c r="AR39" s="15" t="str">
         <f>VLOOKUP(AQ39,Dummy!O:X,10,FALSE)</f>
-        <v>3C3G3J3D3A3F3L3H</v>
+        <v>3E3J3B3D3I3F3L3K</v>
       </c>
     </row>
     <row r="40" spans="1:45" x14ac:dyDescent="0.25">
@@ -17617,7 +17655,7 @@
       <c r="N42" s="46"/>
       <c r="O42" s="47">
         <f>RANK(Q42,$Q$42:$Q$45)+SUM(Y42:AB42)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P42" s="49" t="str">
         <f>Sorteios!C22</f>
@@ -17625,15 +17663,15 @@
       </c>
       <c r="Q42" s="38">
         <f>(S42*3)+(T42*1)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R42" s="38">
         <f>SUM(S42:U42)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S42" s="38">
         <f>COUNTIF(J:J,P42)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" s="38">
         <f>COUNTIF(K:K,P42)+COUNTIF(L:L,P42)</f>
@@ -17645,15 +17683,15 @@
       </c>
       <c r="V42" s="38">
         <f>SUMIF(E:E,P42,F:F)+SUMIF(I:I,P42,H:H)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W42" s="38">
         <f>SUMIF(E:E,P42,H:H)+SUMIF(I:I,P42,F:F)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X42" s="38">
         <f>V42-W42</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y42" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q42)*($X$42:$X$45&gt;X42))</f>
@@ -17661,7 +17699,7 @@
       </c>
       <c r="Z42" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q42)*($X$42:$X$45=X42)*($V$42:$V$45&gt;V42))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA42" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q42)*($X$42:$X$45=X42)*($V$42:$V$45=V42)*($W$42:$W$45&gt;W42))</f>
@@ -17680,15 +17718,15 @@
       </c>
       <c r="AF42" s="83" t="str">
         <f>VLOOKUP($AE42,$O$42:$X$45,2,FALSE)</f>
-        <v>Egito</v>
+        <v>Bélgica</v>
       </c>
       <c r="AG42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,3,FALSE)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,5,FALSE)</f>
@@ -17696,7 +17734,7 @@
       </c>
       <c r="AJ42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,7,FALSE)</f>
@@ -17704,7 +17742,7 @@
       </c>
       <c r="AL42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,8,FALSE)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM42" s="84">
         <f>VLOOKUP($AE42,$O$42:$X$45,9,FALSE)</f>
@@ -17712,7 +17750,7 @@
       </c>
       <c r="AN42" s="85">
         <f>VLOOKUP($AE42,$O$42:$X$45,10,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:45" x14ac:dyDescent="0.25">
@@ -17762,7 +17800,7 @@
       <c r="N43" s="46"/>
       <c r="O43" s="47">
         <f>RANK(Q43,$Q$42:$Q$45)+SUM(Y43:AB43)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P43" s="49" t="str">
         <f>Sorteios!C23</f>
@@ -17770,11 +17808,11 @@
       </c>
       <c r="Q43" s="38">
         <f t="shared" ref="Q43:Q45" si="53">(S43*3)+(T43*1)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R43" s="38">
         <f t="shared" ref="R43:R45" si="54">SUM(S43:U43)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S43" s="38">
         <f>COUNTIF(J:J,P43)</f>
@@ -17782,7 +17820,7 @@
       </c>
       <c r="T43" s="38">
         <f>COUNTIF(K:K,P43)+COUNTIF(L:L,P43)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U43" s="38">
         <f>COUNTIF(M:M,P43)</f>
@@ -17790,11 +17828,11 @@
       </c>
       <c r="V43" s="38">
         <f>SUMIF(E:E,P43,F:F)+SUMIF(I:I,P43,H:H)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W43" s="38">
         <f>SUMIF(E:E,P43,H:H)+SUMIF(I:I,P43,F:F)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X43" s="38">
         <f t="shared" ref="X43:X45" si="55">V43-W43</f>
@@ -17802,7 +17840,7 @@
       </c>
       <c r="Y43" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q43)*($X$42:$X$45&gt;X43))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z43" s="38">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q43)*($X$42:$X$45=X43)*($V$42:$V$45&gt;V43))</f>
@@ -17825,19 +17863,19 @@
       </c>
       <c r="AF43" s="83" t="str">
         <f>VLOOKUP($AE43,$O$42:$X$45,2,FALSE)</f>
-        <v>Irã</v>
+        <v>Egito</v>
       </c>
       <c r="AG43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,3,FALSE)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AH43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,6,FALSE)</f>
@@ -17849,15 +17887,15 @@
       </c>
       <c r="AL43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,8,FALSE)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AM43" s="84">
         <f>VLOOKUP($AE43,$O$42:$X$45,9,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN43" s="85">
         <f>VLOOKUP($AE43,$O$42:$X$45,10,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:45" x14ac:dyDescent="0.25">
@@ -17875,18 +17913,22 @@
         <f>P45</f>
         <v>Nova Zelândia</v>
       </c>
-      <c r="F44" s="123"/>
+      <c r="F44" s="123">
+        <v>1</v>
+      </c>
       <c r="G44" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H44" s="123"/>
+      <c r="H44" s="123">
+        <v>5</v>
+      </c>
       <c r="I44" s="107" t="str">
         <f>P42</f>
         <v>Bélgica</v>
       </c>
       <c r="J44" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Bélgica</v>
       </c>
       <c r="K44" s="38" t="str">
         <f t="shared" si="47"/>
@@ -17898,12 +17940,12 @@
       </c>
       <c r="M44" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Nova Zelândia</v>
       </c>
       <c r="N44" s="46"/>
       <c r="O44" s="47">
         <f>RANK(Q44,$Q$42:$Q$45)+SUM(Y44:AB44)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P44" s="49" t="str">
         <f>Sorteios!C24</f>
@@ -17911,11 +17953,11 @@
       </c>
       <c r="Q44" s="38">
         <f t="shared" si="53"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R44" s="38">
         <f t="shared" si="54"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S44" s="38">
         <f>COUNTIF(J:J,P44)</f>
@@ -17923,7 +17965,7 @@
       </c>
       <c r="T44" s="38">
         <f>COUNTIF(K:K,P44)+COUNTIF(L:L,P44)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U44" s="38">
         <f>COUNTIF(M:M,P44)</f>
@@ -17931,11 +17973,11 @@
       </c>
       <c r="V44" s="38">
         <f>SUMIF(E:E,P44,F:F)+SUMIF(I:I,P44,H:H)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W44" s="38">
         <f>SUMIF(E:E,P44,H:H)+SUMIF(I:I,P44,F:F)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X44" s="38">
         <f t="shared" si="55"/>
@@ -17966,15 +18008,15 @@
       </c>
       <c r="AF44" s="83" t="str">
         <f>VLOOKUP($AE44,$O$42:$X$45,2,FALSE)</f>
-        <v>Bélgica</v>
+        <v>Irã</v>
       </c>
       <c r="AG44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,5,FALSE)</f>
@@ -17982,7 +18024,7 @@
       </c>
       <c r="AJ44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,6,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,7,FALSE)</f>
@@ -17990,11 +18032,11 @@
       </c>
       <c r="AL44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,8,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM44" s="84">
         <f>VLOOKUP($AE44,$O$42:$X$45,9,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN44" s="85">
         <f>VLOOKUP($AE44,$O$42:$X$45,10,FALSE)</f>
@@ -18016,11 +18058,15 @@
         <f>P43</f>
         <v>Egito</v>
       </c>
-      <c r="F45" s="124"/>
+      <c r="F45" s="124">
+        <v>1</v>
+      </c>
       <c r="G45" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="H45" s="124"/>
+      <c r="H45" s="124">
+        <v>1</v>
+      </c>
       <c r="I45" s="109" t="str">
         <f>P44</f>
         <v>Irã</v>
@@ -18031,11 +18077,11 @@
       </c>
       <c r="K45" s="53" t="str">
         <f t="shared" si="47"/>
-        <v/>
+        <v>Egito</v>
       </c>
       <c r="L45" s="53" t="str">
         <f t="shared" si="48"/>
-        <v/>
+        <v>Irã</v>
       </c>
       <c r="M45" s="54" t="str">
         <f t="shared" si="49"/>
@@ -18056,7 +18102,7 @@
       </c>
       <c r="R45" s="53">
         <f t="shared" si="54"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S45" s="38">
         <f>COUNTIF(J:J,P45)</f>
@@ -18068,19 +18114,19 @@
       </c>
       <c r="U45" s="38">
         <f>COUNTIF(M:M,P45)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V45" s="53">
         <f>SUMIF(E:E,P45,F:F)+SUMIF(I:I,P45,H:H)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W45" s="53">
         <f>SUMIF(E:E,P45,H:H)+SUMIF(I:I,P45,F:F)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X45" s="53">
         <f t="shared" si="55"/>
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="Y45" s="53">
         <f>SUMPRODUCT(($Q$42:$Q$45=Q45)*($X$42:$X$45&gt;X45))</f>
@@ -18115,7 +18161,7 @@
       </c>
       <c r="AH45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,5,FALSE)</f>
@@ -18127,19 +18173,19 @@
       </c>
       <c r="AK45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,8,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM45" s="87">
         <f>VLOOKUP($AE45,$O$42:$X$45,9,FALSE)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AN45" s="88">
         <f>VLOOKUP($AE45,$O$42:$X$45,10,FALSE)</f>
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="46" spans="1:45" x14ac:dyDescent="0.25">
@@ -18395,15 +18441,15 @@
       </c>
       <c r="Q48" s="38">
         <f>(S48*3)+(T48*1)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R48" s="38">
         <f>SUM(S48:U48)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S48" s="38">
         <f>COUNTIF(J:J,P48)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T48" s="38">
         <f>COUNTIF(K:K,P48)+COUNTIF(L:L,P48)</f>
@@ -18415,7 +18461,7 @@
       </c>
       <c r="V48" s="38">
         <f>SUMIF(E:E,P48,F:F)+SUMIF(I:I,P48,H:H)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W48" s="38">
         <f>SUMIF(E:E,P48,H:H)+SUMIF(I:I,P48,F:F)</f>
@@ -18423,7 +18469,7 @@
       </c>
       <c r="X48" s="38">
         <f>V48-W48</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y48" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q48)*($X$48:$X$51&gt;X48))</f>
@@ -18454,15 +18500,15 @@
       </c>
       <c r="AG48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,3,FALSE)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AH48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,6,FALSE)</f>
@@ -18474,7 +18520,7 @@
       </c>
       <c r="AL48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,8,FALSE)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM48" s="84">
         <f>VLOOKUP($AE48,$O$48:$X$51,9,FALSE)</f>
@@ -18482,7 +18528,7 @@
       </c>
       <c r="AN48" s="85">
         <f>VLOOKUP($AE48,$O$48:$X$51,10,FALSE)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:40" x14ac:dyDescent="0.25">
@@ -18532,7 +18578,7 @@
       <c r="N49" s="45"/>
       <c r="O49" s="47">
         <f>RANK(Q49,$Q$48:$Q$51)+SUM(Y49:AB49)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P49" s="49" t="str">
         <f>Sorteios!F23</f>
@@ -18540,11 +18586,11 @@
       </c>
       <c r="Q49" s="38">
         <f t="shared" ref="Q49:Q51" si="56">(S49*3)+(T49*1)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R49" s="38">
         <f t="shared" ref="R49:R51" si="57">SUM(S49:U49)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S49" s="38">
         <f>COUNTIF(J:J,P49)</f>
@@ -18552,7 +18598,7 @@
       </c>
       <c r="T49" s="38">
         <f>COUNTIF(K:K,P49)+COUNTIF(L:L,P49)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U49" s="38">
         <f>COUNTIF(M:M,P49)</f>
@@ -18576,7 +18622,7 @@
       </c>
       <c r="Z49" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q49)*($X$48:$X$51=X49)*($V$48:$V$51&gt;V49))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q49)*($X$48:$X$51=X49)*($V$48:$V$51=V49)*($W$48:$W$51&gt;W49))</f>
@@ -18595,15 +18641,15 @@
       </c>
       <c r="AF49" s="83" t="str">
         <f>VLOOKUP($AE49,$O$48:$X$51,2,FALSE)</f>
-        <v>Uruguai</v>
+        <v>Cabo Verde</v>
       </c>
       <c r="AG49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,5,FALSE)</f>
@@ -18611,7 +18657,7 @@
       </c>
       <c r="AJ49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,6,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,7,FALSE)</f>
@@ -18619,11 +18665,11 @@
       </c>
       <c r="AL49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,8,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM49" s="84">
         <f>VLOOKUP($AE49,$O$48:$X$51,9,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN49" s="85">
         <f>VLOOKUP($AE49,$O$48:$X$51,10,FALSE)</f>
@@ -18645,18 +18691,22 @@
         <f>P51</f>
         <v>Uruguai</v>
       </c>
-      <c r="F50" s="123"/>
+      <c r="F50" s="123">
+        <v>0</v>
+      </c>
       <c r="G50" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H50" s="123"/>
+      <c r="H50" s="123">
+        <v>1</v>
+      </c>
       <c r="I50" s="113" t="str">
         <f>P48</f>
         <v>Espanha</v>
       </c>
       <c r="J50" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Espanha</v>
       </c>
       <c r="K50" s="38" t="str">
         <f t="shared" si="47"/>
@@ -18668,7 +18718,7 @@
       </c>
       <c r="M50" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Uruguai</v>
       </c>
       <c r="N50" s="45"/>
       <c r="O50" s="47">
@@ -18681,11 +18731,11 @@
       </c>
       <c r="Q50" s="38">
         <f t="shared" si="56"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R50" s="38">
         <f t="shared" si="57"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S50" s="38">
         <f>COUNTIF(J:J,P50)</f>
@@ -18693,7 +18743,7 @@
       </c>
       <c r="T50" s="38">
         <f>COUNTIF(K:K,P50)+COUNTIF(L:L,P50)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U50" s="38">
         <f>COUNTIF(M:M,P50)</f>
@@ -18713,7 +18763,7 @@
       </c>
       <c r="Y50" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q50)*($X$48:$X$51&gt;X50))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z50" s="38">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q50)*($X$48:$X$51=X50)*($V$48:$V$51&gt;V50))</f>
@@ -18736,7 +18786,7 @@
       </c>
       <c r="AF50" s="83" t="str">
         <f>VLOOKUP($AE50,$O$48:$X$51,2,FALSE)</f>
-        <v>Cabo Verde</v>
+        <v>Uruguai</v>
       </c>
       <c r="AG50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,3,FALSE)</f>
@@ -18744,7 +18794,7 @@
       </c>
       <c r="AH50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,5,FALSE)</f>
@@ -18756,19 +18806,19 @@
       </c>
       <c r="AK50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,8,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM50" s="84">
         <f>VLOOKUP($AE50,$O$48:$X$51,9,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN50" s="85">
         <f>VLOOKUP($AE50,$O$48:$X$51,10,FALSE)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="51" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18786,11 +18836,15 @@
         <f>P49</f>
         <v>Cabo Verde</v>
       </c>
-      <c r="F51" s="126"/>
+      <c r="F51" s="126">
+        <v>0</v>
+      </c>
       <c r="G51" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="H51" s="126"/>
+      <c r="H51" s="126">
+        <v>0</v>
+      </c>
       <c r="I51" s="119" t="str">
         <f>P50</f>
         <v>Arábia Saudita</v>
@@ -18801,11 +18855,11 @@
       </c>
       <c r="K51" s="66" t="str">
         <f t="shared" si="47"/>
-        <v/>
+        <v>Cabo Verde</v>
       </c>
       <c r="L51" s="66" t="str">
         <f t="shared" si="48"/>
-        <v/>
+        <v>Arábia Saudita</v>
       </c>
       <c r="M51" s="67" t="str">
         <f t="shared" si="49"/>
@@ -18814,7 +18868,7 @@
       <c r="N51" s="45"/>
       <c r="O51" s="68">
         <f>RANK(Q51,$Q$48:$Q$51)+SUM(Y51:AB51)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P51" s="49" t="str">
         <f>Sorteios!F25</f>
@@ -18826,7 +18880,7 @@
       </c>
       <c r="R51" s="53">
         <f t="shared" si="57"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S51" s="38">
         <f>COUNTIF(J:J,P51)</f>
@@ -18838,7 +18892,7 @@
       </c>
       <c r="U51" s="38">
         <f>COUNTIF(M:M,P51)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" s="53">
         <f>SUMIF(E:E,P51,F:F)+SUMIF(I:I,P51,H:H)</f>
@@ -18846,11 +18900,11 @@
       </c>
       <c r="W51" s="53">
         <f>SUMIF(E:E,P51,H:H)+SUMIF(I:I,P51,F:F)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X51" s="53">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y51" s="53">
         <f>SUMPRODUCT(($Q$48:$Q$51=Q51)*($X$48:$X$51&gt;X51))</f>
@@ -18881,11 +18935,11 @@
       </c>
       <c r="AG51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,5,FALSE)</f>
@@ -18893,7 +18947,7 @@
       </c>
       <c r="AJ51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK51" s="87">
         <f>VLOOKUP($AE51,$O$48:$X$51,7,FALSE)</f>
@@ -19165,15 +19219,15 @@
       </c>
       <c r="Q54" s="38">
         <f>(S54*3)+(T54*1)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R54" s="38">
         <f>SUM(S54:U54)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S54" s="38">
         <f>COUNTIF(J:J,P54)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" s="38">
         <f>COUNTIF(K:K,P54)+COUNTIF(L:L,P54)</f>
@@ -19185,15 +19239,15 @@
       </c>
       <c r="V54" s="38">
         <f>SUMIF(E:E,P54,F:F)+SUMIF(I:I,P54,H:H)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W54" s="38">
         <f>SUMIF(E:E,P54,H:H)+SUMIF(I:I,P54,F:F)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X54" s="38">
         <f>V54-W54</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y54" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q54)*($X$54:$X$57&gt;X54))</f>
@@ -19224,15 +19278,15 @@
       </c>
       <c r="AG54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,3,FALSE)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AH54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,6,FALSE)</f>
@@ -19244,15 +19298,15 @@
       </c>
       <c r="AL54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,8,FALSE)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AM54" s="84">
         <f>VLOOKUP($AE54,$O$54:$X$57,9,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN54" s="85">
         <f>VLOOKUP($AE54,$O$54:$X$57,10,FALSE)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:40" x14ac:dyDescent="0.25">
@@ -19310,15 +19364,15 @@
       </c>
       <c r="Q55" s="38">
         <f t="shared" ref="Q55:Q57" si="59">(S55*3)+(T55*1)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R55" s="38">
         <f t="shared" ref="R55:R57" si="60">SUM(S55:U55)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S55" s="38">
         <f>COUNTIF(J:J,P55)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" s="38">
         <f>COUNTIF(K:K,P55)+COUNTIF(L:L,P55)</f>
@@ -19330,7 +19384,7 @@
       </c>
       <c r="V55" s="38">
         <f>SUMIF(E:E,P55,F:F)+SUMIF(I:I,P55,H:H)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W55" s="38">
         <f>SUMIF(E:E,P55,H:H)+SUMIF(I:I,P55,F:F)</f>
@@ -19338,7 +19392,7 @@
       </c>
       <c r="X55" s="38">
         <f t="shared" ref="X55:X57" si="61">V55-W55</f>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="Y55" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q55)*($X$54:$X$57&gt;X55))</f>
@@ -19373,7 +19427,7 @@
       </c>
       <c r="AH55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,5,FALSE)</f>
@@ -19385,19 +19439,19 @@
       </c>
       <c r="AK55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,8,FALSE)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM55" s="84">
         <f>VLOOKUP($AE55,$O$54:$X$57,9,FALSE)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AN55" s="85">
         <f>VLOOKUP($AE55,$O$54:$X$57,10,FALSE)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:40" x14ac:dyDescent="0.25">
@@ -19415,18 +19469,22 @@
         <f>P57</f>
         <v>Noruega</v>
       </c>
-      <c r="F56" s="123"/>
+      <c r="F56" s="123">
+        <v>1</v>
+      </c>
       <c r="G56" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H56" s="123"/>
+      <c r="H56" s="123">
+        <v>4</v>
+      </c>
       <c r="I56" s="107" t="str">
         <f>P54</f>
         <v>França</v>
       </c>
       <c r="J56" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>França</v>
       </c>
       <c r="K56" s="38" t="str">
         <f t="shared" si="47"/>
@@ -19438,7 +19496,7 @@
       </c>
       <c r="M56" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Noruega</v>
       </c>
       <c r="N56" s="46"/>
       <c r="O56" s="47">
@@ -19455,7 +19513,7 @@
       </c>
       <c r="R56" s="38">
         <f t="shared" si="60"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S56" s="38">
         <f>COUNTIF(J:J,P56)</f>
@@ -19467,7 +19525,7 @@
       </c>
       <c r="U56" s="38">
         <f>COUNTIF(M:M,P56)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V56" s="38">
         <f>SUMIF(E:E,P56,F:F)+SUMIF(I:I,P56,H:H)</f>
@@ -19475,15 +19533,15 @@
       </c>
       <c r="W56" s="38">
         <f>SUMIF(E:E,P56,H:H)+SUMIF(I:I,P56,F:F)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="X56" s="38">
         <f t="shared" si="61"/>
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="Y56" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q56)*($X$54:$X$57&gt;X56))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z56" s="38">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q56)*($X$54:$X$57=X56)*($V$54:$V$57&gt;V56))</f>
@@ -19510,15 +19568,15 @@
       </c>
       <c r="AG56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,3,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,6,FALSE)</f>
@@ -19530,7 +19588,7 @@
       </c>
       <c r="AL56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,8,FALSE)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AM56" s="84">
         <f>VLOOKUP($AE56,$O$54:$X$57,9,FALSE)</f>
@@ -19538,7 +19596,7 @@
       </c>
       <c r="AN56" s="85">
         <f>VLOOKUP($AE56,$O$54:$X$57,10,FALSE)</f>
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19556,18 +19614,22 @@
         <f>P55</f>
         <v>Senegal</v>
       </c>
-      <c r="F57" s="124"/>
+      <c r="F57" s="124">
+        <v>5</v>
+      </c>
       <c r="G57" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="H57" s="124"/>
+      <c r="H57" s="124">
+        <v>0</v>
+      </c>
       <c r="I57" s="109" t="str">
         <f>P56</f>
         <v>Iraque</v>
       </c>
       <c r="J57" s="53" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Senegal</v>
       </c>
       <c r="K57" s="53" t="str">
         <f t="shared" si="47"/>
@@ -19579,7 +19641,7 @@
       </c>
       <c r="M57" s="54" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Iraque</v>
       </c>
       <c r="N57" s="55"/>
       <c r="O57" s="47">
@@ -19596,7 +19658,7 @@
       </c>
       <c r="R57" s="66">
         <f t="shared" si="60"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S57" s="66">
         <f>COUNTIF(J:J,P57)</f>
@@ -19608,23 +19670,23 @@
       </c>
       <c r="U57" s="66">
         <f>COUNTIF(M:M,P57)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V57" s="66">
         <f>SUMIF(E:E,P57,F:F)+SUMIF(I:I,P57,H:H)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W57" s="66">
         <f>SUMIF(E:E,P57,H:H)+SUMIF(I:I,P57,F:F)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="X57" s="66">
         <f t="shared" si="61"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y57" s="66">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q57)*($X$54:$X$57&gt;X57))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z57" s="66">
         <f>SUMPRODUCT(($Q$54:$Q$57=Q57)*($X$54:$X$57=X57)*($V$54:$V$57&gt;V57))</f>
@@ -19655,7 +19717,7 @@
       </c>
       <c r="AH57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,5,FALSE)</f>
@@ -19667,7 +19729,7 @@
       </c>
       <c r="AK57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,7,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,8,FALSE)</f>
@@ -19675,11 +19737,11 @@
       </c>
       <c r="AM57" s="87">
         <f>VLOOKUP($AE57,$O$54:$X$57,9,FALSE)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AN57" s="88">
         <f>VLOOKUP($AE57,$O$54:$X$57,10,FALSE)</f>
-        <v>-6</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="58" spans="1:40" x14ac:dyDescent="0.25">
@@ -19935,15 +19997,15 @@
       </c>
       <c r="Q60" s="38">
         <f>(S60*3)+(T60*1)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R60" s="38">
         <f>SUM(S60:U60)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S60" s="38">
         <f>COUNTIF(J:J,P60)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T60" s="38">
         <f>COUNTIF(K:K,P60)+COUNTIF(L:L,P60)</f>
@@ -19955,15 +20017,15 @@
       </c>
       <c r="V60" s="38">
         <f>SUMIF(E:E,P60,F:F)+SUMIF(I:I,P60,H:H)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W60" s="38">
         <f>SUMIF(E:E,P60,H:H)+SUMIF(I:I,P60,F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X60" s="38">
         <f>V60-W60</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y60" s="38">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q60)*($X$60:$X$63&gt;X60))</f>
@@ -19994,15 +20056,15 @@
       </c>
       <c r="AG60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,3,FALSE)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AH60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,6,FALSE)</f>
@@ -20014,15 +20076,15 @@
       </c>
       <c r="AL60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,8,FALSE)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AM60" s="84">
         <f>VLOOKUP($AE60,$O$60:$X$63,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN60" s="85">
         <f>VLOOKUP($AE60,$O$60:$X$63,10,FALSE)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:40" x14ac:dyDescent="0.25">
@@ -20080,11 +20142,11 @@
       </c>
       <c r="Q61" s="38">
         <f t="shared" ref="Q61:Q63" si="62">(S61*3)+(T61*1)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R61" s="38">
         <f t="shared" ref="R61:R63" si="63">SUM(S61:U61)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S61" s="38">
         <f>COUNTIF(J:J,P61)</f>
@@ -20092,7 +20154,7 @@
       </c>
       <c r="T61" s="38">
         <f>COUNTIF(K:K,P61)+COUNTIF(L:L,P61)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U61" s="38">
         <f>COUNTIF(M:M,P61)</f>
@@ -20100,11 +20162,11 @@
       </c>
       <c r="V61" s="38">
         <f>SUMIF(E:E,P61,F:F)+SUMIF(I:I,P61,H:H)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W61" s="38">
         <f>SUMIF(E:E,P61,H:H)+SUMIF(I:I,P61,F:F)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X61" s="38">
         <f t="shared" ref="X61:X63" si="64">V61-W61</f>
@@ -20139,11 +20201,11 @@
       </c>
       <c r="AG61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,5,FALSE)</f>
@@ -20151,7 +20213,7 @@
       </c>
       <c r="AJ61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,7,FALSE)</f>
@@ -20159,11 +20221,11 @@
       </c>
       <c r="AL61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,8,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM61" s="84">
         <f>VLOOKUP($AE61,$O$60:$X$63,9,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN61" s="85">
         <f>VLOOKUP($AE61,$O$60:$X$63,10,FALSE)</f>
@@ -20185,18 +20247,22 @@
         <f>P63</f>
         <v>Jordânia</v>
       </c>
-      <c r="F62" s="123"/>
+      <c r="F62" s="123">
+        <v>1</v>
+      </c>
       <c r="G62" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H62" s="123"/>
+      <c r="H62" s="123">
+        <v>3</v>
+      </c>
       <c r="I62" s="113" t="str">
         <f>P60</f>
         <v>Argentina</v>
       </c>
       <c r="J62" s="38" t="str">
         <f t="shared" si="46"/>
-        <v>empate</v>
+        <v>Argentina</v>
       </c>
       <c r="K62" s="38" t="str">
         <f t="shared" si="47"/>
@@ -20208,7 +20274,7 @@
       </c>
       <c r="M62" s="39" t="str">
         <f t="shared" si="49"/>
-        <v>empate</v>
+        <v>Jordânia</v>
       </c>
       <c r="N62" s="45"/>
       <c r="O62" s="47">
@@ -20221,11 +20287,11 @@
       </c>
       <c r="Q62" s="38">
         <f>(S62*3)+(T62*1)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R62" s="38">
         <f>SUM(S62:U62)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S62" s="38">
         <f>COUNTIF(J:J,P62)</f>
@@ -20233,7 +20299,7 @@
       </c>
       <c r="T62" s="38">
         <f>COUNTIF(K:K,P62)+COUNTIF(L:L,P62)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U62" s="38">
         <f>COUNTIF(M:M,P62)</f>
@@ -20241,11 +20307,11 @@
       </c>
       <c r="V62" s="38">
         <f>SUMIF(E:E,P62,F:F)+SUMIF(I:I,P62,H:H)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W62" s="38">
         <f>SUMIF(E:E,P62,H:H)+SUMIF(I:I,P62,F:F)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X62" s="38">
         <f>V62-W62</f>
@@ -20280,11 +20346,11 @@
       </c>
       <c r="AG62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,5,FALSE)</f>
@@ -20292,7 +20358,7 @@
       </c>
       <c r="AJ62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,7,FALSE)</f>
@@ -20300,11 +20366,11 @@
       </c>
       <c r="AL62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,8,FALSE)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AM62" s="84">
         <f>VLOOKUP($AE62,$O$60:$X$63,9,FALSE)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AN62" s="85">
         <f>VLOOKUP($AE62,$O$60:$X$63,10,FALSE)</f>
@@ -20326,11 +20392,15 @@
         <f>P61</f>
         <v>Argélia</v>
       </c>
-      <c r="F63" s="126"/>
+      <c r="F63" s="126">
+        <v>3</v>
+      </c>
       <c r="G63" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="H63" s="126"/>
+      <c r="H63" s="126">
+        <v>3</v>
+      </c>
       <c r="I63" s="119" t="str">
         <f>P62</f>
         <v>Áustria</v>
@@ -20341,11 +20411,11 @@
       </c>
       <c r="K63" s="66" t="str">
         <f t="shared" si="47"/>
-        <v/>
+        <v>Argélia</v>
       </c>
       <c r="L63" s="66" t="str">
         <f t="shared" si="48"/>
-        <v/>
+        <v>Áustria</v>
       </c>
       <c r="M63" s="67" t="str">
         <f t="shared" si="49"/>
@@ -20366,7 +20436,7 @@
       </c>
       <c r="R63" s="53">
         <f t="shared" si="63"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S63" s="38">
         <f>COUNTIF(J:J,P63)</f>
@@ -20378,19 +20448,19 @@
       </c>
       <c r="U63" s="38">
         <f>COUNTIF(M:M,P63)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V63" s="53">
         <f>SUMIF(E:E,P63,F:F)+SUMIF(I:I,P63,H:H)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W63" s="53">
         <f>SUMIF(E:E,P63,H:H)+SUMIF(I:I,P63,F:F)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X63" s="53">
         <f t="shared" si="64"/>
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="Y63" s="53">
         <f>SUMPRODUCT(($Q$60:$Q$63=Q63)*($X$60:$X$63&gt;X63))</f>
@@ -20425,7 +20495,7 @@
       </c>
       <c r="AH63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,5,FALSE)</f>
@@ -20437,19 +20507,19 @@
       </c>
       <c r="AK63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,7,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,8,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM63" s="87">
         <f>VLOOKUP($AE63,$O$60:$X$63,9,FALSE)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN63" s="88">
         <f>VLOOKUP($AE63,$O$60:$X$63,10,FALSE)</f>
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="64" spans="1:40" x14ac:dyDescent="0.25">
@@ -20705,11 +20775,11 @@
       </c>
       <c r="Q66" s="38">
         <f>(S66*3)+(T66*1)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R66" s="38">
         <f>SUM(S66:U66)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S66" s="38">
         <f>COUNTIF(J:J,P66)</f>
@@ -20717,7 +20787,7 @@
       </c>
       <c r="T66" s="38">
         <f>COUNTIF(K:K,P66)+COUNTIF(L:L,P66)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U66" s="38">
         <f>COUNTIF(M:M,P66)</f>
@@ -20764,11 +20834,11 @@
       </c>
       <c r="AG66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,3,FALSE)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,5,FALSE)</f>
@@ -20776,7 +20846,7 @@
       </c>
       <c r="AJ66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK66" s="84">
         <f>VLOOKUP($AE66,$O$66:$X$69,7,FALSE)</f>
@@ -20850,15 +20920,15 @@
       </c>
       <c r="Q67" s="38">
         <f t="shared" ref="Q67:Q69" si="65">(S67*3)+(T67*1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R67" s="38">
         <f t="shared" ref="R67:R69" si="66">SUM(S67:U67)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S67" s="38">
         <f>COUNTIF(J:J,P67)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="38">
         <f>COUNTIF(K:K,P67)+COUNTIF(L:L,P67)</f>
@@ -20870,15 +20940,15 @@
       </c>
       <c r="V67" s="38">
         <f>SUMIF(E:E,P67,F:F)+SUMIF(I:I,P67,H:H)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W67" s="38">
         <f>SUMIF(E:E,P67,H:H)+SUMIF(I:I,P67,F:F)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X67" s="38">
         <f t="shared" ref="X67:X69" si="67">V67-W67</f>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Y67" s="38">
         <f>SUMPRODUCT(($Q$66:$Q$69=Q67)*($X$66:$X$69&gt;X67))</f>
@@ -20909,11 +20979,11 @@
       </c>
       <c r="AG67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,3,FALSE)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,5,FALSE)</f>
@@ -20921,7 +20991,7 @@
       </c>
       <c r="AJ67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK67" s="84">
         <f>VLOOKUP($AE67,$O$66:$X$69,7,FALSE)</f>
@@ -20955,11 +21025,15 @@
         <f>P69</f>
         <v>Colômbia</v>
       </c>
-      <c r="F68" s="123"/>
+      <c r="F68" s="123">
+        <v>0</v>
+      </c>
       <c r="G68" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H68" s="123"/>
+      <c r="H68" s="123">
+        <v>0</v>
+      </c>
       <c r="I68" s="107" t="str">
         <f>P66</f>
         <v>Portugal</v>
@@ -20970,11 +21044,11 @@
       </c>
       <c r="K68" s="38" t="str">
         <f t="shared" ref="K68:K75" si="69">IF(F68="","",IF(H68="","",IF(J68="empate",E68,"")))</f>
-        <v/>
+        <v>Colômbia</v>
       </c>
       <c r="L68" s="38" t="str">
         <f t="shared" ref="L68:L75" si="70">IF(E68="","",IF(F68="","",IF(M68="empate",I68,"")))</f>
-        <v/>
+        <v>Portugal</v>
       </c>
       <c r="M68" s="39" t="str">
         <f t="shared" ref="M68:M75" si="71">IF(F68=H68,"empate",IF(F68&lt;H68,E68,I68))</f>
@@ -20995,7 +21069,7 @@
       </c>
       <c r="R68" s="38">
         <f t="shared" si="66"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S68" s="38">
         <f>COUNTIF(J:J,P68)</f>
@@ -21007,19 +21081,19 @@
       </c>
       <c r="U68" s="38">
         <f>COUNTIF(M:M,P68)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V68" s="38">
         <f>SUMIF(E:E,P68,F:F)+SUMIF(I:I,P68,H:H)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W68" s="38">
         <f>SUMIF(E:E,P68,H:H)+SUMIF(I:I,P68,F:F)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="X68" s="38">
         <f t="shared" si="67"/>
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="Y68" s="38">
         <f>SUMPRODUCT(($Q$66:$Q$69=Q68)*($X$66:$X$69&gt;X68))</f>
@@ -21050,15 +21124,15 @@
       </c>
       <c r="AG68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,3,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,6,FALSE)</f>
@@ -21070,15 +21144,15 @@
       </c>
       <c r="AL68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,8,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AM68" s="84">
         <f>VLOOKUP($AE68,$O$66:$X$69,9,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN68" s="85">
         <f>VLOOKUP($AE68,$O$66:$X$69,10,FALSE)</f>
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -21096,18 +21170,22 @@
         <f>P67</f>
         <v>RD Congo</v>
       </c>
-      <c r="F69" s="124"/>
+      <c r="F69" s="124">
+        <v>3</v>
+      </c>
       <c r="G69" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="H69" s="124"/>
+      <c r="H69" s="124">
+        <v>1</v>
+      </c>
       <c r="I69" s="109" t="str">
         <f>P68</f>
         <v>Uzbequistão</v>
       </c>
       <c r="J69" s="53" t="str">
         <f t="shared" si="68"/>
-        <v>empate</v>
+        <v>RD Congo</v>
       </c>
       <c r="K69" s="53" t="str">
         <f t="shared" si="69"/>
@@ -21119,7 +21197,7 @@
       </c>
       <c r="M69" s="54" t="str">
         <f t="shared" si="71"/>
-        <v>empate</v>
+        <v>Uzbequistão</v>
       </c>
       <c r="N69" s="55"/>
       <c r="O69" s="56">
@@ -21132,11 +21210,11 @@
       </c>
       <c r="Q69" s="53">
         <f t="shared" si="65"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R69" s="53">
         <f t="shared" si="66"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S69" s="53">
         <f>COUNTIF(J:J,P69)</f>
@@ -21144,7 +21222,7 @@
       </c>
       <c r="T69" s="53">
         <f>COUNTIF(K:K,P69)+COUNTIF(L:L,P69)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U69" s="53">
         <f>COUNTIF(M:M,P69)</f>
@@ -21195,7 +21273,7 @@
       </c>
       <c r="AH69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,5,FALSE)</f>
@@ -21207,19 +21285,19 @@
       </c>
       <c r="AK69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,7,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,8,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM69" s="87">
         <f>VLOOKUP($AE69,$O$66:$X$69,9,FALSE)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AN69" s="88">
         <f>VLOOKUP($AE69,$O$66:$X$69,10,FALSE)</f>
-        <v>-7</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="70" spans="1:40" x14ac:dyDescent="0.25">
@@ -21475,15 +21553,15 @@
       </c>
       <c r="Q72" s="38">
         <f>(S72*3)+(T72*1)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R72" s="38">
         <f>SUM(S72:U72)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S72" s="38">
         <f>COUNTIF(J:J,P72)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T72" s="38">
         <f>COUNTIF(K:K,P72)+COUNTIF(L:L,P72)</f>
@@ -21495,7 +21573,7 @@
       </c>
       <c r="V72" s="38">
         <f>SUMIF(E:E,P72,F:F)+SUMIF(I:I,P72,H:H)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W72" s="38">
         <f>SUMIF(E:E,P72,H:H)+SUMIF(I:I,P72,F:F)</f>
@@ -21503,7 +21581,7 @@
       </c>
       <c r="X72" s="38">
         <f>V72-W72</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y72" s="38">
         <f>SUMPRODUCT(($Q$72:$Q$75=Q72)*($X$72:$X$75&gt;X72))</f>
@@ -21534,15 +21612,15 @@
       </c>
       <c r="AG72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,3,FALSE)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AH72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,6,FALSE)</f>
@@ -21554,7 +21632,7 @@
       </c>
       <c r="AL72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,8,FALSE)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM72" s="84">
         <f>VLOOKUP($AE72,$O$72:$X$75,9,FALSE)</f>
@@ -21562,7 +21640,7 @@
       </c>
       <c r="AN72" s="85">
         <f>VLOOKUP($AE72,$O$72:$X$75,10,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:40" x14ac:dyDescent="0.25">
@@ -21612,7 +21690,7 @@
       <c r="N73" s="45"/>
       <c r="O73" s="47">
         <f>RANK(Q73,$Q$72:$Q$75)+SUM(Y73:AB73)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P73" s="49" t="str">
         <f>Sorteios!I31</f>
@@ -21620,15 +21698,15 @@
       </c>
       <c r="Q73" s="38">
         <f t="shared" ref="Q73:Q75" si="72">(S73*3)+(T73*1)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R73" s="38">
         <f t="shared" ref="R73:R75" si="73">SUM(S73:U73)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S73" s="38">
         <f>COUNTIF(J:J,P73)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T73" s="38">
         <f>COUNTIF(K:K,P73)+COUNTIF(L:L,P73)</f>
@@ -21640,15 +21718,15 @@
       </c>
       <c r="V73" s="38">
         <f>SUMIF(E:E,P73,F:F)+SUMIF(I:I,P73,H:H)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W73" s="38">
         <f>SUMIF(E:E,P73,H:H)+SUMIF(I:I,P73,F:F)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X73" s="38">
         <f t="shared" ref="X73:X75" si="74">V73-W73</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y73" s="38">
         <f t="shared" ref="Y73:Y75" si="75">SUMPRODUCT(($Q$72:$Q$75=Q73)*($X$72:$X$75&gt;X73))</f>
@@ -21675,39 +21753,39 @@
       </c>
       <c r="AF73" s="83" t="str">
         <f t="shared" ref="AF73:AF75" si="79">VLOOKUP($AE73,$O$72:$X$75,2,FALSE)</f>
-        <v>Gana</v>
+        <v>Croácia</v>
       </c>
       <c r="AG73" s="84">
         <f t="shared" ref="AG73:AG75" si="80">VLOOKUP($AE73,$O$72:$X$75,3,FALSE)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH73" s="84">
         <f t="shared" ref="AH73:AH75" si="81">VLOOKUP($AE73,$O$72:$X$75,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI73" s="84">
         <f t="shared" ref="AI73:AI75" si="82">VLOOKUP($AE73,$O$72:$X$75,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ73" s="84">
         <f t="shared" ref="AJ73:AJ75" si="83">VLOOKUP($AE73,$O$72:$X$75,6,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK73" s="84">
         <f t="shared" ref="AK73:AK75" si="84">VLOOKUP($AE73,$O$72:$X$75,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL73" s="84">
         <f t="shared" ref="AL73:AL75" si="85">VLOOKUP($AE73,$O$72:$X$75,8,FALSE)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AM73" s="84">
         <f t="shared" ref="AM73:AM75" si="86">VLOOKUP($AE73,$O$72:$X$75,9,FALSE)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN73" s="85">
         <f t="shared" ref="AN73:AN75" si="87">VLOOKUP($AE73,$O$72:$X$75,10,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:40" x14ac:dyDescent="0.25">
@@ -21725,18 +21803,22 @@
         <f>P75</f>
         <v>Panamá</v>
       </c>
-      <c r="F74" s="123"/>
+      <c r="F74" s="123">
+        <v>0</v>
+      </c>
       <c r="G74" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H74" s="123"/>
+      <c r="H74" s="123">
+        <v>2</v>
+      </c>
       <c r="I74" s="113" t="str">
         <f>P72</f>
         <v>Inglaterra</v>
       </c>
       <c r="J74" s="38" t="str">
         <f t="shared" si="68"/>
-        <v>empate</v>
+        <v>Inglaterra</v>
       </c>
       <c r="K74" s="38" t="str">
         <f t="shared" si="69"/>
@@ -21748,12 +21830,12 @@
       </c>
       <c r="M74" s="39" t="str">
         <f t="shared" si="71"/>
-        <v>empate</v>
+        <v>Panamá</v>
       </c>
       <c r="N74" s="45"/>
       <c r="O74" s="47">
         <f>RANK(Q74,$Q$72:$Q$75)+SUM(Y74:AB74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P74" s="49" t="str">
         <f>Sorteios!I32</f>
@@ -21765,7 +21847,7 @@
       </c>
       <c r="R74" s="38">
         <f t="shared" si="73"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S74" s="38">
         <f>COUNTIF(J:J,P74)</f>
@@ -21777,23 +21859,23 @@
       </c>
       <c r="U74" s="38">
         <f>COUNTIF(M:M,P74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V74" s="38">
         <f>SUMIF(E:E,P74,F:F)+SUMIF(I:I,P74,H:H)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W74" s="38">
         <f>SUMIF(E:E,P74,H:H)+SUMIF(I:I,P74,F:F)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X74" s="38">
         <f t="shared" si="74"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y74" s="38">
         <f t="shared" si="75"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z74" s="38">
         <f t="shared" si="76"/>
@@ -21816,15 +21898,15 @@
       </c>
       <c r="AF74" s="83" t="str">
         <f t="shared" si="79"/>
-        <v>Croácia</v>
+        <v>Gana</v>
       </c>
       <c r="AG74" s="84">
         <f t="shared" si="80"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH74" s="84">
         <f t="shared" si="81"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI74" s="84">
         <f t="shared" si="82"/>
@@ -21832,7 +21914,7 @@
       </c>
       <c r="AJ74" s="84">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK74" s="84">
         <f t="shared" si="84"/>
@@ -21840,15 +21922,15 @@
       </c>
       <c r="AL74" s="84">
         <f t="shared" si="85"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM74" s="84">
         <f t="shared" si="86"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN74" s="85">
         <f t="shared" si="87"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -21866,18 +21948,22 @@
         <f>P73</f>
         <v>Croácia</v>
       </c>
-      <c r="F75" s="124"/>
+      <c r="F75" s="124">
+        <v>2</v>
+      </c>
       <c r="G75" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="H75" s="124"/>
+      <c r="H75" s="124">
+        <v>1</v>
+      </c>
       <c r="I75" s="114" t="str">
         <f>P74</f>
         <v>Gana</v>
       </c>
       <c r="J75" s="53" t="str">
         <f t="shared" si="68"/>
-        <v>empate</v>
+        <v>Croácia</v>
       </c>
       <c r="K75" s="53" t="str">
         <f t="shared" si="69"/>
@@ -21889,7 +21975,7 @@
       </c>
       <c r="M75" s="54" t="str">
         <f t="shared" si="71"/>
-        <v>empate</v>
+        <v>Gana</v>
       </c>
       <c r="N75" s="57"/>
       <c r="O75" s="56">
@@ -21906,7 +21992,7 @@
       </c>
       <c r="R75" s="53">
         <f t="shared" si="73"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S75" s="38">
         <f>COUNTIF(J:J,P75)</f>
@@ -21918,7 +22004,7 @@
       </c>
       <c r="U75" s="38">
         <f>COUNTIF(M:M,P75)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V75" s="53">
         <f>SUMIF(E:E,P75,F:F)+SUMIF(I:I,P75,H:H)</f>
@@ -21926,11 +22012,11 @@
       </c>
       <c r="W75" s="53">
         <f>SUMIF(E:E,P75,H:H)+SUMIF(I:I,P75,F:F)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X75" s="53">
         <f t="shared" si="74"/>
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="Y75" s="53">
         <f t="shared" si="75"/>
@@ -21965,7 +22051,7 @@
       </c>
       <c r="AH75" s="87">
         <f t="shared" si="81"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI75" s="87">
         <f t="shared" si="82"/>
@@ -21977,7 +22063,7 @@
       </c>
       <c r="AK75" s="87">
         <f t="shared" si="84"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL75" s="87">
         <f t="shared" si="85"/>
@@ -21985,115 +22071,115 @@
       </c>
       <c r="AM75" s="87">
         <f t="shared" si="86"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN75" s="88">
         <f t="shared" si="87"/>
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="SQxt3xnjLosvPdR5VuDI39jJ8Exg7pNo5QfpFGGeUhP9bCwEfdBtH+uOucbe3pVgIFZMZM1W7ecUs97g1mIdPQ==" saltValue="5T5G2RQHRg8kXfIrbR4BJA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="yMneGrh/V9v9I71ExvSu/Y2aQsnzReoZXlElqaiRdEFQ/HU0DofiNVmtRyr1uLMjGEnHu5TZOHdJIGeVyKwyVA==" saltValue="Bgw7AbWnF5ZQuHYiR+WIGA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="F3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A51 P3 B3:O51">
-    <cfRule type="cellIs" dxfId="47" priority="215" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="215" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:O75">
-    <cfRule type="cellIs" dxfId="46" priority="136" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="136" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E9">
-    <cfRule type="cellIs" dxfId="45" priority="202" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="202" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:E21">
-    <cfRule type="cellIs" dxfId="44" priority="193" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="193" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:E33">
-    <cfRule type="cellIs" dxfId="43" priority="191" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="191" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:E45">
-    <cfRule type="cellIs" dxfId="42" priority="189" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="189" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C52:E57">
-    <cfRule type="cellIs" dxfId="41" priority="130" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="130" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C64:E69">
-    <cfRule type="cellIs" dxfId="40" priority="128" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="128" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I9">
-    <cfRule type="cellIs" dxfId="39" priority="198" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="198" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:I21">
-    <cfRule type="cellIs" dxfId="38" priority="188" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="188" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I28:I33">
-    <cfRule type="cellIs" dxfId="37" priority="187" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="187" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I40:I45">
-    <cfRule type="cellIs" dxfId="36" priority="186" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="186" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I52:I57">
-    <cfRule type="cellIs" dxfId="35" priority="127" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="127" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I64:I69">
-    <cfRule type="cellIs" dxfId="34" priority="126" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="126" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:AN75">
-    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF6:AF7">
-    <cfRule type="expression" dxfId="32" priority="209">
+    <cfRule type="expression" dxfId="4" priority="209">
       <formula>AH6=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF12:AF13 AF18:AF19 AF24:AF25 AF30:AF31 AF36:AF37 AF42:AF43 AF48:AF49 AF54:AF57 AF60:AF61 AF66:AF69 AF72:AF73">
-    <cfRule type="expression" dxfId="31" priority="1">
+  <conditionalFormatting sqref="AF12:AF13 AF18:AF19 AF24:AF25 AF30:AF31 AF36:AF37 AF42:AF43 AF48:AF49 AF60:AF61 AF66:AF67 AF72:AF73 AF54:AF55">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>AH12=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP5:BG17">
-    <cfRule type="cellIs" dxfId="30" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="83" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI4:BR17">
-    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BJ6:BJ17">
-    <cfRule type="expression" dxfId="28" priority="77">
+  <conditionalFormatting sqref="BJ6:BJ13">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>BL6=3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54579,7 +54665,7 @@
       </c>
       <c r="E5" s="106" t="str">
         <f>IF('Fase de Grupos'!AH7=3,'Fase de Grupos'!AF7,"2º do Grupo A")</f>
-        <v>2º do Grupo A</v>
+        <v>África do Sul</v>
       </c>
       <c r="F5" s="149"/>
       <c r="G5" s="123"/>
@@ -54590,7 +54676,7 @@
       <c r="J5" s="150"/>
       <c r="K5" s="151" t="str">
         <f>IF('Fase de Grupos'!AH13=3,'Fase de Grupos'!AF13,"2º do Grupo B")</f>
-        <v>2º do Grupo B</v>
+        <v>Canadá</v>
       </c>
       <c r="L5" s="136" t="str">
         <f>IF(OR(G5="",I5=""),"",IF(G5=I5,"emp",""))</f>
@@ -54653,7 +54739,7 @@
       </c>
       <c r="E6" s="106" t="str">
         <f>IF('Fase de Grupos'!AH30=3,'Fase de Grupos'!AF30,"1º do Grupo E")</f>
-        <v>1º do Grupo E</v>
+        <v>Alemanha</v>
       </c>
       <c r="F6" s="149"/>
       <c r="G6" s="123"/>
@@ -54664,7 +54750,7 @@
       <c r="J6" s="150"/>
       <c r="K6" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R11,"3º A, B, C, D ou F")</f>
-        <v>3º A, B, C, D ou F</v>
+        <v>Paraguai</v>
       </c>
       <c r="L6" s="136" t="str">
         <f t="shared" ref="L6:L12" si="0">IF(OR(G6="",I6=""),"",IF(G6=I6,"emp",""))</f>
@@ -54679,7 +54765,7 @@
       </c>
       <c r="P6" s="133" t="str">
         <f>'Fase de Grupos'!AR39</f>
-        <v>3C3G3J3D3A3F3L3H</v>
+        <v>3E3J3B3D3I3F3L3K</v>
       </c>
       <c r="W6" s="45"/>
       <c r="X6" s="152" t="s">
@@ -54731,7 +54817,7 @@
       </c>
       <c r="E7" s="106" t="str">
         <f>IF('Fase de Grupos'!AH36=3,'Fase de Grupos'!AF36,"1º do Grupo F")</f>
-        <v>1º do Grupo F</v>
+        <v>Países Baixos</v>
       </c>
       <c r="F7" s="149"/>
       <c r="G7" s="123"/>
@@ -54742,7 +54828,7 @@
       <c r="J7" s="150"/>
       <c r="K7" s="151" t="str">
         <f>IF('Fase de Grupos'!AH19=3,'Fase de Grupos'!AF19,"2º do Grupo C")</f>
-        <v>2º do Grupo C</v>
+        <v>Marrocos</v>
       </c>
       <c r="L7" s="136" t="str">
         <f t="shared" si="0"/>
@@ -54805,7 +54891,7 @@
       </c>
       <c r="E8" s="106" t="str">
         <f>IF('Fase de Grupos'!AH18=3,'Fase de Grupos'!AF18,"1º do Grupo C")</f>
-        <v>1º do Grupo C</v>
+        <v>Brasil</v>
       </c>
       <c r="F8" s="149"/>
       <c r="G8" s="123"/>
@@ -54816,7 +54902,7 @@
       <c r="J8" s="150"/>
       <c r="K8" s="151" t="str">
         <f>IF('Fase de Grupos'!AH37=3,'Fase de Grupos'!AF37,"2º do Grupo F")</f>
-        <v>2º do Grupo F</v>
+        <v>Japão</v>
       </c>
       <c r="L8" s="136" t="str">
         <f t="shared" si="0"/>
@@ -54834,11 +54920,11 @@
       </c>
       <c r="Q8" s="133" t="str">
         <f>MID($P$6,1,2)</f>
-        <v>3C</v>
+        <v>3E</v>
       </c>
       <c r="R8" s="15" t="str">
         <f>VLOOKUP(Q8,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Escócia</v>
+        <v>Equador</v>
       </c>
       <c r="T8" s="15" t="s">
         <v>102</v>
@@ -54896,7 +54982,7 @@
       </c>
       <c r="E9" s="106" t="str">
         <f>IF('Fase de Grupos'!AH54=3,'Fase de Grupos'!AF54,"1º do Grupo I")</f>
-        <v>1º do Grupo I</v>
+        <v>França</v>
       </c>
       <c r="F9" s="149"/>
       <c r="G9" s="123"/>
@@ -54907,7 +54993,7 @@
       <c r="J9" s="150"/>
       <c r="K9" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R13,"3º C, D, F, G ou H")</f>
-        <v>3º C, D, F, G ou H</v>
+        <v>Suécia</v>
       </c>
       <c r="L9" s="136" t="str">
         <f t="shared" si="0"/>
@@ -54925,11 +55011,11 @@
       </c>
       <c r="Q9" s="133" t="str">
         <f>MID($P$6,3,2)</f>
-        <v>3G</v>
+        <v>3J</v>
       </c>
       <c r="R9" s="15" t="str">
         <f>VLOOKUP(Q9,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Bélgica</v>
+        <v>Argélia</v>
       </c>
       <c r="T9" s="15" t="s">
         <v>137</v>
@@ -54968,7 +55054,7 @@
       </c>
       <c r="E10" s="106" t="str">
         <f>IF('Fase de Grupos'!AH31=3,'Fase de Grupos'!AF31,"2º do Grupo E")</f>
-        <v>2º do Grupo E</v>
+        <v>Costa do Marfim</v>
       </c>
       <c r="F10" s="149"/>
       <c r="G10" s="123"/>
@@ -54979,7 +55065,7 @@
       <c r="J10" s="150"/>
       <c r="K10" s="151" t="str">
         <f>IF('Fase de Grupos'!AH55=3,'Fase de Grupos'!AF55,"2º do Grupo I")</f>
-        <v>2º do Grupo I</v>
+        <v>Noruega</v>
       </c>
       <c r="L10" s="136" t="str">
         <f t="shared" si="0"/>
@@ -54997,11 +55083,11 @@
       </c>
       <c r="Q10" s="133" t="str">
         <f>MID($P$6,5,2)</f>
-        <v>3J</v>
+        <v>3B</v>
       </c>
       <c r="R10" s="15" t="str">
         <f>VLOOKUP(Q10,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Argélia</v>
+        <v>Bósnia</v>
       </c>
       <c r="T10" s="15" t="s">
         <v>104</v>
@@ -55040,7 +55126,7 @@
       </c>
       <c r="E11" s="106" t="str">
         <f>IF('Fase de Grupos'!AH6=3,'Fase de Grupos'!AF6,"1º do Grupo A")</f>
-        <v>1º do Grupo A</v>
+        <v>México</v>
       </c>
       <c r="F11" s="149"/>
       <c r="G11" s="123"/>
@@ -55051,7 +55137,7 @@
       <c r="J11" s="150"/>
       <c r="K11" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R8,"3º C, E, F, H ou I")</f>
-        <v>3º C, E, F, H ou I</v>
+        <v>Equador</v>
       </c>
       <c r="L11" s="136" t="str">
         <f t="shared" si="0"/>
@@ -55114,7 +55200,7 @@
       </c>
       <c r="E12" s="106" t="str">
         <f>IF('Fase de Grupos'!AH72=3,'Fase de Grupos'!AF72,"1º do Grupo L")</f>
-        <v>1º do Grupo L</v>
+        <v>Inglaterra</v>
       </c>
       <c r="F12" s="149"/>
       <c r="G12" s="123"/>
@@ -55125,7 +55211,7 @@
       <c r="J12" s="150"/>
       <c r="K12" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R15,"3º E, H, I, J ou K")</f>
-        <v>3º E, H, I, J ou K</v>
+        <v>RD Congo</v>
       </c>
       <c r="L12" s="136" t="str">
         <f t="shared" si="0"/>
@@ -55143,11 +55229,11 @@
       </c>
       <c r="Q12" s="133" t="str">
         <f>MID($P$6,9,2)</f>
-        <v>3A</v>
+        <v>3I</v>
       </c>
       <c r="R12" s="15" t="str">
         <f>VLOOKUP(Q12,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>República Tcheca</v>
+        <v>Senegal</v>
       </c>
       <c r="T12" s="15" t="s">
         <v>139</v>
@@ -55196,7 +55282,7 @@
       </c>
       <c r="E13" s="106" t="str">
         <f>IF('Fase de Grupos'!AH24=3,'Fase de Grupos'!AF24,"1º do Grupo D")</f>
-        <v>1º do Grupo D</v>
+        <v>Estados Unidos</v>
       </c>
       <c r="F13" s="149"/>
       <c r="G13" s="123"/>
@@ -55207,7 +55293,7 @@
       <c r="J13" s="150"/>
       <c r="K13" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R10,"3º B, E, F, I ou J")</f>
-        <v>3º B, E, F, I ou J</v>
+        <v>Bósnia</v>
       </c>
       <c r="L13" s="136" t="str">
         <f>IF(OR(G13="",I13=""),"",IF(G13=I13,"emp",""))</f>
@@ -55288,7 +55374,7 @@
       </c>
       <c r="E14" s="106" t="str">
         <f>IF('Fase de Grupos'!AH42=3,'Fase de Grupos'!AF42,"1º do Grupo G")</f>
-        <v>1º do Grupo G</v>
+        <v>Bélgica</v>
       </c>
       <c r="F14" s="149"/>
       <c r="G14" s="123"/>
@@ -55299,7 +55385,7 @@
       <c r="J14" s="150"/>
       <c r="K14" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R12,"3º A, E, H, I ou J")</f>
-        <v>3º A, E, H, I ou J</v>
+        <v>Senegal</v>
       </c>
       <c r="L14" s="136" t="str">
         <f t="shared" ref="L14:L20" si="4">IF(OR(G14="",I14=""),"",IF(G14=I14,"emp",""))</f>
@@ -55321,7 +55407,7 @@
       </c>
       <c r="R14" s="15" t="str">
         <f>VLOOKUP(Q14,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Croácia</v>
+        <v>Gana</v>
       </c>
       <c r="T14" s="15" t="s">
         <v>105</v>
@@ -55380,7 +55466,7 @@
       </c>
       <c r="E15" s="106" t="str">
         <f>IF('Fase de Grupos'!AH67=3,'Fase de Grupos'!AF67,"2º do Grupo K")</f>
-        <v>2º do Grupo K</v>
+        <v>Portugal</v>
       </c>
       <c r="F15" s="149"/>
       <c r="G15" s="123"/>
@@ -55391,7 +55477,7 @@
       <c r="J15" s="150"/>
       <c r="K15" s="151" t="str">
         <f>IF('Fase de Grupos'!AH73=3,'Fase de Grupos'!AF73,"2º do Grupo L")</f>
-        <v>2º do Grupo L</v>
+        <v>Croácia</v>
       </c>
       <c r="L15" s="136" t="str">
         <f t="shared" si="4"/>
@@ -55409,11 +55495,11 @@
       </c>
       <c r="Q15" s="133" t="str">
         <f>MID($P$6,15,2)</f>
-        <v>3H</v>
+        <v>3K</v>
       </c>
       <c r="R15" s="15" t="str">
         <f>VLOOKUP(Q15,'Fase de Grupos'!$AR$30:$AS$37,2,FALSE)</f>
-        <v>Cabo Verde</v>
+        <v>RD Congo</v>
       </c>
       <c r="T15" s="15" t="s">
         <v>135</v>
@@ -55455,7 +55541,7 @@
       </c>
       <c r="E16" s="106" t="str">
         <f>IF('Fase de Grupos'!AH48=3,'Fase de Grupos'!AF48,"1º do Grupo H")</f>
-        <v>1º do Grupo H</v>
+        <v>Espanha</v>
       </c>
       <c r="F16" s="149"/>
       <c r="G16" s="123"/>
@@ -55466,7 +55552,7 @@
       <c r="J16" s="150"/>
       <c r="K16" s="151" t="str">
         <f>IF('Fase de Grupos'!AH61=3,'Fase de Grupos'!AF61,"2º do Grupo J")</f>
-        <v>2º do Grupo J</v>
+        <v>Áustria</v>
       </c>
       <c r="L16" s="136" t="str">
         <f t="shared" si="4"/>
@@ -55519,7 +55605,7 @@
       </c>
       <c r="E17" s="106" t="str">
         <f>IF('Fase de Grupos'!AH12=3,'Fase de Grupos'!AF12,"1º do Grupo B")</f>
-        <v>1º do Grupo B</v>
+        <v>Suiça</v>
       </c>
       <c r="F17" s="149"/>
       <c r="G17" s="123"/>
@@ -55530,7 +55616,7 @@
       <c r="J17" s="150"/>
       <c r="K17" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R9,"3º E, F, G, I ou J")</f>
-        <v>3º E, F, G, I ou J</v>
+        <v>Argélia</v>
       </c>
       <c r="L17" s="136" t="str">
         <f t="shared" si="4"/>
@@ -55582,7 +55668,7 @@
       </c>
       <c r="E18" s="106" t="str">
         <f>IF('Fase de Grupos'!AH60=3,'Fase de Grupos'!AF60,"1º do Grupo J")</f>
-        <v>1º do Grupo J</v>
+        <v>Argentina</v>
       </c>
       <c r="F18" s="149"/>
       <c r="G18" s="123"/>
@@ -55593,7 +55679,7 @@
       <c r="J18" s="150"/>
       <c r="K18" s="151" t="str">
         <f>IF('Fase de Grupos'!AH49=3,'Fase de Grupos'!AF49,"2º do Grupo H")</f>
-        <v>2º do Grupo H</v>
+        <v>Cabo Verde</v>
       </c>
       <c r="L18" s="136" t="str">
         <f t="shared" si="4"/>
@@ -55653,7 +55739,7 @@
       </c>
       <c r="E19" s="106" t="str">
         <f>IF('Fase de Grupos'!AH66=3,'Fase de Grupos'!AF66,"1º do Grupo K")</f>
-        <v>1º do Grupo K</v>
+        <v>Colômbia</v>
       </c>
       <c r="F19" s="149"/>
       <c r="G19" s="123"/>
@@ -55664,7 +55750,7 @@
       <c r="J19" s="150"/>
       <c r="K19" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R14,"3º D, E, I, J ou L")</f>
-        <v>3º D, E, I, J ou L</v>
+        <v>Gana</v>
       </c>
       <c r="L19" s="136" t="str">
         <f t="shared" si="4"/>
@@ -55734,7 +55820,7 @@
       </c>
       <c r="E20" s="106" t="str">
         <f>IF('Fase de Grupos'!AH25=3,'Fase de Grupos'!AF25,"2º do Grupo D")</f>
-        <v>2º do Grupo D</v>
+        <v>Austrália</v>
       </c>
       <c r="F20" s="149"/>
       <c r="G20" s="123"/>
@@ -55745,7 +55831,7 @@
       <c r="J20" s="150"/>
       <c r="K20" s="151" t="str">
         <f>IF('Fase de Grupos'!AH43=3,'Fase de Grupos'!AF43,"2º do Grupo G")</f>
-        <v>2º do Grupo G</v>
+        <v>Egito</v>
       </c>
       <c r="L20" s="136" t="str">
         <f t="shared" si="4"/>
@@ -56561,142 +56647,142 @@
     <mergeCell ref="Y34:AA34"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A2 B2:K2 X9:AG10 X15:AG16 X20:AG21 B21:K22 AB34:AB36 A57:K58 H59:K61 B62:K71 B83:K1048576">
-    <cfRule type="cellIs" dxfId="27" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="76" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:B12 C4:K12">
-    <cfRule type="cellIs" dxfId="26" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="42" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:K20">
-    <cfRule type="cellIs" dxfId="25" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="31" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:B36 C24:K33">
-    <cfRule type="cellIs" dxfId="24" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="20" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F20">
-    <cfRule type="expression" dxfId="23" priority="30">
+    <cfRule type="expression" dxfId="43" priority="30">
       <formula>L5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:F32">
-    <cfRule type="expression" dxfId="22" priority="19">
+    <cfRule type="expression" dxfId="42" priority="19">
       <formula>L25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:J20">
-    <cfRule type="expression" dxfId="21" priority="29">
+    <cfRule type="expression" dxfId="41" priority="29">
       <formula>L5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J25:J32">
-    <cfRule type="expression" dxfId="20" priority="18">
+    <cfRule type="expression" dxfId="40" priority="18">
       <formula>L25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K20">
-    <cfRule type="expression" dxfId="19" priority="21">
+    <cfRule type="expression" dxfId="39" priority="21">
       <formula>Q5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K32">
-    <cfRule type="expression" dxfId="18" priority="17">
+    <cfRule type="expression" dxfId="38" priority="17">
       <formula>Q25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W3:W24 A21:A34 I34:K34 Y34:AB34 Y34:Y36 A62:A1048576">
-    <cfRule type="cellIs" dxfId="17" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="77" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X3:X8 Y4:AG8">
-    <cfRule type="cellIs" dxfId="16" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="16" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X11:X14 Y12:AG14">
-    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="12" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X17:X19 Y18:AG19">
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="8" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X23:X25 Y24:AG25">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y34:AA36">
-    <cfRule type="expression" dxfId="12" priority="65">
+    <cfRule type="expression" dxfId="32" priority="65">
       <formula>AB34&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB5:AB8">
-    <cfRule type="expression" dxfId="11" priority="15">
+    <cfRule type="expression" dxfId="31" priority="15">
       <formula>AH5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB13:AB14">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="30" priority="11">
       <formula>AH13="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB19">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="29" priority="7">
       <formula>AH19="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB25">
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="28" priority="3">
       <formula>AH25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF5:AF8">
-    <cfRule type="expression" dxfId="7" priority="14">
+    <cfRule type="expression" dxfId="27" priority="14">
       <formula>AH5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF13:AF14">
-    <cfRule type="expression" dxfId="6" priority="10">
+    <cfRule type="expression" dxfId="26" priority="10">
       <formula>AH13="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF19">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="25" priority="6">
       <formula>AH19="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF25">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="24" priority="2">
       <formula>AH25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG5:AG8">
-    <cfRule type="expression" dxfId="3" priority="13">
+    <cfRule type="expression" dxfId="23" priority="13">
       <formula>AM5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG13:AG14">
-    <cfRule type="expression" dxfId="2" priority="9">
+    <cfRule type="expression" dxfId="22" priority="9">
       <formula>AM13="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG19">
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="21" priority="5">
       <formula>AM19="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG25">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>AM25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57317,7 +57403,7 @@
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="c6tPJJQuMaLYYVxDkvgugaxcC+Uv5gkJkUqZgIt2uuxbzexMxqxVyEOkWorUUitpEJ1MPNBlUf/aYq65/wymIg==" saltValue="0J8NZQ0DnJYkRWhoKBlPHA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C59:C64">
+  <sortState ref="C59:C64">
     <sortCondition ref="C59:C64"/>
   </sortState>
   <mergeCells count="16">
@@ -57345,23 +57431,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DBF2846C41E31A469E3CED25F2422E48" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5fe40c83f7497f6a132ba44389c75f2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8c20e6-817c-474f-b9c2-eb2b1ac24837" xmlns:ns4="dc8c2798-6aba-4af7-93a4-b89253b03650" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7827a91f6681aa3909757bf20cf55ac7" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
@@ -57588,7 +57657,43 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E4CC2DB-337D-464E-B291-77CE670D3A8E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
+    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
@@ -57605,29 +57710,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E4CC2DB-337D-464E-B291-77CE670D3A8E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
-    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE93637-9C6E-434F-8D2E-067AEB248404}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF302D3-E586-40A4-B7C7-8C07227B9510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BcI4NY5Ohir363+nRCln2YCzlnOeJyINjZ1aV0hb2IpPHmsHZPUFroFzrod6xokqyCn7GUW2N1Z+U/w2mbyNbQ==" workbookSaltValue="VvXyFesAZC8L8IOzNm6PtA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9525" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="7" r:id="rId1"/>
@@ -26,6 +26,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -2962,6 +2973,17 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3066,17 +3088,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9037,25 +9048,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CB5EB0A-66D8-48B4-BC40-E2D214AFC03A}" name="Tabela1" displayName="Tabela1" ref="C3:E51" totalsRowShown="0" headerRowDxfId="88" dataDxfId="87">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CB5EB0A-66D8-48B4-BC40-E2D214AFC03A}" name="Tabela1" displayName="Tabela1" ref="C3:E51" totalsRowShown="0" headerRowDxfId="90" dataDxfId="89">
   <autoFilter ref="C3:E51" xr:uid="{9CB5EB0A-66D8-48B4-BC40-E2D214AFC03A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{BA403FB9-D643-4201-89E9-82280DBD496D}" name=" " dataDxfId="86"/>
-    <tableColumn id="2" xr3:uid="{8927B163-5C71-4390-8413-1CB7AFCDC479}" name="Times" dataDxfId="85"/>
-    <tableColumn id="3" xr3:uid="{95E8A229-CD3E-4FE0-BC0B-3E68BBDC2143}" name="  " dataDxfId="84"/>
+    <tableColumn id="1" xr3:uid="{BA403FB9-D643-4201-89E9-82280DBD496D}" name=" " dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{8927B163-5C71-4390-8413-1CB7AFCDC479}" name="Times" dataDxfId="87"/>
+    <tableColumn id="3" xr3:uid="{95E8A229-CD3E-4FE0-BC0B-3E68BBDC2143}" name="  " dataDxfId="86"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9093,7 +9104,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9199,7 +9210,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9341,7 +9352,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -9650,12 +9661,12 @@
     <mergeCell ref="J33:L33"/>
   </mergeCells>
   <conditionalFormatting sqref="J31:L31 J32:J33">
-    <cfRule type="cellIs" dxfId="90" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="2" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31:L33">
-    <cfRule type="expression" dxfId="89" priority="1">
+    <cfRule type="expression" dxfId="84" priority="1">
       <formula>M31&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22079,7 +22090,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="yMneGrh/V9v9I71ExvSu/Y2aQsnzReoZXlElqaiRdEFQ/HU0DofiNVmtRyr1uLMjGEnHu5TZOHdJIGeVyKwyVA==" saltValue="Bgw7AbWnF5ZQuHYiR+WIGA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jYYlVwSGK2cwUbCoz9yiV/3/qarQWCd0N5s5n0ASO0lHveA2ehdpEX2q+Q+OAp4tWRG8yzgngnOerW0AMWPDhQ==" saltValue="7vEdaL9dS3g/pLdxzX+azg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="F3:H3"/>
   </mergeCells>
@@ -22163,7 +22174,7 @@
       <formula>AH6=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF12:AF13 AF18:AF19 AF24:AF25 AF30:AF31 AF36:AF37 AF42:AF43 AF48:AF49 AF60:AF61 AF66:AF67 AF72:AF73 AF54:AF55">
+  <conditionalFormatting sqref="AF12:AF13 AF18:AF19 AF24:AF25 AF30:AF31 AF36:AF37 AF42:AF43 AF48:AF49 AF54:AF55 AF60:AF61 AF66:AF67 AF72:AF73">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>AH12=3</formula>
     </cfRule>
@@ -22178,7 +22189,7 @@
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BJ6:BJ13">
+  <conditionalFormatting sqref="BJ6:BJ17">
     <cfRule type="expression" dxfId="0" priority="77">
       <formula>BL6=3</formula>
     </cfRule>
@@ -54668,11 +54679,15 @@
         <v>África do Sul</v>
       </c>
       <c r="F5" s="149"/>
-      <c r="G5" s="123"/>
+      <c r="G5" s="123">
+        <v>0</v>
+      </c>
       <c r="H5" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="123"/>
+      <c r="I5" s="123">
+        <v>1</v>
+      </c>
       <c r="J5" s="150"/>
       <c r="K5" s="151" t="str">
         <f>IF('Fase de Grupos'!AH13=3,'Fase de Grupos'!AF13,"2º do Grupo B")</f>
@@ -54684,7 +54699,7 @@
       </c>
       <c r="M5" s="133" t="str">
         <f>IF(OR(G5="",I5=""),"Vencedor 73",IF(G5&lt;&gt;I5,IF(G5&gt;I5,E5,K5),IF(SUM(F5:G5)=SUM(I5:J5),"Vencedor 73",IF(SUM(F5:G5)&gt;SUM(I5:J5),E5,K5))))</f>
-        <v>Vencedor 73</v>
+        <v>Canadá</v>
       </c>
       <c r="N5" s="133">
         <v>73</v>
@@ -54741,24 +54756,32 @@
         <f>IF('Fase de Grupos'!AH30=3,'Fase de Grupos'!AF30,"1º do Grupo E")</f>
         <v>Alemanha</v>
       </c>
-      <c r="F6" s="149"/>
-      <c r="G6" s="123"/>
+      <c r="F6" s="149">
+        <v>3</v>
+      </c>
+      <c r="G6" s="123">
+        <v>1</v>
+      </c>
       <c r="H6" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="123"/>
-      <c r="J6" s="150"/>
+      <c r="I6" s="123">
+        <v>1</v>
+      </c>
+      <c r="J6" s="150">
+        <v>4</v>
+      </c>
       <c r="K6" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R11,"3º A, B, C, D ou F")</f>
         <v>Paraguai</v>
       </c>
       <c r="L6" s="136" t="str">
         <f t="shared" ref="L6:L12" si="0">IF(OR(G6="",I6=""),"",IF(G6=I6,"emp",""))</f>
-        <v/>
+        <v>emp</v>
       </c>
       <c r="M6" s="133" t="str">
         <f>IF(OR(G6="",I6=""),"Vencedor 74",IF(G6&lt;&gt;I6,IF(G6&gt;I6,E6,K6),IF(SUM(F6:G6)=SUM(I6:J6),"Vencedor 74",IF(SUM(F6:G6)&gt;SUM(I6:J6),E6,K6))))</f>
-        <v>Vencedor 74</v>
+        <v>Paraguai</v>
       </c>
       <c r="N6" s="133">
         <v>74</v>
@@ -54819,24 +54842,32 @@
         <f>IF('Fase de Grupos'!AH36=3,'Fase de Grupos'!AF36,"1º do Grupo F")</f>
         <v>Países Baixos</v>
       </c>
-      <c r="F7" s="149"/>
-      <c r="G7" s="123"/>
+      <c r="F7" s="149">
+        <v>2</v>
+      </c>
+      <c r="G7" s="123">
+        <v>1</v>
+      </c>
       <c r="H7" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="123"/>
-      <c r="J7" s="150"/>
+      <c r="I7" s="123">
+        <v>1</v>
+      </c>
+      <c r="J7" s="150">
+        <v>3</v>
+      </c>
       <c r="K7" s="151" t="str">
         <f>IF('Fase de Grupos'!AH19=3,'Fase de Grupos'!AF19,"2º do Grupo C")</f>
         <v>Marrocos</v>
       </c>
       <c r="L7" s="136" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>emp</v>
       </c>
       <c r="M7" s="133" t="str">
         <f>IF(OR(G7="",I7=""),"Vencedor 75",IF(G7&lt;&gt;I7,IF(G7&gt;I7,E7,K7),IF(SUM(F7:G7)=SUM(I7:J7),"Vencedor 75",IF(SUM(F7:G7)&gt;SUM(I7:J7),E7,K7))))</f>
-        <v>Vencedor 75</v>
+        <v>Marrocos</v>
       </c>
       <c r="N7" s="133">
         <v>75</v>
@@ -54894,11 +54925,15 @@
         <v>Brasil</v>
       </c>
       <c r="F8" s="149"/>
-      <c r="G8" s="123"/>
+      <c r="G8" s="123">
+        <v>2</v>
+      </c>
       <c r="H8" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="123"/>
+      <c r="I8" s="123">
+        <v>1</v>
+      </c>
       <c r="J8" s="150"/>
       <c r="K8" s="151" t="str">
         <f>IF('Fase de Grupos'!AH37=3,'Fase de Grupos'!AF37,"2º do Grupo F")</f>
@@ -54910,7 +54945,7 @@
       </c>
       <c r="M8" s="133" t="str">
         <f>IF(OR(G8="",I8=""),"Vencedor 76",IF(G8&lt;&gt;I8,IF(G8&gt;I8,E8,K8),IF(SUM(F8:G8)=SUM(I8:J8),"Vencedor 76",IF(SUM(F8:G8)&gt;SUM(I8:J8),E8,K8))))</f>
-        <v>Vencedor 76</v>
+        <v>Brasil</v>
       </c>
       <c r="N8" s="133">
         <v>76</v>
@@ -56029,7 +56064,7 @@
       </c>
       <c r="E25" s="106" t="str">
         <f>M6</f>
-        <v>Vencedor 74</v>
+        <v>Paraguai</v>
       </c>
       <c r="F25" s="149"/>
       <c r="G25" s="123"/>
@@ -56107,7 +56142,7 @@
       </c>
       <c r="E26" s="106" t="str">
         <f>M5</f>
-        <v>Vencedor 73</v>
+        <v>Canadá</v>
       </c>
       <c r="F26" s="149"/>
       <c r="G26" s="123"/>
@@ -56118,7 +56153,7 @@
       <c r="J26" s="150"/>
       <c r="K26" s="151" t="str">
         <f>M7</f>
-        <v>Vencedor 75</v>
+        <v>Marrocos</v>
       </c>
       <c r="L26" s="136" t="str">
         <f t="shared" ref="L26:L32" si="18">IF(OR(G26="",I26=""),"",IF(G26=I26,"emp",""))</f>
@@ -56151,7 +56186,7 @@
       </c>
       <c r="E27" s="106" t="str">
         <f>M8</f>
-        <v>Vencedor 76</v>
+        <v>Brasil</v>
       </c>
       <c r="F27" s="149"/>
       <c r="G27" s="123"/>
@@ -57403,7 +57438,7 @@
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="c6tPJJQuMaLYYVxDkvgugaxcC+Uv5gkJkUqZgIt2uuxbzexMxqxVyEOkWorUUitpEJ1MPNBlUf/aYq65/wymIg==" saltValue="0J8NZQ0DnJYkRWhoKBlPHA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <sortState ref="C59:C64">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C59:C64">
     <sortCondition ref="C59:C64"/>
   </sortState>
   <mergeCells count="16">

--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF302D3-E586-40A4-B7C7-8C07227B9510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D0651F-0D3B-4A43-AD72-F33B298C78AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BcI4NY5Ohir363+nRCln2YCzlnOeJyINjZ1aV0hb2IpPHmsHZPUFroFzrod6xokqyCn7GUW2N1Z+U/w2mbyNbQ==" workbookSaltValue="VvXyFesAZC8L8IOzNm6PtA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
@@ -2178,123 +2178,6 @@
   </cellStyles>
   <dxfs count="91">
     <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
@@ -2742,6 +2625,123 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -22095,102 +22095,102 @@
     <mergeCell ref="F3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A51 P3 B3:O51">
-    <cfRule type="cellIs" dxfId="19" priority="215" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="215" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:O75">
-    <cfRule type="cellIs" dxfId="18" priority="136" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="136" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E9">
-    <cfRule type="cellIs" dxfId="17" priority="202" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="202" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:E21">
-    <cfRule type="cellIs" dxfId="16" priority="193" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="193" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:E33">
-    <cfRule type="cellIs" dxfId="15" priority="191" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="191" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:E45">
-    <cfRule type="cellIs" dxfId="14" priority="189" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="189" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C52:E57">
-    <cfRule type="cellIs" dxfId="13" priority="130" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="130" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C64:E69">
-    <cfRule type="cellIs" dxfId="12" priority="128" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="128" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I9">
-    <cfRule type="cellIs" dxfId="11" priority="198" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="198" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:I21">
-    <cfRule type="cellIs" dxfId="10" priority="188" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="188" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I28:I33">
-    <cfRule type="cellIs" dxfId="9" priority="187" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="187" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I40:I45">
-    <cfRule type="cellIs" dxfId="8" priority="186" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="186" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I52:I57">
-    <cfRule type="cellIs" dxfId="7" priority="127" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="127" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I64:I69">
-    <cfRule type="cellIs" dxfId="6" priority="126" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="126" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:AN75">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF6:AF7">
-    <cfRule type="expression" dxfId="4" priority="209">
+    <cfRule type="expression" dxfId="32" priority="209">
       <formula>AH6=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF12:AF13 AF18:AF19 AF24:AF25 AF30:AF31 AF36:AF37 AF42:AF43 AF48:AF49 AF54:AF55 AF60:AF61 AF66:AF67 AF72:AF73">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>AH12=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP5:BG17">
-    <cfRule type="cellIs" dxfId="2" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="83" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI4:BR17">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ6:BJ17">
-    <cfRule type="expression" dxfId="0" priority="77">
+    <cfRule type="expression" dxfId="28" priority="77">
       <formula>BL6=3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -55020,11 +55020,15 @@
         <v>França</v>
       </c>
       <c r="F9" s="149"/>
-      <c r="G9" s="123"/>
+      <c r="G9" s="123">
+        <v>3</v>
+      </c>
       <c r="H9" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="123"/>
+      <c r="I9" s="123">
+        <v>0</v>
+      </c>
       <c r="J9" s="150"/>
       <c r="K9" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R13,"3º C, D, F, G ou H")</f>
@@ -55036,7 +55040,7 @@
       </c>
       <c r="M9" s="133" t="str">
         <f>IF(OR(G9="",I9=""),"Vencedor 77",IF(G9&lt;&gt;I9,IF(G9&gt;I9,E9,K9),IF(SUM(F9:G9)=SUM(I9:J9),"Vencedor 77",IF(SUM(F9:G9)&gt;SUM(I9:J9),E9,K9))))</f>
-        <v>Vencedor 77</v>
+        <v>França</v>
       </c>
       <c r="N9" s="133">
         <v>77</v>
@@ -55092,11 +55096,15 @@
         <v>Costa do Marfim</v>
       </c>
       <c r="F10" s="149"/>
-      <c r="G10" s="123"/>
+      <c r="G10" s="123">
+        <v>1</v>
+      </c>
       <c r="H10" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="123"/>
+      <c r="I10" s="123">
+        <v>2</v>
+      </c>
       <c r="J10" s="150"/>
       <c r="K10" s="151" t="str">
         <f>IF('Fase de Grupos'!AH55=3,'Fase de Grupos'!AF55,"2º do Grupo I")</f>
@@ -55108,7 +55116,7 @@
       </c>
       <c r="M10" s="133" t="str">
         <f>IF(OR(G10="",I10=""),"Vencedor 78",IF(G10&lt;&gt;I10,IF(G10&gt;I10,E10,K10),IF(SUM(F10:G10)=SUM(I10:J10),"Vencedor 78",IF(SUM(F10:G10)&gt;SUM(I10:J10),E10,K10))))</f>
-        <v>Vencedor 78</v>
+        <v>Noruega</v>
       </c>
       <c r="N10" s="133">
         <v>78</v>
@@ -55164,11 +55172,15 @@
         <v>México</v>
       </c>
       <c r="F11" s="149"/>
-      <c r="G11" s="123"/>
+      <c r="G11" s="123">
+        <v>2</v>
+      </c>
       <c r="H11" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="123"/>
+      <c r="I11" s="123">
+        <v>0</v>
+      </c>
       <c r="J11" s="150"/>
       <c r="K11" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R8,"3º C, E, F, H ou I")</f>
@@ -55180,7 +55192,7 @@
       </c>
       <c r="M11" s="133" t="str">
         <f>IF(OR(G11="",I11=""),"Vencedor 79",IF(G11&lt;&gt;I11,IF(G11&gt;I11,E11,K11),IF(SUM(F11:G11)=SUM(I11:J11),"Vencedor 79",IF(SUM(F11:G11)&gt;SUM(I11:J11),E11,K11))))</f>
-        <v>Vencedor 79</v>
+        <v>México</v>
       </c>
       <c r="N11" s="133">
         <v>79</v>
@@ -56075,7 +56087,7 @@
       <c r="J25" s="150"/>
       <c r="K25" s="151" t="str">
         <f>M9</f>
-        <v>Vencedor 77</v>
+        <v>França</v>
       </c>
       <c r="L25" s="136" t="str">
         <f>IF(OR(G25="",I25=""),"",IF(G25=I25,"emp",""))</f>
@@ -56197,7 +56209,7 @@
       <c r="J27" s="150"/>
       <c r="K27" s="151" t="str">
         <f>M10</f>
-        <v>Vencedor 78</v>
+        <v>Noruega</v>
       </c>
       <c r="L27" s="136" t="str">
         <f t="shared" si="18"/>
@@ -56230,7 +56242,7 @@
       </c>
       <c r="E28" s="106" t="str">
         <f>M11</f>
-        <v>Vencedor 79</v>
+        <v>México</v>
       </c>
       <c r="F28" s="149"/>
       <c r="G28" s="123"/>
@@ -56682,142 +56694,142 @@
     <mergeCell ref="Y34:AA34"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A2 B2:K2 X9:AG10 X15:AG16 X20:AG21 B21:K22 AB34:AB36 A57:K58 H59:K61 B62:K71 B83:K1048576">
-    <cfRule type="cellIs" dxfId="47" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="76" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:B12 C4:K12">
-    <cfRule type="cellIs" dxfId="46" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="42" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:K20">
-    <cfRule type="cellIs" dxfId="45" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="31" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:B36 C24:K33">
-    <cfRule type="cellIs" dxfId="44" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="20" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F20">
-    <cfRule type="expression" dxfId="43" priority="30">
+    <cfRule type="expression" dxfId="23" priority="30">
       <formula>L5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:F32">
-    <cfRule type="expression" dxfId="42" priority="19">
+    <cfRule type="expression" dxfId="22" priority="19">
       <formula>L25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:J20">
-    <cfRule type="expression" dxfId="41" priority="29">
+    <cfRule type="expression" dxfId="21" priority="29">
       <formula>L5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J25:J32">
-    <cfRule type="expression" dxfId="40" priority="18">
+    <cfRule type="expression" dxfId="20" priority="18">
       <formula>L25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K20">
-    <cfRule type="expression" dxfId="39" priority="21">
+    <cfRule type="expression" dxfId="19" priority="21">
       <formula>Q5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K32">
-    <cfRule type="expression" dxfId="38" priority="17">
+    <cfRule type="expression" dxfId="18" priority="17">
       <formula>Q25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W3:W24 A21:A34 I34:K34 Y34:AB34 Y34:Y36 A62:A1048576">
-    <cfRule type="cellIs" dxfId="37" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="77" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X3:X8 Y4:AG8">
-    <cfRule type="cellIs" dxfId="36" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="16" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X11:X14 Y12:AG14">
-    <cfRule type="cellIs" dxfId="35" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X17:X19 Y18:AG19">
-    <cfRule type="cellIs" dxfId="34" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X23:X25 Y24:AG25">
-    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y34:AA36">
-    <cfRule type="expression" dxfId="32" priority="65">
+    <cfRule type="expression" dxfId="12" priority="65">
       <formula>AB34&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB5:AB8">
-    <cfRule type="expression" dxfId="31" priority="15">
+    <cfRule type="expression" dxfId="11" priority="15">
       <formula>AH5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB13:AB14">
-    <cfRule type="expression" dxfId="30" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>AH13="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB19">
-    <cfRule type="expression" dxfId="29" priority="7">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>AH19="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB25">
-    <cfRule type="expression" dxfId="28" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>AH25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF5:AF8">
-    <cfRule type="expression" dxfId="27" priority="14">
+    <cfRule type="expression" dxfId="7" priority="14">
       <formula>AH5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF13:AF14">
-    <cfRule type="expression" dxfId="26" priority="10">
+    <cfRule type="expression" dxfId="6" priority="10">
       <formula>AH13="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF19">
-    <cfRule type="expression" dxfId="25" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>AH19="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF25">
-    <cfRule type="expression" dxfId="24" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>AH25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG5:AG8">
-    <cfRule type="expression" dxfId="23" priority="13">
+    <cfRule type="expression" dxfId="3" priority="13">
       <formula>AM5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG13:AG14">
-    <cfRule type="expression" dxfId="22" priority="9">
+    <cfRule type="expression" dxfId="2" priority="9">
       <formula>AM13="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG19">
-    <cfRule type="expression" dxfId="21" priority="5">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>AM19="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG25">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AM25="emp"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D0651F-0D3B-4A43-AD72-F33B298C78AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9699A2C-6FD9-466F-82D7-B46D28F5B04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BcI4NY5Ohir363+nRCln2YCzlnOeJyINjZ1aV0hb2IpPHmsHZPUFroFzrod6xokqyCn7GUW2N1Z+U/w2mbyNbQ==" workbookSaltValue="VvXyFesAZC8L8IOzNm6PtA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8985" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8987" uniqueCount="212">
   <si>
     <t>Times</t>
   </si>
@@ -786,6 +786,9 @@
       <t>.</t>
     </r>
   </si>
+  <si>
+    <t>Apoio</t>
+  </si>
 </sst>
 </file>
 
@@ -1125,7 +1128,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -1643,12 +1646,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="204">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2138,6 +2161,15 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2148,15 +2180,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2171,12 +2194,142 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="91">
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2625,123 +2778,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -5114,6 +5150,178 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>4763</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>766762</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95419BAC-1011-4E09-ADE6-2668E33B6843}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{BEBA8EAE-BF5A-486C-A8C5-ECC9F3942E4B}">
+              <a14:imgProps xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a14:imgLayer r:embed="rId5">
+                  <a14:imgEffect>
+                    <a14:colorTemperature colorTemp="4700"/>
+                  </a14:imgEffect>
+                </a14:imgLayer>
+              </a14:imgProps>
+            </a:ext>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8501063" y="5429250"/>
+          <a:ext cx="761999" cy="761999"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>769145</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>64</xdr:col>
+      <xdr:colOff>245270</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>188119</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="CaixaDeTexto 3">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6588783-5929-4477-B6BE-15E2394DA1B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10646570" y="4343400"/>
+          <a:ext cx="1352550" cy="759619"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Albertus MT Lt" panose="020E0502030304020304" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Rei da Pechincha</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="pt-BR" sz="800" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Albertus MT Lt" panose="020E0502030304020304" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Albertus MT Lt" panose="020E0502030304020304" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Promoções &amp;</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Albertus MT Lt" panose="020E0502030304020304" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> Achadinhos</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Albertus MT Lt" panose="020E0502030304020304" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5168,6 +5376,178 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>4763</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>223837</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AEEA6ED-56F8-5305-26CE-2D6B3691CE3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{BEBA8EAE-BF5A-486C-A8C5-ECC9F3942E4B}">
+              <a14:imgProps xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a14:imgLayer r:embed="rId5">
+                  <a14:imgEffect>
+                    <a14:colorTemperature colorTemp="4700"/>
+                  </a14:imgEffect>
+                </a14:imgLayer>
+              </a14:imgProps>
+            </a:ext>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8501063" y="5429250"/>
+          <a:ext cx="761999" cy="761999"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>226220</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>1378744</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>188119</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="CaixaDeTexto 4">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{230368B4-4B95-1780-08EC-C6FAD6D525D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9265445" y="5429250"/>
+          <a:ext cx="1152524" cy="759619"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Albertus MT Lt" panose="020E0502030304020304" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Rei da Pechincha</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="pt-BR" sz="800" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Albertus MT Lt" panose="020E0502030304020304" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Albertus MT Lt" panose="020E0502030304020304" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Promoções &amp;</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Albertus MT Lt" panose="020E0502030304020304" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> Achadinhos</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Albertus MT Lt" panose="020E0502030304020304" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -9654,7 +10034,7 @@
       <c r="L33" s="183"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="R7MKfGIr3q3KasSJACKADhTt/LYOodNa9tmtKJjgNCMenwB8F4JksD1Wb6Inyd7c0WaCL2TG1h5loB5f76zIiQ==" saltValue="vzSxU7R4LDF7bDaBkhG3gA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="JhGV6VcDyvc3i9om8xFJD2TTjYS4KxdyrPHqfmvoUHY8jTzdLhnXdEDqhfq9o8QSGpM59e0FFua65Es5mRgoOA==" saltValue="uIq4f/wxSDvjcYmJtVUiRQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="3">
     <mergeCell ref="J31:L31"/>
     <mergeCell ref="J32:L32"/>
@@ -14992,6 +15372,12 @@
         <f t="shared" ref="AR22:AR28" si="37">CODE(AQ22)</f>
         <v>70</v>
       </c>
+      <c r="BJ22" s="193" t="s">
+        <v>211</v>
+      </c>
+      <c r="BK22" s="194"/>
+      <c r="BL22" s="194"/>
+      <c r="BM22" s="195"/>
     </row>
     <row r="23" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A23" s="45"/>
@@ -15125,6 +15511,10 @@
         <f t="shared" si="37"/>
         <v>69</v>
       </c>
+      <c r="BJ23" s="205"/>
+      <c r="BK23" s="204"/>
+      <c r="BL23" s="204"/>
+      <c r="BM23" s="206"/>
     </row>
     <row r="24" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A24" s="45"/>
@@ -15281,6 +15671,10 @@
         <f t="shared" si="37"/>
         <v>76</v>
       </c>
+      <c r="BJ24" s="205"/>
+      <c r="BK24" s="204"/>
+      <c r="BL24" s="204"/>
+      <c r="BM24" s="207"/>
     </row>
     <row r="25" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A25" s="45"/>
@@ -15437,6 +15831,10 @@
         <f t="shared" si="37"/>
         <v>66</v>
       </c>
+      <c r="BJ25" s="205"/>
+      <c r="BK25" s="204"/>
+      <c r="BL25" s="204"/>
+      <c r="BM25" s="207"/>
     </row>
     <row r="26" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A26" s="45"/>
@@ -15593,6 +15991,10 @@
         <f t="shared" si="37"/>
         <v>74</v>
       </c>
+      <c r="BJ26" s="208"/>
+      <c r="BK26" s="209"/>
+      <c r="BL26" s="209"/>
+      <c r="BM26" s="210"/>
     </row>
     <row r="27" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="45"/>
@@ -22090,107 +22492,108 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jYYlVwSGK2cwUbCoz9yiV/3/qarQWCd0N5s5n0ASO0lHveA2ehdpEX2q+Q+OAp4tWRG8yzgngnOerW0AMWPDhQ==" saltValue="7vEdaL9dS3g/pLdxzX+azg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="1">
+  <sheetProtection algorithmName="SHA-512" hashValue="8zT4037DyHXrLqdq5iYyYrMR0TWaotldz5hVI4fTDbdqZ7l+Cxdqs/9/FGMP4061jLNiKfePtLYXoWPo6TdRXA==" saltValue="fkE/EIHEl7y+xiKxPcgv5w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <mergeCells count="2">
     <mergeCell ref="F3:H3"/>
+    <mergeCell ref="BJ22:BM22"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A51 P3 B3:O51">
-    <cfRule type="cellIs" dxfId="47" priority="215" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="215" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:O75">
-    <cfRule type="cellIs" dxfId="46" priority="136" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="136" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E9">
-    <cfRule type="cellIs" dxfId="45" priority="202" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="202" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:E21">
-    <cfRule type="cellIs" dxfId="44" priority="193" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="193" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:E33">
-    <cfRule type="cellIs" dxfId="43" priority="191" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="191" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:E45">
-    <cfRule type="cellIs" dxfId="42" priority="189" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="189" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C52:E57">
-    <cfRule type="cellIs" dxfId="41" priority="130" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="130" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C64:E69">
-    <cfRule type="cellIs" dxfId="40" priority="128" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="128" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I9">
-    <cfRule type="cellIs" dxfId="39" priority="198" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="198" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:I21">
-    <cfRule type="cellIs" dxfId="38" priority="188" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="188" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I28:I33">
-    <cfRule type="cellIs" dxfId="37" priority="187" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="187" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I40:I45">
-    <cfRule type="cellIs" dxfId="36" priority="186" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="186" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I52:I57">
-    <cfRule type="cellIs" dxfId="35" priority="127" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="127" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I64:I69">
-    <cfRule type="cellIs" dxfId="34" priority="126" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="126" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:AN75">
-    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF6:AF7">
-    <cfRule type="expression" dxfId="32" priority="209">
+    <cfRule type="expression" dxfId="4" priority="209">
       <formula>AH6=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF12:AF13 AF18:AF19 AF24:AF25 AF30:AF31 AF36:AF37 AF42:AF43 AF48:AF49 AF54:AF55 AF60:AF61 AF66:AF67 AF72:AF73">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>AH12=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP5:BG17">
-    <cfRule type="cellIs" dxfId="30" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="83" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI4:BR17">
-    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BJ6:BJ17">
-    <cfRule type="expression" dxfId="28" priority="77">
+  <conditionalFormatting sqref="BJ6:BJ13">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>BL6=3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54570,18 +54973,18 @@
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="130"/>
-      <c r="B3" s="197" t="s">
+      <c r="B3" s="193" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="199"/>
+      <c r="C3" s="194"/>
+      <c r="D3" s="194"/>
+      <c r="E3" s="194"/>
+      <c r="F3" s="194"/>
+      <c r="G3" s="194"/>
+      <c r="H3" s="194"/>
+      <c r="I3" s="194"/>
+      <c r="J3" s="194"/>
+      <c r="K3" s="195"/>
       <c r="L3" s="131"/>
       <c r="M3" s="132"/>
       <c r="N3" s="132"/>
@@ -54589,18 +54992,18 @@
       <c r="P3" s="132"/>
       <c r="Q3" s="132"/>
       <c r="W3" s="130"/>
-      <c r="X3" s="197" t="s">
+      <c r="X3" s="193" t="s">
         <v>73</v>
       </c>
-      <c r="Y3" s="198"/>
-      <c r="Z3" s="198"/>
-      <c r="AA3" s="198"/>
-      <c r="AB3" s="198"/>
-      <c r="AC3" s="198"/>
-      <c r="AD3" s="198"/>
-      <c r="AE3" s="198"/>
-      <c r="AF3" s="198"/>
-      <c r="AG3" s="199"/>
+      <c r="Y3" s="194"/>
+      <c r="Z3" s="194"/>
+      <c r="AA3" s="194"/>
+      <c r="AB3" s="194"/>
+      <c r="AC3" s="194"/>
+      <c r="AD3" s="194"/>
+      <c r="AE3" s="194"/>
+      <c r="AF3" s="194"/>
+      <c r="AG3" s="195"/>
       <c r="AH3" s="131"/>
       <c r="AI3" s="132"/>
       <c r="AJ3" s="132"/>
@@ -54617,19 +55020,19 @@
       <c r="D4" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="193" t="s">
+      <c r="E4" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="193"/>
-      <c r="G4" s="193" t="s">
+      <c r="F4" s="196"/>
+      <c r="G4" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="193"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193" t="s">
+      <c r="H4" s="196"/>
+      <c r="I4" s="196"/>
+      <c r="J4" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="193"/>
+      <c r="K4" s="196"/>
       <c r="L4" s="135"/>
       <c r="M4" s="135"/>
       <c r="N4" s="135"/>
@@ -54644,19 +55047,19 @@
       <c r="Z4" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA4" s="193" t="s">
+      <c r="AA4" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AB4" s="193"/>
-      <c r="AC4" s="193" t="s">
+      <c r="AB4" s="196"/>
+      <c r="AC4" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="AD4" s="193"/>
-      <c r="AE4" s="193"/>
-      <c r="AF4" s="193" t="s">
+      <c r="AD4" s="196"/>
+      <c r="AE4" s="196"/>
+      <c r="AF4" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AG4" s="193"/>
+      <c r="AG4" s="196"/>
       <c r="AH4" s="136"/>
       <c r="AI4" s="133"/>
       <c r="AJ4" s="133"/>
@@ -55216,18 +55619,18 @@
         <v>12</v>
       </c>
       <c r="W11" s="130"/>
-      <c r="X11" s="197" t="s">
+      <c r="X11" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="Y11" s="198"/>
-      <c r="Z11" s="198"/>
-      <c r="AA11" s="198"/>
-      <c r="AB11" s="198"/>
-      <c r="AC11" s="198"/>
-      <c r="AD11" s="198"/>
-      <c r="AE11" s="198"/>
-      <c r="AF11" s="198"/>
-      <c r="AG11" s="199"/>
+      <c r="Y11" s="194"/>
+      <c r="Z11" s="194"/>
+      <c r="AA11" s="194"/>
+      <c r="AB11" s="194"/>
+      <c r="AC11" s="194"/>
+      <c r="AD11" s="194"/>
+      <c r="AE11" s="194"/>
+      <c r="AF11" s="194"/>
+      <c r="AG11" s="195"/>
       <c r="AH11" s="131"/>
       <c r="AI11" s="132"/>
       <c r="AJ11" s="132"/>
@@ -55297,19 +55700,19 @@
       <c r="Z12" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA12" s="193" t="s">
+      <c r="AA12" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AB12" s="193"/>
-      <c r="AC12" s="193" t="s">
+      <c r="AB12" s="196"/>
+      <c r="AC12" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="AD12" s="193"/>
-      <c r="AE12" s="193"/>
-      <c r="AF12" s="193" t="s">
+      <c r="AD12" s="196"/>
+      <c r="AE12" s="196"/>
+      <c r="AF12" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AG12" s="193"/>
+      <c r="AG12" s="196"/>
       <c r="AH12" s="136"/>
       <c r="AI12" s="133"/>
       <c r="AJ12" s="133"/>
@@ -55684,18 +56087,18 @@
         <v>30</v>
       </c>
       <c r="W17" s="130"/>
-      <c r="X17" s="197" t="s">
+      <c r="X17" s="193" t="s">
         <v>77</v>
       </c>
-      <c r="Y17" s="198"/>
-      <c r="Z17" s="198"/>
-      <c r="AA17" s="198"/>
-      <c r="AB17" s="198"/>
-      <c r="AC17" s="198"/>
-      <c r="AD17" s="198"/>
-      <c r="AE17" s="198"/>
-      <c r="AF17" s="198"/>
-      <c r="AG17" s="199"/>
+      <c r="Y17" s="194"/>
+      <c r="Z17" s="194"/>
+      <c r="AA17" s="194"/>
+      <c r="AB17" s="194"/>
+      <c r="AC17" s="194"/>
+      <c r="AD17" s="194"/>
+      <c r="AE17" s="194"/>
+      <c r="AF17" s="194"/>
+      <c r="AG17" s="195"/>
       <c r="AH17" s="131"/>
       <c r="AI17" s="132"/>
       <c r="AJ17" s="132"/>
@@ -55754,19 +56157,19 @@
       <c r="Z18" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA18" s="193" t="s">
+      <c r="AA18" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AB18" s="193"/>
-      <c r="AC18" s="193" t="s">
+      <c r="AB18" s="196"/>
+      <c r="AC18" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="AD18" s="193"/>
-      <c r="AE18" s="193"/>
-      <c r="AF18" s="193" t="s">
+      <c r="AD18" s="196"/>
+      <c r="AE18" s="196"/>
+      <c r="AF18" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AG18" s="193"/>
+      <c r="AG18" s="196"/>
       <c r="AH18" s="136"/>
       <c r="AI18" s="133"/>
       <c r="AJ18" s="133"/>
@@ -55958,18 +56361,18 @@
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" s="130"/>
-      <c r="B23" s="197" t="s">
+      <c r="B23" s="193" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="198"/>
-      <c r="D23" s="198"/>
-      <c r="E23" s="198"/>
-      <c r="F23" s="198"/>
-      <c r="G23" s="198"/>
-      <c r="H23" s="198"/>
-      <c r="I23" s="198"/>
-      <c r="J23" s="198"/>
-      <c r="K23" s="199"/>
+      <c r="C23" s="194"/>
+      <c r="D23" s="194"/>
+      <c r="E23" s="194"/>
+      <c r="F23" s="194"/>
+      <c r="G23" s="194"/>
+      <c r="H23" s="194"/>
+      <c r="I23" s="194"/>
+      <c r="J23" s="194"/>
+      <c r="K23" s="195"/>
       <c r="L23" s="131"/>
       <c r="M23" s="132"/>
       <c r="N23" s="132"/>
@@ -55984,18 +56387,18 @@
         <v>48</v>
       </c>
       <c r="W23" s="45"/>
-      <c r="X23" s="197" t="s">
+      <c r="X23" s="193" t="s">
         <v>79</v>
       </c>
-      <c r="Y23" s="198"/>
-      <c r="Z23" s="198"/>
-      <c r="AA23" s="198"/>
-      <c r="AB23" s="198"/>
-      <c r="AC23" s="198"/>
-      <c r="AD23" s="198"/>
-      <c r="AE23" s="198"/>
-      <c r="AF23" s="198"/>
-      <c r="AG23" s="199"/>
+      <c r="Y23" s="194"/>
+      <c r="Z23" s="194"/>
+      <c r="AA23" s="194"/>
+      <c r="AB23" s="194"/>
+      <c r="AC23" s="194"/>
+      <c r="AD23" s="194"/>
+      <c r="AE23" s="194"/>
+      <c r="AF23" s="194"/>
+      <c r="AG23" s="195"/>
       <c r="AH23" s="131"/>
       <c r="AI23" s="132"/>
       <c r="AJ23" s="132"/>
@@ -56011,19 +56414,19 @@
       <c r="D24" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="193" t="s">
+      <c r="E24" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="F24" s="193"/>
-      <c r="G24" s="193" t="s">
+      <c r="F24" s="196"/>
+      <c r="G24" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="193"/>
-      <c r="I24" s="193"/>
-      <c r="J24" s="193" t="s">
+      <c r="H24" s="196"/>
+      <c r="I24" s="196"/>
+      <c r="J24" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="K24" s="193"/>
+      <c r="K24" s="196"/>
       <c r="L24" s="135"/>
       <c r="M24" s="135"/>
       <c r="N24" s="135"/>
@@ -56045,19 +56448,19 @@
       <c r="Z24" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA24" s="193" t="s">
+      <c r="AA24" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AB24" s="193"/>
-      <c r="AC24" s="193" t="s">
+      <c r="AB24" s="196"/>
+      <c r="AC24" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="AD24" s="193"/>
-      <c r="AE24" s="193"/>
-      <c r="AF24" s="193" t="s">
+      <c r="AD24" s="196"/>
+      <c r="AE24" s="196"/>
+      <c r="AF24" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="AG24" s="193"/>
+      <c r="AG24" s="196"/>
       <c r="AH24" s="136"/>
       <c r="AI24" s="133"/>
       <c r="AJ24" s="133"/>
@@ -56273,6 +56676,12 @@
         <f t="shared" ref="U28:U30" si="21">U27+5</f>
         <v>65</v>
       </c>
+      <c r="AD28" s="193" t="s">
+        <v>211</v>
+      </c>
+      <c r="AE28" s="194"/>
+      <c r="AF28" s="194"/>
+      <c r="AG28" s="195"/>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B29" s="152">
@@ -56317,6 +56726,10 @@
         <f t="shared" ref="U29:U31" si="22">U28+1</f>
         <v>66</v>
       </c>
+      <c r="AD29" s="205"/>
+      <c r="AE29" s="204"/>
+      <c r="AF29" s="204"/>
+      <c r="AG29" s="206"/>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B30" s="152">
@@ -56361,6 +56774,10 @@
         <f t="shared" si="21"/>
         <v>71</v>
       </c>
+      <c r="AD30" s="205"/>
+      <c r="AE30" s="204"/>
+      <c r="AF30" s="204"/>
+      <c r="AG30" s="207"/>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B31" s="152">
@@ -56405,6 +56822,10 @@
         <f t="shared" si="22"/>
         <v>72</v>
       </c>
+      <c r="AD31" s="205"/>
+      <c r="AE31" s="204"/>
+      <c r="AF31" s="204"/>
+      <c r="AG31" s="207"/>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B32" s="152">
@@ -56442,6 +56863,10 @@
       <c r="N32" s="133">
         <v>96</v>
       </c>
+      <c r="AD32" s="208"/>
+      <c r="AE32" s="209"/>
+      <c r="AF32" s="209"/>
+      <c r="AG32" s="210"/>
     </row>
     <row r="33" spans="2:33" x14ac:dyDescent="0.25">
       <c r="C33" s="137"/>
@@ -56456,15 +56881,15 @@
       </c>
       <c r="Z34" s="202"/>
       <c r="AA34" s="202"/>
-      <c r="AB34" s="194" t="str">
+      <c r="AB34" s="197" t="str">
         <f>IF(AI25="1º Lugar","",AI25)</f>
         <v/>
       </c>
-      <c r="AC34" s="194"/>
-      <c r="AD34" s="194"/>
-      <c r="AE34" s="194"/>
-      <c r="AF34" s="194"/>
-      <c r="AG34" s="194"/>
+      <c r="AC34" s="197"/>
+      <c r="AD34" s="197"/>
+      <c r="AE34" s="197"/>
+      <c r="AF34" s="197"/>
+      <c r="AG34" s="197"/>
     </row>
     <row r="35" spans="2:33" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B35" s="140"/>
@@ -56476,15 +56901,15 @@
       </c>
       <c r="Z35" s="200"/>
       <c r="AA35" s="200"/>
-      <c r="AB35" s="195" t="str">
+      <c r="AB35" s="198" t="str">
         <f>IF(M57="2º Lugar","",M57)</f>
         <v/>
       </c>
-      <c r="AC35" s="195"/>
-      <c r="AD35" s="195"/>
-      <c r="AE35" s="195"/>
-      <c r="AF35" s="195"/>
-      <c r="AG35" s="195"/>
+      <c r="AC35" s="198"/>
+      <c r="AD35" s="198"/>
+      <c r="AE35" s="198"/>
+      <c r="AF35" s="198"/>
+      <c r="AG35" s="198"/>
     </row>
     <row r="36" spans="2:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="140"/>
@@ -56496,15 +56921,15 @@
       </c>
       <c r="Z36" s="201"/>
       <c r="AA36" s="201"/>
-      <c r="AB36" s="196" t="str">
+      <c r="AB36" s="199" t="str">
         <f>IF(AI19="3º Lugar","",AI19)</f>
         <v/>
       </c>
-      <c r="AC36" s="196"/>
-      <c r="AD36" s="196"/>
-      <c r="AE36" s="196"/>
-      <c r="AF36" s="196"/>
-      <c r="AG36" s="196"/>
+      <c r="AC36" s="199"/>
+      <c r="AD36" s="199"/>
+      <c r="AE36" s="199"/>
+      <c r="AF36" s="199"/>
+      <c r="AG36" s="199"/>
     </row>
     <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="137"/>
@@ -56660,8 +57085,23 @@
       <c r="K82" s="45"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="e9SwIN3P1gzBH+IVoOp3qqE533HDYkDzheVXRVNRaqt2vhimaHXLKZ+8sDUopKeiKAT5et9NZBvuLRUJOa6zQg==" saltValue="pxuBsAAmB/Bn8sNidXdYpQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="30">
+  <sheetProtection algorithmName="SHA-512" hashValue="8JRv5B/B5jMSXJQTg3Gidv52YDGKsjKvo30SeOBaK6JSNYAMZQ/wPbZnASuXj0gcQnaFpGbQs8ZzG0RfUFK9kg==" saltValue="BbqaqtGKXaW/tQWh+QEg4w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <mergeCells count="31">
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AB34:AG34"/>
+    <mergeCell ref="AB35:AG35"/>
+    <mergeCell ref="AB36:AG36"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="Y35:AA35"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="AF24:AG24"/>
+    <mergeCell ref="Y34:AA34"/>
+    <mergeCell ref="AD28:AG28"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:I4"/>
@@ -56678,158 +57118,144 @@
     <mergeCell ref="AF18:AG18"/>
     <mergeCell ref="AA4:AB4"/>
     <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AB34:AG34"/>
-    <mergeCell ref="AB35:AG35"/>
-    <mergeCell ref="AB36:AG36"/>
-    <mergeCell ref="B23:K23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="Y35:AA35"/>
-    <mergeCell ref="Y36:AA36"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AC24:AE24"/>
-    <mergeCell ref="AF24:AG24"/>
-    <mergeCell ref="Y34:AA34"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A2 B2:K2 X9:AG10 X15:AG16 X20:AG21 B21:K22 AB34:AB36 A57:K58 H59:K61 B62:K71 B83:K1048576">
-    <cfRule type="cellIs" dxfId="27" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="76" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:B12 C4:K12">
-    <cfRule type="cellIs" dxfId="26" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="42" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:K20">
-    <cfRule type="cellIs" dxfId="25" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="31" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:B36 C24:K33">
-    <cfRule type="cellIs" dxfId="24" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="20" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F20">
-    <cfRule type="expression" dxfId="23" priority="30">
+    <cfRule type="expression" dxfId="43" priority="30">
       <formula>L5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:F32">
-    <cfRule type="expression" dxfId="22" priority="19">
+    <cfRule type="expression" dxfId="42" priority="19">
       <formula>L25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:J20">
-    <cfRule type="expression" dxfId="21" priority="29">
+    <cfRule type="expression" dxfId="41" priority="29">
       <formula>L5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J25:J32">
-    <cfRule type="expression" dxfId="20" priority="18">
+    <cfRule type="expression" dxfId="40" priority="18">
       <formula>L25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K20">
-    <cfRule type="expression" dxfId="19" priority="21">
+    <cfRule type="expression" dxfId="39" priority="21">
       <formula>Q5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K32">
-    <cfRule type="expression" dxfId="18" priority="17">
+    <cfRule type="expression" dxfId="38" priority="17">
       <formula>Q25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W3:W24 A21:A34 I34:K34 Y34:AB34 Y34:Y36 A62:A1048576">
-    <cfRule type="cellIs" dxfId="17" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="77" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X3:X8 Y4:AG8">
-    <cfRule type="cellIs" dxfId="16" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="16" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X11:X14 Y12:AG14">
-    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="12" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X17:X19 Y18:AG19">
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="8" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X23:X25 Y24:AG25">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y34:AA36">
-    <cfRule type="expression" dxfId="12" priority="65">
+    <cfRule type="expression" dxfId="32" priority="65">
       <formula>AB34&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB5:AB8">
-    <cfRule type="expression" dxfId="11" priority="15">
+    <cfRule type="expression" dxfId="31" priority="15">
       <formula>AH5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB13:AB14">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="30" priority="11">
       <formula>AH13="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB19">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="29" priority="7">
       <formula>AH19="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB25">
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="28" priority="3">
       <formula>AH25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF5:AF8">
-    <cfRule type="expression" dxfId="7" priority="14">
+    <cfRule type="expression" dxfId="27" priority="14">
       <formula>AH5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF13:AF14">
-    <cfRule type="expression" dxfId="6" priority="10">
+    <cfRule type="expression" dxfId="26" priority="10">
       <formula>AH13="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF19">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="25" priority="6">
       <formula>AH19="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF25">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="24" priority="2">
       <formula>AH25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG5:AG8">
-    <cfRule type="expression" dxfId="3" priority="13">
+    <cfRule type="expression" dxfId="23" priority="13">
       <formula>AM5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG13:AG14">
-    <cfRule type="expression" dxfId="2" priority="9">
+    <cfRule type="expression" dxfId="22" priority="9">
       <formula>AM13="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG19">
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="21" priority="5">
       <formula>AM19="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG25">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>AM25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57454,6 +57880,12 @@
     <sortCondition ref="C59:C64"/>
   </sortState>
   <mergeCells count="16">
+    <mergeCell ref="N4:N6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="L4:L6"/>
     <mergeCell ref="AB4:AB6"/>
     <mergeCell ref="AD4:AD6"/>
     <mergeCell ref="AF4:AF6"/>
@@ -57464,12 +57896,6 @@
     <mergeCell ref="V4:V6"/>
     <mergeCell ref="X4:X6"/>
     <mergeCell ref="Z4:Z6"/>
-    <mergeCell ref="N4:N6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="J4:J6"/>
-    <mergeCell ref="L4:L6"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -57705,20 +58131,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -57741,6 +58167,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
@@ -57755,12 +58189,4 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9699A2C-6FD9-466F-82D7-B46D28F5B04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E09303-BA36-4D6D-A084-05BD5255E3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BcI4NY5Ohir363+nRCln2YCzlnOeJyINjZ1aV0hb2IpPHmsHZPUFroFzrod6xokqyCn7GUW2N1Z+U/w2mbyNbQ==" workbookSaltValue="VvXyFesAZC8L8IOzNm6PtA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
@@ -2125,6 +2125,19 @@
     <xf numFmtId="0" fontId="39" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2135,6 +2148,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2161,15 +2183,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2194,142 +2207,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="91">
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2778,6 +2661,123 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -10007,31 +10007,31 @@
       <c r="I31" s="178" t="s">
         <v>206</v>
       </c>
-      <c r="J31" s="181" t="s">
+      <c r="J31" s="188" t="s">
         <v>81</v>
       </c>
-      <c r="K31" s="181"/>
-      <c r="L31" s="181"/>
+      <c r="K31" s="188"/>
+      <c r="L31" s="188"/>
     </row>
     <row r="32" spans="3:15" ht="18.75" x14ac:dyDescent="0.3">
       <c r="I32" s="179" t="s">
         <v>207</v>
       </c>
-      <c r="J32" s="182" t="s">
+      <c r="J32" s="189" t="s">
         <v>82</v>
       </c>
-      <c r="K32" s="182"/>
-      <c r="L32" s="182"/>
+      <c r="K32" s="189"/>
+      <c r="L32" s="189"/>
     </row>
     <row r="33" spans="9:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="I33" s="180" t="s">
         <v>208</v>
       </c>
-      <c r="J33" s="183" t="s">
+      <c r="J33" s="190" t="s">
         <v>83</v>
       </c>
-      <c r="K33" s="183"/>
-      <c r="L33" s="183"/>
+      <c r="K33" s="190"/>
+      <c r="L33" s="190"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="JhGV6VcDyvc3i9om8xFJD2TTjYS4KxdyrPHqfmvoUHY8jTzdLhnXdEDqhfq9o8QSGpM59e0FFua65Es5mRgoOA==" saltValue="uIq4f/wxSDvjcYmJtVUiRQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
@@ -11531,11 +11531,11 @@
       <c r="E3" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="184" t="s">
+      <c r="F3" s="191" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
+      <c r="G3" s="191"/>
+      <c r="H3" s="191"/>
       <c r="I3" s="91" t="s">
         <v>17</v>
       </c>
@@ -15372,12 +15372,12 @@
         <f t="shared" ref="AR22:AR28" si="37">CODE(AQ22)</f>
         <v>70</v>
       </c>
-      <c r="BJ22" s="193" t="s">
+      <c r="BJ22" s="192" t="s">
         <v>211</v>
       </c>
-      <c r="BK22" s="194"/>
-      <c r="BL22" s="194"/>
-      <c r="BM22" s="195"/>
+      <c r="BK22" s="193"/>
+      <c r="BL22" s="193"/>
+      <c r="BM22" s="194"/>
     </row>
     <row r="23" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A23" s="45"/>
@@ -15511,10 +15511,10 @@
         <f t="shared" si="37"/>
         <v>69</v>
       </c>
-      <c r="BJ23" s="205"/>
-      <c r="BK23" s="204"/>
-      <c r="BL23" s="204"/>
-      <c r="BM23" s="206"/>
+      <c r="BJ23" s="182"/>
+      <c r="BK23" s="181"/>
+      <c r="BL23" s="181"/>
+      <c r="BM23" s="183"/>
     </row>
     <row r="24" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A24" s="45"/>
@@ -15671,10 +15671,10 @@
         <f t="shared" si="37"/>
         <v>76</v>
       </c>
-      <c r="BJ24" s="205"/>
-      <c r="BK24" s="204"/>
-      <c r="BL24" s="204"/>
-      <c r="BM24" s="207"/>
+      <c r="BJ24" s="182"/>
+      <c r="BK24" s="181"/>
+      <c r="BL24" s="181"/>
+      <c r="BM24" s="184"/>
     </row>
     <row r="25" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A25" s="45"/>
@@ -15831,10 +15831,10 @@
         <f t="shared" si="37"/>
         <v>66</v>
       </c>
-      <c r="BJ25" s="205"/>
-      <c r="BK25" s="204"/>
-      <c r="BL25" s="204"/>
-      <c r="BM25" s="207"/>
+      <c r="BJ25" s="182"/>
+      <c r="BK25" s="181"/>
+      <c r="BL25" s="181"/>
+      <c r="BM25" s="184"/>
     </row>
     <row r="26" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A26" s="45"/>
@@ -15991,10 +15991,10 @@
         <f t="shared" si="37"/>
         <v>74</v>
       </c>
-      <c r="BJ26" s="208"/>
-      <c r="BK26" s="209"/>
-      <c r="BL26" s="209"/>
-      <c r="BM26" s="210"/>
+      <c r="BJ26" s="185"/>
+      <c r="BK26" s="186"/>
+      <c r="BL26" s="186"/>
+      <c r="BM26" s="187"/>
     </row>
     <row r="27" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="45"/>
@@ -22498,102 +22498,102 @@
     <mergeCell ref="BJ22:BM22"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A51 P3 B3:O51">
-    <cfRule type="cellIs" dxfId="19" priority="215" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="215" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:O75">
-    <cfRule type="cellIs" dxfId="18" priority="136" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="136" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E9">
-    <cfRule type="cellIs" dxfId="17" priority="202" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="202" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:E21">
-    <cfRule type="cellIs" dxfId="16" priority="193" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="193" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:E33">
-    <cfRule type="cellIs" dxfId="15" priority="191" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="191" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:E45">
-    <cfRule type="cellIs" dxfId="14" priority="189" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="189" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C52:E57">
-    <cfRule type="cellIs" dxfId="13" priority="130" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="130" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C64:E69">
-    <cfRule type="cellIs" dxfId="12" priority="128" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="128" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I9">
-    <cfRule type="cellIs" dxfId="11" priority="198" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="198" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:I21">
-    <cfRule type="cellIs" dxfId="10" priority="188" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="188" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I28:I33">
-    <cfRule type="cellIs" dxfId="9" priority="187" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="187" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I40:I45">
-    <cfRule type="cellIs" dxfId="8" priority="186" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="186" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I52:I57">
-    <cfRule type="cellIs" dxfId="7" priority="127" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="127" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I64:I69">
-    <cfRule type="cellIs" dxfId="6" priority="126" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="126" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:AN75">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF6:AF7">
-    <cfRule type="expression" dxfId="4" priority="209">
+    <cfRule type="expression" dxfId="32" priority="209">
       <formula>AH6=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF12:AF13 AF18:AF19 AF24:AF25 AF30:AF31 AF36:AF37 AF42:AF43 AF48:AF49 AF54:AF55 AF60:AF61 AF66:AF67 AF72:AF73">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>AH12=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP5:BG17">
-    <cfRule type="cellIs" dxfId="2" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="83" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI4:BR17">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ6:BJ13">
-    <cfRule type="expression" dxfId="0" priority="77">
+    <cfRule type="expression" dxfId="28" priority="77">
       <formula>BL6=3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22621,24 +22621,24 @@
   <sheetData>
     <row r="1" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="195" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="187" t="s">
+      <c r="C2" s="197" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="188"/>
-      <c r="E2" s="188"/>
-      <c r="F2" s="188"/>
-      <c r="G2" s="188"/>
-      <c r="H2" s="188"/>
-      <c r="I2" s="188"/>
-      <c r="J2" s="188"/>
-      <c r="K2" s="188"/>
-      <c r="L2" s="188"/>
-      <c r="M2" s="188"/>
-      <c r="N2" s="189"/>
-      <c r="O2" s="185"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
+      <c r="L2" s="198"/>
+      <c r="M2" s="198"/>
+      <c r="N2" s="199"/>
+      <c r="O2" s="195"/>
       <c r="P2" s="5" t="s">
         <v>102</v>
       </c>
@@ -22665,22 +22665,22 @@
       </c>
     </row>
     <row r="3" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="186"/>
-      <c r="C3" s="190" t="s">
+      <c r="B3" s="196"/>
+      <c r="C3" s="200" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="191"/>
-      <c r="E3" s="191"/>
-      <c r="F3" s="191"/>
-      <c r="G3" s="191"/>
-      <c r="H3" s="191"/>
-      <c r="I3" s="191"/>
-      <c r="J3" s="191"/>
-      <c r="K3" s="191"/>
-      <c r="L3" s="191"/>
-      <c r="M3" s="191"/>
-      <c r="N3" s="192"/>
-      <c r="O3" s="186"/>
+      <c r="D3" s="201"/>
+      <c r="E3" s="201"/>
+      <c r="F3" s="201"/>
+      <c r="G3" s="201"/>
+      <c r="H3" s="201"/>
+      <c r="I3" s="201"/>
+      <c r="J3" s="201"/>
+      <c r="K3" s="201"/>
+      <c r="L3" s="201"/>
+      <c r="M3" s="201"/>
+      <c r="N3" s="202"/>
+      <c r="O3" s="196"/>
       <c r="P3" s="1" t="s">
         <v>103</v>
       </c>
@@ -54973,18 +54973,18 @@
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="130"/>
-      <c r="B3" s="193" t="s">
+      <c r="B3" s="192" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="194"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="194"/>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="194"/>
-      <c r="K3" s="195"/>
+      <c r="C3" s="193"/>
+      <c r="D3" s="193"/>
+      <c r="E3" s="193"/>
+      <c r="F3" s="193"/>
+      <c r="G3" s="193"/>
+      <c r="H3" s="193"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="193"/>
+      <c r="K3" s="194"/>
       <c r="L3" s="131"/>
       <c r="M3" s="132"/>
       <c r="N3" s="132"/>
@@ -54992,18 +54992,18 @@
       <c r="P3" s="132"/>
       <c r="Q3" s="132"/>
       <c r="W3" s="130"/>
-      <c r="X3" s="193" t="s">
+      <c r="X3" s="192" t="s">
         <v>73</v>
       </c>
-      <c r="Y3" s="194"/>
-      <c r="Z3" s="194"/>
-      <c r="AA3" s="194"/>
-      <c r="AB3" s="194"/>
-      <c r="AC3" s="194"/>
-      <c r="AD3" s="194"/>
-      <c r="AE3" s="194"/>
-      <c r="AF3" s="194"/>
-      <c r="AG3" s="195"/>
+      <c r="Y3" s="193"/>
+      <c r="Z3" s="193"/>
+      <c r="AA3" s="193"/>
+      <c r="AB3" s="193"/>
+      <c r="AC3" s="193"/>
+      <c r="AD3" s="193"/>
+      <c r="AE3" s="193"/>
+      <c r="AF3" s="193"/>
+      <c r="AG3" s="194"/>
       <c r="AH3" s="131"/>
       <c r="AI3" s="132"/>
       <c r="AJ3" s="132"/>
@@ -55020,19 +55020,19 @@
       <c r="D4" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="196" t="s">
+      <c r="E4" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="196"/>
-      <c r="G4" s="196" t="s">
+      <c r="F4" s="203"/>
+      <c r="G4" s="203" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="196"/>
-      <c r="I4" s="196"/>
-      <c r="J4" s="196" t="s">
+      <c r="H4" s="203"/>
+      <c r="I4" s="203"/>
+      <c r="J4" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="196"/>
+      <c r="K4" s="203"/>
       <c r="L4" s="135"/>
       <c r="M4" s="135"/>
       <c r="N4" s="135"/>
@@ -55047,19 +55047,19 @@
       <c r="Z4" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA4" s="196" t="s">
+      <c r="AA4" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="AB4" s="196"/>
-      <c r="AC4" s="196" t="s">
+      <c r="AB4" s="203"/>
+      <c r="AC4" s="203" t="s">
         <v>18</v>
       </c>
-      <c r="AD4" s="196"/>
-      <c r="AE4" s="196"/>
-      <c r="AF4" s="196" t="s">
+      <c r="AD4" s="203"/>
+      <c r="AE4" s="203"/>
+      <c r="AF4" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="AG4" s="196"/>
+      <c r="AG4" s="203"/>
       <c r="AH4" s="136"/>
       <c r="AI4" s="133"/>
       <c r="AJ4" s="133"/>
@@ -55619,18 +55619,18 @@
         <v>12</v>
       </c>
       <c r="W11" s="130"/>
-      <c r="X11" s="193" t="s">
+      <c r="X11" s="192" t="s">
         <v>74</v>
       </c>
-      <c r="Y11" s="194"/>
-      <c r="Z11" s="194"/>
-      <c r="AA11" s="194"/>
-      <c r="AB11" s="194"/>
-      <c r="AC11" s="194"/>
-      <c r="AD11" s="194"/>
-      <c r="AE11" s="194"/>
-      <c r="AF11" s="194"/>
-      <c r="AG11" s="195"/>
+      <c r="Y11" s="193"/>
+      <c r="Z11" s="193"/>
+      <c r="AA11" s="193"/>
+      <c r="AB11" s="193"/>
+      <c r="AC11" s="193"/>
+      <c r="AD11" s="193"/>
+      <c r="AE11" s="193"/>
+      <c r="AF11" s="193"/>
+      <c r="AG11" s="194"/>
       <c r="AH11" s="131"/>
       <c r="AI11" s="132"/>
       <c r="AJ11" s="132"/>
@@ -55653,11 +55653,15 @@
         <v>Inglaterra</v>
       </c>
       <c r="F12" s="149"/>
-      <c r="G12" s="123"/>
+      <c r="G12" s="123">
+        <v>2</v>
+      </c>
       <c r="H12" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="123"/>
+      <c r="I12" s="123">
+        <v>1</v>
+      </c>
       <c r="J12" s="150"/>
       <c r="K12" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R15,"3º E, H, I, J ou K")</f>
@@ -55669,7 +55673,7 @@
       </c>
       <c r="M12" s="133" t="str">
         <f>IF(OR(G12="",I12=""),"Vencedor 80",IF(G12&lt;&gt;I12,IF(G12&gt;I12,E12,K12),IF(SUM(F12:G12)=SUM(I12:J12),"Vencedor 80",IF(SUM(F12:G12)&gt;SUM(I12:J12),E12,K12))))</f>
-        <v>Vencedor 80</v>
+        <v>Inglaterra</v>
       </c>
       <c r="N12" s="133">
         <v>80</v>
@@ -55700,19 +55704,19 @@
       <c r="Z12" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA12" s="196" t="s">
+      <c r="AA12" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="AB12" s="196"/>
-      <c r="AC12" s="196" t="s">
+      <c r="AB12" s="203"/>
+      <c r="AC12" s="203" t="s">
         <v>18</v>
       </c>
-      <c r="AD12" s="196"/>
-      <c r="AE12" s="196"/>
-      <c r="AF12" s="196" t="s">
+      <c r="AD12" s="203"/>
+      <c r="AE12" s="203"/>
+      <c r="AF12" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="AG12" s="196"/>
+      <c r="AG12" s="203"/>
       <c r="AH12" s="136"/>
       <c r="AI12" s="133"/>
       <c r="AJ12" s="133"/>
@@ -55735,11 +55739,15 @@
         <v>Estados Unidos</v>
       </c>
       <c r="F13" s="149"/>
-      <c r="G13" s="123"/>
+      <c r="G13" s="123">
+        <v>2</v>
+      </c>
       <c r="H13" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="123"/>
+      <c r="I13" s="123">
+        <v>0</v>
+      </c>
       <c r="J13" s="150"/>
       <c r="K13" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R10,"3º B, E, F, I ou J")</f>
@@ -55751,7 +55759,7 @@
       </c>
       <c r="M13" s="133" t="str">
         <f>IF(OR(G13="",I13=""),"Vencedor 81",IF(G13&lt;&gt;I13,IF(G13&gt;I13,E13,K13),IF(SUM(F13:G13)=SUM(I13:J13),"Vencedor 81",IF(SUM(F13:G13)&gt;SUM(I13:J13),E13,K13))))</f>
-        <v>Vencedor 81</v>
+        <v>Estados Unidos</v>
       </c>
       <c r="N13" s="133">
         <v>81</v>
@@ -55827,11 +55835,15 @@
         <v>Bélgica</v>
       </c>
       <c r="F14" s="149"/>
-      <c r="G14" s="123"/>
+      <c r="G14" s="123">
+        <v>3</v>
+      </c>
       <c r="H14" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="123"/>
+      <c r="I14" s="123">
+        <v>2</v>
+      </c>
       <c r="J14" s="150"/>
       <c r="K14" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R12,"3º A, E, H, I ou J")</f>
@@ -55843,7 +55855,7 @@
       </c>
       <c r="M14" s="133" t="str">
         <f>IF(OR(G14="",I14=""),"Vencedor 82",IF(G14&lt;&gt;I14,IF(G14&gt;I14,E14,K14),IF(SUM(F14:G14)=SUM(I14:J14),"Vencedor 82",IF(SUM(F14:G14)&gt;SUM(I14:J14),E14,K14))))</f>
-        <v>Vencedor 82</v>
+        <v>Bélgica</v>
       </c>
       <c r="N14" s="133">
         <v>82</v>
@@ -56087,18 +56099,18 @@
         <v>30</v>
       </c>
       <c r="W17" s="130"/>
-      <c r="X17" s="193" t="s">
+      <c r="X17" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="Y17" s="194"/>
-      <c r="Z17" s="194"/>
-      <c r="AA17" s="194"/>
-      <c r="AB17" s="194"/>
-      <c r="AC17" s="194"/>
-      <c r="AD17" s="194"/>
-      <c r="AE17" s="194"/>
-      <c r="AF17" s="194"/>
-      <c r="AG17" s="195"/>
+      <c r="Y17" s="193"/>
+      <c r="Z17" s="193"/>
+      <c r="AA17" s="193"/>
+      <c r="AB17" s="193"/>
+      <c r="AC17" s="193"/>
+      <c r="AD17" s="193"/>
+      <c r="AE17" s="193"/>
+      <c r="AF17" s="193"/>
+      <c r="AG17" s="194"/>
       <c r="AH17" s="131"/>
       <c r="AI17" s="132"/>
       <c r="AJ17" s="132"/>
@@ -56157,19 +56169,19 @@
       <c r="Z18" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA18" s="196" t="s">
+      <c r="AA18" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="AB18" s="196"/>
-      <c r="AC18" s="196" t="s">
+      <c r="AB18" s="203"/>
+      <c r="AC18" s="203" t="s">
         <v>18</v>
       </c>
-      <c r="AD18" s="196"/>
-      <c r="AE18" s="196"/>
-      <c r="AF18" s="196" t="s">
+      <c r="AD18" s="203"/>
+      <c r="AE18" s="203"/>
+      <c r="AF18" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="AG18" s="196"/>
+      <c r="AG18" s="203"/>
       <c r="AH18" s="136"/>
       <c r="AI18" s="133"/>
       <c r="AJ18" s="133"/>
@@ -56361,18 +56373,18 @@
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" s="130"/>
-      <c r="B23" s="193" t="s">
+      <c r="B23" s="192" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="194"/>
-      <c r="D23" s="194"/>
-      <c r="E23" s="194"/>
-      <c r="F23" s="194"/>
-      <c r="G23" s="194"/>
-      <c r="H23" s="194"/>
-      <c r="I23" s="194"/>
-      <c r="J23" s="194"/>
-      <c r="K23" s="195"/>
+      <c r="C23" s="193"/>
+      <c r="D23" s="193"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="193"/>
+      <c r="H23" s="193"/>
+      <c r="I23" s="193"/>
+      <c r="J23" s="193"/>
+      <c r="K23" s="194"/>
       <c r="L23" s="131"/>
       <c r="M23" s="132"/>
       <c r="N23" s="132"/>
@@ -56387,18 +56399,18 @@
         <v>48</v>
       </c>
       <c r="W23" s="45"/>
-      <c r="X23" s="193" t="s">
+      <c r="X23" s="192" t="s">
         <v>79</v>
       </c>
-      <c r="Y23" s="194"/>
-      <c r="Z23" s="194"/>
-      <c r="AA23" s="194"/>
-      <c r="AB23" s="194"/>
-      <c r="AC23" s="194"/>
-      <c r="AD23" s="194"/>
-      <c r="AE23" s="194"/>
-      <c r="AF23" s="194"/>
-      <c r="AG23" s="195"/>
+      <c r="Y23" s="193"/>
+      <c r="Z23" s="193"/>
+      <c r="AA23" s="193"/>
+      <c r="AB23" s="193"/>
+      <c r="AC23" s="193"/>
+      <c r="AD23" s="193"/>
+      <c r="AE23" s="193"/>
+      <c r="AF23" s="193"/>
+      <c r="AG23" s="194"/>
       <c r="AH23" s="131"/>
       <c r="AI23" s="132"/>
       <c r="AJ23" s="132"/>
@@ -56414,19 +56426,19 @@
       <c r="D24" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="196" t="s">
+      <c r="E24" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="F24" s="196"/>
-      <c r="G24" s="196" t="s">
+      <c r="F24" s="203"/>
+      <c r="G24" s="203" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="196"/>
-      <c r="I24" s="196"/>
-      <c r="J24" s="196" t="s">
+      <c r="H24" s="203"/>
+      <c r="I24" s="203"/>
+      <c r="J24" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="K24" s="196"/>
+      <c r="K24" s="203"/>
       <c r="L24" s="135"/>
       <c r="M24" s="135"/>
       <c r="N24" s="135"/>
@@ -56448,19 +56460,19 @@
       <c r="Z24" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="AA24" s="196" t="s">
+      <c r="AA24" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="AB24" s="196"/>
-      <c r="AC24" s="196" t="s">
+      <c r="AB24" s="203"/>
+      <c r="AC24" s="203" t="s">
         <v>18</v>
       </c>
-      <c r="AD24" s="196"/>
-      <c r="AE24" s="196"/>
-      <c r="AF24" s="196" t="s">
+      <c r="AD24" s="203"/>
+      <c r="AE24" s="203"/>
+      <c r="AF24" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="AG24" s="196"/>
+      <c r="AG24" s="203"/>
       <c r="AH24" s="136"/>
       <c r="AI24" s="133"/>
       <c r="AJ24" s="133"/>
@@ -56656,7 +56668,7 @@
       <c r="J28" s="150"/>
       <c r="K28" s="151" t="str">
         <f>M12</f>
-        <v>Vencedor 80</v>
+        <v>Inglaterra</v>
       </c>
       <c r="L28" s="136" t="str">
         <f t="shared" si="18"/>
@@ -56676,12 +56688,12 @@
         <f t="shared" ref="U28:U30" si="21">U27+5</f>
         <v>65</v>
       </c>
-      <c r="AD28" s="193" t="s">
+      <c r="AD28" s="192" t="s">
         <v>211</v>
       </c>
-      <c r="AE28" s="194"/>
-      <c r="AF28" s="194"/>
-      <c r="AG28" s="195"/>
+      <c r="AE28" s="193"/>
+      <c r="AF28" s="193"/>
+      <c r="AG28" s="194"/>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B29" s="152">
@@ -56726,10 +56738,10 @@
         <f t="shared" ref="U29:U31" si="22">U28+1</f>
         <v>66</v>
       </c>
-      <c r="AD29" s="205"/>
-      <c r="AE29" s="204"/>
-      <c r="AF29" s="204"/>
-      <c r="AG29" s="206"/>
+      <c r="AD29" s="182"/>
+      <c r="AE29" s="181"/>
+      <c r="AF29" s="181"/>
+      <c r="AG29" s="183"/>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B30" s="152">
@@ -56743,7 +56755,7 @@
       </c>
       <c r="E30" s="106" t="str">
         <f>M13</f>
-        <v>Vencedor 81</v>
+        <v>Estados Unidos</v>
       </c>
       <c r="F30" s="149"/>
       <c r="G30" s="123"/>
@@ -56754,7 +56766,7 @@
       <c r="J30" s="150"/>
       <c r="K30" s="151" t="str">
         <f>M14</f>
-        <v>Vencedor 82</v>
+        <v>Bélgica</v>
       </c>
       <c r="L30" s="136" t="str">
         <f t="shared" si="18"/>
@@ -56774,10 +56786,10 @@
         <f t="shared" si="21"/>
         <v>71</v>
       </c>
-      <c r="AD30" s="205"/>
-      <c r="AE30" s="204"/>
-      <c r="AF30" s="204"/>
-      <c r="AG30" s="207"/>
+      <c r="AD30" s="182"/>
+      <c r="AE30" s="181"/>
+      <c r="AF30" s="181"/>
+      <c r="AG30" s="184"/>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B31" s="152">
@@ -56822,10 +56834,10 @@
         <f t="shared" si="22"/>
         <v>72</v>
       </c>
-      <c r="AD31" s="205"/>
-      <c r="AE31" s="204"/>
-      <c r="AF31" s="204"/>
-      <c r="AG31" s="207"/>
+      <c r="AD31" s="182"/>
+      <c r="AE31" s="181"/>
+      <c r="AF31" s="181"/>
+      <c r="AG31" s="184"/>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B32" s="152">
@@ -56863,10 +56875,10 @@
       <c r="N32" s="133">
         <v>96</v>
       </c>
-      <c r="AD32" s="208"/>
-      <c r="AE32" s="209"/>
-      <c r="AF32" s="209"/>
-      <c r="AG32" s="210"/>
+      <c r="AD32" s="185"/>
+      <c r="AE32" s="186"/>
+      <c r="AF32" s="186"/>
+      <c r="AG32" s="187"/>
     </row>
     <row r="33" spans="2:33" x14ac:dyDescent="0.25">
       <c r="C33" s="137"/>
@@ -56876,60 +56888,60 @@
       <c r="X34" s="158" t="s">
         <v>206</v>
       </c>
-      <c r="Y34" s="202" t="s">
+      <c r="Y34" s="209" t="s">
         <v>81</v>
       </c>
-      <c r="Z34" s="202"/>
-      <c r="AA34" s="202"/>
-      <c r="AB34" s="197" t="str">
+      <c r="Z34" s="209"/>
+      <c r="AA34" s="209"/>
+      <c r="AB34" s="204" t="str">
         <f>IF(AI25="1º Lugar","",AI25)</f>
         <v/>
       </c>
-      <c r="AC34" s="197"/>
-      <c r="AD34" s="197"/>
-      <c r="AE34" s="197"/>
-      <c r="AF34" s="197"/>
-      <c r="AG34" s="197"/>
+      <c r="AC34" s="204"/>
+      <c r="AD34" s="204"/>
+      <c r="AE34" s="204"/>
+      <c r="AF34" s="204"/>
+      <c r="AG34" s="204"/>
     </row>
     <row r="35" spans="2:33" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B35" s="140"/>
       <c r="X35" s="159" t="s">
         <v>207</v>
       </c>
-      <c r="Y35" s="200" t="s">
+      <c r="Y35" s="207" t="s">
         <v>82</v>
       </c>
-      <c r="Z35" s="200"/>
-      <c r="AA35" s="200"/>
-      <c r="AB35" s="198" t="str">
+      <c r="Z35" s="207"/>
+      <c r="AA35" s="207"/>
+      <c r="AB35" s="205" t="str">
         <f>IF(M57="2º Lugar","",M57)</f>
         <v/>
       </c>
-      <c r="AC35" s="198"/>
-      <c r="AD35" s="198"/>
-      <c r="AE35" s="198"/>
-      <c r="AF35" s="198"/>
-      <c r="AG35" s="198"/>
+      <c r="AC35" s="205"/>
+      <c r="AD35" s="205"/>
+      <c r="AE35" s="205"/>
+      <c r="AF35" s="205"/>
+      <c r="AG35" s="205"/>
     </row>
     <row r="36" spans="2:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="140"/>
       <c r="X36" s="160" t="s">
         <v>208</v>
       </c>
-      <c r="Y36" s="201" t="s">
+      <c r="Y36" s="208" t="s">
         <v>83</v>
       </c>
-      <c r="Z36" s="201"/>
-      <c r="AA36" s="201"/>
-      <c r="AB36" s="199" t="str">
+      <c r="Z36" s="208"/>
+      <c r="AA36" s="208"/>
+      <c r="AB36" s="206" t="str">
         <f>IF(AI19="3º Lugar","",AI19)</f>
         <v/>
       </c>
-      <c r="AC36" s="199"/>
-      <c r="AD36" s="199"/>
-      <c r="AE36" s="199"/>
-      <c r="AF36" s="199"/>
-      <c r="AG36" s="199"/>
+      <c r="AC36" s="206"/>
+      <c r="AD36" s="206"/>
+      <c r="AE36" s="206"/>
+      <c r="AF36" s="206"/>
+      <c r="AG36" s="206"/>
     </row>
     <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="137"/>
@@ -57120,142 +57132,142 @@
     <mergeCell ref="AC4:AE4"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A2 B2:K2 X9:AG10 X15:AG16 X20:AG21 B21:K22 AB34:AB36 A57:K58 H59:K61 B62:K71 B83:K1048576">
-    <cfRule type="cellIs" dxfId="47" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="76" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:B12 C4:K12">
-    <cfRule type="cellIs" dxfId="46" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="42" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:K20">
-    <cfRule type="cellIs" dxfId="45" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="31" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:B36 C24:K33">
-    <cfRule type="cellIs" dxfId="44" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="20" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F20">
-    <cfRule type="expression" dxfId="43" priority="30">
+    <cfRule type="expression" dxfId="23" priority="30">
       <formula>L5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:F32">
-    <cfRule type="expression" dxfId="42" priority="19">
+    <cfRule type="expression" dxfId="22" priority="19">
       <formula>L25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:J20">
-    <cfRule type="expression" dxfId="41" priority="29">
+    <cfRule type="expression" dxfId="21" priority="29">
       <formula>L5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J25:J32">
-    <cfRule type="expression" dxfId="40" priority="18">
+    <cfRule type="expression" dxfId="20" priority="18">
       <formula>L25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K20">
-    <cfRule type="expression" dxfId="39" priority="21">
+    <cfRule type="expression" dxfId="19" priority="21">
       <formula>Q5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K32">
-    <cfRule type="expression" dxfId="38" priority="17">
+    <cfRule type="expression" dxfId="18" priority="17">
       <formula>Q25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W3:W24 A21:A34 I34:K34 Y34:AB34 Y34:Y36 A62:A1048576">
-    <cfRule type="cellIs" dxfId="37" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="77" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X3:X8 Y4:AG8">
-    <cfRule type="cellIs" dxfId="36" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="16" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X11:X14 Y12:AG14">
-    <cfRule type="cellIs" dxfId="35" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X17:X19 Y18:AG19">
-    <cfRule type="cellIs" dxfId="34" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X23:X25 Y24:AG25">
-    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y34:AA36">
-    <cfRule type="expression" dxfId="32" priority="65">
+    <cfRule type="expression" dxfId="12" priority="65">
       <formula>AB34&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB5:AB8">
-    <cfRule type="expression" dxfId="31" priority="15">
+    <cfRule type="expression" dxfId="11" priority="15">
       <formula>AH5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB13:AB14">
-    <cfRule type="expression" dxfId="30" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>AH13="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB19">
-    <cfRule type="expression" dxfId="29" priority="7">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>AH19="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB25">
-    <cfRule type="expression" dxfId="28" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>AH25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF5:AF8">
-    <cfRule type="expression" dxfId="27" priority="14">
+    <cfRule type="expression" dxfId="7" priority="14">
       <formula>AH5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF13:AF14">
-    <cfRule type="expression" dxfId="26" priority="10">
+    <cfRule type="expression" dxfId="6" priority="10">
       <formula>AH13="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF19">
-    <cfRule type="expression" dxfId="25" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>AH19="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF25">
-    <cfRule type="expression" dxfId="24" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>AH25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG5:AG8">
-    <cfRule type="expression" dxfId="23" priority="13">
+    <cfRule type="expression" dxfId="3" priority="13">
       <formula>AM5="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG13:AG14">
-    <cfRule type="expression" dxfId="22" priority="9">
+    <cfRule type="expression" dxfId="2" priority="9">
       <formula>AM13="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG19">
-    <cfRule type="expression" dxfId="21" priority="5">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>AM19="emp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG25">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AM25="emp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57322,64 +57334,64 @@
       <c r="C4" s="169" t="s">
         <v>161</v>
       </c>
-      <c r="D4" s="203"/>
-      <c r="F4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="J4" s="203"/>
-      <c r="L4" s="203"/>
-      <c r="N4" s="203"/>
-      <c r="P4" s="203"/>
-      <c r="R4" s="203"/>
-      <c r="T4" s="203"/>
-      <c r="V4" s="203"/>
-      <c r="X4" s="203"/>
-      <c r="Z4" s="203"/>
-      <c r="AB4" s="203"/>
-      <c r="AD4" s="203"/>
-      <c r="AF4" s="203"/>
-      <c r="AH4" s="203"/>
+      <c r="D4" s="210"/>
+      <c r="F4" s="210"/>
+      <c r="H4" s="210"/>
+      <c r="J4" s="210"/>
+      <c r="L4" s="210"/>
+      <c r="N4" s="210"/>
+      <c r="P4" s="210"/>
+      <c r="R4" s="210"/>
+      <c r="T4" s="210"/>
+      <c r="V4" s="210"/>
+      <c r="X4" s="210"/>
+      <c r="Z4" s="210"/>
+      <c r="AB4" s="210"/>
+      <c r="AD4" s="210"/>
+      <c r="AF4" s="210"/>
+      <c r="AH4" s="210"/>
     </row>
     <row r="5" spans="2:34" x14ac:dyDescent="0.3">
       <c r="C5" s="169" t="s">
         <v>163</v>
       </c>
-      <c r="D5" s="203"/>
-      <c r="F5" s="203"/>
-      <c r="H5" s="203"/>
-      <c r="J5" s="203"/>
-      <c r="L5" s="203"/>
-      <c r="N5" s="203"/>
-      <c r="P5" s="203"/>
-      <c r="R5" s="203"/>
-      <c r="T5" s="203"/>
-      <c r="V5" s="203"/>
-      <c r="X5" s="203"/>
-      <c r="Z5" s="203"/>
-      <c r="AB5" s="203"/>
-      <c r="AD5" s="203"/>
-      <c r="AF5" s="203"/>
-      <c r="AH5" s="203"/>
+      <c r="D5" s="210"/>
+      <c r="F5" s="210"/>
+      <c r="H5" s="210"/>
+      <c r="J5" s="210"/>
+      <c r="L5" s="210"/>
+      <c r="N5" s="210"/>
+      <c r="P5" s="210"/>
+      <c r="R5" s="210"/>
+      <c r="T5" s="210"/>
+      <c r="V5" s="210"/>
+      <c r="X5" s="210"/>
+      <c r="Z5" s="210"/>
+      <c r="AB5" s="210"/>
+      <c r="AD5" s="210"/>
+      <c r="AF5" s="210"/>
+      <c r="AH5" s="210"/>
     </row>
     <row r="6" spans="2:34" x14ac:dyDescent="0.3">
       <c r="C6" s="169" t="s">
         <v>162</v>
       </c>
-      <c r="D6" s="203"/>
-      <c r="F6" s="203"/>
-      <c r="H6" s="203"/>
-      <c r="J6" s="203"/>
-      <c r="L6" s="203"/>
-      <c r="N6" s="203"/>
-      <c r="P6" s="203"/>
-      <c r="R6" s="203"/>
-      <c r="T6" s="203"/>
-      <c r="V6" s="203"/>
-      <c r="X6" s="203"/>
-      <c r="Z6" s="203"/>
-      <c r="AB6" s="203"/>
-      <c r="AD6" s="203"/>
-      <c r="AF6" s="203"/>
-      <c r="AH6" s="203"/>
+      <c r="D6" s="210"/>
+      <c r="F6" s="210"/>
+      <c r="H6" s="210"/>
+      <c r="J6" s="210"/>
+      <c r="L6" s="210"/>
+      <c r="N6" s="210"/>
+      <c r="P6" s="210"/>
+      <c r="R6" s="210"/>
+      <c r="T6" s="210"/>
+      <c r="V6" s="210"/>
+      <c r="X6" s="210"/>
+      <c r="Z6" s="210"/>
+      <c r="AB6" s="210"/>
+      <c r="AD6" s="210"/>
+      <c r="AF6" s="210"/>
+      <c r="AH6" s="210"/>
     </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.3">
       <c r="C7" s="169" t="s">

--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E09303-BA36-4D6D-A084-05BD5255E3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED78202-39B0-4377-A87D-8EDFD748F56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BcI4NY5Ohir363+nRCln2YCzlnOeJyINjZ1aV0hb2IpPHmsHZPUFroFzrod6xokqyCn7GUW2N1Z+U/w2mbyNbQ==" workbookSaltValue="VvXyFesAZC8L8IOzNm6PtA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
@@ -55119,7 +55119,7 @@
       </c>
       <c r="AA5" s="106" t="str">
         <f>M25</f>
-        <v>Vencedor 89</v>
+        <v>França</v>
       </c>
       <c r="AB5" s="149"/>
       <c r="AC5" s="123"/>
@@ -55130,7 +55130,7 @@
       <c r="AF5" s="150"/>
       <c r="AG5" s="151" t="str">
         <f>M26</f>
-        <v>Vencedor 90</v>
+        <v>Marrocos</v>
       </c>
       <c r="AH5" s="136" t="str">
         <f>IF(OR(AC5="",AE5=""),"",IF(AC5=AE5,"emp",""))</f>
@@ -55287,7 +55287,7 @@
       </c>
       <c r="AA7" s="106" t="str">
         <f>M27</f>
-        <v>Vencedor 91</v>
+        <v>Noruega</v>
       </c>
       <c r="AB7" s="149"/>
       <c r="AC7" s="123"/>
@@ -55298,7 +55298,7 @@
       <c r="AF7" s="150"/>
       <c r="AG7" s="151" t="str">
         <f>M28</f>
-        <v>Vencedor 92</v>
+        <v>Inglaterra</v>
       </c>
       <c r="AH7" s="136" t="str">
         <f t="shared" si="1"/>
@@ -55883,7 +55883,7 @@
         <v>76</v>
       </c>
       <c r="Y14" s="148">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="Z14" s="36" t="s">
         <v>46</v>
@@ -55931,11 +55931,15 @@
         <v>Portugal</v>
       </c>
       <c r="F15" s="149"/>
-      <c r="G15" s="123"/>
+      <c r="G15" s="123">
+        <v>2</v>
+      </c>
       <c r="H15" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="123"/>
+      <c r="I15" s="123">
+        <v>1</v>
+      </c>
       <c r="J15" s="150"/>
       <c r="K15" s="151" t="str">
         <f>IF('Fase de Grupos'!AH73=3,'Fase de Grupos'!AF73,"2º do Grupo L")</f>
@@ -55947,7 +55951,7 @@
       </c>
       <c r="M15" s="133" t="str">
         <f>IF(OR(G15="",I15=""),"Vencedor 83",IF(G15&lt;&gt;I15,IF(G15&gt;I15,E15,K15),IF(SUM(F15:G15)=SUM(I15:J15),"Vencedor 83",IF(SUM(F15:G15)&gt;SUM(I15:J15),E15,K15))))</f>
-        <v>Vencedor 83</v>
+        <v>Portugal</v>
       </c>
       <c r="N15" s="133">
         <v>83</v>
@@ -56006,11 +56010,15 @@
         <v>Espanha</v>
       </c>
       <c r="F16" s="149"/>
-      <c r="G16" s="123"/>
+      <c r="G16" s="123">
+        <v>3</v>
+      </c>
       <c r="H16" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="123"/>
+      <c r="I16" s="123">
+        <v>0</v>
+      </c>
       <c r="J16" s="150"/>
       <c r="K16" s="151" t="str">
         <f>IF('Fase de Grupos'!AH61=3,'Fase de Grupos'!AF61,"2º do Grupo J")</f>
@@ -56022,7 +56030,7 @@
       </c>
       <c r="M16" s="133" t="str">
         <f>IF(OR(G16="",I16=""),"Vencedor 84",IF(G16&lt;&gt;I16,IF(G16&gt;I16,E16,K16),IF(SUM(F16:G16)=SUM(I16:J16),"Vencedor 84",IF(SUM(F16:G16)&gt;SUM(I16:J16),E16,K16))))</f>
-        <v>Vencedor 84</v>
+        <v>Espanha</v>
       </c>
       <c r="N16" s="133">
         <v>84</v>
@@ -56070,11 +56078,15 @@
         <v>Suiça</v>
       </c>
       <c r="F17" s="149"/>
-      <c r="G17" s="123"/>
+      <c r="G17" s="123">
+        <v>2</v>
+      </c>
       <c r="H17" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I17" s="123"/>
+      <c r="I17" s="123">
+        <v>0</v>
+      </c>
       <c r="J17" s="150"/>
       <c r="K17" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R9,"3º E, F, G, I ou J")</f>
@@ -56086,7 +56098,7 @@
       </c>
       <c r="M17" s="133" t="str">
         <f>IF(OR(G17="",I17=""),"Vencedor 85",IF(G17&lt;&gt;I17,IF(G17&gt;I17,E17,K17),IF(SUM(F17:G17)=SUM(I17:J17),"Vencedor 85",IF(SUM(F17:G17)&gt;SUM(I17:J17),E17,K17))))</f>
-        <v>Vencedor 85</v>
+        <v>Suiça</v>
       </c>
       <c r="N17" s="133">
         <v>85</v>
@@ -56133,11 +56145,15 @@
         <v>Argentina</v>
       </c>
       <c r="F18" s="149"/>
-      <c r="G18" s="123"/>
+      <c r="G18" s="123">
+        <v>3</v>
+      </c>
       <c r="H18" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="123"/>
+      <c r="I18" s="123">
+        <v>2</v>
+      </c>
       <c r="J18" s="150"/>
       <c r="K18" s="151" t="str">
         <f>IF('Fase de Grupos'!AH49=3,'Fase de Grupos'!AF49,"2º do Grupo H")</f>
@@ -56149,7 +56165,7 @@
       </c>
       <c r="M18" s="133" t="str">
         <f>IF(OR(G18="",I18=""),"Vencedor 86",IF(G18&lt;&gt;I18,IF(G18&gt;I18,E18,K18),IF(SUM(F18:G18)=SUM(I18:J18),"Vencedor 86",IF(SUM(F18:G18)&gt;SUM(I18:J18),E18,K18))))</f>
-        <v>Vencedor 86</v>
+        <v>Argentina</v>
       </c>
       <c r="N18" s="133">
         <v>86</v>
@@ -56204,11 +56220,15 @@
         <v>Colômbia</v>
       </c>
       <c r="F19" s="149"/>
-      <c r="G19" s="123"/>
+      <c r="G19" s="123">
+        <v>1</v>
+      </c>
       <c r="H19" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="123"/>
+      <c r="I19" s="123">
+        <v>1</v>
+      </c>
       <c r="J19" s="150"/>
       <c r="K19" s="151" t="str">
         <f>IF('Fase de Grupos'!$BL$18=36,R14,"3º D, E, I, J ou L")</f>
@@ -56216,7 +56236,7 @@
       </c>
       <c r="L19" s="136" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>emp</v>
       </c>
       <c r="M19" s="133" t="str">
         <f>IF(OR(G19="",I19=""),"Vencedor 87",IF(G19&lt;&gt;I19,IF(G19&gt;I19,E19,K19),IF(SUM(F19:G19)=SUM(I19:J19),"Vencedor 87",IF(SUM(F19:G19)&gt;SUM(I19:J19),E19,K19))))</f>
@@ -56284,24 +56304,32 @@
         <f>IF('Fase de Grupos'!AH25=3,'Fase de Grupos'!AF25,"2º do Grupo D")</f>
         <v>Austrália</v>
       </c>
-      <c r="F20" s="149"/>
-      <c r="G20" s="123"/>
+      <c r="F20" s="149">
+        <v>2</v>
+      </c>
+      <c r="G20" s="123">
+        <v>1</v>
+      </c>
       <c r="H20" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I20" s="123"/>
-      <c r="J20" s="150"/>
+      <c r="I20" s="123">
+        <v>1</v>
+      </c>
+      <c r="J20" s="150">
+        <v>4</v>
+      </c>
       <c r="K20" s="151" t="str">
         <f>IF('Fase de Grupos'!AH43=3,'Fase de Grupos'!AF43,"2º do Grupo G")</f>
         <v>Egito</v>
       </c>
       <c r="L20" s="136" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>emp</v>
       </c>
       <c r="M20" s="133" t="str">
         <f>IF(OR(G20="",I20=""),"Vencedor 88",IF(G20&lt;&gt;I20,IF(G20&gt;I20,E20,K20),IF(SUM(F20:G20)=SUM(I20:J20),"Vencedor 88",IF(SUM(F20:G20)&gt;SUM(I20:J20),E20,K20))))</f>
-        <v>Vencedor 88</v>
+        <v>Egito</v>
       </c>
       <c r="N20" s="133">
         <v>88</v>
@@ -56494,11 +56522,15 @@
         <v>Paraguai</v>
       </c>
       <c r="F25" s="149"/>
-      <c r="G25" s="123"/>
+      <c r="G25" s="123">
+        <v>0</v>
+      </c>
       <c r="H25" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I25" s="123"/>
+      <c r="I25" s="123">
+        <v>1</v>
+      </c>
       <c r="J25" s="150"/>
       <c r="K25" s="151" t="str">
         <f>M9</f>
@@ -56510,7 +56542,7 @@
       </c>
       <c r="M25" s="133" t="str">
         <f>IF(OR(G25="",I25=""),"Vencedor 89",IF(G25&lt;&gt;I25,IF(G25&gt;I25,E25,K25),IF(SUM(F25:G25)=SUM(I25:J25),"Vencedor 89",IF(SUM(F25:G25)&gt;SUM(I25:J25),E25,K25))))</f>
-        <v>Vencedor 89</v>
+        <v>França</v>
       </c>
       <c r="N25" s="133">
         <v>89</v>
@@ -56572,11 +56604,15 @@
         <v>Canadá</v>
       </c>
       <c r="F26" s="149"/>
-      <c r="G26" s="123"/>
+      <c r="G26" s="123">
+        <v>0</v>
+      </c>
       <c r="H26" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I26" s="123"/>
+      <c r="I26" s="123">
+        <v>3</v>
+      </c>
       <c r="J26" s="150"/>
       <c r="K26" s="151" t="str">
         <f>M7</f>
@@ -56588,7 +56624,7 @@
       </c>
       <c r="M26" s="133" t="str">
         <f>IF(OR(G26="",I26=""),"Vencedor 90",IF(G26&lt;&gt;I26,IF(G26&gt;I26,E26,K26),IF(SUM(F26:G26)=SUM(I26:J26),"Vencedor 90",IF(SUM(F26:G26)&gt;SUM(I26:J26),E26,K26))))</f>
-        <v>Vencedor 90</v>
+        <v>Marrocos</v>
       </c>
       <c r="N26" s="133">
         <v>90</v>
@@ -56616,11 +56652,15 @@
         <v>Brasil</v>
       </c>
       <c r="F27" s="149"/>
-      <c r="G27" s="123"/>
+      <c r="G27" s="123">
+        <v>1</v>
+      </c>
       <c r="H27" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="123"/>
+      <c r="I27" s="123">
+        <v>2</v>
+      </c>
       <c r="J27" s="150"/>
       <c r="K27" s="151" t="str">
         <f>M10</f>
@@ -56632,7 +56672,7 @@
       </c>
       <c r="M27" s="133" t="str">
         <f>IF(OR(G27="",I27=""),"Vencedor 91",IF(G27&lt;&gt;I27,IF(G27&gt;I27,E27,K27),IF(SUM(F27:G27)=SUM(I27:J27),"Vencedor 91",IF(SUM(F27:G27)&gt;SUM(I27:J27),E27,K27))))</f>
-        <v>Vencedor 91</v>
+        <v>Noruega</v>
       </c>
       <c r="N27" s="133">
         <v>91</v>
@@ -56660,11 +56700,15 @@
         <v>México</v>
       </c>
       <c r="F28" s="149"/>
-      <c r="G28" s="123"/>
+      <c r="G28" s="123">
+        <v>2</v>
+      </c>
       <c r="H28" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="123"/>
+      <c r="I28" s="123">
+        <v>3</v>
+      </c>
       <c r="J28" s="150"/>
       <c r="K28" s="151" t="str">
         <f>M12</f>
@@ -56676,7 +56720,7 @@
       </c>
       <c r="M28" s="133" t="str">
         <f>IF(OR(G28="",I28=""),"Vencedor 92",IF(G28&lt;&gt;I28,IF(G28&gt;I28,E28,K28),IF(SUM(F28:G28)=SUM(I28:J28),"Vencedor 92",IF(SUM(F28:G28)&gt;SUM(I28:J28),E28,K28))))</f>
-        <v>Vencedor 92</v>
+        <v>Inglaterra</v>
       </c>
       <c r="N28" s="133">
         <v>92</v>
@@ -56707,7 +56751,7 @@
       </c>
       <c r="E29" s="106" t="str">
         <f>M15</f>
-        <v>Vencedor 83</v>
+        <v>Portugal</v>
       </c>
       <c r="F29" s="149"/>
       <c r="G29" s="123"/>
@@ -56718,7 +56762,7 @@
       <c r="J29" s="150"/>
       <c r="K29" s="151" t="str">
         <f>M16</f>
-        <v>Vencedor 84</v>
+        <v>Espanha</v>
       </c>
       <c r="L29" s="136" t="str">
         <f t="shared" si="18"/>
@@ -56803,7 +56847,7 @@
       </c>
       <c r="E31" s="106" t="str">
         <f>M18</f>
-        <v>Vencedor 86</v>
+        <v>Argentina</v>
       </c>
       <c r="F31" s="149"/>
       <c r="G31" s="123"/>
@@ -56814,7 +56858,7 @@
       <c r="J31" s="150"/>
       <c r="K31" s="151" t="str">
         <f>M20</f>
-        <v>Vencedor 88</v>
+        <v>Egito</v>
       </c>
       <c r="L31" s="136" t="str">
         <f t="shared" si="18"/>
@@ -56851,7 +56895,7 @@
       </c>
       <c r="E32" s="106" t="str">
         <f>M17</f>
-        <v>Vencedor 85</v>
+        <v>Suiça</v>
       </c>
       <c r="F32" s="149"/>
       <c r="G32" s="123"/>
@@ -57097,23 +57141,8 @@
       <c r="K82" s="45"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8JRv5B/B5jMSXJQTg3Gidv52YDGKsjKvo30SeOBaK6JSNYAMZQ/wPbZnASuXj0gcQnaFpGbQs8ZzG0RfUFK9kg==" saltValue="BbqaqtGKXaW/tQWh+QEg4w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vyOy7e+Kipl/iIim/AhmV04T3MRdO7XqZOrn9PPXS3pWOghvTWOXD8HUj7i1Pq8tpKgw5m5Lutctpe8ebuImew==" saltValue="GsBJjoEg17jBuxUGR0mlBg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="31">
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AB34:AG34"/>
-    <mergeCell ref="AB35:AG35"/>
-    <mergeCell ref="AB36:AG36"/>
-    <mergeCell ref="B23:K23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="Y35:AA35"/>
-    <mergeCell ref="Y36:AA36"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AC24:AE24"/>
-    <mergeCell ref="AF24:AG24"/>
-    <mergeCell ref="Y34:AA34"/>
-    <mergeCell ref="AD28:AG28"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:I4"/>
@@ -57130,6 +57159,21 @@
     <mergeCell ref="AF18:AG18"/>
     <mergeCell ref="AA4:AB4"/>
     <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AB34:AG34"/>
+    <mergeCell ref="AB35:AG35"/>
+    <mergeCell ref="AB36:AG36"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="Y35:AA35"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="AF24:AG24"/>
+    <mergeCell ref="Y34:AA34"/>
+    <mergeCell ref="AD28:AG28"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A2 B2:K2 X9:AG10 X15:AG16 X20:AG21 B21:K22 AB34:AB36 A57:K58 H59:K61 B62:K71 B83:K1048576">
     <cfRule type="cellIs" dxfId="27" priority="76" operator="equal">
@@ -57892,12 +57936,6 @@
     <sortCondition ref="C59:C64"/>
   </sortState>
   <mergeCells count="16">
-    <mergeCell ref="N4:N6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="J4:J6"/>
-    <mergeCell ref="L4:L6"/>
     <mergeCell ref="AB4:AB6"/>
     <mergeCell ref="AD4:AD6"/>
     <mergeCell ref="AF4:AF6"/>
@@ -57908,6 +57946,12 @@
     <mergeCell ref="V4:V6"/>
     <mergeCell ref="X4:X6"/>
     <mergeCell ref="Z4:Z6"/>
+    <mergeCell ref="N4:N6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="L4:L6"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -58143,20 +58187,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -58179,14 +58223,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
@@ -58201,4 +58237,12 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED78202-39B0-4377-A87D-8EDFD748F56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C004B20-35B6-49E6-8924-68E165489957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BcI4NY5Ohir363+nRCln2YCzlnOeJyINjZ1aV0hb2IpPHmsHZPUFroFzrod6xokqyCn7GUW2N1Z+U/w2mbyNbQ==" workbookSaltValue="VvXyFesAZC8L8IOzNm6PtA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
@@ -55205,7 +55205,7 @@
       </c>
       <c r="AA6" s="106" t="str">
         <f>M29</f>
-        <v>Vencedor 93</v>
+        <v>Espanha</v>
       </c>
       <c r="AB6" s="149"/>
       <c r="AC6" s="123"/>
@@ -55216,7 +55216,7 @@
       <c r="AF6" s="150"/>
       <c r="AG6" s="151" t="str">
         <f>M30</f>
-        <v>Vencedor 94</v>
+        <v>Bélgica</v>
       </c>
       <c r="AH6" s="136" t="str">
         <f t="shared" ref="AH6:AH8" si="1">IF(OR(AC6="",AE6=""),"",IF(AC6=AE6,"emp",""))</f>
@@ -56227,7 +56227,7 @@
         <v>22</v>
       </c>
       <c r="I19" s="123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="150"/>
       <c r="K19" s="151" t="str">
@@ -56236,11 +56236,11 @@
       </c>
       <c r="L19" s="136" t="str">
         <f t="shared" si="4"/>
-        <v>emp</v>
+        <v/>
       </c>
       <c r="M19" s="133" t="str">
         <f>IF(OR(G19="",I19=""),"Vencedor 87",IF(G19&lt;&gt;I19,IF(G19&gt;I19,E19,K19),IF(SUM(F19:G19)=SUM(I19:J19),"Vencedor 87",IF(SUM(F19:G19)&gt;SUM(I19:J19),E19,K19))))</f>
-        <v>Vencedor 87</v>
+        <v>Colômbia</v>
       </c>
       <c r="N19" s="133">
         <v>87</v>
@@ -56754,11 +56754,15 @@
         <v>Portugal</v>
       </c>
       <c r="F29" s="149"/>
-      <c r="G29" s="123"/>
+      <c r="G29" s="123">
+        <v>0</v>
+      </c>
       <c r="H29" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I29" s="123"/>
+      <c r="I29" s="123">
+        <v>1</v>
+      </c>
       <c r="J29" s="150"/>
       <c r="K29" s="151" t="str">
         <f>M16</f>
@@ -56770,7 +56774,7 @@
       </c>
       <c r="M29" s="133" t="str">
         <f>IF(OR(G29="",I29=""),"Vencedor 93",IF(G29&lt;&gt;I29,IF(G29&gt;I29,E29,K29),IF(SUM(F29:G29)=SUM(I29:J29),"Vencedor 93",IF(SUM(F29:G29)&gt;SUM(I29:J29),E29,K29))))</f>
-        <v>Vencedor 93</v>
+        <v>Espanha</v>
       </c>
       <c r="N29" s="133">
         <v>93</v>
@@ -56802,11 +56806,15 @@
         <v>Estados Unidos</v>
       </c>
       <c r="F30" s="149"/>
-      <c r="G30" s="123"/>
+      <c r="G30" s="123">
+        <v>1</v>
+      </c>
       <c r="H30" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I30" s="123"/>
+      <c r="I30" s="123">
+        <v>4</v>
+      </c>
       <c r="J30" s="150"/>
       <c r="K30" s="151" t="str">
         <f>M14</f>
@@ -56818,7 +56826,7 @@
       </c>
       <c r="M30" s="133" t="str">
         <f>IF(OR(G30="",I30=""),"Vencedor 94",IF(G30&lt;&gt;I30,IF(G30&gt;I30,E30,K30),IF(SUM(F30:G30)=SUM(I30:J30),"Vencedor 94",IF(SUM(F30:G30)&gt;SUM(I30:J30),E30,K30))))</f>
-        <v>Vencedor 94</v>
+        <v>Bélgica</v>
       </c>
       <c r="N30" s="133">
         <v>94</v>
@@ -56906,7 +56914,7 @@
       <c r="J32" s="150"/>
       <c r="K32" s="151" t="str">
         <f>M19</f>
-        <v>Vencedor 87</v>
+        <v>Colômbia</v>
       </c>
       <c r="L32" s="136" t="str">
         <f t="shared" si="18"/>
@@ -57143,6 +57151,21 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="vyOy7e+Kipl/iIim/AhmV04T3MRdO7XqZOrn9PPXS3pWOghvTWOXD8HUj7i1Pq8tpKgw5m5Lutctpe8ebuImew==" saltValue="GsBJjoEg17jBuxUGR0mlBg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="31">
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AB34:AG34"/>
+    <mergeCell ref="AB35:AG35"/>
+    <mergeCell ref="AB36:AG36"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="Y35:AA35"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="AF24:AG24"/>
+    <mergeCell ref="Y34:AA34"/>
+    <mergeCell ref="AD28:AG28"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:I4"/>
@@ -57159,21 +57182,6 @@
     <mergeCell ref="AF18:AG18"/>
     <mergeCell ref="AA4:AB4"/>
     <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AB34:AG34"/>
-    <mergeCell ref="AB35:AG35"/>
-    <mergeCell ref="AB36:AG36"/>
-    <mergeCell ref="B23:K23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="Y35:AA35"/>
-    <mergeCell ref="Y36:AA36"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AC24:AE24"/>
-    <mergeCell ref="AF24:AG24"/>
-    <mergeCell ref="Y34:AA34"/>
-    <mergeCell ref="AD28:AG28"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A2 B2:K2 X9:AG10 X15:AG16 X20:AG21 B21:K22 AB34:AB36 A57:K58 H59:K61 B62:K71 B83:K1048576">
     <cfRule type="cellIs" dxfId="27" priority="76" operator="equal">
@@ -57936,6 +57944,12 @@
     <sortCondition ref="C59:C64"/>
   </sortState>
   <mergeCells count="16">
+    <mergeCell ref="N4:N6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="L4:L6"/>
     <mergeCell ref="AB4:AB6"/>
     <mergeCell ref="AD4:AD6"/>
     <mergeCell ref="AF4:AF6"/>
@@ -57946,12 +57960,6 @@
     <mergeCell ref="V4:V6"/>
     <mergeCell ref="X4:X6"/>
     <mergeCell ref="Z4:Z6"/>
-    <mergeCell ref="N4:N6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="J4:J6"/>
-    <mergeCell ref="L4:L6"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -58187,20 +58195,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -58223,6 +58231,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
@@ -58237,12 +58253,4 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C004B20-35B6-49E6-8924-68E165489957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14BCC7B-B706-4F61-ABEE-DBA77B085FD5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BcI4NY5Ohir363+nRCln2YCzlnOeJyINjZ1aV0hb2IpPHmsHZPUFroFzrod6xokqyCn7GUW2N1Z+U/w2mbyNbQ==" workbookSaltValue="VvXyFesAZC8L8IOzNm6PtA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9525" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="7" r:id="rId1"/>
@@ -26,17 +26,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -3009,17 +2998,6 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3124,6 +3102,17 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9428,25 +9417,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CB5EB0A-66D8-48B4-BC40-E2D214AFC03A}" name="Tabela1" displayName="Tabela1" ref="C3:E51" totalsRowShown="0" headerRowDxfId="90" dataDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CB5EB0A-66D8-48B4-BC40-E2D214AFC03A}" name="Tabela1" displayName="Tabela1" ref="C3:E51" totalsRowShown="0" headerRowDxfId="88" dataDxfId="87">
   <autoFilter ref="C3:E51" xr:uid="{9CB5EB0A-66D8-48B4-BC40-E2D214AFC03A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{BA403FB9-D643-4201-89E9-82280DBD496D}" name=" " dataDxfId="88"/>
-    <tableColumn id="2" xr3:uid="{8927B163-5C71-4390-8413-1CB7AFCDC479}" name="Times" dataDxfId="87"/>
-    <tableColumn id="3" xr3:uid="{95E8A229-CD3E-4FE0-BC0B-3E68BBDC2143}" name="  " dataDxfId="86"/>
+    <tableColumn id="1" xr3:uid="{BA403FB9-D643-4201-89E9-82280DBD496D}" name=" " dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{8927B163-5C71-4390-8413-1CB7AFCDC479}" name="Times" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{95E8A229-CD3E-4FE0-BC0B-3E68BBDC2143}" name="  " dataDxfId="84"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9484,7 +9473,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9590,7 +9579,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9732,7 +9721,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -10041,12 +10030,12 @@
     <mergeCell ref="J33:L33"/>
   </mergeCells>
   <conditionalFormatting sqref="J31:L31 J32:J33">
-    <cfRule type="cellIs" dxfId="85" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="2" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31:L33">
-    <cfRule type="expression" dxfId="84" priority="1">
+    <cfRule type="expression" dxfId="89" priority="1">
       <formula>M31&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -55122,11 +55111,15 @@
         <v>França</v>
       </c>
       <c r="AB5" s="149"/>
-      <c r="AC5" s="123"/>
+      <c r="AC5" s="123">
+        <v>2</v>
+      </c>
       <c r="AD5" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="AE5" s="123"/>
+      <c r="AE5" s="123">
+        <v>0</v>
+      </c>
       <c r="AF5" s="150"/>
       <c r="AG5" s="151" t="str">
         <f>M26</f>
@@ -55138,7 +55131,7 @@
       </c>
       <c r="AI5" s="133" t="str">
         <f>IF(OR(AC5="",AE5=""),"Vencedor Q1",IF(AC5&lt;&gt;AE5,IF(AC5&gt;AE5,AA5,AG5),IF(SUM(AB5:AC5)=SUM(AE5:AF5),"Vencedor Q1",IF(SUM(AB5:AC5)&gt;SUM(AE5:AF5),AA5,AG5))))</f>
-        <v>Vencedor Q1</v>
+        <v>França</v>
       </c>
       <c r="AJ5" s="133"/>
       <c r="AK5" s="133"/>
@@ -55208,11 +55201,15 @@
         <v>Espanha</v>
       </c>
       <c r="AB6" s="149"/>
-      <c r="AC6" s="123"/>
+      <c r="AC6" s="123">
+        <v>2</v>
+      </c>
       <c r="AD6" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="AE6" s="123"/>
+      <c r="AE6" s="123">
+        <v>1</v>
+      </c>
       <c r="AF6" s="150"/>
       <c r="AG6" s="151" t="str">
         <f>M30</f>
@@ -55224,7 +55221,7 @@
       </c>
       <c r="AI6" s="133" t="str">
         <f>IF(OR(AC6="",AE6=""),"Vencedor Q2",IF(AC6&lt;&gt;AE6,IF(AC6&gt;AE6,AA6,AG6),IF(SUM(AB6:AC6)=SUM(AE6:AF6),"Vencedor Q2",IF(SUM(AB6:AC6)&gt;SUM(AE6:AF6),AA6,AG6))))</f>
-        <v>Vencedor Q2</v>
+        <v>Espanha</v>
       </c>
       <c r="AJ6" s="133"/>
       <c r="AK6" s="133"/>
@@ -55290,11 +55287,15 @@
         <v>Noruega</v>
       </c>
       <c r="AB7" s="149"/>
-      <c r="AC7" s="123"/>
+      <c r="AC7" s="123">
+        <v>1</v>
+      </c>
       <c r="AD7" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="AE7" s="123"/>
+      <c r="AE7" s="123">
+        <v>2</v>
+      </c>
       <c r="AF7" s="150"/>
       <c r="AG7" s="151" t="str">
         <f>M28</f>
@@ -55306,7 +55307,7 @@
       </c>
       <c r="AI7" s="133" t="str">
         <f>IF(OR(AC7="",AE7=""),"Vencedor Q3",IF(AC7&lt;&gt;AE7,IF(AC7&gt;AE7,AA7,AG7),IF(SUM(AB7:AC7)=SUM(AE7:AF7),"Vencedor Q3",IF(SUM(AB7:AC7)&gt;SUM(AE7:AF7),AA7,AG7))))</f>
-        <v>Vencedor Q3</v>
+        <v>Inglaterra</v>
       </c>
       <c r="AJ7" s="133"/>
       <c r="AK7" s="133"/>
@@ -55382,18 +55383,22 @@
       </c>
       <c r="AA8" s="106" t="str">
         <f>M31</f>
-        <v>Vencedor 95</v>
+        <v>Argentina</v>
       </c>
       <c r="AB8" s="149"/>
-      <c r="AC8" s="123"/>
+      <c r="AC8" s="123">
+        <v>3</v>
+      </c>
       <c r="AD8" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="AE8" s="123"/>
+      <c r="AE8" s="123">
+        <v>1</v>
+      </c>
       <c r="AF8" s="150"/>
       <c r="AG8" s="151" t="str">
         <f>M32</f>
-        <v>Vencedor 96</v>
+        <v>Suiça</v>
       </c>
       <c r="AH8" s="136" t="str">
         <f t="shared" si="1"/>
@@ -55401,7 +55406,7 @@
       </c>
       <c r="AI8" s="133" t="str">
         <f>IF(OR(AC8="",AE8=""),"Vencedor Q4",IF(AC8&lt;&gt;AE8,IF(AC8&gt;AE8,AA8,AG8),IF(SUM(AB8:AC8)=SUM(AE8:AF8),"Vencedor Q4",IF(SUM(AB8:AC8)&gt;SUM(AE8:AF8),AA8,AG8))))</f>
-        <v>Vencedor Q4</v>
+        <v>Argentina</v>
       </c>
       <c r="AJ8" s="133"/>
       <c r="AK8" s="133"/>
@@ -55794,7 +55799,7 @@
       </c>
       <c r="AA13" s="106" t="str">
         <f>AI5</f>
-        <v>Vencedor Q1</v>
+        <v>França</v>
       </c>
       <c r="AB13" s="149"/>
       <c r="AC13" s="123"/>
@@ -55805,7 +55810,7 @@
       <c r="AF13" s="150"/>
       <c r="AG13" s="151" t="str">
         <f>AI6</f>
-        <v>Vencedor Q2</v>
+        <v>Espanha</v>
       </c>
       <c r="AH13" s="136" t="str">
         <f>IF(OR(AC13="",AE13=""),"",IF(AC13=AE13,"emp",""))</f>
@@ -55890,7 +55895,7 @@
       </c>
       <c r="AA14" s="106" t="str">
         <f>AI7</f>
-        <v>Vencedor Q3</v>
+        <v>Inglaterra</v>
       </c>
       <c r="AB14" s="149"/>
       <c r="AC14" s="123"/>
@@ -55901,7 +55906,7 @@
       <c r="AF14" s="150"/>
       <c r="AG14" s="151" t="str">
         <f>AI8</f>
-        <v>Vencedor Q4</v>
+        <v>Argentina</v>
       </c>
       <c r="AH14" s="136" t="str">
         <f t="shared" ref="AH14" si="6">IF(OR(AC14="",AE14=""),"",IF(AC14=AE14,"emp",""))</f>
@@ -56858,11 +56863,15 @@
         <v>Argentina</v>
       </c>
       <c r="F31" s="149"/>
-      <c r="G31" s="123"/>
+      <c r="G31" s="123">
+        <v>3</v>
+      </c>
       <c r="H31" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I31" s="123"/>
+      <c r="I31" s="123">
+        <v>2</v>
+      </c>
       <c r="J31" s="150"/>
       <c r="K31" s="151" t="str">
         <f>M20</f>
@@ -56874,7 +56883,7 @@
       </c>
       <c r="M31" s="133" t="str">
         <f>IF(OR(G31="",I31=""),"Vencedor 95",IF(G31&lt;&gt;I31,IF(G31&gt;I31,E31,K31),IF(SUM(F31:G31)=SUM(I31:J31),"Vencedor 95",IF(SUM(F31:G31)&gt;SUM(I31:J31),E31,K31))))</f>
-        <v>Vencedor 95</v>
+        <v>Argentina</v>
       </c>
       <c r="N31" s="133">
         <v>95</v>
@@ -56905,24 +56914,32 @@
         <f>M17</f>
         <v>Suiça</v>
       </c>
-      <c r="F32" s="149"/>
-      <c r="G32" s="123"/>
+      <c r="F32" s="149">
+        <v>4</v>
+      </c>
+      <c r="G32" s="123">
+        <v>0</v>
+      </c>
       <c r="H32" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I32" s="123"/>
-      <c r="J32" s="150"/>
+      <c r="I32" s="123">
+        <v>0</v>
+      </c>
+      <c r="J32" s="150">
+        <v>3</v>
+      </c>
       <c r="K32" s="151" t="str">
         <f>M19</f>
         <v>Colômbia</v>
       </c>
       <c r="L32" s="136" t="str">
         <f t="shared" si="18"/>
-        <v/>
+        <v>emp</v>
       </c>
       <c r="M32" s="133" t="str">
         <f>IF(OR(G32="",I32=""),"Vencedor 96",IF(G32&lt;&gt;I32,IF(G32&gt;I32,E32,K32),IF(SUM(F32:G32)=SUM(I32:J32),"Vencedor 96",IF(SUM(F32:G32)&gt;SUM(I32:J32),E32,K32))))</f>
-        <v>Vencedor 96</v>
+        <v>Suiça</v>
       </c>
       <c r="N32" s="133">
         <v>96</v>
@@ -57151,21 +57168,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="vyOy7e+Kipl/iIim/AhmV04T3MRdO7XqZOrn9PPXS3pWOghvTWOXD8HUj7i1Pq8tpKgw5m5Lutctpe8ebuImew==" saltValue="GsBJjoEg17jBuxUGR0mlBg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="31">
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AB34:AG34"/>
-    <mergeCell ref="AB35:AG35"/>
-    <mergeCell ref="AB36:AG36"/>
-    <mergeCell ref="B23:K23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="Y35:AA35"/>
-    <mergeCell ref="Y36:AA36"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AC24:AE24"/>
-    <mergeCell ref="AF24:AG24"/>
-    <mergeCell ref="Y34:AA34"/>
-    <mergeCell ref="AD28:AG28"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:I4"/>
@@ -57182,6 +57184,21 @@
     <mergeCell ref="AF18:AG18"/>
     <mergeCell ref="AA4:AB4"/>
     <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AB34:AG34"/>
+    <mergeCell ref="AB35:AG35"/>
+    <mergeCell ref="AB36:AG36"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="Y35:AA35"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="AF24:AG24"/>
+    <mergeCell ref="Y34:AA34"/>
+    <mergeCell ref="AD28:AG28"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A2 B2:K2 X9:AG10 X15:AG16 X20:AG21 B21:K22 AB34:AB36 A57:K58 H59:K61 B62:K71 B83:K1048576">
     <cfRule type="cellIs" dxfId="27" priority="76" operator="equal">
@@ -57940,16 +57957,10 @@
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="c6tPJJQuMaLYYVxDkvgugaxcC+Uv5gkJkUqZgIt2uuxbzexMxqxVyEOkWorUUitpEJ1MPNBlUf/aYq65/wymIg==" saltValue="0J8NZQ0DnJYkRWhoKBlPHA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C59:C64">
+  <sortState ref="C59:C64">
     <sortCondition ref="C59:C64"/>
   </sortState>
   <mergeCells count="16">
-    <mergeCell ref="N4:N6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="J4:J6"/>
-    <mergeCell ref="L4:L6"/>
     <mergeCell ref="AB4:AB6"/>
     <mergeCell ref="AD4:AD6"/>
     <mergeCell ref="AF4:AF6"/>
@@ -57960,6 +57971,12 @@
     <mergeCell ref="V4:V6"/>
     <mergeCell ref="X4:X6"/>
     <mergeCell ref="Z4:Z6"/>
+    <mergeCell ref="N4:N6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="L4:L6"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -57968,6 +57985,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DBF2846C41E31A469E3CED25F2422E48" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5fe40c83f7497f6a132ba44389c75f2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8c20e6-817c-474f-b9c2-eb2b1ac24837" xmlns:ns4="dc8c2798-6aba-4af7-93a4-b89253b03650" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7827a91f6681aa3909757bf20cf55ac7" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
@@ -58194,24 +58228,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E4CC2DB-337D-464E-B291-77CE670D3A8E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -58228,29 +58270,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14BCC7B-B706-4F61-ABEE-DBA77B085FD5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6ECDD4-2AF6-4095-9544-8BD51793B524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BcI4NY5Ohir363+nRCln2YCzlnOeJyINjZ1aV0hb2IpPHmsHZPUFroFzrod6xokqyCn7GUW2N1Z+U/w2mbyNbQ==" workbookSaltValue="VvXyFesAZC8L8IOzNm6PtA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9525" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="7" r:id="rId1"/>
@@ -26,6 +26,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -2998,6 +3009,17 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3102,17 +3124,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9417,25 +9428,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CB5EB0A-66D8-48B4-BC40-E2D214AFC03A}" name="Tabela1" displayName="Tabela1" ref="C3:E51" totalsRowShown="0" headerRowDxfId="88" dataDxfId="87">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CB5EB0A-66D8-48B4-BC40-E2D214AFC03A}" name="Tabela1" displayName="Tabela1" ref="C3:E51" totalsRowShown="0" headerRowDxfId="90" dataDxfId="89">
   <autoFilter ref="C3:E51" xr:uid="{9CB5EB0A-66D8-48B4-BC40-E2D214AFC03A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{BA403FB9-D643-4201-89E9-82280DBD496D}" name=" " dataDxfId="86"/>
-    <tableColumn id="2" xr3:uid="{8927B163-5C71-4390-8413-1CB7AFCDC479}" name="Times" dataDxfId="85"/>
-    <tableColumn id="3" xr3:uid="{95E8A229-CD3E-4FE0-BC0B-3E68BBDC2143}" name="  " dataDxfId="84"/>
+    <tableColumn id="1" xr3:uid="{BA403FB9-D643-4201-89E9-82280DBD496D}" name=" " dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{8927B163-5C71-4390-8413-1CB7AFCDC479}" name="Times" dataDxfId="87"/>
+    <tableColumn id="3" xr3:uid="{95E8A229-CD3E-4FE0-BC0B-3E68BBDC2143}" name="  " dataDxfId="86"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9473,7 +9484,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9579,7 +9590,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9721,7 +9732,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -10030,12 +10041,12 @@
     <mergeCell ref="J33:L33"/>
   </mergeCells>
   <conditionalFormatting sqref="J31:L31 J32:J33">
-    <cfRule type="cellIs" dxfId="90" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="2" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31:L33">
-    <cfRule type="expression" dxfId="89" priority="1">
+    <cfRule type="expression" dxfId="84" priority="1">
       <formula>M31&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -55802,11 +55813,15 @@
         <v>França</v>
       </c>
       <c r="AB13" s="149"/>
-      <c r="AC13" s="123"/>
+      <c r="AC13" s="123">
+        <v>0</v>
+      </c>
       <c r="AD13" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="AE13" s="123"/>
+      <c r="AE13" s="123">
+        <v>2</v>
+      </c>
       <c r="AF13" s="150"/>
       <c r="AG13" s="151" t="str">
         <f>AI6</f>
@@ -55818,7 +55833,7 @@
       </c>
       <c r="AI13" s="133" t="str">
         <f>IF(OR(AC13="",AE13=""),"Vencedor S1",IF(AC13&lt;&gt;AE13,IF(AC13&gt;AE13,AA13,AG13),IF(SUM(AB13:AC13)=SUM(AE13:AF13),"Vencedor S1",IF(SUM(AB13:AC13)&gt;SUM(AE13:AF13),AA13,AG13))))</f>
-        <v>Vencedor S1</v>
+        <v>Espanha</v>
       </c>
       <c r="AJ13" s="133"/>
       <c r="AK13" s="133"/>
@@ -55993,7 +56008,7 @@
       <c r="AH15" s="136"/>
       <c r="AI15" s="133" t="str">
         <f>IF(OR(AC13="",AE13=""),"Perdedor S1",IF(AC13&lt;&gt;AE13,IF(AC13&lt;AE13,AA13,AG13),IF(SUM(AB13:AC13)=SUM(AE13:AF13),"Perdedor S1",IF(SUM(AB13:AC13)&lt;SUM(AE13:AF13),AA13,AG13))))</f>
-        <v>Perdedor S1</v>
+        <v>França</v>
       </c>
       <c r="AJ15" s="133"/>
       <c r="AK15" s="133"/>
@@ -56269,7 +56284,7 @@
       </c>
       <c r="AA19" s="106" t="str">
         <f>AI15</f>
-        <v>Perdedor S1</v>
+        <v>França</v>
       </c>
       <c r="AB19" s="149"/>
       <c r="AC19" s="123"/>
@@ -56570,7 +56585,7 @@
       </c>
       <c r="AA25" s="106" t="str">
         <f>AI13</f>
-        <v>Vencedor S1</v>
+        <v>Espanha</v>
       </c>
       <c r="AB25" s="149"/>
       <c r="AC25" s="123"/>
@@ -57957,7 +57972,7 @@
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="c6tPJJQuMaLYYVxDkvgugaxcC+Uv5gkJkUqZgIt2uuxbzexMxqxVyEOkWorUUitpEJ1MPNBlUf/aYq65/wymIg==" saltValue="0J8NZQ0DnJYkRWhoKBlPHA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <sortState ref="C59:C64">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C59:C64">
     <sortCondition ref="C59:C64"/>
   </sortState>
   <mergeCells count="16">
@@ -57985,23 +58000,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DBF2846C41E31A469E3CED25F2422E48" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5fe40c83f7497f6a132ba44389c75f2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8c20e6-817c-474f-b9c2-eb2b1ac24837" xmlns:ns4="dc8c2798-6aba-4af7-93a4-b89253b03650" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7827a91f6681aa3909757bf20cf55ac7" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
@@ -58228,7 +58226,43 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E4CC2DB-337D-464E-B291-77CE670D3A8E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
+    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
@@ -58245,29 +58279,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E4CC2DB-337D-464E-B291-77CE670D3A8E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
-    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6ECDD4-2AF6-4095-9544-8BD51793B524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161D2953-7B4D-4A07-8B98-0814C2A11B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BcI4NY5Ohir363+nRCln2YCzlnOeJyINjZ1aV0hb2IpPHmsHZPUFroFzrod6xokqyCn7GUW2N1Z+U/w2mbyNbQ==" workbookSaltValue="VvXyFesAZC8L8IOzNm6PtA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
@@ -55913,11 +55913,15 @@
         <v>Inglaterra</v>
       </c>
       <c r="AB14" s="149"/>
-      <c r="AC14" s="123"/>
+      <c r="AC14" s="123">
+        <v>1</v>
+      </c>
       <c r="AD14" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="AE14" s="123"/>
+      <c r="AE14" s="123">
+        <v>2</v>
+      </c>
       <c r="AF14" s="150"/>
       <c r="AG14" s="151" t="str">
         <f>AI8</f>
@@ -55929,7 +55933,7 @@
       </c>
       <c r="AI14" s="133" t="str">
         <f>IF(OR(AC14="",AE14=""),"Vencedor S2",IF(AC14&lt;&gt;AE14,IF(AC14&gt;AE14,AA14,AG14),IF(SUM(AB14:AC14)=SUM(AE14:AF14),"Vencedor S2",IF(SUM(AB14:AC14)&gt;SUM(AE14:AF14),AA14,AG14))))</f>
-        <v>Vencedor S2</v>
+        <v>Argentina</v>
       </c>
       <c r="AJ14" s="133"/>
       <c r="AK14" s="133"/>
@@ -56076,7 +56080,7 @@
       <c r="AH16" s="136"/>
       <c r="AI16" s="133" t="str">
         <f>IF(OR(AC14="",AE14=""),"Perdedor S2",IF(AC14&lt;&gt;AE14,IF(AC14&lt;AE14,AA14,AG14),IF(SUM(AB14:AC14)=SUM(AE14:AF14),"Perdedor S2",IF(SUM(AB14:AC14)&lt;SUM(AE14:AF14),AA14,AG14))))</f>
-        <v>Perdedor S2</v>
+        <v>Inglaterra</v>
       </c>
       <c r="AJ16" s="133"/>
       <c r="AK16" s="133"/>
@@ -56295,7 +56299,7 @@
       <c r="AF19" s="150"/>
       <c r="AG19" s="151" t="str">
         <f>AI16</f>
-        <v>Perdedor S2</v>
+        <v>Inglaterra</v>
       </c>
       <c r="AH19" s="136" t="str">
         <f>IF(OR(AC19="",AE19=""),"",IF(AC19=AE19,"emp",""))</f>
@@ -56596,7 +56600,7 @@
       <c r="AF25" s="150"/>
       <c r="AG25" s="151" t="str">
         <f>AI14</f>
-        <v>Vencedor S2</v>
+        <v>Argentina</v>
       </c>
       <c r="AH25" s="136" t="str">
         <f>IF(OR(AC25="",AE25=""),"",IF(AC25=AE25,"emp",""))</f>
@@ -58000,6 +58004,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DBF2846C41E31A469E3CED25F2422E48" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5fe40c83f7497f6a132ba44389c75f2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8c20e6-817c-474f-b9c2-eb2b1ac24837" xmlns:ns4="dc8c2798-6aba-4af7-93a4-b89253b03650" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7827a91f6681aa3909757bf20cf55ac7" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
@@ -58226,7 +58239,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
@@ -58234,16 +58247,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E4CC2DB-337D-464E-B291-77CE670D3A8E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -58262,7 +58274,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
@@ -58277,12 +58289,4 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Copa do Mundo FIFA 2026.xlsx
+++ b/Copa do Mundo FIFA 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161D2953-7B4D-4A07-8B98-0814C2A11B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1092D87-EB00-49AE-B0BA-62CFC66E89E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BcI4NY5Ohir363+nRCln2YCzlnOeJyINjZ1aV0hb2IpPHmsHZPUFroFzrod6xokqyCn7GUW2N1Z+U/w2mbyNbQ==" workbookSaltValue="VvXyFesAZC8L8IOzNm6PtA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{076F3B28-812E-4458-A424-96085A053123}"/>
@@ -56291,11 +56291,15 @@
         <v>França</v>
       </c>
       <c r="AB19" s="149"/>
-      <c r="AC19" s="123"/>
+      <c r="AC19" s="123">
+        <v>4</v>
+      </c>
       <c r="AD19" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="AE19" s="123"/>
+      <c r="AE19" s="123">
+        <v>6</v>
+      </c>
       <c r="AF19" s="150"/>
       <c r="AG19" s="151" t="str">
         <f>AI16</f>
@@ -56307,7 +56311,7 @@
       </c>
       <c r="AI19" s="133" t="str">
         <f>IF(OR(AC19="",AE19=""),"3º Lugar",IF(AC19&lt;&gt;AE19,IF(AC19&gt;AE19,AA19,AG19),IF(SUM(AB19:AC19)=SUM(AE19:AF19),"3º Lugar",IF(SUM(AB19:AC19)&gt;SUM(AE19:AF19),AA19,AG19))))</f>
-        <v>3º Lugar</v>
+        <v>Inglaterra</v>
       </c>
       <c r="AJ19" s="133"/>
       <c r="AK19" s="133"/>
@@ -56379,7 +56383,7 @@
       <c r="AH20" s="136"/>
       <c r="AI20" s="133" t="str">
         <f>IF(OR(AC19="",AE19=""),"4º Lugar",IF(AC19&lt;&gt;AE19,IF(AC19&lt;AE19,AA19,AG19),IF(SUM(AB19:AC19)=SUM(AE19:AF19),"4º Lugar",IF(SUM(AB19:AC19)&lt;SUM(AE19:AF19),AA19,AG19))))</f>
-        <v>4º Lugar</v>
+        <v>França</v>
       </c>
       <c r="AJ20" s="133"/>
       <c r="AK20" s="133"/>
@@ -56592,11 +56596,15 @@
         <v>Espanha</v>
       </c>
       <c r="AB25" s="149"/>
-      <c r="AC25" s="123"/>
+      <c r="AC25" s="123">
+        <v>1</v>
+      </c>
       <c r="AD25" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="AE25" s="123"/>
+      <c r="AE25" s="123">
+        <v>0</v>
+      </c>
       <c r="AF25" s="150"/>
       <c r="AG25" s="151" t="str">
         <f>AI14</f>
@@ -56608,7 +56616,7 @@
       </c>
       <c r="AI25" s="133" t="str">
         <f>IF(OR(AC25="",AE25=""),"1º Lugar",IF(AC25&lt;&gt;AE25,IF(AC25&gt;AE25,AA25,AG25),IF(SUM(AB25:AC25)=SUM(AE25:AF25),"1º Lugar",IF(SUM(AB25:AC25)&gt;SUM(AE25:AF25),AA25,AG25))))</f>
-        <v>1º Lugar</v>
+        <v>Espanha</v>
       </c>
       <c r="AJ25" s="133"/>
       <c r="AK25" s="133"/>
@@ -56983,7 +56991,7 @@
       <c r="AA34" s="209"/>
       <c r="AB34" s="204" t="str">
         <f>IF(AI25="1º Lugar","",AI25)</f>
-        <v/>
+        <v>Espanha</v>
       </c>
       <c r="AC34" s="204"/>
       <c r="AD34" s="204"/>
@@ -57003,7 +57011,7 @@
       <c r="AA35" s="207"/>
       <c r="AB35" s="205" t="str">
         <f>IF(M57="2º Lugar","",M57)</f>
-        <v/>
+        <v>Argentina</v>
       </c>
       <c r="AC35" s="205"/>
       <c r="AD35" s="205"/>
@@ -57023,7 +57031,7 @@
       <c r="AA36" s="208"/>
       <c r="AB36" s="206" t="str">
         <f>IF(AI19="3º Lugar","",AI19)</f>
-        <v/>
+        <v>Inglaterra</v>
       </c>
       <c r="AC36" s="206"/>
       <c r="AD36" s="206"/>
@@ -57035,7 +57043,7 @@
       <c r="C57" s="137"/>
       <c r="M57" s="133" t="str">
         <f>IF(OR(AC25="",AE25=""),"2º Lugar",IF(AC25&lt;&gt;AE25,IF(AC25&lt;AE25,AA25,AG25),IF(SUM(AB25:AC25)=SUM(AE25:AF25),"2º Lugar",IF(SUM(AB25:AC25)&lt;SUM(AE25:AF25),AA25,AG25))))</f>
-        <v>2º Lugar</v>
+        <v>Argentina</v>
       </c>
     </row>
     <row r="58" spans="3:17" x14ac:dyDescent="0.25">
@@ -57187,6 +57195,21 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="vyOy7e+Kipl/iIim/AhmV04T3MRdO7XqZOrn9PPXS3pWOghvTWOXD8HUj7i1Pq8tpKgw5m5Lutctpe8ebuImew==" saltValue="GsBJjoEg17jBuxUGR0mlBg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="31">
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AB34:AG34"/>
+    <mergeCell ref="AB35:AG35"/>
+    <mergeCell ref="AB36:AG36"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="Y35:AA35"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="AF24:AG24"/>
+    <mergeCell ref="Y34:AA34"/>
+    <mergeCell ref="AD28:AG28"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:I4"/>
@@ -57203,21 +57226,6 @@
     <mergeCell ref="AF18:AG18"/>
     <mergeCell ref="AA4:AB4"/>
     <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AB34:AG34"/>
-    <mergeCell ref="AB35:AG35"/>
-    <mergeCell ref="AB36:AG36"/>
-    <mergeCell ref="B23:K23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="Y35:AA35"/>
-    <mergeCell ref="Y36:AA36"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AC24:AE24"/>
-    <mergeCell ref="AF24:AG24"/>
-    <mergeCell ref="Y34:AA34"/>
-    <mergeCell ref="AD28:AG28"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A2 B2:K2 X9:AG10 X15:AG16 X20:AG21 B21:K22 AB34:AB36 A57:K58 H59:K61 B62:K71 B83:K1048576">
     <cfRule type="cellIs" dxfId="27" priority="76" operator="equal">
@@ -57980,6 +57988,12 @@
     <sortCondition ref="C59:C64"/>
   </sortState>
   <mergeCells count="16">
+    <mergeCell ref="N4:N6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="L4:L6"/>
     <mergeCell ref="AB4:AB6"/>
     <mergeCell ref="AD4:AD6"/>
     <mergeCell ref="AF4:AF6"/>
@@ -57990,12 +58004,6 @@
     <mergeCell ref="V4:V6"/>
     <mergeCell ref="X4:X6"/>
     <mergeCell ref="Z4:Z6"/>
-    <mergeCell ref="N4:N6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="J4:J6"/>
-    <mergeCell ref="L4:L6"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -58013,6 +58021,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DBF2846C41E31A469E3CED25F2422E48" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5fe40c83f7497f6a132ba44389c75f2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8c20e6-817c-474f-b9c2-eb2b1ac24837" xmlns:ns4="dc8c2798-6aba-4af7-93a4-b89253b03650" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7827a91f6681aa3909757bf20cf55ac7" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
@@ -58239,14 +58255,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A45D7D45-1E18-48AE-827B-096C3C02C976}">
   <ds:schemaRefs>
@@ -58256,6 +58264,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E4CC2DB-337D-464E-B291-77CE670D3A8E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -58272,21 +58297,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83E7837-68AD-48B2-A1AB-AAB452317AF5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>